--- a/exports/lote3_questoes_autorais.xlsx
+++ b/exports/lote3_questoes_autorais.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os métodos de medida do volume pulmonar não mensuram a mesma coisa. As técnicas de &lt;strong&gt;diluição de gases inertes&lt;/strong&gt; (hélio) e de &lt;strong&gt;lavagem de nitrogênio&lt;/strong&gt; dependem de o gás traçador alcançar os alvéolos: elas quantificam apenas o volume em comunicação efetiva com as vias aéreas dentro do tempo do exame. Já a &lt;strong&gt;pletismografia corporal&lt;/strong&gt; baseia-se na lei de Boyle, relacionando variações de pressão na boca e na cabine durante esforços contra via aérea ocluída, e por isso mensura &lt;em&gt;todo o gás intratorácico compressível&lt;/em&gt;, incluindo o aprisionado atrás de vias aéreas colapsadas e até bolhas.&lt;/p&gt;&lt;p&gt;Em doenças obstrutivas com aprisionamento aéreo, a pletismografia fornece valores sistematicamente maiores, e a diferença entre os dois métodos é uma estimativa do volume de gás aprisionado — no caso, cerca de 1,3 L. Esse achado tem tradução anestésica direta: hiperinsuflação dinâmica, risco de auto-PEEP e de barotrauma sob ventilação com pressão positiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a relação: a diluição de hélio &lt;em&gt;subestima&lt;/em&gt; o volume nos obstrutivos, justamente por equilíbrio incompleto. (B) descreve a limitação da diluição, não da pletismografia; ambos os métodos incluem o volume residual quando o gás é acessível. (D) a espirometria não mede volume residual nem capacidade residual funcional, apenas volumes mobilizáveis.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os métodos de medida do volume pulmonar não mensuram a mesma coisa. As técnicas de &lt;strong&gt;diluição de gases inertes&lt;/strong&gt; (hélio) e de &lt;strong&gt;lavagem de nitrogênio&lt;/strong&gt; dependem de o gás traçador alcançar os alvéolos: elas quantificam apenas o volume em comunicação efetiva com as vias aéreas dentro do tempo do exame. Já a &lt;strong&gt;pletismografia corporal&lt;/strong&gt; baseia-se na lei de Boyle, relacionando variações de pressão na boca e na cabine durante esforços contra via aérea ocluída, e por isso mensura &lt;em&gt;todo o gás intratorácico compressível&lt;/em&gt;, incluindo o aprisionado atrás de vias aéreas colapsadas e até bolhas.&lt;/p&gt;&lt;p&gt;Em doenças obstrutivas com aprisionamento aéreo, a pletismografia fornece valores sistematicamente maiores, e a diferença entre os dois métodos é uma estimativa do volume de gás aprisionado: no caso, cerca de 1,3 L. Esse achado tem tradução anestésica direta: hiperinsuflação dinâmica, risco de auto-PEEP e de barotrauma sob ventilação com pressão positiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a relação: a diluição de hélio &lt;em&gt;subestima&lt;/em&gt; o volume nos obstrutivos, justamente por equilíbrio incompleto. (B) descreve a limitação da diluição, não da pletismografia; ambos os métodos incluem o volume residual quando o gás é acessível. (D) a espirometria não mede volume residual nem capacidade residual funcional, apenas volumes mobilizáveis.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As &lt;strong&gt;zonas de West&lt;/strong&gt; descrevem a relação entre pressão alveolar (PA), pressão arterial pulmonar (Pa) e pressão venosa pulmonar (Pv) ao longo do eixo gravitacional. Na zona 1, PA &amp;gt; Pa &amp;gt; Pv e o capilar é comprimido: a unidade é ventilada mas não perfundida, ou seja, &lt;strong&gt;espaço morto alveolar&lt;/strong&gt;. Na zona 2, Pa &amp;gt; PA &amp;gt; Pv, com fluxo pulsátil dependente do gradiente arterioalveolar. Na zona 3, Pa &amp;gt; Pv &amp;gt; PA, com fluxo contínuo. A zona 4, nas regiões mais dependentes, decorre da compressão de vasos extra-alveolares em baixo volume pulmonar.&lt;/p&gt;&lt;p&gt;No pulmão normal, em normovolemia e respiração espontânea, praticamente não existe zona 1. Ela aparece quando a pressão alveolar sobe (ventilação com pressão positiva, PEEP elevada) ou quando a pressão arterial pulmonar cai (hipovolemia, hipotensão) — e a posição sentada acentua o problema por aumentar a distância vertical entre o coração e o ápice. O caso reúne as três condições, e o alargamento do gradiente entre a PaCO&lt;sub&gt;2&lt;/sub&gt; e o CO&lt;sub&gt;2&lt;/sub&gt; expirado é exatamente a assinatura clínica do aumento do espaço morto alveolar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a zona 3 predomina nas bases e não explica aumento de espaço morto. (B) a zona 2 ocupa a região intermediária e mantém perfusão. (C) a zona 4 ocorre nas regiões dependentes com baixo volume pulmonar, não no ápice.&lt;/p&gt;</t>
+          <t>&lt;p&gt;As &lt;strong&gt;zonas de West&lt;/strong&gt; descrevem a relação entre pressão alveolar (PA), pressão arterial pulmonar (Pa) e pressão venosa pulmonar (Pv) ao longo do eixo gravitacional. Na zona 1, PA &amp;gt; Pa &amp;gt; Pv e o capilar é comprimido: a unidade é ventilada mas não perfundida, ou seja, &lt;strong&gt;espaço morto alveolar&lt;/strong&gt;. Na zona 2, Pa &amp;gt; PA &amp;gt; Pv, com fluxo pulsátil dependente do gradiente arterioalveolar. Na zona 3, Pa &amp;gt; Pv &amp;gt; PA, com fluxo contínuo. A zona 4, nas regiões mais dependentes, decorre da compressão de vasos extra-alveolares em baixo volume pulmonar.&lt;/p&gt;&lt;p&gt;No pulmão normal, em normovolemia e respiração espontânea, praticamente não existe zona 1. Ela aparece quando a pressão alveolar sobe (ventilação com pressão positiva, PEEP elevada) ou quando a pressão arterial pulmonar cai (hipovolemia, hipotensão), e a posição sentada acentua o problema por aumentar a distância vertical entre o coração e o ápice. O caso reúne as três condições, e o alargamento do gradiente entre a PaCO&lt;sub&gt;2&lt;/sub&gt; e o CO&lt;sub&gt;2&lt;/sub&gt; expirado é exatamente a assinatura clínica do aumento do espaço morto alveolar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a zona 3 predomina nas bases e não explica aumento de espaço morto. (B) a zona 2 ocupa a região intermediária e mantém perfusão. (C) a zona 4 ocorre nas regiões dependentes com baixo volume pulmonar, não no ápice.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A PaCO&lt;sub&gt;2&lt;/sub&gt; é governada por uma relação simples: ela é &lt;strong&gt;diretamente proporcional à produção metabólica de CO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt; e &lt;strong&gt;inversamente proporcional à ventilação alveolar&lt;/strong&gt;. O ponto que os residentes costumam errar é usar a ventilação-minuto total em vez da ventilação alveolar, que desconta o espaço morto a cada incursão.&lt;/p&gt;&lt;p&gt;No caso: ventilação alveolar inicial = (500 - 150) × 12 = 4.200 mL/min. Após a mudança = (500 - 150) × 6 = 2.100 mL/min. A ventilação alveolar caiu exatamente à metade e, com produção de CO&lt;sub&gt;2&lt;/sub&gt; constante, a PaCO&lt;sub&gt;2&lt;/sub&gt; dobra, passando de 40 para aproximadamente &lt;strong&gt;80 mmHg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Note que a ventilação-minuto total caiu de 6.000 para 3.000 mL/min — também metade, coincidência que aqui não altera o resultado porque apenas a frequência foi modificada. Se, em vez disso, o volume corrente tivesse sido reduzido pela metade mantendo a frequência, a queda da ventilação alveolar seria proporcionalmente &lt;em&gt;maior&lt;/em&gt;, pois o espaço morto passaria a consumir fração maior de cada incursão. Na prática, portanto, ventilar com volumes muito baixos exige frequências desproporcionalmente altas para manter a normocapnia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 45 mmHg subestima grosseiramente o efeito, supondo compensação inexistente. (B) 60 mmHg corresponderia a uma queda de apenas um terço da ventilação alveolar. (D) 120 mmHg triplicaria a PaCO&lt;sub&gt;2&lt;/sub&gt;, o que exigiria redução da ventilação alveolar a um terço do valor inicial.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A PaCO&lt;sub&gt;2&lt;/sub&gt; é governada por uma relação simples: ela é &lt;strong&gt;diretamente proporcional à produção metabólica de CO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt; e &lt;strong&gt;inversamente proporcional à ventilação alveolar&lt;/strong&gt;. O ponto que os residentes costumam errar é usar a ventilação-minuto total em vez da ventilação alveolar, que desconta o espaço morto a cada incursão.&lt;/p&gt;&lt;p&gt;No caso: ventilação alveolar inicial = (500 - 150) × 12 = 4.200 mL/min. Após a mudança = (500 - 150) × 6 = 2.100 mL/min. A ventilação alveolar caiu exatamente à metade e, com produção de CO&lt;sub&gt;2&lt;/sub&gt; constante, a PaCO&lt;sub&gt;2&lt;/sub&gt; dobra, passando de 40 para aproximadamente &lt;strong&gt;80 mmHg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Note que a ventilação-minuto total caiu de 6.000 para 3.000 mL/min, também metade, coincidência que aqui não altera o resultado porque apenas a frequência foi modificada. Se, em vez disso, o volume corrente tivesse sido reduzido pela metade mantendo a frequência, a queda da ventilação alveolar seria proporcionalmente &lt;em&gt;maior&lt;/em&gt;, pois o espaço morto passaria a consumir fração maior de cada incursão. Na prática, portanto, ventilar com volumes muito baixos exige frequências desproporcionalmente altas para manter a normocapnia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 45 mmHg subestima grosseiramente o efeito, supondo compensação inexistente. (B) 60 mmHg corresponderia a uma queda de apenas um terço da ventilação alveolar. (D) 120 mmHg triplicaria a PaCO&lt;sub&gt;2&lt;/sub&gt;, o que exigiria redução da ventilação alveolar a um terço do valor inicial.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os anestésicos inalatórios deprimem as duas alças de controle ventilatório, mas em &lt;strong&gt;graus e limiares diferentes&lt;/strong&gt;. A resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt;, de origem predominantemente central, é atenuada de modo dose-dependente e torna-se clinicamente relevante em concentrações anestésicas. Já a &lt;strong&gt;resposta ventilatória à hipóxia&lt;/strong&gt;, mediada pelos quimiorreceptores periféricos dos corpos carotídeos, é notavelmente sensível: concentrações da ordem de &lt;strong&gt;0,1 CAM&lt;/strong&gt; — as que persistem na recuperação — já a reduzem de forma expressiva.&lt;/p&gt;&lt;p&gt;A implicação prática é importante. O paciente que sai de sala com halogenado residual perde justamente o mecanismo de defesa que deveria aumentar a ventilação diante da queda da PaO&lt;sub&gt;2&lt;/sub&gt;. Ele pode hipoventilar e dessaturar sem manifestar taquipneia compensatória. Isso justifica a oxigenoterapia suplementar e a monitorização com oximetria de pulso na sala de recuperação, ainda mais quando há opioides, obesidade ou apneia do sono associados.&lt;/p&gt;&lt;p&gt;O padrão típico de depressão respiratória por halogenados combina redução do volume corrente com aumento da frequência, resultando em ventilação-minuto menor e elevação da PaCO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a resposta ao CO&lt;sub&gt;2&lt;/sub&gt; é atenuada, não abolida, e o paciente descrito respira espontaneamente. (C) o halogenado reduz o volume corrente; não há compensação preservando a ventilação alveolar. (D) a depressão da resposta hipóxica independe de bloqueio neuromuscular residual, embora este agrave o quadro.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os anestésicos inalatórios deprimem as duas alças de controle ventilatório, mas em &lt;strong&gt;graus e limiares diferentes&lt;/strong&gt;. A resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt;, de origem predominantemente central, é atenuada de modo dose-dependente e torna-se clinicamente relevante em concentrações anestésicas. Já a &lt;strong&gt;resposta ventilatória à hipóxia&lt;/strong&gt;, mediada pelos quimiorreceptores periféricos dos corpos carotídeos, é notavelmente sensível: concentrações da ordem de &lt;strong&gt;0,1 CAM&lt;/strong&gt; (as que persistem na recuperação) já a reduzem de forma expressiva.&lt;/p&gt;&lt;p&gt;A implicação prática é importante. O paciente que sai de sala com halogenado residual perde justamente o mecanismo de defesa que deveria aumentar a ventilação diante da queda da PaO&lt;sub&gt;2&lt;/sub&gt;. Ele pode hipoventilar e dessaturar sem manifestar taquipneia compensatória. Isso justifica a oxigenoterapia suplementar e a monitorização com oximetria de pulso na sala de recuperação, ainda mais quando há opioides, obesidade ou apneia do sono associados.&lt;/p&gt;&lt;p&gt;O padrão típico de depressão respiratória por halogenados combina redução do volume corrente com aumento da frequência, resultando em ventilação-minuto menor e elevação da PaCO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a resposta ao CO&lt;sub&gt;2&lt;/sub&gt; é atenuada, não abolida, e o paciente descrito respira espontaneamente. (C) o halogenado reduz o volume corrente; não há compensação preservando a ventilação alveolar. (D) a depressão da resposta hipóxica independe de bloqueio neuromuscular residual, embora este agrave o quadro.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;hipocapnia aguda&lt;/strong&gt; tem efeitos que vão muito além do valor numérico da PaCO&lt;sub&gt;2&lt;/sub&gt;. No sistema nervoso central, a queda do CO&lt;sub&gt;2&lt;/sub&gt; provoca &lt;strong&gt;vasoconstrição cerebral&lt;/strong&gt;: o fluxo sanguíneo cerebral varia cerca de 1 a 2 mL/100 g/min para cada 1 mmHg de variação da PaCO&lt;sub&gt;2&lt;/sub&gt; dentro da faixa fisiológica. Essa é a base da hiperventilação como manobra de resgate na hipertensão intracraniana — e também o motivo pelo qual a hipocapnia mantida é perigosa, por risco de isquemia.&lt;/p&gt;&lt;p&gt;No transporte de oxigênio, a alcalose desloca a &lt;strong&gt;curva de dissociação da hemoglobina para a esquerda&lt;/strong&gt; (efeito Bohr), aumentando a afinidade da hemoglobina pelo oxigênio e dificultando sua liberação nos tecidos. Somam-se ainda queda do cálcio ionizado (maior ligação à albumina em pH alcalino, com parestesias e espasmo carpopedal no paciente acordado), hipocalemia por deslocamento do potássio para o meio intracelular, broncodilatação leve e redução do débito cardíaco quando associada a pressão positiva.&lt;/p&gt;&lt;p&gt;A hipercapnia produz o oposto: vasodilatação cerebral, desvio da curva para a direita, estímulo simpático, hipercalemia e aumento do cálcio ionizado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na alcalose o cálcio ionizado &lt;em&gt;cai&lt;/em&gt;, pois mais cálcio se liga à albumina. (C) descreve o efeito da hipercapnia, não da hipocapnia. (D) inverte o comportamento do potássio, que se desloca para dentro da célula na alcalose.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;hipocapnia aguda&lt;/strong&gt; tem efeitos que vão muito além do valor numérico da PaCO&lt;sub&gt;2&lt;/sub&gt;. No sistema nervoso central, a queda do CO&lt;sub&gt;2&lt;/sub&gt; provoca &lt;strong&gt;vasoconstrição cerebral&lt;/strong&gt;: o fluxo sanguíneo cerebral varia cerca de 1 a 2 mL/100 g/min para cada 1 mmHg de variação da PaCO&lt;sub&gt;2&lt;/sub&gt; dentro da faixa fisiológica. Essa é a base da hiperventilação como manobra de resgate na hipertensão intracraniana, e também o motivo pelo qual a hipocapnia mantida é perigosa, por risco de isquemia.&lt;/p&gt;&lt;p&gt;No transporte de oxigênio, a alcalose desloca a &lt;strong&gt;curva de dissociação da hemoglobina para a esquerda&lt;/strong&gt; (efeito Bohr), aumentando a afinidade da hemoglobina pelo oxigênio e dificultando sua liberação nos tecidos. Somam-se ainda queda do cálcio ionizado (maior ligação à albumina em pH alcalino, com parestesias e espasmo carpopedal no paciente acordado), hipocalemia por deslocamento do potássio para o meio intracelular, broncodilatação leve e redução do débito cardíaco quando associada a pressão positiva.&lt;/p&gt;&lt;p&gt;A hipercapnia produz o oposto: vasodilatação cerebral, desvio da curva para a direita, estímulo simpático, hipercalemia e aumento do cálcio ionizado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na alcalose o cálcio ionizado &lt;em&gt;cai&lt;/em&gt;, pois mais cálcio se liga à albumina. (C) descreve o efeito da hipercapnia, não da hipocapnia. (D) inverte o comportamento do potássio, que se desloca para dentro da célula na alcalose.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A circulação pulmonar comporta dois compartimentos vasculares que respondem em sentidos opostos à insuflação. Os &lt;strong&gt;vasos alveolares&lt;/strong&gt; (capilares no septo interalveolar) sofrem o efeito da pressão alveolar: quando o volume pulmonar aumenta, o septo se estira e os capilares são &lt;em&gt;comprimidos e alongados&lt;/em&gt;, elevando sua resistência. Os &lt;strong&gt;vasos extra-alveolares&lt;/strong&gt; sofrem o efeito da pressão intersticial: em volumes baixos eles se estreitam por perda da tração radial do parênquima, e em volumes altos se dilatam.&lt;/p&gt;&lt;p&gt;A soma dessas duas curvas opostas gera uma relação em &lt;strong&gt;U&lt;/strong&gt;: a resistência vascular pulmonar é &lt;strong&gt;mínima em torno da capacidade residual funcional&lt;/strong&gt; e aumenta tanto em volumes muito baixos (colapso de vasos extra-alveolares) quanto em volumes elevados (compressão capilar). No caso descrito, a PEEP alta levou o pulmão bem acima da CRF: a resistência subiu, o ventrículo direito passou a ejetar contra pós-carga maior, o débito caiu e áreas ventiladas perderam perfusão — daí o alargamento do gradiente entre a PaCO&lt;sub&gt;2&lt;/sub&gt; e o CO&lt;sub&gt;2&lt;/sub&gt; expirado, que denuncia aumento de espaço morto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o ponto de mínima resistência é a capacidade residual funcional, não a capacidade pulmonar total. (C) o recrutamento de vasos extra-alveolares existe, mas é sobrepujado pela compressão capilar em volumes altos, e a relação não é linear. (D) a dependência do volume pulmonar é um determinante clássico e bem estabelecido da resistência vascular pulmonar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A circulação pulmonar comporta dois compartimentos vasculares que respondem em sentidos opostos à insuflação. Os &lt;strong&gt;vasos alveolares&lt;/strong&gt; (capilares no septo interalveolar) sofrem o efeito da pressão alveolar: quando o volume pulmonar aumenta, o septo se estira e os capilares são &lt;em&gt;comprimidos e alongados&lt;/em&gt;, elevando sua resistência. Os &lt;strong&gt;vasos extra-alveolares&lt;/strong&gt; sofrem o efeito da pressão intersticial: em volumes baixos eles se estreitam por perda da tração radial do parênquima, e em volumes altos se dilatam.&lt;/p&gt;&lt;p&gt;A soma dessas duas curvas opostas gera uma relação em &lt;strong&gt;U&lt;/strong&gt;: a resistência vascular pulmonar é &lt;strong&gt;mínima em torno da capacidade residual funcional&lt;/strong&gt; e aumenta tanto em volumes muito baixos (colapso de vasos extra-alveolares) quanto em volumes elevados (compressão capilar). No caso descrito, a PEEP alta levou o pulmão bem acima da CRF: a resistência subiu, o ventrículo direito passou a ejetar contra pós-carga maior, o débito caiu e áreas ventiladas perderam perfusão. Daí o alargamento do gradiente entre a PaCO&lt;sub&gt;2&lt;/sub&gt; e o CO&lt;sub&gt;2&lt;/sub&gt; expirado, que denuncia aumento de espaço morto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o ponto de mínima resistência é a capacidade residual funcional, não a capacidade pulmonar total. (C) o recrutamento de vasos extra-alveolares existe, mas é sobrepujado pela compressão capilar em volumes altos, e a relação não é linear. (D) a dependência do volume pulmonar é um determinante clássico e bem estabelecido da resistência vascular pulmonar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O CO&lt;sub&gt;2&lt;/sub&gt; é transportado em três formas, com proporções bastante assimétricas. A maior fração — em torno de &lt;strong&gt;70%&lt;/strong&gt; — circula como &lt;strong&gt;bicarbonato&lt;/strong&gt;. O CO&lt;sub&gt;2&lt;/sub&gt; difunde-se para dentro da hemácia, onde a &lt;strong&gt;anidrase carbônica&lt;/strong&gt; acelera enormemente sua hidratação a ácido carbônico, que se dissocia em H&lt;sup&gt;+&lt;/sup&gt; e HCO&lt;sub&gt;3&lt;/sub&gt;&lt;sup&gt;-&lt;/sup&gt;. O bicarbonato sai da hemácia em troca de cloreto (desvio do cloreto, ou fenômeno de Hamburger), enquanto o H&lt;sup&gt;+&lt;/sup&gt; é tamponado pela hemoglobina desoxigenada.&lt;/p&gt;&lt;p&gt;Aproximadamente &lt;strong&gt;20 a 25%&lt;/strong&gt; são transportados como &lt;strong&gt;compostos carbamínicos&lt;/strong&gt;, ligados aos grupos amino terminais da globina — e não ao heme, que é o sítio do oxigênio. Os &lt;strong&gt;5 a 10%&lt;/strong&gt; restantes viajam &lt;strong&gt;dissolvidos&lt;/strong&gt; no plasma; essa fração, embora pequena, é a que gera a pressão parcial medida na gasometria, pois a lei de Henry relaciona pressão parcial ao gás fisicamente dissolvido. O CO&lt;sub&gt;2&lt;/sub&gt; é cerca de vinte vezes mais solúvel que o oxigênio, o que explica sua eliminação eficiente mesmo em distúrbios de difusão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;efeito Haldane&lt;/strong&gt; completa o quadro: a hemoglobina desoxigenada transporta mais CO&lt;sub&gt;2&lt;/sub&gt;, o que favorece a captação tecidual e a liberação pulmonar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a fração dissolvida é pequena, ainda que seja a determinante da PaCO&lt;sub&gt;2&lt;/sub&gt;. (C) o CO&lt;sub&gt;2&lt;/sub&gt; liga-se aos grupos amino da globina, sem competir com o oxigênio pelo heme, e essa fração é minoritária. (D) o ácido carbônico é intermediário instável e depende da anidrase carbônica para se formar em velocidade fisiológica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O CO&lt;sub&gt;2&lt;/sub&gt; é transportado em três formas, com proporções bastante assimétricas. A maior fração, em torno de &lt;strong&gt;70%&lt;/strong&gt;, circula como &lt;strong&gt;bicarbonato&lt;/strong&gt;. O CO&lt;sub&gt;2&lt;/sub&gt; difunde-se para dentro da hemácia, onde a &lt;strong&gt;anidrase carbônica&lt;/strong&gt; acelera enormemente sua hidratação a ácido carbônico, que se dissocia em H&lt;sup&gt;+&lt;/sup&gt; e HCO&lt;sub&gt;3&lt;/sub&gt;&lt;sup&gt;-&lt;/sup&gt;. O bicarbonato sai da hemácia em troca de cloreto (desvio do cloreto, ou fenômeno de Hamburger), enquanto o H&lt;sup&gt;+&lt;/sup&gt; é tamponado pela hemoglobina desoxigenada.&lt;/p&gt;&lt;p&gt;Aproximadamente &lt;strong&gt;20 a 25%&lt;/strong&gt; são transportados como &lt;strong&gt;compostos carbamínicos&lt;/strong&gt;, ligados aos grupos amino terminais da globina, e não ao heme, que é o sítio do oxigênio. Os &lt;strong&gt;5 a 10%&lt;/strong&gt; restantes viajam &lt;strong&gt;dissolvidos&lt;/strong&gt; no plasma; essa fração, embora pequena, é a que gera a pressão parcial medida na gasometria, pois a lei de Henry relaciona pressão parcial ao gás fisicamente dissolvido. O CO&lt;sub&gt;2&lt;/sub&gt; é cerca de vinte vezes mais solúvel que o oxigênio, o que explica sua eliminação eficiente mesmo em distúrbios de difusão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;efeito Haldane&lt;/strong&gt; completa o quadro: a hemoglobina desoxigenada transporta mais CO&lt;sub&gt;2&lt;/sub&gt;, o que favorece a captação tecidual e a liberação pulmonar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a fração dissolvida é pequena, ainda que seja a determinante da PaCO&lt;sub&gt;2&lt;/sub&gt;. (C) o CO&lt;sub&gt;2&lt;/sub&gt; liga-se aos grupos amino da globina, sem competir com o oxigênio pelo heme, e essa fração é minoritária. (D) o ácido carbônico é intermediário instável e depende da anidrase carbônica para se formar em velocidade fisiológica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O broncoespasmo intraoperatório grave segue uma sequência de tratamento bem estabelecida. Primeiro, confirmar que se trata mesmo de broncoespasmo: a diferença aumentada entre pressão de pico e pressão de platô confirma componente &lt;strong&gt;resistivo&lt;/strong&gt;, e é preciso afastar tubo malposicionado, obstruído ou herniação do balonete. Em seguida, &lt;strong&gt;aprofundar a anestesia&lt;/strong&gt; (halogenado, propofol ou cetamina) e administrar &lt;strong&gt;beta-2 agonista inalatório&lt;/strong&gt; — lembrando que, através do tubo traqueal, a deposição pulmonar é muito baixa e frequentemente são necessários múltiplos disparos sucessivos.&lt;/p&gt;&lt;p&gt;Quando o quadro é refratário e há repercussão sobre a oxigenação, a &lt;strong&gt;adrenalina&lt;/strong&gt; é a droga de resgate. Por via venosa, em bolus pequenos e titulados (tipicamente 10 a 100 mcg no adulto) ou em infusão contínua, combina broncodilatação beta-2 potente com suporte hemodinâmico. Corticosteroide venoso deve ser administrado, mas seu efeito só aparece em algumas horas — não resolve a crise aguda.&lt;/p&gt;&lt;p&gt;Enquanto isso, ajusta-se o ventilador para tempo expiratório longo, volume corrente modesto e tolerância à hipercapnia, vigiando auto-PEEP e hipotensão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a aminofilina tem janela terapêutica estreita, potencial arritmogênico e eficácia inferior à dos beta-2 agonistas, estando praticamente abandonada nesse contexto. (B) o corticosteroide é indicado, mas seu início de ação é de horas e não resolve a emergência. (C) o bloqueio neuromuscular não trata broncoespasmo, e a curarização já estava presente; insistir nela atrasa a terapia efetiva.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O broncoespasmo intraoperatório grave segue uma sequência de tratamento bem estabelecida. Primeiro, confirmar que se trata mesmo de broncoespasmo: a diferença aumentada entre pressão de pico e pressão de platô confirma componente &lt;strong&gt;resistivo&lt;/strong&gt;, e é preciso afastar tubo malposicionado, obstruído ou herniação do balonete. Em seguida, &lt;strong&gt;aprofundar a anestesia&lt;/strong&gt; (halogenado, propofol ou cetamina) e administrar &lt;strong&gt;beta-2 agonista inalatório&lt;/strong&gt;. Vale lembrar que, através do tubo traqueal, a deposição pulmonar é muito baixa e frequentemente são necessários múltiplos disparos sucessivos.&lt;/p&gt;&lt;p&gt;Quando o quadro é refratário e há repercussão sobre a oxigenação, a &lt;strong&gt;adrenalina&lt;/strong&gt; é a droga de resgate. Por via venosa, em bolus pequenos e titulados (tipicamente 10 a 100 mcg no adulto) ou em infusão contínua, combina broncodilatação beta-2 potente com suporte hemodinâmico. Corticosteroide venoso deve ser administrado, mas seu efeito só aparece em algumas horas; não resolve a crise aguda.&lt;/p&gt;&lt;p&gt;Enquanto isso, ajusta-se o ventilador para tempo expiratório longo, volume corrente modesto e tolerância à hipercapnia, vigiando auto-PEEP e hipotensão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a aminofilina tem janela terapêutica estreita, potencial arritmogênico e eficácia inferior à dos beta-2 agonistas, estando praticamente abandonada nesse contexto. (B) o corticosteroide é indicado, mas seu início de ação é de horas e não resolve a emergência. (C) o bloqueio neuromuscular não trata broncoespasmo, e a curarização já estava presente; insistir nela atrasa a terapia efetiva.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A distinção entre &lt;strong&gt;pressão de pico&lt;/strong&gt; e &lt;strong&gt;pressão de platô&lt;/strong&gt; é a ferramenta diagnóstica mais rápida diante de aumento de pressão na via aérea, e depende de um raciocínio simples. A pressão de pico vence &lt;em&gt;resistência mais complacência&lt;/em&gt;; a pressão de platô, medida em pausa inspiratória com fluxo zero, reflete apenas a &lt;strong&gt;complacência&lt;/strong&gt; do sistema respiratório. A diferença entre as duas é, portanto, a parcela &lt;strong&gt;resistiva&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Assim:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Pico alto com platô normal&lt;/strong&gt; (diferença alargada): problema de resistência — broncoespasmo, tubo dobrado, mordido ou obstruído por secreção, herniação do balonete, filtro obstruído.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pico e platô igualmente altos&lt;/strong&gt; (diferença preservada): problema de complacência — pneumotórax, atelectasia, intubação seletiva, edema pulmonar, pneumoperitônio excessivo, Trendelenburg acentuado, compressão cirúrgica.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No caso, a diferença pico-platô saltou de 4 para 23 cmH&lt;sub&gt;2&lt;/sub&gt;O com platô praticamente inalterado: o problema é inequivocamente resistivo. A conduta imediata é inspecionar o tubo e o circuito, passar sonda de aspiração para verificar patência, auscultar e, se confirmado broncoespasmo, aprofundar a anestesia e administrar broncodilatador.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A), (B) e (D) descrevem condições que reduzem a complacência e, por isso, elevariam também a pressão de platô — o que não ocorreu neste paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A distinção entre &lt;strong&gt;pressão de pico&lt;/strong&gt; e &lt;strong&gt;pressão de platô&lt;/strong&gt; é a ferramenta diagnóstica mais rápida diante de aumento de pressão na via aérea, e depende de um raciocínio simples. A pressão de pico vence &lt;em&gt;resistência mais complacência&lt;/em&gt;; a pressão de platô, medida em pausa inspiratória com fluxo zero, reflete apenas a &lt;strong&gt;complacência&lt;/strong&gt; do sistema respiratório. A diferença entre as duas é, portanto, a parcela &lt;strong&gt;resistiva&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Assim:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Pico alto com platô normal&lt;/strong&gt; (diferença alargada): problema de resistência: broncoespasmo, tubo dobrado, mordido ou obstruído por secreção, herniação do balonete, filtro obstruído.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pico e platô igualmente altos&lt;/strong&gt; (diferença preservada): problema de complacência: pneumotórax, atelectasia, intubação seletiva, edema pulmonar, pneumoperitônio excessivo, Trendelenburg acentuado, compressão cirúrgica.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No caso, a diferença pico-platô saltou de 4 para 23 cmH&lt;sub&gt;2&lt;/sub&gt;O com platô praticamente inalterado: o problema é inequivocamente resistivo. A conduta imediata é inspecionar o tubo e o circuito, passar sonda de aspiração para verificar patência, auscultar e, se confirmado broncoespasmo, aprofundar a anestesia e administrar broncodilatador.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A), (B) e (D) descrevem condições que reduzem a complacência e, por isso, elevariam também a pressão de platô, o que não ocorreu neste paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;auto-PEEP&lt;/strong&gt; (PEEP intrínseca) surge quando o tempo expiratório é insuficiente para o esvaziamento pulmonar completo, situação típica da limitação ao fluxo expiratório na DPOC e na asma. Além de hiperinsuflação, repercussão hemodinâmica e risco de barotrauma, ela impõe um &lt;strong&gt;limiar inspiratório&lt;/strong&gt;: para que a pressão alveolar caia até o valor de disparo do ventilador, o paciente precisa primeiro gerar um esforço que anule toda a auto-PEEP. Daí os &lt;em&gt;esforços inefetivos&lt;/em&gt; — o diafragma trabalha e nenhum ciclo é entregue.&lt;/p&gt;&lt;p&gt;A solução fisiologicamente correta é aplicar &lt;strong&gt;PEEP externa em torno de 75 a 85% da auto-PEEP medida&lt;/strong&gt;. Nos pacientes com limitação ao fluxo, a PEEP externa nesse patamar equilibra a pressão a montante do ponto de colapso dinâmico sem aumentar o volume pulmonar total, reduzindo drasticamente o trabalho necessário para disparar o ventilador. Para auto-PEEP de 8 cmH&lt;sub&gt;2&lt;/sub&gt;O, algo próximo de 6 cmH&lt;sub&gt;2&lt;/sub&gt;O é apropriado, com reavaliação da pressão de platô e da hemodinâmica após o ajuste.&lt;/p&gt;&lt;p&gt;Complementarmente, deve-se prolongar o tempo expiratório, broncodilatar e tratar a causa da hiperinsuflação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) aumentar a frequência &lt;em&gt;encurta&lt;/em&gt; o tempo expiratório e agrava o aprisionamento aéreo. (C) PEEP externa acima da auto-PEEP eleva o volume pulmonar, piora a hiperinsuflação e compromete o retorno venoso. (D) volumes correntes maiores exigem tempos expiratórios ainda mais longos e aumentam a auto-PEEP.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;auto-PEEP&lt;/strong&gt; (PEEP intrínseca) surge quando o tempo expiratório é insuficiente para o esvaziamento pulmonar completo, situação típica da limitação ao fluxo expiratório na DPOC e na asma. Além de hiperinsuflação, repercussão hemodinâmica e risco de barotrauma, ela impõe um &lt;strong&gt;limiar inspiratório&lt;/strong&gt;: para que a pressão alveolar caia até o valor de disparo do ventilador, o paciente precisa primeiro gerar um esforço que anule toda a auto-PEEP. Daí os &lt;em&gt;esforços inefetivos&lt;/em&gt;: o diafragma trabalha e nenhum ciclo é entregue.&lt;/p&gt;&lt;p&gt;A solução fisiologicamente correta é aplicar &lt;strong&gt;PEEP externa em torno de 75 a 85% da auto-PEEP medida&lt;/strong&gt;. Nos pacientes com limitação ao fluxo, a PEEP externa nesse patamar equilibra a pressão a montante do ponto de colapso dinâmico sem aumentar o volume pulmonar total, reduzindo drasticamente o trabalho necessário para disparar o ventilador. Para auto-PEEP de 8 cmH&lt;sub&gt;2&lt;/sub&gt;O, algo próximo de 6 cmH&lt;sub&gt;2&lt;/sub&gt;O é apropriado, com reavaliação da pressão de platô e da hemodinâmica após o ajuste.&lt;/p&gt;&lt;p&gt;Complementarmente, deve-se prolongar o tempo expiratório, broncodilatar e tratar a causa da hiperinsuflação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) aumentar a frequência &lt;em&gt;encurta&lt;/em&gt; o tempo expiratório e agrava o aprisionamento aéreo. (C) PEEP externa acima da auto-PEEP eleva o volume pulmonar, piora a hiperinsuflação e compromete o retorno venoso. (D) volumes correntes maiores exigem tempos expiratórios ainda mais longos e aumentam a auto-PEEP.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escolha entre os dois grandes grupos de modos ventilatórios se resume a decidir &lt;strong&gt;qual variável se garante e qual se aceita variar&lt;/strong&gt;.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ventilação a volume (VCV)&lt;/strong&gt;: o volume corrente é programado e garantido; a &lt;strong&gt;pressão&lt;/strong&gt; é a variável dependente e sobe quando a complacência cai ou a resistência aumenta. O fluxo costuma ser constante (onda quadrada). O risco é o barotrauma silencioso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação a pressão (PCV)&lt;/strong&gt;: a pressão inspiratória é programada e limitada; o &lt;strong&gt;volume corrente&lt;/strong&gt; é a variável dependente e cai quando a complacência piora. O fluxo é desacelerado, o que gera pressão média de via aérea mais alta e melhor distribuição do gás. O risco é a hipoventilação silenciosa.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No caso, o pneumoperitônio e o Trendelenburg deslocam o diafragma cefalicamente, reduzem a capacidade residual funcional e derrubam a complacência toracopulmonar. Com pressão fixa de 18 cmH&lt;sub&gt;2&lt;/sub&gt;O, o volume entregue necessariamente diminui — de 480 para 330 mL, o que corresponde a queda da complacência de cerca de 27 para 18 mL/cmH&lt;sub&gt;2&lt;/sub&gt;O. A conduta é elevar a pressão inspiratória e/ou a frequência, ajustar a PEEP e recrutar, sempre com alarme de volume-minuto ativo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte o conceito básico do modo. (C) o problema aqui é de complacência, não de resistência, e em PCV a pressão não ultrapassa o valor programado. (D) o fluxo em PCV é desacelerado, e o tempo inspiratório permaneceu inalterado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escolha entre os dois grandes grupos de modos ventilatórios se resume a decidir &lt;strong&gt;qual variável se garante e qual se aceita variar&lt;/strong&gt;.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ventilação a volume (VCV)&lt;/strong&gt;: o volume corrente é programado e garantido; a &lt;strong&gt;pressão&lt;/strong&gt; é a variável dependente e sobe quando a complacência cai ou a resistência aumenta. O fluxo costuma ser constante (onda quadrada). O risco é o barotrauma silencioso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação a pressão (PCV)&lt;/strong&gt;: a pressão inspiratória é programada e limitada; o &lt;strong&gt;volume corrente&lt;/strong&gt; é a variável dependente e cai quando a complacência piora. O fluxo é desacelerado, o que gera pressão média de via aérea mais alta e melhor distribuição do gás. O risco é a hipoventilação silenciosa.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No caso, o pneumoperitônio e o Trendelenburg deslocam o diafragma cefalicamente, reduzem a capacidade residual funcional e derrubam a complacência toracopulmonar. Com pressão fixa de 18 cmH&lt;sub&gt;2&lt;/sub&gt;O, o volume entregue necessariamente diminui: de 480 para 330 mL, o que corresponde a queda da complacência de cerca de 27 para 18 mL/cmH&lt;sub&gt;2&lt;/sub&gt;O. A conduta é elevar a pressão inspiratória e/ou a frequência, ajustar a PEEP e recrutar, sempre com alarme de volume-minuto ativo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte o conceito básico do modo. (C) o problema aqui é de complacência, não de resistência, e em PCV a pressão não ultrapassa o valor programado. (D) o fluxo em PCV é desacelerado, e o tempo inspiratório permaneceu inalterado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Diante de hipoxemia durante a &lt;strong&gt;ventilação monopulmonar&lt;/strong&gt;, a primeira hipótese é sempre &lt;strong&gt;malposição do tubo de duplo lúmen&lt;/strong&gt;. A mudança do decúbito dorsal para o lateral é o momento clássico de deslocamento: o tubo pode migrar distalmente e ocluir o lobo superior esquerdo, ou recuar para a traqueia e perder o isolamento. A tríade descrita — queda da saturação, elevação da pressão de pico e assimetria da ausculta no pulmão dependente, tudo surgindo logo após a lateralização — é altamente sugestiva.&lt;/p&gt;&lt;p&gt;A sequência recomendada é: confirmar FiO&lt;sub&gt;2&lt;/sub&gt; de 1,0, verificar a estabilidade hemodinâmica e &lt;strong&gt;reavaliar a posição do tubo com o broncoscópio&lt;/strong&gt;, aspirando secreções ou sangue se necessário. Só depois de excluída a causa mecânica passa-se às manobras fisiológicas: recrutamento e PEEP de 5 a 10 cmH&lt;sub&gt;2&lt;/sub&gt;O no pulmão dependente, CPAP no pulmão não dependente (com anuência do cirurgião, pois insufla o campo), insuflação intermitente, e, em último caso, clampeamento da artéria pulmonar do lado operado ou retorno à ventilação bipulmonar.&lt;/p&gt;&lt;p&gt;Corrigir o posicionamento resolve grande parte dos episódios em segundos e evita medidas que apenas mascaram o problema.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) PEEP no pulmão dependente é medida válida, mas não resolve um brônquio ocluído e pode desviar fluxo para o pulmão operado. (B) o CPAP no pulmão não dependente vem depois, e atrapalha o campo cirúrgico. (C) retomar a ventilação bipulmonar sem investigar a causa mecânica interrompe a cirurgia desnecessariamente e não corrige a malposição.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Diante de hipoxemia durante a &lt;strong&gt;ventilação monopulmonar&lt;/strong&gt;, a primeira hipótese é sempre &lt;strong&gt;malposição do tubo de duplo lúmen&lt;/strong&gt;. A mudança do decúbito dorsal para o lateral é o momento clássico de deslocamento: o tubo pode migrar distalmente e ocluir o lobo superior esquerdo, ou recuar para a traqueia e perder o isolamento. A tríade descrita (queda da saturação, elevação da pressão de pico e assimetria da ausculta no pulmão dependente, tudo surgindo logo após a lateralização) é altamente sugestiva.&lt;/p&gt;&lt;p&gt;A sequência recomendada é: confirmar FiO&lt;sub&gt;2&lt;/sub&gt; de 1,0, verificar a estabilidade hemodinâmica e &lt;strong&gt;reavaliar a posição do tubo com o broncoscópio&lt;/strong&gt;, aspirando secreções ou sangue se necessário. Só depois de excluída a causa mecânica passa-se às manobras fisiológicas: recrutamento e PEEP de 5 a 10 cmH&lt;sub&gt;2&lt;/sub&gt;O no pulmão dependente, CPAP no pulmão não dependente (com anuência do cirurgião, pois insufla o campo), insuflação intermitente, e, em último caso, clampeamento da artéria pulmonar do lado operado ou retorno à ventilação bipulmonar.&lt;/p&gt;&lt;p&gt;Corrigir o posicionamento resolve grande parte dos episódios em segundos e evita medidas que apenas mascaram o problema.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) PEEP no pulmão dependente é medida válida, mas não resolve um brônquio ocluído e pode desviar fluxo para o pulmão operado. (B) o CPAP no pulmão não dependente vem depois, e atrapalha o campo cirúrgico. (C) retomar a ventilação bipulmonar sem investigar a causa mecânica interrompe a cirurgia desnecessariamente e não corrige a malposição.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A separação entre indicações absolutas e relativas de &lt;strong&gt;isolamento pulmonar&lt;/strong&gt; é conceitualmente simples: é &lt;em&gt;absoluta&lt;/em&gt; quando, sem o isolamento, existe risco direto de contaminação do pulmão sadio, de perda da ventilação ou de impossibilidade de ventilar; é &lt;em&gt;relativa&lt;/em&gt; quando o benefício é a exposição cirúrgica.&lt;/p&gt;&lt;p&gt;São &lt;strong&gt;indicações absolutas&lt;/strong&gt;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;proteção do pulmão sadio contra contaminação — hemorragia pulmonar maciça e abscesso ou infecção purulenta unilateral volumosa;&lt;/li&gt;&lt;li&gt;controle da distribuição da ventilação — fístula broncopleural ou broncocutânea de alto débito, ruptura de árvore traqueobrônquica, cisto ou bolha gigante unilateral com risco de ruptura;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;lavagem pulmonar total&lt;/strong&gt; na proteinose alveolar, em que um pulmão é literalmente preenchido por líquido enquanto o outro sustenta as trocas gasosas — o isolamento estanque é condição de sobrevivência.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;São &lt;strong&gt;relativas&lt;/strong&gt; praticamente todas as demais: lobectomias, pneumonectomia, esofagectomia, cirurgia de aorta torácica descendente, cirurgia de mediastino, simpatectomia torácica e procedimentos videotoracoscópicos, em que o colapso pulmonar melhora a exposição mas não é imprescindível.&lt;/p&gt;&lt;p&gt;Essa classificação orienta o planejamento: nas absolutas, o tubo de duplo lúmen é preferível ao bloqueador brônquico, por oferecer isolamento mais confiável e permitir aspiração do pulmão isolado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A), (B) e (D) descrevem procedimentos em que o isolamento é desejável por facilitar a exposição cirúrgica, configurando indicações relativas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A separação entre indicações absolutas e relativas de &lt;strong&gt;isolamento pulmonar&lt;/strong&gt; é conceitualmente simples: é &lt;em&gt;absoluta&lt;/em&gt; quando, sem o isolamento, existe risco direto de contaminação do pulmão sadio, de perda da ventilação ou de impossibilidade de ventilar; é &lt;em&gt;relativa&lt;/em&gt; quando o benefício é a exposição cirúrgica.&lt;/p&gt;&lt;p&gt;São &lt;strong&gt;indicações absolutas&lt;/strong&gt;:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;proteção do pulmão sadio contra contaminação: hemorragia pulmonar maciça e abscesso ou infecção purulenta unilateral volumosa;&lt;/li&gt;&lt;li&gt;controle da distribuição da ventilação: fístula broncopleural ou broncocutânea de alto débito, ruptura de árvore traqueobrônquica, cisto ou bolha gigante unilateral com risco de ruptura;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;lavagem pulmonar total&lt;/strong&gt; na proteinose alveolar, em que um pulmão é literalmente preenchido por líquido enquanto o outro sustenta as trocas gasosas; o isolamento estanque é condição de sobrevivência.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;São &lt;strong&gt;relativas&lt;/strong&gt; praticamente todas as demais: lobectomias, pneumonectomia, esofagectomia, cirurgia de aorta torácica descendente, cirurgia de mediastino, simpatectomia torácica e procedimentos videotoracoscópicos, em que o colapso pulmonar melhora a exposição mas não é imprescindível.&lt;/p&gt;&lt;p&gt;Essa classificação orienta o planejamento: nas absolutas, o tubo de duplo lúmen é preferível ao bloqueador brônquico, por oferecer isolamento mais confiável e permitir aspiração do pulmão isolado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A), (B) e (D) descrevem procedimentos em que o isolamento é desejável por facilitar a exposição cirúrgica, configurando indicações relativas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pneumonectomia remove metade do leito vascular pulmonar. A resistência vascular pulmonar sobe de imediato e o &lt;strong&gt;ventrículo direito&lt;/strong&gt; — câmara de paredes finas, adaptada a pós-carga baixa e pouco tolerante a aumentos agudos — pode entrar em falência. O quadro descrito é típico: hipotensão com pressão venosa central alta, ventrículo direito dilatado e hipocinético e ventrículo esquerdo pequeno por &lt;em&gt;interdependência ventricular&lt;/em&gt;, com o septo desviado para a esquerda comprometendo o enchimento esquerdo.&lt;/p&gt;&lt;p&gt;O tratamento assenta em três pilares:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Restaurar a pressão de perfusão coronariana do VD.&lt;/strong&gt; Diferentemente do VE, o VD é perfundido em sístole e diástole, mas essa vantagem se perde quando a pressão sistêmica cai abaixo da pressão ventricular direita. A noradrenalina eleva a pressão aórtica proporcionalmente mais do que a pulmonar, sendo o vasopressor de escolha.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Reduzir a pós-carga pulmonar.&lt;/strong&gt; Corrigir hipoxemia, hipercapnia e acidose — potentes vasoconstritores pulmonares — e evitar PEEP e volumes correntes excessivos. Óxido nítrico inalado ou prostaciclina inalatória são opções por atuarem seletivamente no leito pulmonar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Otimizar, sem sobrecarregar, a volemia.&lt;/strong&gt; O VD dilatado piora com volume adicional.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bolus volêmico distende ainda mais o VD e agrava o desvio septal. (C) a nitroglicerina sistêmica derruba a pressão aórtica e piora a perfusão coronariana do VD. (D) PEEP elevada aumenta a resistência vascular pulmonar e a pós-carga do VD.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pneumonectomia remove metade do leito vascular pulmonar. A resistência vascular pulmonar sobe de imediato e o &lt;strong&gt;ventrículo direito&lt;/strong&gt;, câmara de paredes finas, adaptada a pós-carga baixa e pouco tolerante a aumentos agudos, pode entrar em falência. O quadro descrito é típico: hipotensão com pressão venosa central alta, ventrículo direito dilatado e hipocinético e ventrículo esquerdo pequeno por &lt;em&gt;interdependência ventricular&lt;/em&gt;, com o septo desviado para a esquerda comprometendo o enchimento esquerdo.&lt;/p&gt;&lt;p&gt;O tratamento assenta em três pilares:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Restaurar a pressão de perfusão coronariana do VD.&lt;/strong&gt; Diferentemente do VE, o VD é perfundido em sístole e diástole, mas essa vantagem se perde quando a pressão sistêmica cai abaixo da pressão ventricular direita. A noradrenalina eleva a pressão aórtica proporcionalmente mais do que a pulmonar, sendo o vasopressor de escolha.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Reduzir a pós-carga pulmonar.&lt;/strong&gt; Corrigir hipoxemia, hipercapnia e acidose (potentes vasoconstritores pulmonares) e evitar PEEP e volumes correntes excessivos. Óxido nítrico inalado ou prostaciclina inalatória são opções por atuarem seletivamente no leito pulmonar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Otimizar, sem sobrecarregar, a volemia.&lt;/strong&gt; O VD dilatado piora com volume adicional.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bolus volêmico distende ainda mais o VD e agrava o desvio septal. (C) a nitroglicerina sistêmica derruba a pressão aórtica e piora a perfusão coronariana do VD. (D) PEEP elevada aumenta a resistência vascular pulmonar e a pós-carga do VD.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;bloqueador brônquico&lt;/strong&gt; é a solução de escolha quando a via aérea impõe dificuldade. Ele é introduzido através de um tubo traqueal de lúmen único — que pode ser posicionado com o paciente acordado, guiado por fibrobroncoscópio — e depois direcionado ao brônquio-alvo sob visão direta, com o balonete insuflado para promover o colapso do pulmão operado.&lt;/p&gt;&lt;p&gt;Suas &lt;strong&gt;vantagens&lt;/strong&gt;: dispensa a passagem de um tubo de duplo lúmen, volumoso e rígido; serve a pacientes já intubados, traqueostomizados, com intubação nasal, e a crianças; permite bloqueio seletivo lobar; e evita a troca de tubo ao final da cirurgia quando o paciente permanecerá ventilado.&lt;/p&gt;&lt;p&gt;Suas &lt;strong&gt;limitações&lt;/strong&gt; devem ser conhecidas: colapso pulmonar mais lento, maior tendência ao deslocamento com a manipulação cirúrgica, canal interno estreito que dificulta aspiração e aplicação de CPAP no pulmão isolado, e menor confiabilidade quando o objetivo é proteger o pulmão sadio de sangue ou pus.&lt;/p&gt;&lt;p&gt;Nas indicações absolutas de isolamento com risco de contaminação, o tubo de duplo lúmen continua preferível — mas jamais à custa de perder uma via aérea reconhecidamente difícil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) indução em sequência rápida e passagem às cegas de tubo de duplo lúmen em via aérea difícil prevista é conduta de risco elevado. (C) o tubo de duplo lúmen direito tem margem de segurança &lt;em&gt;menor&lt;/em&gt;, pelo brônquio principal direito curto e pela origem precoce do lobo superior, e não resolve a dificuldade de intubação. (D) a intubação seletiva com tubo comum não isola de forma confiável, não permite aspirar o pulmão operado e não facilita a via aérea difícil.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;bloqueador brônquico&lt;/strong&gt; é a solução de escolha quando a via aérea impõe dificuldade. Ele é introduzido através de um tubo traqueal de lúmen único (que pode ser posicionado com o paciente acordado, guiado por fibrobroncoscópio) e depois direcionado ao brônquio-alvo sob visão direta, com o balonete insuflado para promover o colapso do pulmão operado.&lt;/p&gt;&lt;p&gt;Suas &lt;strong&gt;vantagens&lt;/strong&gt;: dispensa a passagem de um tubo de duplo lúmen, volumoso e rígido; serve a pacientes já intubados, traqueostomizados, com intubação nasal, e a crianças; permite bloqueio seletivo lobar; e evita a troca de tubo ao final da cirurgia quando o paciente permanecerá ventilado.&lt;/p&gt;&lt;p&gt;Suas &lt;strong&gt;limitações&lt;/strong&gt; devem ser conhecidas: colapso pulmonar mais lento, maior tendência ao deslocamento com a manipulação cirúrgica, canal interno estreito que dificulta aspiração e aplicação de CPAP no pulmão isolado, e menor confiabilidade quando o objetivo é proteger o pulmão sadio de sangue ou pus.&lt;/p&gt;&lt;p&gt;Nas indicações absolutas de isolamento com risco de contaminação, o tubo de duplo lúmen continua preferível, mas jamais à custa de perder uma via aérea reconhecidamente difícil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) indução em sequência rápida e passagem às cegas de tubo de duplo lúmen em via aérea difícil prevista é conduta de risco elevado. (C) o tubo de duplo lúmen direito tem margem de segurança &lt;em&gt;menor&lt;/em&gt;, pelo brônquio principal direito curto e pela origem precoce do lobo superior, e não resolve a dificuldade de intubação. (D) a intubação seletiva com tubo comum não isola de forma confiável, não permite aspirar o pulmão operado e não facilita a via aérea difícil.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A associação de &lt;strong&gt;massa mediastinal anterior&lt;/strong&gt; com &lt;strong&gt;síndrome da veia cava superior&lt;/strong&gt; reúne dois perigos distintos, e o plano anestésico precisa endereçar os dois.&lt;/p&gt;&lt;p&gt;O primeiro é a &lt;strong&gt;obstrução dinâmica de via aérea e de estruturas cardiovasculares&lt;/strong&gt;. Com a indução, a perda do tônus muscular, a mudança para decúbito dorsal, o bloqueio neuromuscular e a pressão positiva podem transformar uma compressão parcial em colapso completo da traqueia ou dos brônquios principais, ou em compressão da artéria pulmonar e do átrio, com parada cardíaca refratária. Por isso preserva-se a &lt;strong&gt;ventilação espontânea&lt;/strong&gt; sempre que possível — indução inalatória ou venosa titulada, evitando ou postergando ao máximo o bloqueio neuromuscular —, mantém-se o paciente com o tronco elevado, conhece-se de antemão a posição que alivia os sintomas e tem-se plano de resgate (broncoscópio rígido disponível, decúbito lateral ou prono, e circulação extracorpórea considerada nos casos mais graves). Sempre que houver alternativa, prefere-se biópsia sob anestesia local ou sedação leve.&lt;/p&gt;&lt;p&gt;O segundo é a &lt;strong&gt;obstrução da veia cava superior&lt;/strong&gt;: fármacos infundidos em veias de membros superiores ou do território cervical chegam com atraso e de modo imprevisível. Os acessos devem ser obtidos em &lt;strong&gt;membros inferiores&lt;/strong&gt;, tipicamente veia femoral, e a monitorização hemodinâmica planejada nesse mesmo território.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (C) associam indução venosa com curarização precoce — o cenário clássico de colapso — a acessos em território drenado pela cava superior obstruída. (B) acerta na ventilação espontânea, mas erra no acesso em membro superior.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A associação de &lt;strong&gt;massa mediastinal anterior&lt;/strong&gt; com &lt;strong&gt;síndrome da veia cava superior&lt;/strong&gt; reúne dois perigos distintos, e o plano anestésico precisa endereçar os dois.&lt;/p&gt;&lt;p&gt;O primeiro é a &lt;strong&gt;obstrução dinâmica de via aérea e de estruturas cardiovasculares&lt;/strong&gt;. Com a indução, a perda do tônus muscular, a mudança para decúbito dorsal, o bloqueio neuromuscular e a pressão positiva podem transformar uma compressão parcial em colapso completo da traqueia ou dos brônquios principais, ou em compressão da artéria pulmonar e do átrio, com parada cardíaca refratária. Por isso preserva-se a &lt;strong&gt;ventilação espontânea&lt;/strong&gt; sempre que possível (indução inalatória ou venosa titulada, evitando ou postergando ao máximo o bloqueio neuromuscular), mantém-se o paciente com o tronco elevado, conhece-se de antemão a posição que alivia os sintomas e tem-se plano de resgate (broncoscópio rígido disponível, decúbito lateral ou prono, e circulação extracorpórea considerada nos casos mais graves). Sempre que houver alternativa, prefere-se biópsia sob anestesia local ou sedação leve.&lt;/p&gt;&lt;p&gt;O segundo é a &lt;strong&gt;obstrução da veia cava superior&lt;/strong&gt;: fármacos infundidos em veias de membros superiores ou do território cervical chegam com atraso e de modo imprevisível. Os acessos devem ser obtidos em &lt;strong&gt;membros inferiores&lt;/strong&gt;, tipicamente veia femoral, e a monitorização hemodinâmica planejada nesse mesmo território.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (C) associam indução venosa com curarização precoce (o cenário clássico de colapso) a acessos em território drenado pela cava superior obstruída. (B) acerta na ventilação espontânea, mas erra no acesso em membro superior.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A esofagectomia reúne quase todos os fatores de risco para complicação pulmonar: paciente &lt;strong&gt;desnutrido&lt;/strong&gt; e frequentemente sarcopênico após neoadjuvância, &lt;strong&gt;alto risco de aspiração&lt;/strong&gt; por estase esofágica e disfagia, toracotomia com ventilação monopulmonar prolongada, manipulação e retração do pulmão, linfadenectomia extensa e dor pós-operatória intensa. A complicação pulmonar é a principal causa de morbimortalidade do procedimento.&lt;/p&gt;&lt;p&gt;As medidas com maior impacto são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Indução em sequência rápida&lt;/strong&gt; com proteção de via aérea, pelo risco de regurgitação de conteúdo retido.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação protetora&lt;/strong&gt;, com volume corrente calculado pelo &lt;em&gt;peso predito&lt;/em&gt; (cerca de 4 a 6 mL/kg durante a ventilação monopulmonar), PEEP adequada no pulmão dependente, manobras de recrutamento e limitação das pressões de platô e de distensão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Balanço hídrico restritivo, guiado por metas&lt;/strong&gt;: a sobrecarga volêmica associa-se a edema pulmonar, síndrome do desconforto respiratório agudo e edema da alça de reconstrução, sem benefício sobre a anastomose. Quando necessário, prefere-se vasopressor a volume adicional.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Analgesia regional eficaz&lt;/strong&gt; — peridural torácica ou bloqueio de parede — e &lt;strong&gt;extubação precoce&lt;/strong&gt;, que reduz pneumonia e permite fisioterapia e mobilização imediatas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) volumes correntes altos, ainda mais calculados pelo peso real, causam lesão induzida pela ventilação. (B) a estratégia liberal aumenta complicações pulmonares e edema tecidual. (D) a ventilação mecânica prolongada de rotina eleva o risco de pneumonia associada e não protege a anastomose.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A esofagectomia reúne quase todos os fatores de risco para complicação pulmonar: paciente &lt;strong&gt;desnutrido&lt;/strong&gt; e frequentemente sarcopênico após neoadjuvância, &lt;strong&gt;alto risco de aspiração&lt;/strong&gt; por estase esofágica e disfagia, toracotomia com ventilação monopulmonar prolongada, manipulação e retração do pulmão, linfadenectomia extensa e dor pós-operatória intensa. A complicação pulmonar é a principal causa de morbimortalidade do procedimento.&lt;/p&gt;&lt;p&gt;As medidas com maior impacto são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Indução em sequência rápida&lt;/strong&gt; com proteção de via aérea, pelo risco de regurgitação de conteúdo retido.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação protetora&lt;/strong&gt;, com volume corrente calculado pelo &lt;em&gt;peso predito&lt;/em&gt; (cerca de 4 a 6 mL/kg durante a ventilação monopulmonar), PEEP adequada no pulmão dependente, manobras de recrutamento e limitação das pressões de platô e de distensão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Balanço hídrico restritivo, guiado por metas&lt;/strong&gt;: a sobrecarga volêmica associa-se a edema pulmonar, síndrome do desconforto respiratório agudo e edema da alça de reconstrução, sem benefício sobre a anastomose. Quando necessário, prefere-se vasopressor a volume adicional.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Analgesia regional eficaz&lt;/strong&gt; (peridural torácica ou bloqueio de parede) e &lt;strong&gt;extubação precoce&lt;/strong&gt;, que reduz pneumonia e permite fisioterapia e mobilização imediatas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) volumes correntes altos, ainda mais calculados pelo peso real, causam lesão induzida pela ventilação. (B) a estratégia liberal aumenta complicações pulmonares e edema tecidual. (D) a ventilação mecânica prolongada de rotina eleva o risco de pneumonia associada e não protege a anastomose.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A curva de função ventricular traduz a lei de Frank-Starling: dentro de certos limites, quanto maior o estiramento das fibras miocárdicas ao final da diástole, maior a força de contração e o volume ejetado. Dois movimentos precisam ser distinguidos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;em&gt;Deslocamento ao longo da mesma curva&lt;/em&gt; — é o que a infusão de volume faz, aumentando a pré-carga sem alterar o estado contrátil.&lt;/li&gt;&lt;li&gt;&lt;em&gt;Mudança de curva&lt;/em&gt; — é o que um inotrópico faz, elevando a contratilidade e gerando maior volume sistólico para qualquer pressão de enchimento.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso a alternativa correta descreve o efeito do inotrópico: curva deslocada para cima e para a esquerda. O reconhecimento do ponto em que o paciente se encontra é o que orienta a terapia: na porção íngreme, volume ainda produz ganho; na porção plana, volume só eleva pressões de enchimento e congestão, sendo necessário atuar sobre contratilidade e pós-carga.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o ventrículo insuficiente tem curva achatada e deslocada para baixo e para a direita, com resposta pobre a volume (B). É na porção plana, e não na ascendente, que o volume deixa de aumentar o débito e apenas eleva a pressão venosa (C). O aumento da pós-carga desloca a curva para baixo e para a direita, reduzindo o volume sistólico para a mesma pré-carga (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A curva de função ventricular traduz a lei de Frank-Starling: dentro de certos limites, quanto maior o estiramento das fibras miocárdicas ao final da diástole, maior a força de contração e o volume ejetado. Dois movimentos precisam ser distinguidos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;em&gt;Deslocamento ao longo da mesma curva&lt;/em&gt;: é o que a infusão de volume faz, aumentando a pré-carga sem alterar o estado contrátil.&lt;/li&gt;&lt;li&gt;&lt;em&gt;Mudança de curva&lt;/em&gt;: é o que um inotrópico faz, elevando a contratilidade e gerando maior volume sistólico para qualquer pressão de enchimento.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso a alternativa correta descreve o efeito do inotrópico: curva deslocada para cima e para a esquerda. O reconhecimento do ponto em que o paciente se encontra é o que orienta a terapia: na porção íngreme, volume ainda produz ganho; na porção plana, volume só eleva pressões de enchimento e congestão, sendo necessário atuar sobre contratilidade e pós-carga.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o ventrículo insuficiente tem curva achatada e deslocada para baixo e para a direita, com resposta pobre a volume (B). É na porção plana, e não na ascendente, que o volume deixa de aumentar o débito e apenas eleva a pressão venosa (C). O aumento da pós-carga desloca a curva para baixo e para a direita, reduzindo o volume sistólico para a mesma pré-carga (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;biotransformação&lt;/strong&gt; converte fármacos lipossolúveis em produtos mais hidrossolúveis, passíveis de excreção renal ou biliar. As reações de &lt;strong&gt;fase I&lt;/strong&gt; (oxidação, redução e hidrólise) são conduzidas majoritariamente pelo sistema &lt;em&gt;citocromo P450&lt;/em&gt; do retículo endoplasmático hepático e apenas introduzem ou expõem um grupamento funcional. As de &lt;strong&gt;fase II&lt;/strong&gt; são conjugações — glicuronidação, sulfatação, acetilação e ligação à glutationa — que acoplam uma molécula endógena polar ao fármaco ou ao seu metabólito de fase I.&lt;/p&gt;&lt;p&gt;Todo fármaco absorvido no trato gastrintestinal alcança o fígado pela veia porta antes de chegar à circulação sistêmica. Essa passagem obrigatória, somada ao CYP3A4 abundante nos enterócitos, constitui o &lt;strong&gt;efeito de primeira passagem&lt;/strong&gt;. O midazolam é um substrato clássico do CYP3A4 e tem biodisponibilidade oral em torno de um terço a metade da dose administrada, o que explica a sedação modesta observada. É também a razão pela qual a dose oral pediátrica costuma ser várias vezes maior que a venosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a glicuronidação é reação de fase II e ocorre no fígado, não na mucosa gástrica (A). O midazolam é uma base fraca com ligação proteica alta, mas isso não distingue a via oral da venosa, pois a mesma ligação existiria após injeção (B). A ionização gástrica retarda a absorção no estômago, porém a absorção efetiva ocorre no intestino delgado e não é o determinante principal da baixa biodisponibilidade (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;biotransformação&lt;/strong&gt; converte fármacos lipossolúveis em produtos mais hidrossolúveis, passíveis de excreção renal ou biliar. As reações de &lt;strong&gt;fase I&lt;/strong&gt; (oxidação, redução e hidrólise) são conduzidas majoritariamente pelo sistema &lt;em&gt;citocromo P450&lt;/em&gt; do retículo endoplasmático hepático e apenas introduzem ou expõem um grupamento funcional. As de &lt;strong&gt;fase II&lt;/strong&gt; são conjugações (glicuronidação, sulfatação, acetilação e ligação à glutationa) que acoplam uma molécula endógena polar ao fármaco ou ao seu metabólito de fase I.&lt;/p&gt;&lt;p&gt;Todo fármaco absorvido no trato gastrintestinal alcança o fígado pela veia porta antes de chegar à circulação sistêmica. Essa passagem obrigatória, somada ao CYP3A4 abundante nos enterócitos, constitui o &lt;strong&gt;efeito de primeira passagem&lt;/strong&gt;. O midazolam é um substrato clássico do CYP3A4 e tem biodisponibilidade oral em torno de um terço a metade da dose administrada, o que explica a sedação modesta observada. É também a razão pela qual a dose oral pediátrica costuma ser várias vezes maior que a venosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a glicuronidação é reação de fase II e ocorre no fígado, não na mucosa gástrica (A). O midazolam é uma base fraca com ligação proteica alta, mas isso não distingue a via oral da venosa, pois a mesma ligação existiria após injeção (B). A ionização gástrica retarda a absorção no estômago, porém a absorção efetiva ocorre no intestino delgado e não é o determinante principal da baixa biodisponibilidade (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;anti-inflamatórios não esteroidais&lt;/strong&gt; inibem a ciclo-oxigenase e reduzem a conversão do ácido araquidônico em prostaglandinas e tromboxano. A &lt;em&gt;COX-1&lt;/em&gt; é constitutiva e responde pela citoproteção gástrica, pela produção plaquetária de tromboxano A2 e pela manutenção do fluxo sanguíneo renal; a &lt;em&gt;COX-2&lt;/em&gt; é predominantemente induzida pela inflamação, embora também seja constitutiva no rim.&lt;/p&gt;&lt;p&gt;Em condições de normovolemia, as prostaglandinas renais têm papel pequeno na hemodinâmica glomerular. Quando há redução do volume circulante efetivo, ativação do eixo renina-angiotensina-aldosterona ou uso de diuréticos, a &lt;strong&gt;vasodilatação da arteríola aferente mediada por PGE2 e PGI2&lt;/strong&gt; passa a ser essencial para sustentar a taxa de filtração. O bloqueio dessa via com um AINE potente derruba a filtração glomerular. O paciente reunia os três fatores de risco clássicos: idade avançada, diurético tiazídico e inibidor da ECA, que impede a vasoconstrição eferente compensatória.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a nefrite intersticial por AINE existe, mas costuma manifestar-se após semanas de uso e acomete o interstício, não os túbulos proximais em horas (B). O cetorolaco não causa nefropatia por precipitação de cristais, mecanismo típico de aciclovir e de alguns sulfonamídicos (C). O inibidor da ECA produz vasodilatação, e não vasoconstrição, da arteríola eferente — é justamente esse efeito que agrava a queda da filtração quando associado ao AINE (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;anti-inflamatórios não esteroidais&lt;/strong&gt; inibem a ciclo-oxigenase e reduzem a conversão do ácido araquidônico em prostaglandinas e tromboxano. A &lt;em&gt;COX-1&lt;/em&gt; é constitutiva e responde pela citoproteção gástrica, pela produção plaquetária de tromboxano A2 e pela manutenção do fluxo sanguíneo renal; a &lt;em&gt;COX-2&lt;/em&gt; é predominantemente induzida pela inflamação, embora também seja constitutiva no rim.&lt;/p&gt;&lt;p&gt;Em condições de normovolemia, as prostaglandinas renais têm papel pequeno na hemodinâmica glomerular. Quando há redução do volume circulante efetivo, ativação do eixo renina-angiotensina-aldosterona ou uso de diuréticos, a &lt;strong&gt;vasodilatação da arteríola aferente mediada por PGE2 e PGI2&lt;/strong&gt; passa a ser essencial para sustentar a taxa de filtração. O bloqueio dessa via com um AINE potente derruba a filtração glomerular. O paciente reunia os três fatores de risco clássicos: idade avançada, diurético tiazídico e inibidor da ECA, que impede a vasoconstrição eferente compensatória.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a nefrite intersticial por AINE existe, mas costuma manifestar-se após semanas de uso e acomete o interstício, não os túbulos proximais em horas (B). O cetorolaco não causa nefropatia por precipitação de cristais, mecanismo típico de aciclovir e de alguns sulfonamídicos (C). O inibidor da ECA produz vasodilatação, e não vasoconstrição, da arteríola eferente; é justamente esse efeito que agrava a queda da filtração quando associado ao AINE (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;dose de ataque&lt;/strong&gt; responde a uma pergunta de espaço: quanto fármaco é necessário para preencher o compartimento em que ele se distribui e alcançar a concentração desejada. Por isso é dada por &lt;em&gt;volume de distribuição × concentração-alvo&lt;/em&gt;, dividido pela biodisponibilidade quando a via não é a venosa. Ela não depende da capacidade de depuração do organismo.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;dose de manutenção&lt;/strong&gt; responde a uma pergunta de tempo: quanto fármaco é preciso repor por unidade de tempo para compensar o que está sendo eliminado. É dada por &lt;em&gt;clearance × concentração-alvo&lt;/em&gt;, também corrigida pela biodisponibilidade. Fármacos com volume de distribuição grande exigem doses de ataque altas mesmo quando o clearance é baixo — situação frequente com agentes muito lipofílicos.&lt;/p&gt;&lt;p&gt;Por definição, a via venosa tem biodisponibilidade igual a 1, pois toda a dose alcança a circulação sistêmica; é ela que serve de referência para as demais vias. As vias sublingual, retal baixa, transdérmica e inalatória escapam total ou parcialmente da drenagem portal e, portanto, do efeito de primeira passagem hepático.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a alternativa A inverte os determinantes das duas doses (A). A biodisponibilidade venosa é 100% por convenção, ainda que exista sequestro pulmonar transitório de bases fracas (B). A via sublingual costuma apresentar biodisponibilidade &lt;em&gt;maior&lt;/em&gt; que a oral justamente por evitar a primeira passagem hepática (C).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;dose de ataque&lt;/strong&gt; responde a uma pergunta de espaço: quanto fármaco é necessário para preencher o compartimento em que ele se distribui e alcançar a concentração desejada. Por isso é dada por &lt;em&gt;volume de distribuição × concentração-alvo&lt;/em&gt;, dividido pela biodisponibilidade quando a via não é a venosa. Ela não depende da capacidade de depuração do organismo.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;dose de manutenção&lt;/strong&gt; responde a uma pergunta de tempo: quanto fármaco é preciso repor por unidade de tempo para compensar o que está sendo eliminado. É dada por &lt;em&gt;clearance × concentração-alvo&lt;/em&gt;, também corrigida pela biodisponibilidade. Fármacos com volume de distribuição grande exigem doses de ataque altas mesmo quando o clearance é baixo, situação frequente com agentes muito lipofílicos.&lt;/p&gt;&lt;p&gt;Por definição, a via venosa tem biodisponibilidade igual a 1, pois toda a dose alcança a circulação sistêmica; é ela que serve de referência para as demais vias. As vias sublingual, retal baixa, transdérmica e inalatória escapam total ou parcialmente da drenagem portal e, portanto, do efeito de primeira passagem hepático.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a alternativa A inverte os determinantes das duas doses (A). A biodisponibilidade venosa é 100% por convenção, ainda que exista sequestro pulmonar transitório de bases fracas (B). A via sublingual costuma apresentar biodisponibilidade &lt;em&gt;maior&lt;/em&gt; que a oral justamente por evitar a primeira passagem hepática (C).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Apenas a forma &lt;strong&gt;não ionizada&lt;/strong&gt; de um fármaco atravessa livremente as membranas lipídicas. Como o grau de ionização de eletrólitos fracos depende do pH do meio e do pKa da molécula, manipular o pH urinário permite manipular a reabsorção tubular passiva — princípio conhecido como &lt;em&gt;aprisionamento iônico&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;O ácido acetilsalicílico é um &lt;strong&gt;ácido fraco&lt;/strong&gt; com pKa baixo. Em urina alcalina, encontra-se quase inteiramente na forma ionizada dentro do lúmen tubular; nessa condição não retorna ao plasma pelo epitélio tubular e é excretado. A mesma lógica se aplica ao fenobarbital. Para bases fracas, como as anfetaminas, o raciocínio se inverte: seria a acidificação urinária que aumentaria a excreção.&lt;/p&gt;&lt;p&gt;Vale lembrar que a alcalinização plasmática também é benéfica na intoxicação por salicilatos por reduzir a fração não ionizada capaz de penetrar no sistema nervoso central, atenuando a neurotoxicidade. A ligação proteica é outro determinante da farmacocinética: ácidos fracos ligam-se preferencialmente à albumina, enquanto bases fracas ligam-se sobretudo à alfa-1-glicoproteína ácida.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o bicarbonato não aumenta a ligação à albumina; na intoxicação, a saturação dos sítios de ligação aumenta a fração livre (A). A secreção tubular ativa é uma via de eliminação, e inibi-la reduziria — e não aumentaria — a excreção (B). A alternativa D inverte o efeito do pH sobre um ácido fraco e atribui a depuração a um metabolismo hepático que está saturado na intoxicação (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Apenas a forma &lt;strong&gt;não ionizada&lt;/strong&gt; de um fármaco atravessa livremente as membranas lipídicas. Como o grau de ionização de eletrólitos fracos depende do pH do meio e do pKa da molécula, manipular o pH urinário permite manipular a reabsorção tubular passiva, princípio conhecido como &lt;em&gt;aprisionamento iônico&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;O ácido acetilsalicílico é um &lt;strong&gt;ácido fraco&lt;/strong&gt; com pKa baixo. Em urina alcalina, encontra-se quase inteiramente na forma ionizada dentro do lúmen tubular; nessa condição não retorna ao plasma pelo epitélio tubular e é excretado. A mesma lógica se aplica ao fenobarbital. Para bases fracas, como as anfetaminas, o raciocínio se inverte: seria a acidificação urinária que aumentaria a excreção.&lt;/p&gt;&lt;p&gt;Vale lembrar que a alcalinização plasmática também é benéfica na intoxicação por salicilatos por reduzir a fração não ionizada capaz de penetrar no sistema nervoso central, atenuando a neurotoxicidade. A ligação proteica é outro determinante da farmacocinética: ácidos fracos ligam-se preferencialmente à albumina, enquanto bases fracas ligam-se sobretudo à alfa-1-glicoproteína ácida.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o bicarbonato não aumenta a ligação à albumina; na intoxicação, a saturação dos sítios de ligação aumenta a fração livre (A). A secreção tubular ativa é uma via de eliminação, e inibi-la reduziria, e não aumentaria, a excreção (B). A alternativa D inverte o efeito do pH sobre um ácido fraco e atribui a depuração a um metabolismo hepático que está saturado na intoxicação (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;taquifilaxia&lt;/strong&gt; é a perda rápida de eficácia após doses repetidas em curto intervalo, distinta da tolerância, que se instala ao longo de dias a semanas. Seu exemplo mais didático na anestesia é a &lt;em&gt;efedrina&lt;/em&gt;, um simpaticomimético de ação mista: parte de seu efeito vem da ativação direta dos receptores adrenérgicos, mas a parcela predominante depende do deslocamento de noradrenalina armazenada nas vesículas das terminações simpáticas pós-ganglionares.&lt;/p&gt;&lt;p&gt;Doses sucessivas esgotam progressivamente esse estoque endógeno, e a resposta pressórica diminui a cada administração. A solução racional não é aumentar a dose, e sim mudar o mecanismo: agentes de &lt;strong&gt;ação direta&lt;/strong&gt; — fenilefrina, noradrenalina, vasopressina — independem das reservas neuronais e restauram a pressão de forma previsível. O mesmo raciocínio explica a resposta atenuada à efedrina em pacientes cronicamente tratados com reserpina ou com depleção catecolaminérgica por doença grave.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a regulação para cima de receptores aumentaria, e não reduziria, a resposta; além disso, dobrar sucessivamente a dose de efedrina expõe a taquicardia e hipertensão de rebote sem corrigir a causa (B). Efeito teto é conceito de agonistas parciais, como a buprenorfina, e não se aplica à efedrina (C). A efedrina sofre pouca metabolização hepática, sendo excretada em grande parte inalterada pela urina, e não induz o citocromo P450 de forma clinicamente relevante em minutos (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;taquifilaxia&lt;/strong&gt; é a perda rápida de eficácia após doses repetidas em curto intervalo, distinta da tolerância, que se instala ao longo de dias a semanas. Seu exemplo mais didático na anestesia é a &lt;em&gt;efedrina&lt;/em&gt;, um simpaticomimético de ação mista: parte de seu efeito vem da ativação direta dos receptores adrenérgicos, mas a parcela predominante depende do deslocamento de noradrenalina armazenada nas vesículas das terminações simpáticas pós-ganglionares.&lt;/p&gt;&lt;p&gt;Doses sucessivas esgotam progressivamente esse estoque endógeno, e a resposta pressórica diminui a cada administração. A solução racional não é aumentar a dose, e sim mudar o mecanismo: agentes de &lt;strong&gt;ação direta&lt;/strong&gt; (fenilefrina, noradrenalina, vasopressina) independem das reservas neuronais e restauram a pressão de forma previsível. O mesmo raciocínio explica a resposta atenuada à efedrina em pacientes cronicamente tratados com reserpina ou com depleção catecolaminérgica por doença grave.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a regulação para cima de receptores aumentaria, e não reduziria, a resposta; além disso, dobrar sucessivamente a dose de efedrina expõe a taquicardia e hipertensão de rebote sem corrigir a causa (B). Efeito teto é conceito de agonistas parciais, como a buprenorfina, e não se aplica à efedrina (C). A efedrina sofre pouca metabolização hepática, sendo excretada em grande parte inalterada pela urina, e não induz o citocromo P450 de forma clinicamente relevante em minutos (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;inibidores da monoaminoxidase&lt;/strong&gt; bloqueiam a degradação intraneuronal de noradrenalina, dopamina e serotonina, aumentando o conteúdo vesicular dessas aminas. Duas consequências dominam o manejo anestésico.&lt;/p&gt;&lt;p&gt;A primeira é a resposta exagerada a &lt;em&gt;simpaticomiméticos indiretos&lt;/em&gt;: efedrina e outros agentes que deslocam noradrenalina armazenada podem desencadear crise hipertensiva grave. A conduta correta na hipotensão é usar vasopressores de &lt;strong&gt;ação direta&lt;/strong&gt;, como fenilefrina ou noradrenalina, iniciando com frações da dose habitual e titulando, já que a sensibilidade também pode estar aumentada por regulação de receptores.&lt;/p&gt;&lt;p&gt;A segunda é a &lt;strong&gt;reação excitatória&lt;/strong&gt; com opioides de atividade serotoninérgica — meperidina em primeiro lugar, além de tramadol e dextrometorfano. Manifesta-se com agitação, hipertermia, rigidez, hipertensão e instabilidade autonômica, quadro compatível com síndrome serotoninérgica, potencialmente fatal. Morfina, fentanil e seus congêneres são considerados seguros em doses tituladas.&lt;/p&gt;&lt;p&gt;Considerações análogas valem para os antidepressivos tricíclicos (potencialização de simpaticomiméticos indiretos, efeitos anticolinérgicos) e para o lítio, que prolonga a duração dos bloqueadores neuromusculares e tem margem terapêutica estreita.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a efedrina em dose habitual é justamente o que se deve evitar, e o fentanil não tem relação particular com rigidez nesse contexto (A). A liberação de histamina pela morfina não é agravada pelos inibidores da MAO (B). A noradrenalina é apropriada, mas em dose reduzida e titulada, não plena (C).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;inibidores da monoaminoxidase&lt;/strong&gt; bloqueiam a degradação intraneuronal de noradrenalina, dopamina e serotonina, aumentando o conteúdo vesicular dessas aminas. Duas consequências dominam o manejo anestésico.&lt;/p&gt;&lt;p&gt;A primeira é a resposta exagerada a &lt;em&gt;simpaticomiméticos indiretos&lt;/em&gt;: efedrina e outros agentes que deslocam noradrenalina armazenada podem desencadear crise hipertensiva grave. A conduta correta na hipotensão é usar vasopressores de &lt;strong&gt;ação direta&lt;/strong&gt;, como fenilefrina ou noradrenalina, iniciando com frações da dose habitual e titulando, já que a sensibilidade também pode estar aumentada por regulação de receptores.&lt;/p&gt;&lt;p&gt;A segunda é a &lt;strong&gt;reação excitatória&lt;/strong&gt; com opioides de atividade serotoninérgica: meperidina em primeiro lugar, além de tramadol e dextrometorfano. Manifesta-se com agitação, hipertermia, rigidez, hipertensão e instabilidade autonômica, quadro compatível com síndrome serotoninérgica, potencialmente fatal. Morfina, fentanil e seus congêneres são considerados seguros em doses tituladas.&lt;/p&gt;&lt;p&gt;Considerações análogas valem para os antidepressivos tricíclicos (potencialização de simpaticomiméticos indiretos, efeitos anticolinérgicos) e para o lítio, que prolonga a duração dos bloqueadores neuromusculares e tem margem terapêutica estreita.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a efedrina em dose habitual é justamente o que se deve evitar, e o fentanil não tem relação particular com rigidez nesse contexto (A). A liberação de histamina pela morfina não é agravada pelos inibidores da MAO (B). A noradrenalina é apropriada, mas em dose reduzida e titulada, não plena (C).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Na &lt;strong&gt;porfiria aguda intermitente&lt;/strong&gt;, a deficiência parcial de uma enzima da via de síntese do heme faz com que qualquer estímulo à &lt;em&gt;ALA-sintetase&lt;/em&gt;, enzima limitante da via, provoque acúmulo de precursores neurotóxicos. As crises cursam com dor abdominal intensa, disautonomia, hiponatremia, neuropatia motora progressiva e alterações neuropsiquiátricas.&lt;/p&gt;&lt;p&gt;Os principais desencadeantes são jejum e restrição calórica, desidratação, infecção, estresse cirúrgico e fármacos indutores enzimáticos — que consomem heme hepático e desinibem a ALA-sintetase. Entre os anestésicos, os &lt;strong&gt;barbitúricos&lt;/strong&gt; são o exemplo histórico e o etomidato também é considerado desaconselhável. A cetamina é objeto de controvérsia e costuma ser evitada quando há alternativa.&lt;/p&gt;&lt;p&gt;São considerados seguros o &lt;strong&gt;propofol&lt;/strong&gt;, os opioides, os bloqueadores neuromusculares despolarizantes e adespolarizantes, o óxido nitroso e os halogenados. Além da escolha farmacológica, o suporte é decisivo: &lt;em&gt;aporte de carboidrato&lt;/em&gt;, hidratação, controle da dor e tratamento precoce de infecção. Nas crises instaladas, hematina e glicose em altas doses são o tratamento específico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o tiopental é o protótipo do fármaco proscrito na porfiria, e manter jejum prolongado é um gatilho adicional (A). O etomidato deve ser evitado, e a restrição hídrica agrava o quadro em vez de protegê-lo (C). Opioides e bloqueadores neuromusculares figuram entre os fármacos seguros e não precisam ser suprimidos (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Na &lt;strong&gt;porfiria aguda intermitente&lt;/strong&gt;, a deficiência parcial de uma enzima da via de síntese do heme faz com que qualquer estímulo à &lt;em&gt;ALA-sintetase&lt;/em&gt;, enzima limitante da via, provoque acúmulo de precursores neurotóxicos. As crises cursam com dor abdominal intensa, disautonomia, hiponatremia, neuropatia motora progressiva e alterações neuropsiquiátricas.&lt;/p&gt;&lt;p&gt;Os principais desencadeantes são jejum e restrição calórica, desidratação, infecção, estresse cirúrgico e fármacos indutores enzimáticos, que consomem heme hepático e desinibem a ALA-sintetase. Entre os anestésicos, os &lt;strong&gt;barbitúricos&lt;/strong&gt; são o exemplo histórico e o etomidato também é considerado desaconselhável. A cetamina é objeto de controvérsia e costuma ser evitada quando há alternativa.&lt;/p&gt;&lt;p&gt;São considerados seguros o &lt;strong&gt;propofol&lt;/strong&gt;, os opioides, os bloqueadores neuromusculares despolarizantes e adespolarizantes, o óxido nitroso e os halogenados. Além da escolha farmacológica, o suporte é decisivo: &lt;em&gt;aporte de carboidrato&lt;/em&gt;, hidratação, controle da dor e tratamento precoce de infecção. Nas crises instaladas, hematina e glicose em altas doses são o tratamento específico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o tiopental é o protótipo do fármaco proscrito na porfiria, e manter jejum prolongado é um gatilho adicional (A). O etomidato deve ser evitado, e a restrição hídrica agrava o quadro em vez de protegê-lo (C). Opioides e bloqueadores neuromusculares figuram entre os fármacos seguros e não precisam ser suprimidos (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A extensão da &lt;strong&gt;biotransformação&lt;/strong&gt; difere muito entre os halogenados: aproximadamente 20% do halotano absorvido é metabolizado, contra cerca de 2% a 5% do sevoflurano, 0,2% do isoflurano e menos de 0,05% do desflurano. O metabolismo oxidativo é conduzido principalmente pelo &lt;em&gt;CYP2E1&lt;/em&gt;, isoforma induzida por etanol e isoniazida.&lt;/p&gt;&lt;p&gt;A chamada &lt;strong&gt;hepatite pelo halotano&lt;/strong&gt;, forma grave e rara, é imunomediada. A oxidação do halotano gera um intermediário que &lt;em&gt;trifluoroacetila&lt;/em&gt; proteínas do hepatócito; esses adutos funcionam como neoantígenos e desencadeiam resposta imune em indivíduos sensibilizados, tipicamente após reexposição. Isoflurano e desflurano produzem os mesmos adutos trifluoroacetilados, ainda que em quantidades muito menores, o que sustenta a possibilidade teórica de reação cruzada.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;sevoflurano&lt;/strong&gt; segue outra rota: é degradado a hexafluoroisopropanol e flúor inorgânico, sem formação de metabólitos trifluoroacetilados. Por isso é o halogenado preferido em paciente com história de hepatotoxicidade prévia por halotano. Suas preocupações específicas são de outra natureza — composto A com absorvedores de CO&lt;sub&gt;2&lt;/sub&gt; e concentração de flúor inorgânico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o isoflurano metaboliza pouco, mas ainda assim gera adutos trifluoroacetilados, mantendo risco teórico de reação cruzada (A). O desflurano também forma esses adutos, e a solubilidade sanguínea não determina o risco imunológico (B). O óxido nitroso sofre metabolização por bactérias intestinais e, sobretudo, não é capaz de prover anestesia geral isoladamente (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A extensão da &lt;strong&gt;biotransformação&lt;/strong&gt; difere muito entre os halogenados: aproximadamente 20% do halotano absorvido é metabolizado, contra cerca de 2% a 5% do sevoflurano, 0,2% do isoflurano e menos de 0,05% do desflurano. O metabolismo oxidativo é conduzido principalmente pelo &lt;em&gt;CYP2E1&lt;/em&gt;, isoforma induzida por etanol e isoniazida.&lt;/p&gt;&lt;p&gt;A chamada &lt;strong&gt;hepatite pelo halotano&lt;/strong&gt;, forma grave e rara, é imunomediada. A oxidação do halotano gera um intermediário que &lt;em&gt;trifluoroacetila&lt;/em&gt; proteínas do hepatócito; esses adutos funcionam como neoantígenos e desencadeiam resposta imune em indivíduos sensibilizados, tipicamente após reexposição. Isoflurano e desflurano produzem os mesmos adutos trifluoroacetilados, ainda que em quantidades muito menores, o que sustenta a possibilidade teórica de reação cruzada.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;sevoflurano&lt;/strong&gt; segue outra rota: é degradado a hexafluoroisopropanol e flúor inorgânico, sem formação de metabólitos trifluoroacetilados. Por isso é o halogenado preferido em paciente com história de hepatotoxicidade prévia por halotano. Suas preocupações específicas são de outra natureza: composto A com absorvedores de CO&lt;sub&gt;2&lt;/sub&gt; e concentração de flúor inorgânico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o isoflurano metaboliza pouco, mas ainda assim gera adutos trifluoroacetilados, mantendo risco teórico de reação cruzada (A). O desflurano também forma esses adutos, e a solubilidade sanguínea não determina o risco imunológico (B). O óxido nitroso sofre metabolização por bactérias intestinais e, sobretudo, não é capaz de prover anestesia geral isoladamente (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A velocidade de indução inalatória é descrita pela razão entre a &lt;strong&gt;fração alveolar e a fração inspirada&lt;/strong&gt; do agente. Essa razão sobe quando a entrega ao alvéolo supera a remoção pelo sangue. A captação pelo sangue capilar pulmonar é proporcional ao produto de três fatores: &lt;em&gt;solubilidade sanguínea, débito cardíaco e gradiente de pressão parcial alvéolo-venosa&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;Quando o débito cardíaco cai, menos sangue passa pelo capilar pulmonar por unidade de tempo e menos agente é removido do alvéolo. A pressão parcial alveolar sobe mais depressa, e como ela determina a pressão parcial cerebral, o paciente aprofunda rapidamente. O efeito é particularmente perigoso no choque, em que a mesma queda de débito que acelera a curva também reduz a reserva hemodinâmica para tolerar a depressão miocárdica e a vasodilatação do halogenado. A conduta prática é reduzir a concentração inspirada e titular com cautela.&lt;/p&gt;&lt;p&gt;O raciocínio inverso explica por que débito cardíaco elevado — sepse hiperdinâmica, hipertireoidismo, ansiedade — retarda a indução inalatória. Outros determinantes da curva são a ventilação alveolar, o fluxo de gases frescos, o volume do circuito e a solubilidade do agente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o baixo débito reduz, e não aumenta, a captação pulmonar, e a solubilidade é uma propriedade físico-química do agente, não modificável pela hemodinâmica (B). A frequência cardíaca não altera a ventilação alveolar nem o coeficiente de partição (C). A hipovolemia não amplia o grupo de tecidos ricamente vascularizados, e o efeito descrito é o oposto do observado (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A velocidade de indução inalatória é descrita pela razão entre a &lt;strong&gt;fração alveolar e a fração inspirada&lt;/strong&gt; do agente. Essa razão sobe quando a entrega ao alvéolo supera a remoção pelo sangue. A captação pelo sangue capilar pulmonar é proporcional ao produto de três fatores: &lt;em&gt;solubilidade sanguínea, débito cardíaco e gradiente de pressão parcial alvéolo-venosa&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;Quando o débito cardíaco cai, menos sangue passa pelo capilar pulmonar por unidade de tempo e menos agente é removido do alvéolo. A pressão parcial alveolar sobe mais depressa, e como ela determina a pressão parcial cerebral, o paciente aprofunda rapidamente. O efeito é particularmente perigoso no choque, em que a mesma queda de débito que acelera a curva também reduz a reserva hemodinâmica para tolerar a depressão miocárdica e a vasodilatação do halogenado. A conduta prática é reduzir a concentração inspirada e titular com cautela.&lt;/p&gt;&lt;p&gt;O raciocínio inverso explica por que débito cardíaco elevado (sepse hiperdinâmica, hipertireoidismo, ansiedade) retarda a indução inalatória. Outros determinantes da curva são a ventilação alveolar, o fluxo de gases frescos, o volume do circuito e a solubilidade do agente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o baixo débito reduz, e não aumenta, a captação pulmonar, e a solubilidade é uma propriedade físico-química do agente, não modificável pela hemodinâmica (B). A frequência cardíaca não altera a ventilação alveolar nem o coeficiente de partição (C). A hipovolemia não amplia o grupo de tecidos ricamente vascularizados, e o efeito descrito é o oposto do observado (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Após um &lt;strong&gt;bolus único&lt;/strong&gt; de hipnótico lipossolúvel, o encéfalo — órgão do grupo ricamente vascularizado — equilibra-se com o plasma em poucas dezenas de segundos, o que explica a perda de consciência em um tempo de circulação braço-cérebro. Em seguida, o fármaco se desloca do plasma e do cérebro para compartimentos de menor perfusão porém grande capacidade, sobretudo músculo esquelético e, mais tarde, gordura.&lt;/p&gt;&lt;p&gt;É essa &lt;strong&gt;redistribuição&lt;/strong&gt;, e não a eliminação, que encerra o efeito de um bolus isolado. O fenômeno é comum ao propofol, ao tiopental e ao etomidato, e é a razão pela qual doses repetidas saturam progressivamente os compartimentos periféricos e prolongam o despertar. O propofol se distingue por um clearance muito elevado, que excede o fluxo sanguíneo hepático e implica metabolismo extra-hepático, e por uma meia-vida contexto-dependente favorável, o que o torna adequado à infusão contínua.&lt;/p&gt;&lt;p&gt;Entre seus efeitos sistêmicos destacam-se a queda da resistência vascular sistêmica, a depressão miocárdica direta e a atenuação do barorreflexo, além de propriedade antiemética em doses subipnóticas e dor à injeção. O &lt;em&gt;fospropofol&lt;/em&gt; é um pró-fármaco hidrossolúvel hidrolisado por fosfatases alcalinas, com início de ação mais lento e parestesia perineal característica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; quem sofre hidrólise por esterases plasmáticas é o remifentanil, não o propofol (A). Mesmo com clearance alto, a metabolização não é rápida o bastante para explicar o despertar em minutos após bolus único (B). Não há dessensibilização aguda relevante do receptor GABA-A ao propofol nesse intervalo (C).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Após um &lt;strong&gt;bolus único&lt;/strong&gt; de hipnótico lipossolúvel, o encéfalo, órgão do grupo ricamente vascularizado, equilibra-se com o plasma em poucas dezenas de segundos, o que explica a perda de consciência em um tempo de circulação braço-cérebro. Em seguida, o fármaco se desloca do plasma e do cérebro para compartimentos de menor perfusão porém grande capacidade, sobretudo músculo esquelético e, mais tarde, gordura.&lt;/p&gt;&lt;p&gt;É essa &lt;strong&gt;redistribuição&lt;/strong&gt;, e não a eliminação, que encerra o efeito de um bolus isolado. O fenômeno é comum ao propofol, ao tiopental e ao etomidato, e é a razão pela qual doses repetidas saturam progressivamente os compartimentos periféricos e prolongam o despertar. O propofol se distingue por um clearance muito elevado, que excede o fluxo sanguíneo hepático e implica metabolismo extra-hepático, e por uma meia-vida contexto-dependente favorável, o que o torna adequado à infusão contínua.&lt;/p&gt;&lt;p&gt;Entre seus efeitos sistêmicos destacam-se a queda da resistência vascular sistêmica, a depressão miocárdica direta e a atenuação do barorreflexo, além de propriedade antiemética em doses subipnóticas e dor à injeção. O &lt;em&gt;fospropofol&lt;/em&gt; é um pró-fármaco hidrossolúvel hidrolisado por fosfatases alcalinas, com início de ação mais lento e parestesia perineal característica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; quem sofre hidrólise por esterases plasmáticas é o remifentanil, não o propofol (A). Mesmo com clearance alto, a metabolização não é rápida o bastante para explicar o despertar em minutos após bolus único (B). Não há dessensibilização aguda relevante do receptor GABA-A ao propofol nesse intervalo (C).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;naloxona&lt;/strong&gt; é um antagonista competitivo puro dos receptores opioides, sem qualquer atividade agonista intrínseca. Administrada por via venosa, tem início de ação em um a dois minutos, mas duração clínica de apenas cerca de 30 a 60 minutos, com meia-vida em torno de uma hora. Quando o opioide antagonizado tem duração maior — como morfina, metadona ou buprenorfina, ou ainda formulações de liberação prolongada —, o desaparecimento do antagonista permite a &lt;em&gt;renarcotização&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;Por isso, todo paciente que recebeu naloxona deve permanecer sob vigilância respiratória por várias horas. Doses fracionadas de 0,04 a 0,1 mg permitem reverter a depressão respiratória preservando parte da analgesia; a reversão abrupta com doses altas provoca dor intensa, hipertensão, taquicardia, arritmias e edema pulmonar. Quando a renarcotização se repete, a &lt;strong&gt;infusão contínua&lt;/strong&gt; titulada é a solução racional. Vale lembrar que a morfina gera morfina-6-glicuronídeo, metabólito ativo que se acumula na disfunção renal e prolonga o risco.&lt;/p&gt;&lt;p&gt;Entre os demais antagonistas, a naltrexona é oral e de ação prolongada, adequada a programas de manutenção, não à emergência. A &lt;em&gt;nalbufina&lt;/em&gt; é agonista kappa e antagonista mu, com efeito teto sobre a depressão respiratória; a &lt;em&gt;buprenorfina&lt;/em&gt; é agonista parcial de alta afinidade, difícil de antagonizar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; não há tolerância aguda à naloxona, e a naltrexona oral é inadequada em paciente sonolento (A). A naloxona é antagonista puro, e a nalbufina não é o fármaco de resgate nessa situação (C). A naloxona não produz metabólitos com atividade agonista, e apenas observar seria negligente (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;naloxona&lt;/strong&gt; é um antagonista competitivo puro dos receptores opioides, sem qualquer atividade agonista intrínseca. Administrada por via venosa, tem início de ação em um a dois minutos, mas duração clínica de apenas cerca de 30 a 60 minutos, com meia-vida em torno de uma hora. Quando o opioide antagonizado tem duração maior (como morfina, metadona ou buprenorfina, ou ainda formulações de liberação prolongada), o desaparecimento do antagonista permite a &lt;em&gt;renarcotização&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;Por isso, todo paciente que recebeu naloxona deve permanecer sob vigilância respiratória por várias horas. Doses fracionadas de 0,04 a 0,1 mg permitem reverter a depressão respiratória preservando parte da analgesia; a reversão abrupta com doses altas provoca dor intensa, hipertensão, taquicardia, arritmias e edema pulmonar. Quando a renarcotização se repete, a &lt;strong&gt;infusão contínua&lt;/strong&gt; titulada é a solução racional. Vale lembrar que a morfina gera morfina-6-glicuronídeo, metabólito ativo que se acumula na disfunção renal e prolonga o risco.&lt;/p&gt;&lt;p&gt;Entre os demais antagonistas, a naltrexona é oral e de ação prolongada, adequada a programas de manutenção, não à emergência. A &lt;em&gt;nalbufina&lt;/em&gt; é agonista kappa e antagonista mu, com efeito teto sobre a depressão respiratória; a &lt;em&gt;buprenorfina&lt;/em&gt; é agonista parcial de alta afinidade, difícil de antagonizar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; não há tolerância aguda à naloxona, e a naltrexona oral é inadequada em paciente sonolento (A). A naloxona é antagonista puro, e a nalbufina não é o fármaco de resgate nessa situação (C). A naloxona não produz metabólitos com atividade agonista, e apenas observar seria negligente (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;tiopental&lt;/strong&gt; é preparado como sal sódico em solução fortemente alcalina, com pH em torno de 10 a 11. Ao entrar em contato com o pH sanguíneo, precipita sob a forma de cristais que ocluem a microcirculação distal; soma-se a isso intenso vasoespasmo arterial reflexo e liberação local de mediadores, com risco real de trombose, necrose e perda de segmentos do membro.&lt;/p&gt;&lt;p&gt;O tratamento visa a três objetivos: &lt;em&gt;diluir&lt;/em&gt; o fármaco, &lt;em&gt;quebrar o vasoespasmo&lt;/em&gt; e &lt;em&gt;prevenir a trombose&lt;/em&gt;. Por isso o cateter deve ser &lt;strong&gt;mantido no lugar&lt;/strong&gt; — ele é a via de acesso arterial já disponível — para injeção de solução salina, lidocaína ou papaverina. O bloqueio simpático do membro, por bloqueio de plexo braquial ou de gânglio estrelado, promove vasodilatação sustentada. A anticoagulação com heparina reduz o risco trombótico, e a analgesia costuma exigir opioide. Corticosteroides são adjuvantes de valor discutível.&lt;/p&gt;&lt;p&gt;Vale contrastar com o &lt;em&gt;etomidato&lt;/em&gt;, o outro hipnótico desta família: causa dor à injeção e mioclonias, apresenta alta incidência de náuseas e vômitos e, mesmo em dose única, inibe a 11-beta-hidroxilase com supressão adrenal que pode durar cerca de 24 horas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; retirar o cateter descarta a via de tratamento, e o frio agrava o vasoespasmo (A). O tiopental já é alcalino; administrar bicarbonato não neutraliza nada e pode piorar a lesão (B). A hidratação sistêmica por outro acesso não alcança o leito arterial comprometido e não trata o vasoespasmo (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;tiopental&lt;/strong&gt; é preparado como sal sódico em solução fortemente alcalina, com pH em torno de 10 a 11. Ao entrar em contato com o pH sanguíneo, precipita sob a forma de cristais que ocluem a microcirculação distal; soma-se a isso intenso vasoespasmo arterial reflexo e liberação local de mediadores, com risco real de trombose, necrose e perda de segmentos do membro.&lt;/p&gt;&lt;p&gt;O tratamento visa a três objetivos: &lt;em&gt;diluir&lt;/em&gt; o fármaco, &lt;em&gt;quebrar o vasoespasmo&lt;/em&gt; e &lt;em&gt;prevenir a trombose&lt;/em&gt;. Por isso o cateter deve ser &lt;strong&gt;mantido no lugar&lt;/strong&gt; (ele é a via de acesso arterial já disponível) para injeção de solução salina, lidocaína ou papaverina. O bloqueio simpático do membro, por bloqueio de plexo braquial ou de gânglio estrelado, promove vasodilatação sustentada. A anticoagulação com heparina reduz o risco trombótico, e a analgesia costuma exigir opioide. Corticosteroides são adjuvantes de valor discutível.&lt;/p&gt;&lt;p&gt;Vale contrastar com o &lt;em&gt;etomidato&lt;/em&gt;, o outro hipnótico desta família: causa dor à injeção e mioclonias, apresenta alta incidência de náuseas e vômitos e, mesmo em dose única, inibe a 11-beta-hidroxilase com supressão adrenal que pode durar cerca de 24 horas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; retirar o cateter descarta a via de tratamento, e o frio agrava o vasoespasmo (A). O tiopental já é alcalino; administrar bicarbonato não neutraliza nada e pode piorar a lesão (B). A hidratação sistêmica por outro acesso não alcança o leito arterial comprometido e não trata o vasoespasmo (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;cetamina&lt;/strong&gt; é antagonista não competitivo do receptor NMDA e produz o característico &lt;em&gt;estado dissociativo&lt;/em&gt;, com analgesia intensa, amnésia e dissociação funcional entre os sistemas talamocortical e límbico. O paciente pode permanecer de olhos abertos, com nistagmo e reflexos parcialmente preservados, ainda que sem responsividade.&lt;/p&gt;&lt;p&gt;Seu perfil hemodinâmico habitual — elevação de frequência cardíaca, pressão arterial e débito — não é um efeito direto, e sim &lt;strong&gt;simpaticomimético indireto&lt;/strong&gt;: resulta da estimulação central do fluxo simpático e da inibição da recaptação neuronal de catecolaminas. Isoladamente, sobre o músculo cardíaco, a cetamina é &lt;em&gt;depressora&lt;/em&gt;. Quando o paciente já esgotou suas reservas simpáticas — choque prolongado, sepse avançada, catecolaminas exógenas em dose alta, desnutrição grave —, o componente indireto não se manifesta e resta a depressão miocárdica direta, com hipotensão que pode ser abrupta. Nesses casos, doses reduzidas e vasopressor prontamente disponível são obrigatórios.&lt;/p&gt;&lt;p&gt;Outros pontos práticos: aumento de secreções, broncodilatação, preservação relativa do drive ventilatório e &lt;em&gt;delirium&lt;/em&gt; de emergência, cuja incidência diminui com benzodiazepínico associado e ambiente tranquilo no despertar. A dose venosa de indução situa-se em torno de 1 a 2 mg/kg e a intramuscular, entre 4 e 6 mg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a cetamina não bloqueia receptores alfa-1 (B). Ela inibe a recaptação de noradrenalina, o que &lt;em&gt;potencializa&lt;/em&gt; e não esgota o efeito do vasopressor infundido (C). Liberação relevante de histamina é característica de morfina e de alguns bloqueadores neuromusculares, não da cetamina (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;cetamina&lt;/strong&gt; é antagonista não competitivo do receptor NMDA e produz o característico &lt;em&gt;estado dissociativo&lt;/em&gt;, com analgesia intensa, amnésia e dissociação funcional entre os sistemas talamocortical e límbico. O paciente pode permanecer de olhos abertos, com nistagmo e reflexos parcialmente preservados, ainda que sem responsividade.&lt;/p&gt;&lt;p&gt;Seu perfil hemodinâmico habitual (elevação de frequência cardíaca, pressão arterial e débito) não é um efeito direto, e sim &lt;strong&gt;simpaticomimético indireto&lt;/strong&gt;: resulta da estimulação central do fluxo simpático e da inibição da recaptação neuronal de catecolaminas. Isoladamente, sobre o músculo cardíaco, a cetamina é &lt;em&gt;depressora&lt;/em&gt;. Quando o paciente já esgotou suas reservas simpáticas (choque prolongado, sepse avançada, catecolaminas exógenas em dose alta, desnutrição grave), o componente indireto não se manifesta e resta a depressão miocárdica direta, com hipotensão que pode ser abrupta. Nesses casos, doses reduzidas e vasopressor prontamente disponível são obrigatórios.&lt;/p&gt;&lt;p&gt;Outros pontos práticos: aumento de secreções, broncodilatação, preservação relativa do drive ventilatório e &lt;em&gt;delirium&lt;/em&gt; de emergência, cuja incidência diminui com benzodiazepínico associado e ambiente tranquilo no despertar. A dose venosa de indução situa-se em torno de 1 a 2 mg/kg e a intramuscular, entre 4 e 6 mg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a cetamina não bloqueia receptores alfa-1 (B). Ela inibe a recaptação de noradrenalina, o que &lt;em&gt;potencializa&lt;/em&gt; e não esgota o efeito do vasopressor infundido (C). Liberação relevante de histamina é característica de morfina e de alguns bloqueadores neuromusculares, não da cetamina (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;benzodiazepínicos&lt;/strong&gt; ligam-se a um sítio modulador situado na interface das subunidades alfa e gama do receptor GABA-A e atuam como moduladores alostéricos positivos: não abrem o canal por si, mas aumentam a &lt;em&gt;frequência&lt;/em&gt; de abertura do canal de cloreto na presença do GABA. Os &lt;strong&gt;barbitúricos&lt;/strong&gt; ligam-se a sítio distinto e prolongam a &lt;em&gt;duração&lt;/em&gt; da abertura, além de, em concentrações altas, ativarem o canal diretamente — o que explica sua menor margem de segurança.&lt;/p&gt;&lt;p&gt;Os veículos também diferem. O diazepam é insolúvel em água e é formulado em &lt;em&gt;propilenoglicol&lt;/em&gt;, responsável pela dor à injeção e pela tromboflebite. O midazolam possui um anel imidazólico cuja ionização depende do pH: é hidrossolúvel na ampola, em pH ácido, e torna-se lipofílico no pH do plasma, o que lhe confere rápida penetração no sistema nervoso central sem irritação venosa.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;flumazenil&lt;/strong&gt; é antagonista competitivo no mesmo sítio, titulado em incrementos de cerca de 0,2 mg. Sua duração é curta, com meia-vida ao redor de uma hora, inferior à do midazolam e muito inferior à do diazepam, de modo que a &lt;em&gt;ressedação&lt;/em&gt; é risco real. Deve ser evitado em usuários crônicos de benzodiazepínicos e na intoxicação por antidepressivos tricíclicos, pelo risco de convulsão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a alternativa A inverte os mecanismos das duas classes (A). A alternativa B troca os veículos e as propriedades dos dois fármacos (B). A alternativa C atribui ao flumazenil uma duração longa que ele não tem (C).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;benzodiazepínicos&lt;/strong&gt; ligam-se a um sítio modulador situado na interface das subunidades alfa e gama do receptor GABA-A e atuam como moduladores alostéricos positivos: não abrem o canal por si, mas aumentam a &lt;em&gt;frequência&lt;/em&gt; de abertura do canal de cloreto na presença do GABA. Os &lt;strong&gt;barbitúricos&lt;/strong&gt; ligam-se a sítio distinto e prolongam a &lt;em&gt;duração&lt;/em&gt; da abertura, além de, em concentrações altas, ativarem o canal diretamente, o que explica sua menor margem de segurança.&lt;/p&gt;&lt;p&gt;Os veículos também diferem. O diazepam é insolúvel em água e é formulado em &lt;em&gt;propilenoglicol&lt;/em&gt;, responsável pela dor à injeção e pela tromboflebite. O midazolam possui um anel imidazólico cuja ionização depende do pH: é hidrossolúvel na ampola, em pH ácido, e torna-se lipofílico no pH do plasma, o que lhe confere rápida penetração no sistema nervoso central sem irritação venosa.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;flumazenil&lt;/strong&gt; é antagonista competitivo no mesmo sítio, titulado em incrementos de cerca de 0,2 mg. Sua duração é curta, com meia-vida ao redor de uma hora, inferior à do midazolam e muito inferior à do diazepam, de modo que a &lt;em&gt;ressedação&lt;/em&gt; é risco real. Deve ser evitado em usuários crônicos de benzodiazepínicos e na intoxicação por antidepressivos tricíclicos, pelo risco de convulsão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a alternativa A inverte os mecanismos das duas classes (A). A alternativa B troca os veículos e as propriedades dos dois fármacos (B). A alternativa C atribui ao flumazenil uma duração longa que ele não tem (C).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;benzodiazepínicos&lt;/strong&gt; diferem muito quanto à presença de metabólitos ativos, e essa diferença domina o comportamento clínico em infusões prolongadas.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;midazolam&lt;/strong&gt; é oxidado pelo CYP3A4 a &lt;em&gt;alfa-hidroximidazolam&lt;/em&gt;, metabólito com atividade sedativa próxima à do composto original, posteriormente conjugado a alfa-hidroximidazolam-glicuronídeo — que, ao contrário do que a intuição sugere, também é farmacologicamente ativo. Ambos dependem de excreção renal. Na lesão renal, acumulam-se e produzem sedação prolongada por muitas horas ou dias após a suspensão, quadro típico do idoso em terapia intensiva, no qual se somam ainda o aumento do volume de distribuição pela lipofilia e a meia-vida contexto-dependente crescente da infusão.&lt;/p&gt;&lt;p&gt;Para comparação: o &lt;strong&gt;diazepam&lt;/strong&gt; gera desmetildiazepam, oxazepam e temazepam, sendo o primeiro de meia-vida muito longa, o que explica sedação residual por dias. O &lt;strong&gt;lorazepam&lt;/strong&gt; sofre apenas glicuronidação direta, não tem metabólitos ativos e é preferível na hepatopatia e no idoso, embora seu veículo com propilenoglicol imponha limites na infusão prolongada. Todos produzem amnésia &lt;em&gt;anterógrada&lt;/em&gt;, e não retrógrada: o paciente deixa de formar novas memórias, mas preserva as anteriores à administração.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; maior ligação proteica reduziria a fração livre e o efeito, não o prolongaria (A). Desmetildiazepam é metabólito do diazepam, não do midazolam (C). Os benzodiazepínicos são metabolizados pelo fígado, e não por esterases plasmáticas, via característica de remifentanil e succinilcolina (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;benzodiazepínicos&lt;/strong&gt; diferem muito quanto à presença de metabólitos ativos, e essa diferença domina o comportamento clínico em infusões prolongadas.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;midazolam&lt;/strong&gt; é oxidado pelo CYP3A4 a &lt;em&gt;alfa-hidroximidazolam&lt;/em&gt;, metabólito com atividade sedativa próxima à do composto original, posteriormente conjugado a alfa-hidroximidazolam-glicuronídeo, que, ao contrário do que a intuição sugere, também é farmacologicamente ativo. Ambos dependem de excreção renal. Na lesão renal, acumulam-se e produzem sedação prolongada por muitas horas ou dias após a suspensão, quadro típico do idoso em terapia intensiva, no qual se somam ainda o aumento do volume de distribuição pela lipofilia e a meia-vida contexto-dependente crescente da infusão.&lt;/p&gt;&lt;p&gt;Para comparação: o &lt;strong&gt;diazepam&lt;/strong&gt; gera desmetildiazepam, oxazepam e temazepam, sendo o primeiro de meia-vida muito longa, o que explica sedação residual por dias. O &lt;strong&gt;lorazepam&lt;/strong&gt; sofre apenas glicuronidação direta, não tem metabólitos ativos e é preferível na hepatopatia e no idoso, embora seu veículo com propilenoglicol imponha limites na infusão prolongada. Todos produzem amnésia &lt;em&gt;anterógrada&lt;/em&gt;, e não retrógrada: o paciente deixa de formar novas memórias, mas preserva as anteriores à administração.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; maior ligação proteica reduziria a fração livre e o efeito, não o prolongaria (A). Desmetildiazepam é metabólito do diazepam, não do midazolam (C). Os benzodiazepínicos são metabolizados pelo fígado, e não por esterases plasmáticas, via característica de remifentanil e succinilcolina (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;constante de tempo&lt;/strong&gt; de um sistema com mistura contínua é a razão entre o volume do sistema e o fluxo que o atravessa. No circuito anestésico, corresponde ao volume total do sistema dividido pelo fluxo de gases frescos, descontada a captação pelo paciente. Com 6 litros de volume e 1 L/min de fluxo, ela vale aproximadamente &lt;em&gt;6 minutos&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;A resposta de um sistema desse tipo é exponencial: após uma constante de tempo, cerca de &lt;strong&gt;63%&lt;/strong&gt; da mudança já ocorreu; após duas, cerca de 86%; após três, aproximadamente 95%. Em outras palavras, no exemplo seriam necessários quase 18 minutos para que a concentração no circuito se aproximasse do novo valor ajustado no vaporizador — intervalo incompatível com qualquer necessidade de correção rápida.&lt;/p&gt;&lt;p&gt;A consequência prática é fundamental na anestesia de baixo fluxo: sempre que se deseja &lt;em&gt;mudar depressa&lt;/em&gt; a concentração, para mais ou para menos, aumenta-se transitoriamente o fluxo de gases frescos, o que encurta a constante de tempo. Com fluxos altos, a concentração inspirada aproxima-se da fornecida pelo vaporizador; com fluxos baixos, o circuito torna-se um reservatório inercial e a captação do paciente passa a influenciar de modo significativo a concentração resultante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o coeficiente de partição sangue/gás influencia a captação pelo paciente, mas a constante de tempo do circuito é determinada por volume e fluxo (B). O cálculo em segundos está errado por três ordens de grandeza, e a liberação tecidual é fator contributivo, não exclusivo (C). Uma constante de tempo corresponde a cerca de 63%, e não a 95%, da mudança total (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;constante de tempo&lt;/strong&gt; de um sistema com mistura contínua é a razão entre o volume do sistema e o fluxo que o atravessa. No circuito anestésico, corresponde ao volume total do sistema dividido pelo fluxo de gases frescos, descontada a captação pelo paciente. Com 6 litros de volume e 1 L/min de fluxo, ela vale aproximadamente &lt;em&gt;6 minutos&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;A resposta de um sistema desse tipo é exponencial: após uma constante de tempo, cerca de &lt;strong&gt;63%&lt;/strong&gt; da mudança já ocorreu; após duas, cerca de 86%; após três, aproximadamente 95%. Em outras palavras, no exemplo seriam necessários quase 18 minutos para que a concentração no circuito se aproximasse do novo valor ajustado no vaporizador, intervalo incompatível com qualquer necessidade de correção rápida.&lt;/p&gt;&lt;p&gt;A consequência prática é fundamental na anestesia de baixo fluxo: sempre que se deseja &lt;em&gt;mudar depressa&lt;/em&gt; a concentração, para mais ou para menos, aumenta-se transitoriamente o fluxo de gases frescos, o que encurta a constante de tempo. Com fluxos altos, a concentração inspirada aproxima-se da fornecida pelo vaporizador; com fluxos baixos, o circuito torna-se um reservatório inercial e a captação do paciente passa a influenciar de modo significativo a concentração resultante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o coeficiente de partição sangue/gás influencia a captação pelo paciente, mas a constante de tempo do circuito é determinada por volume e fluxo (B). O cálculo em segundos está errado por três ordens de grandeza, e a liberação tecidual é fator contributivo, não exclusivo (C). Uma constante de tempo corresponde a cerca de 63%, e não a 95%, da mudança total (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;sistema de exaustão de gases&lt;/strong&gt; recolhe o excesso de gases da válvula de escape do circuito e da válvula de alívio do ventilador e os conduz para fora da sala. É composto por dispositivo coletor, tubo de transferência, &lt;em&gt;interface&lt;/em&gt;, tubo de descarte e sistema de eliminação, ativo ou passivo.&lt;/p&gt;&lt;p&gt;A interface é o componente de segurança. Nas &lt;strong&gt;interfaces abertas&lt;/strong&gt;, o reservatório é permanentemente comunicado com a atmosfera por orifícios e não possui válvulas; por isso não podem gerar pressão positiva nem negativa, mas exigem obrigatoriamente sistema de eliminação ativo. Nas &lt;strong&gt;interfaces fechadas&lt;/strong&gt;, o reservatório é um balão fechado e a segurança depende de válvulas: uma de &lt;em&gt;alívio de pressão positiva&lt;/em&gt;, que abre para a sala quando o descarte obstrui, e, nos sistemas ativos, uma de &lt;em&gt;alívio de pressão negativa&lt;/em&gt;, que admite ar ambiente quando o vácuo é excessivo.&lt;/p&gt;&lt;p&gt;O quadro descrito — reservatório distendido e pressão de vias aéreas crescente sem causa pulmonar — é o cenário clássico de obstrução do tubo de descarte com falha da válvula de alívio positiva. A pressão retorna ao circuito e ao paciente, com risco de barotrauma e de comprometimento hemodinâmico. A conduta imediata é desconectar o sistema de exaustão do circuito, ventilando o paciente com o ambiente enquanto se corrige a obstrução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; interfaces abertas comunicam-se com a atmosfera e não acumulam pressão (A). Vácuo excessivo colaba o reservatório em vez de distendê-lo (B). Interfaces fechadas dependem justamente de válvulas de alívio para serem seguras (C).&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;sistema de exaustão de gases&lt;/strong&gt; recolhe o excesso de gases da válvula de escape do circuito e da válvula de alívio do ventilador e os conduz para fora da sala. É composto por dispositivo coletor, tubo de transferência, &lt;em&gt;interface&lt;/em&gt;, tubo de descarte e sistema de eliminação, ativo ou passivo.&lt;/p&gt;&lt;p&gt;A interface é o componente de segurança. Nas &lt;strong&gt;interfaces abertas&lt;/strong&gt;, o reservatório é permanentemente comunicado com a atmosfera por orifícios e não possui válvulas; por isso não podem gerar pressão positiva nem negativa, mas exigem obrigatoriamente sistema de eliminação ativo. Nas &lt;strong&gt;interfaces fechadas&lt;/strong&gt;, o reservatório é um balão fechado e a segurança depende de válvulas: uma de &lt;em&gt;alívio de pressão positiva&lt;/em&gt;, que abre para a sala quando o descarte obstrui, e, nos sistemas ativos, uma de &lt;em&gt;alívio de pressão negativa&lt;/em&gt;, que admite ar ambiente quando o vácuo é excessivo.&lt;/p&gt;&lt;p&gt;O quadro descrito (reservatório distendido e pressão de vias aéreas crescente sem causa pulmonar) é o cenário clássico de obstrução do tubo de descarte com falha da válvula de alívio positiva. A pressão retorna ao circuito e ao paciente, com risco de barotrauma e de comprometimento hemodinâmico. A conduta imediata é desconectar o sistema de exaustão do circuito, ventilando o paciente com o ambiente enquanto se corrige a obstrução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; interfaces abertas comunicam-se com a atmosfera e não acumulam pressão (A). Vácuo excessivo colaba o reservatório em vez de distendê-lo (B). Interfaces fechadas dependem justamente de válvulas de alívio para serem seguras (C).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A formação de &lt;strong&gt;monóxido de carbono&lt;/strong&gt; no absorvedor depende de duas condições simultâneas: um absorvedor &lt;em&gt;ressecado&lt;/em&gt; e um halogenado que contenha o grupamento difluorometil. O ressecamento resulta tipicamente da passagem prolongada de gás seco em alto fluxo por um aparelho deixado ligado durante a noite ou o fim de semana, cenário que dá ao problema seu nome informal de acidente de segunda-feira.&lt;/p&gt;&lt;p&gt;A produção segue uma hierarquia relativamente constante: &lt;strong&gt;desflurano&lt;/strong&gt; e enflurano encabeçam a lista, seguidos pelo isoflurano, enquanto sevoflurano e halotano produzem quantidades desprezíveis. As bases fortes — hidróxido de potássio e hidróxido de sódio — catalisam a reação, razão pela qual absorvedores à base de &lt;em&gt;hidróxido de cálcio&lt;/em&gt; sem essas bases praticamente não geram monóxido de carbono nem composto A.&lt;/p&gt;&lt;p&gt;O sevoflurano tem risco distinto: com absorvedor ressecado, produz reação intensamente exotérmica capaz de gerar calor extremo, degradação do agente e até incêndio no canister; com absorvedor normalmente hidratado, forma o &lt;em&gt;composto A&lt;/em&gt;, de nefrotoxicidade demonstrada em animais.&lt;/p&gt;&lt;p&gt;A prevenção é organizacional: desligar os fluxômetros ao fim do dia, trocar o absorvedor após períodos de fluxo alto sem uso e desconfiar de qualquer canister cuja mudança de cor esteja ausente após uso prolongado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o sevoflurano é dos que menos produzem monóxido de carbono, e o composto A não depende de umidificação excessiva (A). É o ressecamento, e não a umidade, que desencadeia o problema (B). Os absorvedores sem bases fortes produzem menos, e não mais, monóxido de carbono (D).&lt;/p&gt;</t>
+          <t>&lt;p&gt;A formação de &lt;strong&gt;monóxido de carbono&lt;/strong&gt; no absorvedor depende de duas condições simultâneas: um absorvedor &lt;em&gt;ressecado&lt;/em&gt; e um halogenado que contenha o grupamento difluorometil. O ressecamento resulta tipicamente da passagem prolongada de gás seco em alto fluxo por um aparelho deixado ligado durante a noite ou o fim de semana, cenário que dá ao problema seu nome informal de acidente de segunda-feira.&lt;/p&gt;&lt;p&gt;A produção segue uma hierarquia relativamente constante: &lt;strong&gt;desflurano&lt;/strong&gt; e enflurano encabeçam a lista, seguidos pelo isoflurano, enquanto sevoflurano e halotano produzem quantidades desprezíveis. As bases fortes (hidróxido de potássio e hidróxido de sódio) catalisam a reação, razão pela qual absorvedores à base de &lt;em&gt;hidróxido de cálcio&lt;/em&gt; sem essas bases praticamente não geram monóxido de carbono nem composto A.&lt;/p&gt;&lt;p&gt;O sevoflurano tem risco distinto: com absorvedor ressecado, produz reação intensamente exotérmica capaz de gerar calor extremo, degradação do agente e até incêndio no canister; com absorvedor normalmente hidratado, forma o &lt;em&gt;composto A&lt;/em&gt;, de nefrotoxicidade demonstrada em animais.&lt;/p&gt;&lt;p&gt;A prevenção é organizacional: desligar os fluxômetros ao fim do dia, trocar o absorvedor após períodos de fluxo alto sem uso e desconfiar de qualquer canister cuja mudança de cor esteja ausente após uso prolongado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o sevoflurano é dos que menos produzem monóxido de carbono, e o composto A não depende de umidificação excessiva (A). É o ressecamento, e não a umidade, que desencadeia o problema (B). Os absorvedores sem bases fortes produzem menos, e não mais, monóxido de carbono (D).&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A laringe infantil é mais cefálica (em torno de C3 a C4, contra C5 a C6 no adulto), a língua é relativamente grande, a epiglote é longa e angulada em ômega e o occipúcio é proeminente. A região cricoide, cartilaginosa e completa, funciona como zona de menor complacência do funil laríngeo, o que historicamente justificou o uso de tubos sem balonete. Com os tubos de balonete de alto volume e baixa pressão, essa restrição caiu: eles são seguros a partir do período neonatal, reduzem reintubações por tubo inadequado, melhoram a capnografia e permitem ventilação com menor vazamento.&lt;/p&gt;&lt;p&gt;A fórmula usual para tubo &lt;em&gt;com&lt;/em&gt; balonete é idade/4 + 3,5, resultando em 4,5 mm para 4 anos (a fórmula idade/4 + 4 vale para tubos &lt;em&gt;sem&lt;/em&gt; balonete). A profundidade aproximada é diâmetro interno x 3, ou seja, cerca de 13,5 cm. O ponto crítico é monitorar a pressão do balonete, mantendo-a abaixo de 20 a 25 cmH&lt;sub&gt;2&lt;/sub&gt;O para preservar a perfusão da mucosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) confunde as duas fórmulas e resultaria em tubo grosseiramente grande, com risco de edema subglótico; (C) o balonete não é contraindicado na criança pequena desde que a pressão seja controlada; (D) 3,5 mm seria adequado a um recém-nascido, e o occipúcio proeminente já flexiona a cabeça, dispensando coxim occipital — na criança pequena o coxim, quando necessário, é sob os ombros.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A laringe infantil é mais cefálica (em torno de C3 a C4, contra C5 a C6 no adulto), a língua é relativamente grande, a epiglote é longa e angulada em ômega e o occipúcio é proeminente. A região cricoide, cartilaginosa e completa, funciona como zona de menor complacência do funil laríngeo, o que historicamente justificou o uso de tubos sem balonete. Com os tubos de balonete de alto volume e baixa pressão, essa restrição caiu: eles são seguros a partir do período neonatal, reduzem reintubações por tubo inadequado, melhoram a capnografia e permitem ventilação com menor vazamento.&lt;/p&gt;&lt;p&gt;A fórmula usual para tubo &lt;em&gt;com&lt;/em&gt; balonete é idade/4 + 3,5, resultando em 4,5 mm para 4 anos (a fórmula idade/4 + 4 vale para tubos &lt;em&gt;sem&lt;/em&gt; balonete). A profundidade aproximada é diâmetro interno x 3, ou seja, cerca de 13,5 cm. O ponto crítico é monitorar a pressão do balonete, mantendo-a abaixo de 20 a 25 cmH&lt;sub&gt;2&lt;/sub&gt;O para preservar a perfusão da mucosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) confunde as duas fórmulas e resultaria em tubo grosseiramente grande, com risco de edema subglótico; (C) o balonete não é contraindicado na criança pequena desde que a pressão seja controlada; (D) 3,5 mm seria adequado a um recém-nascido, e o occipúcio proeminente já flexiona a cabeça, dispensando coxim occipital; na criança pequena o coxim, quando necessário, é sob os ombros.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A inervação da laringe se divide entre dois ramos do vago. O nervo laríngeo superior emite o &lt;em&gt;ramo interno&lt;/em&gt;, puramente sensitivo, que supre a mucosa da face laríngea da epiglote até a superfície superior das cordas vocais, e o &lt;em&gt;ramo externo&lt;/em&gt;, motor exclusivo do músculo cricotireóideo. O nervo laríngeo recorrente dá a sensibilidade abaixo das cordas e a motricidade de todos os demais músculos intrínsecos, incluindo o cricoaritenóideo posterior, único abdutor.&lt;/p&gt;&lt;p&gt;O cricotireóideo alonga e tensiona a prega vocal, sendo o principal responsável pela elevação da frequência fundamental. Sua desnervação, complicação clássica da ligadura alta do pedículo tireóideo superior, produz voz soprosa, fadiga vocal e perda dos agudos, com mobilidade em adução e abdução preservadas e sem repercussão sobre a permeabilidade da via aérea. É, por isso, uma lesão subdiagnosticada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a lesão unilateral do recorrente cursa com corda paramediana e rouquidão franca, com alteração da mobilidade à laringoscopia, o que não ocorreu; (B) a lesão bilateral aguda dos recorrentes é emergência, com cordas aduzidas por ação sem oposição do cricotireóideo, estridor e obstrução — quadro incompatível com a evolução descrita; (C) a lesão do ramo interno gera perda de sensibilidade supraglótica e risco de aspiração, não alteração da tensão nem da altura vocal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A inervação da laringe se divide entre dois ramos do vago. O nervo laríngeo superior emite o &lt;em&gt;ramo interno&lt;/em&gt;, puramente sensitivo, que supre a mucosa da face laríngea da epiglote até a superfície superior das cordas vocais, e o &lt;em&gt;ramo externo&lt;/em&gt;, motor exclusivo do músculo cricotireóideo. O nervo laríngeo recorrente dá a sensibilidade abaixo das cordas e a motricidade de todos os demais músculos intrínsecos, incluindo o cricoaritenóideo posterior, único abdutor.&lt;/p&gt;&lt;p&gt;O cricotireóideo alonga e tensiona a prega vocal, sendo o principal responsável pela elevação da frequência fundamental. Sua desnervação, complicação clássica da ligadura alta do pedículo tireóideo superior, produz voz soprosa, fadiga vocal e perda dos agudos, com mobilidade em adução e abdução preservadas e sem repercussão sobre a permeabilidade da via aérea. É, por isso, uma lesão subdiagnosticada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a lesão unilateral do recorrente cursa com corda paramediana e rouquidão franca, com alteração da mobilidade à laringoscopia, o que não ocorreu; (B) a lesão bilateral aguda dos recorrentes é emergência, com cordas aduzidas por ação sem oposição do cricotireóideo, estridor e obstrução, quadro incompatível com a evolução descrita; (C) a lesão do ramo interno gera perda de sensibilidade supraglótica e risco de aspiração, não alteração da tensão nem da altura vocal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A parturiente concentra fatores que tornam a intubação difícil e a dessaturação rápida: edema e friabilidade da mucosa das vias aéreas, ingurgitamento capilar, mamas volumosas que atrapalham o cabo do laringoscópio, redução da capacidade residual funcional e aumento do consumo de oxigênio. Os algoritmos obstétricos são, por isso, deliberadamente restritivos quanto ao número de tentativas: no máximo duas laringoscopias, sendo a segunda com otimização máxima (posição em rampa, videolaringoscópio, manipulação laríngea externa, eventual terceira tentativa apenas por operador mais experiente).&lt;/p&gt;&lt;p&gt;Falhada a intubação, a prioridade absoluta passa a ser &lt;strong&gt;oxigenação&lt;/strong&gt;, e o dispositivo supraglótico de segunda geração — que permite drenagem gástrica e tolera pressões mais altas — é o resgate de eleição. Restabelecida a oxigenação, toma-se a decisão de acordar ou prosseguir, ponderando urgência materno-fetal, viabilidade de anestesia regional, obesidade e experiência da equipe.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) tentativas repetidas causam edema, sangramento e conversão de uma via aérea difícil em via aérea impossível; (B) o acesso cervical anterior está reservado ao cenário em que a oxigenação falha por todas as vias, o que ainda não se configurou, pois o supraglótico não foi testado; (C) acordar é uma das opções legítimas, mas não antes de assegurar oxigenação, e a decisão deve considerar a condição fetal, não ignorá-la.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A parturiente concentra fatores que tornam a intubação difícil e a dessaturação rápida: edema e friabilidade da mucosa das vias aéreas, ingurgitamento capilar, mamas volumosas que atrapalham o cabo do laringoscópio, redução da capacidade residual funcional e aumento do consumo de oxigênio. Os algoritmos obstétricos são, por isso, deliberadamente restritivos quanto ao número de tentativas: no máximo duas laringoscopias, sendo a segunda com otimização máxima (posição em rampa, videolaringoscópio, manipulação laríngea externa, eventual terceira tentativa apenas por operador mais experiente).&lt;/p&gt;&lt;p&gt;Falhada a intubação, a prioridade absoluta passa a ser &lt;strong&gt;oxigenação&lt;/strong&gt;, e o dispositivo supraglótico de segunda geração, que permite drenagem gástrica e tolera pressões mais altas, é o resgate de eleição. Restabelecida a oxigenação, toma-se a decisão de acordar ou prosseguir, ponderando urgência materno-fetal, viabilidade de anestesia regional, obesidade e experiência da equipe.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) tentativas repetidas causam edema, sangramento e conversão de uma via aérea difícil em via aérea impossível; (B) o acesso cervical anterior está reservado ao cenário em que a oxigenação falha por todas as vias, o que ainda não se configurou, pois o supraglótico não foi testado; (C) acordar é uma das opções legítimas, mas não antes de assegurar oxigenação, e a decisão deve considerar a condição fetal, não ignorá-la.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A abrasão de córnea é a complicação ocular mais frequente da anestesia geral. Sob anestesia, o reflexo de Bell se abole, a produção lacrimal cai e cerca de metade dos pacientes desenvolve lagoftalmo, deixando a córnea exposta. Somam-se o contato direto com máscara, campos, crachás e cabos, e o uso de decúbito ventral, situação de risco particular. O quadro típico é de dor em queimação, fotofobia e sensação de corpo estranho, com &lt;em&gt;acuidade visual preservada&lt;/em&gt; — dado que separa a abrasão das causas graves de perda visual.&lt;/p&gt;&lt;p&gt;O manejo é conservador: lubrificante ocular, evitar coçar o olho, analgesia simples e reavaliação. A maioria dos casos cicatriza em 24 a 72 horas; a persistência dos sintomas além desse período exige avaliação oftalmológica. A prevenção é simples e eficaz: oclusão palpebral com fita logo após a indução, antes da laringoscopia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a neuropatia óptica isquêmica, embora associada a cirurgia de coluna em decúbito ventral, cursa com &lt;em&gt;perda visual&lt;/em&gt; e alteração pupilar, ausentes aqui; (C) a ceratite química exige irrigação e avaliação especializada, e corticoide tópico prolongado sem diagnóstico definido é conduta arriscada, com risco de retardo de cicatrização e infecção; (D) o glaucoma agudo cursa com dor intensa, halos, córnea edemaciada e pupila em midríase média fixa, e a atropina tópica, midriática, agravaria o bloqueio angular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A abrasão de córnea é a complicação ocular mais frequente da anestesia geral. Sob anestesia, o reflexo de Bell se abole, a produção lacrimal cai e cerca de metade dos pacientes desenvolve lagoftalmo, deixando a córnea exposta. Somam-se o contato direto com máscara, campos, crachás e cabos, e o uso de decúbito ventral, situação de risco particular. O quadro típico é de dor em queimação, fotofobia e sensação de corpo estranho, com &lt;em&gt;acuidade visual preservada&lt;/em&gt;, dado que separa a abrasão das causas graves de perda visual.&lt;/p&gt;&lt;p&gt;O manejo é conservador: lubrificante ocular, evitar coçar o olho, analgesia simples e reavaliação. A maioria dos casos cicatriza em 24 a 72 horas; a persistência dos sintomas além desse período exige avaliação oftalmológica. A prevenção é simples e eficaz: oclusão palpebral com fita logo após a indução, antes da laringoscopia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a neuropatia óptica isquêmica, embora associada a cirurgia de coluna em decúbito ventral, cursa com &lt;em&gt;perda visual&lt;/em&gt; e alteração pupilar, ausentes aqui; (C) a ceratite química exige irrigação e avaliação especializada, e corticoide tópico prolongado sem diagnóstico definido é conduta arriscada, com risco de retardo de cicatrização e infecção; (D) o glaucoma agudo cursa com dor intensa, halos, córnea edemaciada e pupila em midríase média fixa, e a atropina tópica, midriática, agravaria o bloqueio angular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O edema subglótico pós-intubação, ou crupe pós-extubação, resulta de trauma e isquemia da mucosa na região cricoide, o ponto de menor complacência do funil laríngeo infantil. Como a resistência ao fluxo é inversamente proporcional à quarta potência do raio, poucos milímetros de edema circunferencial produzem obstrução clinicamente relevante em uma via aérea de pequeno calibre. Os fatores de risco reconhecidos são tubo excessivamente calibroso (a ausência de escape com 20 a 25 cmH&lt;sub&gt;2&lt;/sub&gt;O é um alerta), intubações traumáticas ou repetidas, mobilização da cabeça durante o procedimento, intubação prolongada e infecção respiratória recente.&lt;/p&gt;&lt;p&gt;O tratamento combina oxigênio umidificado, adrenalina por nebulização — que reduz o edema por vasoconstrição da mucosa — e corticoide sistêmico, tipicamente dexametasona. Como a duração do efeito da adrenalina inalatória é de cerca de duas horas, o paciente deve permanecer em observação pelo risco de retorno dos sintomas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a reintubação está reservada à obstrução grave com insuficiência respiratória ou falha do tratamento clínico, e reinstrumentar a mucosa já edemaciada agrava a lesão; (C) o quadro é obstrutivo alto, não broncoespasmo, e a alta precoce ignora o risco de recidiva após o término do efeito de qualquer nebulização; (D) o edema é inflamatório e traumático, não hidrostático, e diuréticos não têm papel, além do risco de hipovolemia na criança.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O edema subglótico pós-intubação, ou crupe pós-extubação, resulta de trauma e isquemia da mucosa na região cricoide, o ponto de menor complacência do funil laríngeo infantil. Como a resistência ao fluxo é inversamente proporcional à quarta potência do raio, poucos milímetros de edema circunferencial produzem obstrução clinicamente relevante em uma via aérea de pequeno calibre. Os fatores de risco reconhecidos são tubo excessivamente calibroso (a ausência de escape com 20 a 25 cmH&lt;sub&gt;2&lt;/sub&gt;O é um alerta), intubações traumáticas ou repetidas, mobilização da cabeça durante o procedimento, intubação prolongada e infecção respiratória recente.&lt;/p&gt;&lt;p&gt;O tratamento combina oxigênio umidificado, adrenalina por nebulização (que reduz o edema por vasoconstrição da mucosa) e corticoide sistêmico, tipicamente dexametasona. Como a duração do efeito da adrenalina inalatória é de cerca de duas horas, o paciente deve permanecer em observação pelo risco de retorno dos sintomas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a reintubação está reservada à obstrução grave com insuficiência respiratória ou falha do tratamento clínico, e reinstrumentar a mucosa já edemaciada agrava a lesão; (C) o quadro é obstrutivo alto, não broncoespasmo, e a alta precoce ignora o risco de recidiva após o término do efeito de qualquer nebulização; (D) o edema é inflamatório e traumático, não hidrostático, e diuréticos não têm papel, além do risco de hipovolemia na criança.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A injeção intra-arterial acidental é mais provável quando se puncionam a fossa antecubital (artéria braquial em posição aberrante) ou a face volar do punho. O reconhecimento imediato depende de dor desproporcional em queimação com irradiação distal, palidez ou moteamento, refluxo pulsátil e sangue vermelho vivo no cateter. As lesões decorrem de vasoespasmo intenso, precipitação de cristais do fármaco em pH sanguíneo, lesão endotelial direta e trombose, podendo culminar em necrose e amputação.&lt;/p&gt;&lt;p&gt;A conduta prioriza o membro: &lt;strong&gt;manter o cateter no lugar&lt;/strong&gt; (é a via de acesso ao território lesado), interromper a injeção, diluir com salina, administrar vasodilatador intra-arterial (lidocaína, papaverina ou análogos), anticoagular para prevenir trombose e realizar bloqueio simpático — bloqueio de plexo braquial ou de gânglio estrelado — que promove vasodilatação e analgesia. Analgesia sistêmica e avaliação vascular precoce completam o manejo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) retirar o cateter elimina o único acesso direto ao território comprometido, e calor local com observação isolada é conduta passiva diante de risco de isquemia; (C) noradrenalina agrava o vasoespasmo, e o mecanismo do dano não é vasodilatação reflexa; (D) bicarbonato hipertônico por via intra-arterial não tem respaldo e acrescenta lesão endotelial e osmótica ao leito já comprometido.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A injeção intra-arterial acidental é mais provável quando se puncionam a fossa antecubital (artéria braquial em posição aberrante) ou a face volar do punho. O reconhecimento imediato depende de dor desproporcional em queimação com irradiação distal, palidez ou moteamento, refluxo pulsátil e sangue vermelho vivo no cateter. As lesões decorrem de vasoespasmo intenso, precipitação de cristais do fármaco em pH sanguíneo, lesão endotelial direta e trombose, podendo culminar em necrose e amputação.&lt;/p&gt;&lt;p&gt;A conduta prioriza o membro: &lt;strong&gt;manter o cateter no lugar&lt;/strong&gt; (é a via de acesso ao território lesado), interromper a injeção, diluir com salina, administrar vasodilatador intra-arterial (lidocaína, papaverina ou análogos), anticoagular para prevenir trombose e realizar bloqueio simpático, seja de plexo braquial, seja de gânglio estrelado, que promove vasodilatação e analgesia. Analgesia sistêmica e avaliação vascular precoce completam o manejo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) retirar o cateter elimina o único acesso direto ao território comprometido, e calor local com observação isolada é conduta passiva diante de risco de isquemia; (C) noradrenalina agrava o vasoespasmo, e o mecanismo do dano não é vasodilatação reflexa; (D) bicarbonato hipertônico por via intra-arterial não tem respaldo e acrescenta lesão endotelial e osmótica ao leito já comprometido.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipertensão na sala de recuperação é, na maioria das vezes, &lt;em&gt;sintoma&lt;/em&gt; e não doença primária. As causas reversíveis mais comuns são dor, hipoxemia, hipercapnia por hipoventilação, distensão vesical, hipotermia com tremores e resposta adrenérgica associada, ansiedade e despertar agitado, náusea, hipervolemia e suspensão abrupta de anti-hipertensivos de uso crônico, sobretudo betabloqueadores e clonidina. O paciente descrito reúne pelo menos três desses gatilhos: dor, bexiga obstruída e hipotermia com tremores.&lt;/p&gt;&lt;p&gt;A sequência correta é identificar e corrigir o gatilho — analgesia adequada, oxigenação e ventilação, desobstrução ou passagem de sonda, aquecimento ativo — e só então reavaliar. Persistindo hipertensão significativa, ou havendo risco de sangramento em sítio cirúrgico, isquemia miocárdica ou doença aórtica, usam-se agentes venosos tituláveis como labetalol, esmolol, hidralazina ou nicardipino, com redução gradual, da ordem de 20% a 25% da pressão arterial média inicial.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) reduzir 40% da pressão arterial média em 15 minutos é queda excessiva e abrupta, com risco de isquemia cerebral, coronariana e renal, sobretudo em hipertenso crônico com curva de autorregulação desviada; (B) o nifedipino sublingual produz queda imprevisível e taquicardia reflexa, prática abandonada; (D) a losartana tem início lento e não trata dor, hipotermia nem retenção urinária, ainda que a reintrodução da terapia crônica seja apropriada mais adiante.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipertensão na sala de recuperação é, na maioria das vezes, &lt;em&gt;sintoma&lt;/em&gt; e não doença primária. As causas reversíveis mais comuns são dor, hipoxemia, hipercapnia por hipoventilação, distensão vesical, hipotermia com tremores e resposta adrenérgica associada, ansiedade e despertar agitado, náusea, hipervolemia e suspensão abrupta de anti-hipertensivos de uso crônico, sobretudo betabloqueadores e clonidina. O paciente descrito reúne pelo menos três desses gatilhos: dor, bexiga obstruída e hipotermia com tremores.&lt;/p&gt;&lt;p&gt;A sequência correta é identificar e corrigir o gatilho (analgesia adequada, oxigenação e ventilação, desobstrução ou passagem de sonda, aquecimento ativo) e só então reavaliar. Persistindo hipertensão significativa, ou havendo risco de sangramento em sítio cirúrgico, isquemia miocárdica ou doença aórtica, usam-se agentes venosos tituláveis como labetalol, esmolol, hidralazina ou nicardipino, com redução gradual, da ordem de 20% a 25% da pressão arterial média inicial.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) reduzir 40% da pressão arterial média em 15 minutos é queda excessiva e abrupta, com risco de isquemia cerebral, coronariana e renal, sobretudo em hipertenso crônico com curva de autorregulação desviada; (B) o nifedipino sublingual produz queda imprevisível e taquicardia reflexa, prática abandonada; (D) a losartana tem início lento e não trata dor, hipotermia nem retenção urinária, ainda que a reintrodução da terapia crônica seja apropriada mais adiante.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Obesidade e apneia obstrutiva do sono são os fatores de risco mais consistentes para depressão respiratória induzida por opioides no pós-operatório. Nesses pacientes, a capacidade residual funcional está reduzida, o colapso faríngeo é facilitado pela sedação e a resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt; está deprimida, de modo que a hipoventilação evolui rapidamente para hipoxemia. O ronco alto associado a sonolência profunda sugere obstrução dinâmica somada à depressão central.&lt;/p&gt;&lt;p&gt;O manejo combina medidas de suporte — elevação da cabeceira, manobras de abertura da via aérea, oxigênio, ventilação assistida e, quando disponível, pressão positiva não invasiva — com antagonização &lt;strong&gt;titulada&lt;/strong&gt;. A naloxona deve ser fracionada em bolus pequenos, tipicamente de 40 a 80 microgramas, repetidos até que a ventilação seja adequada, preservando parte da analgesia e evitando dor súbita, hipertensão, taquicardia e edema pulmonar. Como a meia-vida da naloxona é de aproximadamente 30 a 60 minutos, inferior à da morfina, a paciente exige observação prolongada e monitorização contínua pelo risco de renarcotização.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 0,4 mg em bolus único é dose excessiva para esse cenário e a alta precoce ignora a farmacocinética do antagonista; (B) o flumazenil não reverte opioides e não se aplica a um quadro cuja causa é claramente a morfina titulada; (C) suporte isolado é insuficiente diante de frequência de 6 incursões por minuto e saturação de 85%, além de o oxigênio poder mascarar a hipoventilação persistente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Obesidade e apneia obstrutiva do sono são os fatores de risco mais consistentes para depressão respiratória induzida por opioides no pós-operatório. Nesses pacientes, a capacidade residual funcional está reduzida, o colapso faríngeo é facilitado pela sedação e a resposta ventilatória ao CO&lt;sub&gt;2&lt;/sub&gt; está deprimida, de modo que a hipoventilação evolui rapidamente para hipoxemia. O ronco alto associado a sonolência profunda sugere obstrução dinâmica somada à depressão central.&lt;/p&gt;&lt;p&gt;O manejo combina medidas de suporte (elevação da cabeceira, manobras de abertura da via aérea, oxigênio, ventilação assistida e, quando disponível, pressão positiva não invasiva) com antagonização &lt;strong&gt;titulada&lt;/strong&gt;. A naloxona deve ser fracionada em bolus pequenos, tipicamente de 40 a 80 microgramas, repetidos até que a ventilação seja adequada, preservando parte da analgesia e evitando dor súbita, hipertensão, taquicardia e edema pulmonar. Como a meia-vida da naloxona é de aproximadamente 30 a 60 minutos, inferior à da morfina, a paciente exige observação prolongada e monitorização contínua pelo risco de renarcotização.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 0,4 mg em bolus único é dose excessiva para esse cenário e a alta precoce ignora a farmacocinética do antagonista; (B) o flumazenil não reverte opioides e não se aplica a um quadro cuja causa é claramente a morfina titulada; (C) suporte isolado é insuficiente diante de frequência de 6 incursões por minuto e saturação de 85%, além de o oxigênio poder mascarar a hipoventilação persistente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A substância P é um neuropeptídeo da família das taquicininas, abundante nos núcleos do tronco encefálico envolvidos no reflexo emético, particularmente na área postrema e no núcleo do trato solitário, onde se liga ao receptor de neurocinina-1 (NK1). Essa via é uma das quatro grandes vias do vômito, ao lado das vias serotoninérgica (5-HT&lt;sub&gt;3&lt;/sub&gt;), dopaminérgica (D&lt;sub&gt;2&lt;/sub&gt;) e colinérgica/histaminérgica — o que fundamenta a lógica da profilaxia multimodal com fármacos de classes diferentes.&lt;/p&gt;&lt;p&gt;Os antagonistas NK1, dos quais o aprepitanto é o representante mais conhecido, são administrados por via oral antes da indução e caracterizam-se por &lt;strong&gt;meia-vida longa&lt;/strong&gt;, da ordem de 9 a 13 horas, o que confere cobertura estendida por até 48 horas. Seu efeito é mais marcante na redução de &lt;em&gt;vômitos&lt;/em&gt; do que na redução da náusea, e por isso são especialmente úteis quando o vômito é particularmente indesejável, como em cirurgias de cabeça e pescoço, neurocirurgia e cirurgia oftalmológica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde as classes: o alvo é o receptor NK1, não o 5-HT&lt;sub&gt;3&lt;/sub&gt;; (C) inverte a farmacocinética, pois a meia-vida longa é justamente a característica distintiva da classe, com administração pré-operatória; (D) o bloqueio dopaminérgico e os sintomas extrapiramidais pertencem a butirofenonas e benzamidas, não aos antagonistas NK1, que têm perfil de efeitos adversos favorável.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A substância P é um neuropeptídeo da família das taquicininas, abundante nos núcleos do tronco encefálico envolvidos no reflexo emético, particularmente na área postrema e no núcleo do trato solitário, onde se liga ao receptor de neurocinina-1 (NK1). Essa via é uma das quatro grandes vias do vômito, ao lado das vias serotoninérgica (5-HT&lt;sub&gt;3&lt;/sub&gt;), dopaminérgica (D&lt;sub&gt;2&lt;/sub&gt;) e colinérgica/histaminérgica, o que fundamenta a lógica da profilaxia multimodal com fármacos de classes diferentes.&lt;/p&gt;&lt;p&gt;Os antagonistas NK1, dos quais o aprepitanto é o representante mais conhecido, são administrados por via oral antes da indução e caracterizam-se por &lt;strong&gt;meia-vida longa&lt;/strong&gt;, da ordem de 9 a 13 horas, o que confere cobertura estendida por até 48 horas. Seu efeito é mais marcante na redução de &lt;em&gt;vômitos&lt;/em&gt; do que na redução da náusea, e por isso são especialmente úteis quando o vômito é particularmente indesejável, como em cirurgias de cabeça e pescoço, neurocirurgia e cirurgia oftalmológica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde as classes: o alvo é o receptor NK1, não o 5-HT&lt;sub&gt;3&lt;/sub&gt;; (C) inverte a farmacocinética, pois a meia-vida longa é justamente a característica distintiva da classe, com administração pré-operatória; (D) o bloqueio dopaminérgico e os sintomas extrapiramidais pertencem a butirofenonas e benzamidas, não aos antagonistas NK1, que têm perfil de efeitos adversos favorável.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A vasopressina é um hormônio antidiurético endógeno que, em doses suprafisiológicas, atua sobre receptores &lt;strong&gt;V1&lt;/strong&gt; do músculo liso vascular, promovendo vasoconstrição por via não adrenérgica, mediada por fosfolipase C e mobilização de cálcio intracelular. Essa independência dos receptores adrenérgicos é a base do argumento teórico a seu favor: ao contrário das catecolaminas, cuja resposta se reduz em meio acidótico e hipóxico, a vasopressina mantém o efeito pressor, elevando a pressão diastólica aórtica e, com ela, a pressão de perfusão coronariana. Os receptores V2, renais, medeiam a retenção de água e não têm papel nesse contexto.&lt;/p&gt;&lt;p&gt;A evidência clínica, contudo, não confirmou a promessa: estudos comparativos e a experiência acumulada não mostraram superioridade em retorno da circulação espontânea, sobrevida ou desfecho neurológico. Por isso ela foi retirada do algoritmo principal do suporte avançado como substituta rotineira da adrenalina, podendo ser considerada em situações específicas, isoladamente ou em associação, sem vantagem demonstrada. A adrenalina permanece o vasopressor de escolha, 1 mg a cada 3 a 5 minutos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) atribui a vasoconstrição ao receptor V2 e acrescenta efeito inotrópico direto, que a vasopressina não possui; (B) não há recomendação de substituição obrigatória, e 1 mg é a dose da adrenalina, não da vasopressina, cuja dose estudada é de 40 unidades; (D) o efeito vasoconstritor é justamente &lt;em&gt;preservado&lt;/em&gt; na acidose — a limitação é de eficácia clínica comprovada, não de farmacologia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A vasopressina é um hormônio antidiurético endógeno que, em doses suprafisiológicas, atua sobre receptores &lt;strong&gt;V1&lt;/strong&gt; do músculo liso vascular, promovendo vasoconstrição por via não adrenérgica, mediada por fosfolipase C e mobilização de cálcio intracelular. Essa independência dos receptores adrenérgicos é a base do argumento teórico a seu favor: ao contrário das catecolaminas, cuja resposta se reduz em meio acidótico e hipóxico, a vasopressina mantém o efeito pressor, elevando a pressão diastólica aórtica e, com ela, a pressão de perfusão coronariana. Os receptores V2, renais, medeiam a retenção de água e não têm papel nesse contexto.&lt;/p&gt;&lt;p&gt;A evidência clínica, contudo, não confirmou a promessa: estudos comparativos e a experiência acumulada não mostraram superioridade em retorno da circulação espontânea, sobrevida ou desfecho neurológico. Por isso ela foi retirada do algoritmo principal do suporte avançado como substituta rotineira da adrenalina, podendo ser considerada em situações específicas, isoladamente ou em associação, sem vantagem demonstrada. A adrenalina permanece o vasopressor de escolha, 1 mg a cada 3 a 5 minutos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) atribui a vasoconstrição ao receptor V2 e acrescenta efeito inotrópico direto, que a vasopressina não possui; (B) não há recomendação de substituição obrigatória, e 1 mg é a dose da adrenalina, não da vasopressina, cuja dose estudada é de 40 unidades; (D) o efeito vasoconstritor é justamente &lt;em&gt;preservado&lt;/em&gt; na acidose; a limitação é de eficácia clínica comprovada, não de farmacologia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O fluxo coronariano ocorre predominantemente na diástole, e durante a reanimação a &lt;strong&gt;pressão de perfusão coronariana&lt;/strong&gt; é definida como a diferença entre a pressão diastólica aórtica e a pressão diastólica do átrio direito. É o determinante hemodinâmico mais fortemente associado ao retorno da circulação espontânea: valores abaixo de aproximadamente 15 mmHg tornam o retorno improvável, e uma diastólica invasiva de 14 mmHg sinaliza compressões insuficientes ou vasoplegia importante.&lt;/p&gt;&lt;p&gt;Quando há monitorização invasiva já instalada, a reanimação pode ser guiada por esses dados, buscando-se elevar a pressão diastólica com compressões mais profundas e com retorno completo do tórax, na frequência de 100 a 120 por minuto, além do uso de vasopressor. O ponto crítico é que a pressão de perfusão coronariana &lt;em&gt;despenca a cada interrupção&lt;/em&gt; das compressões e só se restabelece após vários ciclos consecutivos — motivo pelo qual as pausas devem ser minimizadas, idealmente com menos de 10 segundos, e as checagens de pulso restritas às trocas de socorrista a cada 2 minutos. O CO&lt;sub&gt;2&lt;/sub&gt; expirado é o outro parâmetro útil, com valores persistentemente abaixo de 10 mmHg indicando compressões ineficazes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte o conceito: é a diastólica, não a sistólica, que determina a perfusão coronariana; (C) 14 mmHg é valor criticamente baixo, e aumentar a frequência das checagens agrava o problema ao multiplicar as pausas; (D) a fórmula está errada, pois o parâmetro relevante é diastólica aórtica menos pressão diastólica do átrio direito.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O fluxo coronariano ocorre predominantemente na diástole, e durante a reanimação a &lt;strong&gt;pressão de perfusão coronariana&lt;/strong&gt; é definida como a diferença entre a pressão diastólica aórtica e a pressão diastólica do átrio direito. É o determinante hemodinâmico mais fortemente associado ao retorno da circulação espontânea: valores abaixo de aproximadamente 15 mmHg tornam o retorno improvável, e uma diastólica invasiva de 14 mmHg sinaliza compressões insuficientes ou vasoplegia importante.&lt;/p&gt;&lt;p&gt;Quando há monitorização invasiva já instalada, a reanimação pode ser guiada por esses dados, buscando-se elevar a pressão diastólica com compressões mais profundas e com retorno completo do tórax, na frequência de 100 a 120 por minuto, além do uso de vasopressor. O ponto crítico é que a pressão de perfusão coronariana &lt;em&gt;despenca a cada interrupção&lt;/em&gt; das compressões e só se restabelece após vários ciclos consecutivos, motivo pelo qual as pausas devem ser minimizadas, idealmente com menos de 10 segundos, e as checagens de pulso restritas às trocas de socorrista a cada 2 minutos. O CO&lt;sub&gt;2&lt;/sub&gt; expirado é o outro parâmetro útil, com valores persistentemente abaixo de 10 mmHg indicando compressões ineficazes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte o conceito: é a diastólica, não a sistólica, que determina a perfusão coronariana; (C) 14 mmHg é valor criticamente baixo, e aumentar a frequência das checagens agrava o problema ao multiplicar as pausas; (D) a fórmula está errada, pois o parâmetro relevante é diastólica aórtica menos pressão diastólica do átrio direito.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O oxímetro de pulso convencional emite luz em dois comprimentos de onda, 660 nm (vermelho) e 940 nm (infravermelho), e calcula a razão &lt;em&gt;R&lt;/em&gt; entre as absorbâncias pulsáteis nesses dois canais. Como o aparelho resolve apenas duas espécies (oxi-hemoglobina e desoxi-hemoglobina), qualquer terceira hemoglobina distorce a leitura.&lt;/p&gt;&lt;p&gt;A meta-hemoglobina tem coeficiente de absorção elevado e aproximadamente igual nos dois comprimentos de onda. Quando sua fração é alta, a razão &lt;em&gt;R&lt;/em&gt; converge para 1, valor que a curva de calibração empírica dos monitores traduz em SpO2 próxima de 85%. Por isso a leitura fica presa nesse patamar, independentemente da PaO2 real — daí o descolamento clássico entre SpO2 baixa e PaO2 elevada (&lt;em&gt;saturation gap&lt;/em&gt;). O diagnóstico exige co-oximetria; o tratamento é azul de metileno, 1 a 2 mg/kg por via venosa, contraindicado na deficiência de G6PD.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a meta-hemoglobina de fato desvia a curva para a esquerda nas moléculas remanescentes, e o erro do oxímetro não é proporcional à PaO2, mas fixo em torno de 85%. (C) a leitura falsamente próxima de 100% é o padrão da carboxi-hemoglobina, que absorve em 660 nm de forma semelhante à oxi-hemoglobina. (D) a dis-hemoglobinemia altera o componente pulsátil analisado, não produz oscilação batimento a batimento, e o componente não pulsátil é justamente o que o aparelho descarta.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O oxímetro de pulso convencional emite luz em dois comprimentos de onda, 660 nm (vermelho) e 940 nm (infravermelho), e calcula a razão &lt;em&gt;R&lt;/em&gt; entre as absorbâncias pulsáteis nesses dois canais. Como o aparelho resolve apenas duas espécies (oxi-hemoglobina e desoxi-hemoglobina), qualquer terceira hemoglobina distorce a leitura.&lt;/p&gt;&lt;p&gt;A meta-hemoglobina tem coeficiente de absorção elevado e aproximadamente igual nos dois comprimentos de onda. Quando sua fração é alta, a razão &lt;em&gt;R&lt;/em&gt; converge para 1, valor que a curva de calibração empírica dos monitores traduz em SpO2 próxima de 85%. Por isso a leitura fica presa nesse patamar, independentemente da PaO2 real; daí o descolamento clássico entre SpO2 baixa e PaO2 elevada (&lt;em&gt;saturation gap&lt;/em&gt;). O diagnóstico exige co-oximetria; o tratamento é azul de metileno, 1 a 2 mg/kg por via venosa, contraindicado na deficiência de G6PD.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a meta-hemoglobina de fato desvia a curva para a esquerda nas moléculas remanescentes, e o erro do oxímetro não é proporcional à PaO2, mas fixo em torno de 85%. (C) a leitura falsamente próxima de 100% é o padrão da carboxi-hemoglobina, que absorve em 660 nm de forma semelhante à oxi-hemoglobina. (D) a dis-hemoglobinemia altera o componente pulsátil analisado, não produz oscilação batimento a batimento, e o componente não pulsátil é justamente o que o aparelho descarta.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Em pulmões normais o EtCO2 é 2 a 5 mmHg menor que a PaCO&lt;sub&gt;2&lt;/sub&gt;, diferença explicada pela mistura do gás alveolar com o gás do espaço morto anatômico e por pequena heterogeneidade ventilação-perfusão. O gradiente é, portanto, um índice de espaço morto fisiológico.&lt;/p&gt;&lt;p&gt;No caso, o gradiente saltou para 27 mmHg de forma abrupta, com hipotensão simultânea e ventilação inalterada. Isso caracteriza aumento agudo do espaço morto alveolar: unidades que continuam recebendo ventilação deixam de ser perfundidas e devolvem gás praticamente isento de CO&lt;sub&gt;2&lt;/sub&gt;, que dilui o gás proveniente das unidades ainda perfundidas e derruba o EtCO2. As causas típicas são queda súbita do débito cardíaco, embolia pulmonar trombótica, gasosa, gordurosa ou de cimento — todas plausíveis nesse cenário ortopédico e hemorrágico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipotermia reduz a produção de CO&lt;sub&gt;2&lt;/sub&gt; e derruba o EtCO2, mas faz a PaCO&lt;sub&gt;2&lt;/sub&gt; cair junto, sem alargar o gradiente, e não ocorre em minutos. (B) a reinalação eleva o CO2 inspirado e tende a aumentar o EtCO2, movimento oposto ao observado. (D) a ventilação foi explicitamente mantida constante, e a hiperventilação também reduziria as duas medidas de modo paralelo, preservando o gradiente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Em pulmões normais o EtCO2 é 2 a 5 mmHg menor que a PaCO&lt;sub&gt;2&lt;/sub&gt;, diferença explicada pela mistura do gás alveolar com o gás do espaço morto anatômico e por pequena heterogeneidade ventilação-perfusão. O gradiente é, portanto, um índice de espaço morto fisiológico.&lt;/p&gt;&lt;p&gt;No caso, o gradiente saltou para 27 mmHg de forma abrupta, com hipotensão simultânea e ventilação inalterada. Isso caracteriza aumento agudo do espaço morto alveolar: unidades que continuam recebendo ventilação deixam de ser perfundidas e devolvem gás praticamente isento de CO&lt;sub&gt;2&lt;/sub&gt;, que dilui o gás proveniente das unidades ainda perfundidas e derruba o EtCO2. As causas típicas são queda súbita do débito cardíaco, embolia pulmonar trombótica, gasosa, gordurosa ou de cimento, todas plausíveis nesse cenário ortopédico e hemorrágico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipotermia reduz a produção de CO&lt;sub&gt;2&lt;/sub&gt; e derruba o EtCO2, mas faz a PaCO&lt;sub&gt;2&lt;/sub&gt; cair junto, sem alargar o gradiente, e não ocorre em minutos. (B) a reinalação eleva o CO2 inspirado e tende a aumentar o EtCO2, movimento oposto ao observado. (D) a ventilação foi explicitamente mantida constante, e a hiperventilação também reduziria as duas medidas de modo paralelo, preservando o gradiente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O EtCO2 resulta do equilíbrio entre três fatores: produção tecidual de CO&lt;sub&gt;2&lt;/sub&gt;, transporte até o pulmão pelo débito cardíaco e eliminação pela ventilação alveolar. Com ventilação fixa, qualquer aumento de oferta de CO&lt;sub&gt;2&lt;/sub&gt; ao alvéolo eleva o valor expirado.&lt;/p&gt;&lt;p&gt;No pneumoperitônio com dióxido de carbono, o gás difunde do peritônio para a circulação de forma contínua, com pico entre 15 e 30 minutos de insuflação. Esse aporte extra soma-se à produção metabólica e eleva o EtCO2 em 5 a 15 mmHg quando não se ajusta o volume minuto. A conduta é aumentar a ventilação alveolar, preferencialmente pela frequência respiratória, e revisar a pressão de insuflação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a exaustão do absorvedor é reconhecida pela fração inspirada de CO2 maior que zero, isto é, pela elevação da linha de base inspiratória — o enunciado informa explicitamente que ela permanece nula. (B) o aumento do espaço morto alveolar reduz o EtCO2 e alarga o gradiente em relação à PaCO&lt;sub&gt;2&lt;/sub&gt;, movimento contrário ao observado. (D) a hipertermia maligna cursa com elevação do EtCO2 refratária ao aumento do volume minuto, taquicardia, rigidez muscular, acidose e hipertermia progressiva; a temperatura normal e a explicação mecânica evidente do pneumoperitônio tornam esse diagnóstico improvável nesse momento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O EtCO2 resulta do equilíbrio entre três fatores: produção tecidual de CO&lt;sub&gt;2&lt;/sub&gt;, transporte até o pulmão pelo débito cardíaco e eliminação pela ventilação alveolar. Com ventilação fixa, qualquer aumento de oferta de CO&lt;sub&gt;2&lt;/sub&gt; ao alvéolo eleva o valor expirado.&lt;/p&gt;&lt;p&gt;No pneumoperitônio com dióxido de carbono, o gás difunde do peritônio para a circulação de forma contínua, com pico entre 15 e 30 minutos de insuflação. Esse aporte extra soma-se à produção metabólica e eleva o EtCO2 em 5 a 15 mmHg quando não se ajusta o volume minuto. A conduta é aumentar a ventilação alveolar, preferencialmente pela frequência respiratória, e revisar a pressão de insuflação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a exaustão do absorvedor é reconhecida pela fração inspirada de CO2 maior que zero, isto é, pela elevação da linha de base inspiratória, e o enunciado informa explicitamente que ela permanece nula. (B) o aumento do espaço morto alveolar reduz o EtCO2 e alarga o gradiente em relação à PaCO&lt;sub&gt;2&lt;/sub&gt;, movimento contrário ao observado. (D) a hipertermia maligna cursa com elevação do EtCO2 refratária ao aumento do volume minuto, taquicardia, rigidez muscular, acidose e hipertermia progressiva; a temperatura normal e a explicação mecânica evidente do pneumoperitônio tornam esse diagnóstico improvável nesse momento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os potenciais evocados motores são obtidos por estimulação transcraniana do córtex motor e registrados como resposta muscular composta. Eles atravessam sinapses no corno anterior e dependem da junção neuromuscular, o que os torna a modalidade mais vulnerável do arsenal neurofisiológico: agentes halogenados deprimem a transmissão sináptica medular de modo dose-dependente e, acima de 0,5 CAM, costumam abolir as respostas; bloqueadores neuromusculares eliminam a resposta muscular registrada.&lt;/p&gt;&lt;p&gt;Os potenciais somatossensitivos, ao contrário, percorrem vias predominantemente axonais com menos sinapses e toleram concentrações maiores de halogenado — daí a dissociação descrita, que é assinatura de causa anestésica e não cirúrgica.&lt;/p&gt;&lt;p&gt;A conduta correta é remover a causa: converter para anestesia venosa total com propofol e remifentanil, técnica de referência quando se monitorizam potenciais motores, e evitar bloqueio neuromuscular após a intubação. Só depois de restaurado o sinal faz sentido interpretar alterações como lesão medular.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) abrir mão dos potenciais motores é perder justamente a via anterior, a mais suscetível a lesão pela instrumentação e por isquemia. (C) elevar a pressão é útil quando a perda é isquêmica, mas manter o halogenado alto e o bloqueio profundo perpetua a causa real. (D) propofol em bolus deprime ainda mais a resposta de forma transitória, e manter o sevoflurano não resolve o problema identificado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os potenciais evocados motores são obtidos por estimulação transcraniana do córtex motor e registrados como resposta muscular composta. Eles atravessam sinapses no corno anterior e dependem da junção neuromuscular, o que os torna a modalidade mais vulnerável do arsenal neurofisiológico: agentes halogenados deprimem a transmissão sináptica medular de modo dose-dependente e, acima de 0,5 CAM, costumam abolir as respostas; bloqueadores neuromusculares eliminam a resposta muscular registrada.&lt;/p&gt;&lt;p&gt;Os potenciais somatossensitivos, ao contrário, percorrem vias predominantemente axonais com menos sinapses e toleram concentrações maiores de halogenado, daí a dissociação descrita, que é assinatura de causa anestésica e não cirúrgica.&lt;/p&gt;&lt;p&gt;A conduta correta é remover a causa: converter para anestesia venosa total com propofol e remifentanil, técnica de referência quando se monitorizam potenciais motores, e evitar bloqueio neuromuscular após a intubação. Só depois de restaurado o sinal faz sentido interpretar alterações como lesão medular.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) abrir mão dos potenciais motores é perder justamente a via anterior, a mais suscetível a lesão pela instrumentação e por isquemia. (C) elevar a pressão é útil quando a perda é isquêmica, mas manter o halogenado alto e o bloqueio profundo perpetua a causa real. (D) propofol em bolus deprime ainda mais a resposta de forma transitória, e manter o sevoflurano não resolve o problema identificado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A monitorização medular precisa acompanhar a anatomia vascular. A artéria espinhal anterior, alimentada de forma crítica pela artéria radicular magna de Adamkiewicz, irriga os dois terços anteriores da medula, onde estão o trato corticoespinhal e a substância cinzenta do corno anterior. As duas artérias espinhais posteriores irrigam o terço posterior, que contém os fascículos grácil e cuneiforme.&lt;/p&gt;&lt;p&gt;Os potenciais evocados somatossensitivos ascendem pelas colunas posteriores, território das artérias espinhais posteriores. Os potenciais evocados motores descem pelo trato corticoespinhal, território da artéria espinhal anterior. Consequentemente, na síndrome da artéria espinhal anterior — quadro típico da cirurgia aórtica, com paraplegia e preservação de propriocepção e sensibilidade vibratória — os potenciais somatossensitivos podem permanecer inalterados enquanto a lesão motora já se instalou. Por isso a recomendação é monitorizar as duas modalidades em cirurgia toracoabdominal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as vias: o trato corticoespinhal é avaliado pelos potenciais motores, não pelos somatossensitivos. (B) atribui aos somatossensitivos a origem e a dependência vascular que pertencem aos potenciais motores. (C) o oposto é verdadeiro: por dependerem de sinapses e da substância cinzenta anterior, os potenciais motores alteram-se mais precocemente na isquemia, com latência de minutos, enquanto os somatossensitivos podem demorar ou nem se modificar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A monitorização medular precisa acompanhar a anatomia vascular. A artéria espinhal anterior, alimentada de forma crítica pela artéria radicular magna de Adamkiewicz, irriga os dois terços anteriores da medula, onde estão o trato corticoespinhal e a substância cinzenta do corno anterior. As duas artérias espinhais posteriores irrigam o terço posterior, que contém os fascículos grácil e cuneiforme.&lt;/p&gt;&lt;p&gt;Os potenciais evocados somatossensitivos ascendem pelas colunas posteriores, território das artérias espinhais posteriores. Os potenciais evocados motores descem pelo trato corticoespinhal, território da artéria espinhal anterior. Consequentemente, na síndrome da artéria espinhal anterior (quadro típico da cirurgia aórtica, com paraplegia e preservação de propriocepção e sensibilidade vibratória), os potenciais somatossensitivos podem permanecer inalterados enquanto a lesão motora já se instalou. Por isso a recomendação é monitorizar as duas modalidades em cirurgia toracoabdominal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as vias: o trato corticoespinhal é avaliado pelos potenciais motores, não pelos somatossensitivos. (B) atribui aos somatossensitivos a origem e a dependência vascular que pertencem aos potenciais motores. (C) o oposto é verdadeiro: por dependerem de sinapses e da substância cinzenta anterior, os potenciais motores alteram-se mais precocemente na isquemia, com latência de minutos, enquanto os somatossensitivos podem demorar ou nem se modificar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A espectrofotometria por infravermelho depende de que a molécula tenha momento de dipolo variável durante a vibração, condição atendida por moléculas com pelo menos dois átomos diferentes. Por isso CO&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt;O, vapor d'água e todos os agentes halogenados são mensuráveis por essa técnica.&lt;/p&gt;&lt;p&gt;Moléculas diatômicas homonucleares — O&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt; — e gases monoatômicos, como hélio, argônio e xenônio, não têm dipolo e são invisíveis ao infravermelho. Daí a necessidade de um princípio distinto para o oxigênio: célula galvânica (eletroquímica, consumível, de resposta lenta, tipicamente instalada no ramo inspiratório), célula polarográfica ou sensor paramagnético, este último rápido o bastante para leitura respiração a respiração.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a célula galvânica é justamente o sensor mais lento, com constante de tempo de dezenas de segundos, imprestável para análise batimento a batimento; ela também se esgota, o que explica a troca periódica descrita no enunciado. (B) o nitrogênio não é detectável por infravermelho pelo mesmo motivo que o oxigênio; sua medida exigiria espectrometria de massa ou Raman. (D) há sobreposição parcial de bandas e, sobretudo, alargamento por colisão entre N&lt;sub&gt;2&lt;/sub&gt;O e CO&lt;sub&gt;2&lt;/sub&gt;, fenômeno que superestima o CO&lt;sub&gt;2&lt;/sub&gt; e que os monitores modernos precisam compensar por algoritmo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A espectrofotometria por infravermelho depende de que a molécula tenha momento de dipolo variável durante a vibração, condição atendida por moléculas com pelo menos dois átomos diferentes. Por isso CO&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt;O, vapor d'água e todos os agentes halogenados são mensuráveis por essa técnica.&lt;/p&gt;&lt;p&gt;Moléculas diatômicas homonucleares (O&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt;) e gases monoatômicos, como hélio, argônio e xenônio, não têm dipolo e são invisíveis ao infravermelho. Daí a necessidade de um princípio distinto para o oxigênio: célula galvânica (eletroquímica, consumível, de resposta lenta, tipicamente instalada no ramo inspiratório), célula polarográfica ou sensor paramagnético, este último rápido o bastante para leitura respiração a respiração.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a célula galvânica é justamente o sensor mais lento, com constante de tempo de dezenas de segundos, imprestável para análise batimento a batimento; ela também se esgota, o que explica a troca periódica descrita no enunciado. (B) o nitrogênio não é detectável por infravermelho pelo mesmo motivo que o oxigênio; sua medida exigiria espectrometria de massa ou Raman. (D) há sobreposição parcial de bandas e, sobretudo, alargamento por colisão entre N&lt;sub&gt;2&lt;/sub&gt;O e CO&lt;sub&gt;2&lt;/sub&gt;, fenômeno que superestima o CO&lt;sub&gt;2&lt;/sub&gt; e que os monitores modernos precisam compensar por algoritmo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pressão de oclusão da artéria pulmonar só estima a pressão de átrio esquerdo quando existe uma coluna de sangue contínua e sem interrupção entre a ponta do cateter e o átrio — condição da zona 3 de West, em que a pressão venosa pulmonar supera a pressão alveolar.&lt;/p&gt;&lt;p&gt;Com PEEP elevada, a pressão alveolar pode ultrapassar a pressão venosa e mesmo a arterial pulmonar em regiões não dependentes, convertendo-as em zona 1 ou 2. Nessa situação o capilar é comprimido e o número exibido passa a refletir pressão alveolar transmitida, superestimando a pré-carga esquerda. O achado clássico é exatamente o descrito: pressão de oclusão alta com ventrículo pequeno e sinais de responsividade a volume.&lt;/p&gt;&lt;p&gt;Outras causas de superestimativa incluem estenose mitral, mixoma, pressão intratorácica elevada e complacência ventricular reduzida, situação em que uma pressão alta convive com volume normal ou baixo. Por isso a pressão de oclusão foi progressivamente substituída por índices dinâmicos e pela ecocardiografia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a sedação não altera de forma aguda a complacência ventricular, e o erro descrito é de superestimativa, não de subestimativa. (B) descartar o exame ecocardiográfico coerente com todos os demais sinais clínicos é o erro conceitual que a questão pretende expor. (C) a pressão positiva eleva, e não reduz, a pressão de oclusão medida, por transmissão da pressão intratorácica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pressão de oclusão da artéria pulmonar só estima a pressão de átrio esquerdo quando existe uma coluna de sangue contínua e sem interrupção entre a ponta do cateter e o átrio, condição da zona 3 de West, em que a pressão venosa pulmonar supera a pressão alveolar.&lt;/p&gt;&lt;p&gt;Com PEEP elevada, a pressão alveolar pode ultrapassar a pressão venosa e mesmo a arterial pulmonar em regiões não dependentes, convertendo-as em zona 1 ou 2. Nessa situação o capilar é comprimido e o número exibido passa a refletir pressão alveolar transmitida, superestimando a pré-carga esquerda. O achado clássico é exatamente o descrito: pressão de oclusão alta com ventrículo pequeno e sinais de responsividade a volume.&lt;/p&gt;&lt;p&gt;Outras causas de superestimativa incluem estenose mitral, mixoma, pressão intratorácica elevada e complacência ventricular reduzida, situação em que uma pressão alta convive com volume normal ou baixo. Por isso a pressão de oclusão foi progressivamente substituída por índices dinâmicos e pela ecocardiografia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a sedação não altera de forma aguda a complacência ventricular, e o erro descrito é de superestimativa, não de subestimativa. (B) descartar o exame ecocardiográfico coerente com todos os demais sinais clínicos é o erro conceitual que a questão pretende expor. (C) a pressão positiva eleva, e não reduz, a pressão de oclusão medida, por transmissão da pressão intratorácica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O monóxido de carbono tem afinidade pela hemoglobina cerca de 200 a 250 vezes maior que a do oxigênio, forma carboxi-hemoglobina e desloca a curva de dissociação para a esquerda, comprometendo tanto o transporte quanto a liberação tecidual de oxigênio. O resultado é hipóxia tecidual com acidose láctica, exatamente como no caso.&lt;/p&gt;&lt;p&gt;O oxímetro de pulso convencional não enxerga esse problema: a carboxi-hemoglobina tem absorbância em 660 nm próxima à da oxi-hemoglobina e absorve pouco em 940 nm, de modo que o aparelho a contabiliza como sangue oxigenado e exibe SpO2 falsamente normal, próxima de 100%. A PaO2 também permanece normal ou elevada, porque mede oxigênio dissolvido, que não é afetado pelo CO — e a saturação calculada pelos gasômetros deriva da PaO2, herdando o mesmo erro. Apenas a co-oximetria, que usa múltiplos comprimentos de onda, quantifica a carboxi-hemoglobina. O tratamento é oxigênio a 100%, com oxigenoterapia hiperbárica considerada nos casos graves.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aceitar a SpO2 como verdadeira diante de acidose láctica e história de incêndio em ambiente fechado é o erro que mais retarda o diagnóstico. (C) a PaO2 normal ou alta é esperada na intoxicação e não a exclui de modo algum. (D) a saturação calculada não distingue carboxi-hemoglobina de oxi-hemoglobina e não serve para quantificá-la.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O monóxido de carbono tem afinidade pela hemoglobina cerca de 200 a 250 vezes maior que a do oxigênio, forma carboxi-hemoglobina e desloca a curva de dissociação para a esquerda, comprometendo tanto o transporte quanto a liberação tecidual de oxigênio. O resultado é hipóxia tecidual com acidose láctica, exatamente como no caso.&lt;/p&gt;&lt;p&gt;O oxímetro de pulso convencional não enxerga esse problema: a carboxi-hemoglobina tem absorbância em 660 nm próxima à da oxi-hemoglobina e absorve pouco em 940 nm, de modo que o aparelho a contabiliza como sangue oxigenado e exibe SpO2 falsamente normal, próxima de 100%. A PaO2 também permanece normal ou elevada, porque mede oxigênio dissolvido, que não é afetado pelo CO; a saturação calculada pelos gasômetros deriva da PaO2, herdando o mesmo erro. Apenas a co-oximetria, que usa múltiplos comprimentos de onda, quantifica a carboxi-hemoglobina. O tratamento é oxigênio a 100%, com oxigenoterapia hiperbárica considerada nos casos graves.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aceitar a SpO2 como verdadeira diante de acidose láctica e história de incêndio em ambiente fechado é o erro que mais retarda o diagnóstico. (C) a PaO2 normal ou alta é esperada na intoxicação e não a exclui de modo algum. (D) a saturação calculada não distingue carboxi-hemoglobina de oxi-hemoglobina e não serve para quantificá-la.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escolha de derivações no intraoperatório segue a anatomia coronariana e o rendimento diagnóstico já bem estabelecido:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;DII, DIII e aVF:&lt;/strong&gt; parede inferior, território da coronária direita; DII é também a melhor derivação para análise da onda P e do ritmo, pelo alinhamento com o eixo elétrico;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DI e aVL:&lt;/strong&gt; parede lateral alta, território da artéria circunflexa;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;V3 a V5:&lt;/strong&gt; parede anterior e anterolateral, território da artéria descendente anterior;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;V1 e V2:&lt;/strong&gt; septo, com sensibilidade baixa para isquemia intraoperatória.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Isoladamente, V5 detecta cerca de três quartos dos episódios isquêmicos intraoperatórios. A combinação de DII com V5 eleva a detecção para próximo de 80 a 90% e reúne, num monitor de dois canais, vigilância de ritmo e cobertura do território mais volumoso do ventrículo esquerdo — a escolha correta para um paciente com lesão proximal de descendente anterior.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) DII com DIII duplica a informação do mesmo território inferior e ignora justamente a parede em risco. (C) aVR e V1 têm baixo rendimento para isquemia subendocárdica intraoperatória e não cobrem a parede anterolateral. (D) DI e aVL exploram a circunflexa, não a descendente anterior, e deixam o monitor sem uma derivação adequada para análise do ritmo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escolha de derivações no intraoperatório segue a anatomia coronariana e o rendimento diagnóstico já bem estabelecido:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;DII, DIII e aVF:&lt;/strong&gt; parede inferior, território da coronária direita; DII é também a melhor derivação para análise da onda P e do ritmo, pelo alinhamento com o eixo elétrico;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;DI e aVL:&lt;/strong&gt; parede lateral alta, território da artéria circunflexa;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;V3 a V5:&lt;/strong&gt; parede anterior e anterolateral, território da artéria descendente anterior;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;V1 e V2:&lt;/strong&gt; septo, com sensibilidade baixa para isquemia intraoperatória.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Isoladamente, V5 detecta cerca de três quartos dos episódios isquêmicos intraoperatórios. A combinação de DII com V5 eleva a detecção para próximo de 80 a 90% e reúne, num monitor de dois canais, vigilância de ritmo e cobertura do território mais volumoso do ventrículo esquerdo, a escolha correta para um paciente com lesão proximal de descendente anterior.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) DII com DIII duplica a informação do mesmo território inferior e ignora justamente a parede em risco. (C) aVR e V1 têm baixo rendimento para isquemia subendocárdica intraoperatória e não cobrem a parede anterolateral. (D) DI e aVL exploram a circunflexa, não a descendente anterior, e deixam o monitor sem uma derivação adequada para análise do ritmo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A saturação venosa mista, colhida na artéria pulmonar, é o resultado global do balanço entre oferta e consumo de oxigênio. Seu valor normal fica entre 65 e 75%; a saturação venosa central, colhida em veia cava superior, costuma ser 5 a 8 pontos mais alta no choque. Uma SvO2 baixa aponta para queda do débito cardíaco, anemia, hipoxemia ou aumento do consumo.&lt;/p&gt;&lt;p&gt;Valores anormalmente altos, porém, não significam bem-estar tecidual. Na sepse, o desvio microcirculatório do fluxo, com abertura de shunts e heterogeneidade capilar, somado à disfunção mitocondrial, impede que a célula extraia o oxigênio ofertado. O sangue retorna às câmaras direitas ainda saturado enquanto o tecido permanece em dívida — situação evidenciada pelo lactato de 5,2 mmol/L, pelo enchimento capilar lentificado e pela oligúria. As mesmas leituras falsamente tranquilizadoras aparecem na intoxicação por cianeto, nos shunts arteriovenosos e na hipotermia profunda.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) interpretar a SvO2 alta como adequação tecidual e desescalonar o suporte ignora todos os marcadores de hipoperfusão presentes. (B) a aspiração excessivamente rápida de fato arterializa a amostra, mas atribuir a esse artefato um quadro clínico inteiramente coerente é implausível. (D) não há hipotermia no caso, e ela não é mecanismo habitual da sepse abdominal, que cursa mais frequentemente com febre e consumo aumentado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A saturação venosa mista, colhida na artéria pulmonar, é o resultado global do balanço entre oferta e consumo de oxigênio. Seu valor normal fica entre 65 e 75%; a saturação venosa central, colhida em veia cava superior, costuma ser 5 a 8 pontos mais alta no choque. Uma SvO2 baixa aponta para queda do débito cardíaco, anemia, hipoxemia ou aumento do consumo.&lt;/p&gt;&lt;p&gt;Valores anormalmente altos, porém, não significam bem-estar tecidual. Na sepse, o desvio microcirculatório do fluxo, com abertura de shunts e heterogeneidade capilar, somado à disfunção mitocondrial, impede que a célula extraia o oxigênio ofertado. O sangue retorna às câmaras direitas ainda saturado enquanto o tecido permanece em dívida, situação evidenciada pelo lactato de 5,2 mmol/L, pelo enchimento capilar lentificado e pela oligúria. As mesmas leituras falsamente tranquilizadoras aparecem na intoxicação por cianeto, nos shunts arteriovenosos e na hipotermia profunda.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) interpretar a SvO2 alta como adequação tecidual e desescalonar o suporte ignora todos os marcadores de hipoperfusão presentes. (B) a aspiração excessivamente rápida de fato arterializa a amostra, mas atribuir a esse artefato um quadro clínico inteiramente coerente é implausível. (D) não há hipotermia no caso, e ela não é mecanismo habitual da sepse abdominal, que cursa mais frequentemente com febre e consumo aumentado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O sistema elétrico isolado separa a rede da sala do aterramento por meio de um transformador de isolamento. Com isso, o contato acidental de uma pessoa com um dos condutores não fecha circuito para a terra e não produz choque. O monitor de isolamento de linha vigia continuamente essa condição e mede a corrente que fluiria caso houvesse um segundo defeito de isolamento.&lt;/p&gt;&lt;p&gt;Quando o alarme dispara, o que ele informa é que a soma das correntes de fuga dos equipamentos conectados ultrapassou o limiar do aparelho, tipicamente ajustado entre 2 e 5 mA. Isso significa perda de &lt;em&gt;redundância&lt;/em&gt;, não eletrocussão em curso: o sistema ainda protege, mas está a uma falha de deixar de proteger. A conduta é remover o último equipamento conectado; se o alarme cessar, o defeito estava nele. Se o alarme persistir, retiram-se sequencialmente os demais aparelhos não essenciais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o alarme é preditivo e não indica corrente circulando pelo paciente; desligar tudo indiscriminadamente pode interromper suporte vital sem necessidade. (C) 10 microampères é o limite de fuga admitido para equipamentos com contato elétrico direto com o coração, e o monitor de isolamento não opera nessa ordem de grandeza — ele trabalha em miliampères. (D) o sistema continua funcionando; interromper a cirurgia é desproporcional e não é a recomendação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O sistema elétrico isolado separa a rede da sala do aterramento por meio de um transformador de isolamento. Com isso, o contato acidental de uma pessoa com um dos condutores não fecha circuito para a terra e não produz choque. O monitor de isolamento de linha vigia continuamente essa condição e mede a corrente que fluiria caso houvesse um segundo defeito de isolamento.&lt;/p&gt;&lt;p&gt;Quando o alarme dispara, o que ele informa é que a soma das correntes de fuga dos equipamentos conectados ultrapassou o limiar do aparelho, tipicamente ajustado entre 2 e 5 mA. Isso significa perda de &lt;em&gt;redundância&lt;/em&gt;, não eletrocussão em curso: o sistema ainda protege, mas está a uma falha de deixar de proteger. A conduta é remover o último equipamento conectado; se o alarme cessar, o defeito estava nele. Se o alarme persistir, retiram-se sequencialmente os demais aparelhos não essenciais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o alarme é preditivo e não indica corrente circulando pelo paciente; desligar tudo indiscriminadamente pode interromper suporte vital sem necessidade. (C) 10 microampères é o limite de fuga admitido para equipamentos com contato elétrico direto com o coração, e o monitor de isolamento não opera nessa ordem de grandeza: ele trabalha em miliampères. (D) o sistema continua funcionando; interromper a cirurgia é desproporcional e não é a recomendação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No rotâmetro, a queda de pressão através do flutuador é constante — ela apenas equilibra o peso do flutuador — e o que varia é a área do espaço anular, que aumenta à medida que o flutuador sobe pelo tubo cônico. Daí a denominação de dispositivo de pressão constante e orifício variável.&lt;/p&gt;&lt;p&gt;A física do gás muda ao longo da escala. Na base do tubo o ânulo é muito estreito em relação ao seu comprimento e se comporta como um tubo longo e fino: o regime é laminar e a lei de Poiseuille se aplica, de modo que a resistência depende da &lt;strong&gt;viscosidade&lt;/strong&gt;. No alto do tubo o ânulo é largo e curto, comportando-se como um orifício: o regime torna-se turbulento e a variável determinante passa a ser a &lt;strong&gt;densidade&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Como viscosidade e densidade diferem entre oxigênio, ar e óxido nitroso, cada tubo é calibrado individualmente para o seu gás, com o flutuador que lhe pertence, e não pode ser intercambiado. O mesmo raciocínio explica por que o hélio, de baixa densidade, é útil em obstruções de via aérea alta, onde o fluxo é turbulento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os regimes: em altos fluxos o comportamento é turbulento e dependente da densidade. (B) a densidade governa apenas a porção superior da escala, não toda ela. (C) descreve exatamente o oposto do princípio de funcionamento: a pressão é constante e a área é que varia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No rotâmetro, a queda de pressão através do flutuador é constante (ela apenas equilibra o peso do flutuador) e o que varia é a área do espaço anular, que aumenta à medida que o flutuador sobe pelo tubo cônico. Daí a denominação de dispositivo de pressão constante e orifício variável.&lt;/p&gt;&lt;p&gt;A física do gás muda ao longo da escala. Na base do tubo o ânulo é muito estreito em relação ao seu comprimento e se comporta como um tubo longo e fino: o regime é laminar e a lei de Poiseuille se aplica, de modo que a resistência depende da &lt;strong&gt;viscosidade&lt;/strong&gt;. No alto do tubo o ânulo é largo e curto, comportando-se como um orifício: o regime torna-se turbulento e a variável determinante passa a ser a &lt;strong&gt;densidade&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Como viscosidade e densidade diferem entre oxigênio, ar e óxido nitroso, cada tubo é calibrado individualmente para o seu gás, com o flutuador que lhe pertence, e não pode ser intercambiado. O mesmo raciocínio explica por que o hélio, de baixa densidade, é útil em obstruções de via aérea alta, onde o fluxo é turbulento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os regimes: em altos fluxos o comportamento é turbulento e dependente da densidade. (B) a densidade governa apenas a porção superior da escala, não toda ela. (C) descreve exatamente o oposto do princípio de funcionamento: a pressão é constante e a área é que varia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cal sodada é composta em cerca de 80% por hidróxido de cálcio, com pequenas frações de hidróxido de sódio e de potássio como ativadores, além de 14 a 19% de água — indispensável, porque a reação ocorre em fase aquosa. O CO&lt;sub&gt;2&lt;/sub&gt; dissolve-se na água formando ácido carbônico, que é neutralizado gerando carbonato de cálcio, água e &lt;strong&gt;calor&lt;/strong&gt;: a reação é exotérmica.&lt;/p&gt;&lt;p&gt;Fluxo de gás seco mantido por dias, especialmente em fins de semana, resseca o absorvente. Perdida a água, os hidróxidos fortes expostos degradam os anestésicos halogenados que contêm o grupo difluorometil — desflurano, enflurano e isoflurano — produzindo monóxido de carbono, com pico para o desflurano. A carboxi-hemoglobina resultante pode alcançar níveis tóxicos, e a oximetria de pulso não a detecta. A mesma dessecação favorece a formação de composto A com sevoflurano e já foi associada a reações exotérmicas extremas com absorventes contendo hidróxido de bário. A prevenção é desligar os fluxos ao fim do dia e trocar o absorvente quando houver suspeita de ressecamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o etil violeta muda de branco para roxo com a queda do pH, e não o contrário; além disso, a cor pode reverter com o repouso, tornando o indicador pouco confiável isoladamente. (C) o componente majoritário é o hidróxido de cálcio. (D) a reação é exotérmica; o aquecimento do canister é sinal de absorvente em atividade.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cal sodada é composta em cerca de 80% por hidróxido de cálcio, com pequenas frações de hidróxido de sódio e de potássio como ativadores, além de 14 a 19% de água, indispensável porque a reação ocorre em fase aquosa. O CO&lt;sub&gt;2&lt;/sub&gt; dissolve-se na água formando ácido carbônico, que é neutralizado gerando carbonato de cálcio, água e &lt;strong&gt;calor&lt;/strong&gt;: a reação é exotérmica.&lt;/p&gt;&lt;p&gt;Fluxo de gás seco mantido por dias, especialmente em fins de semana, resseca o absorvente. Perdida a água, os hidróxidos fortes expostos degradam os anestésicos halogenados que contêm o grupo difluorometil (desflurano, enflurano e isoflurano), produzindo monóxido de carbono, com pico para o desflurano. A carboxi-hemoglobina resultante pode alcançar níveis tóxicos, e a oximetria de pulso não a detecta. A mesma dessecação favorece a formação de composto A com sevoflurano e já foi associada a reações exotérmicas extremas com absorventes contendo hidróxido de bário. A prevenção é desligar os fluxos ao fim do dia e trocar o absorvente quando houver suspeita de ressecamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o etil violeta muda de branco para roxo com a queda do pH, e não o contrário; além disso, a cor pode reverter com o repouso, tornando o indicador pouco confiável isoladamente. (C) o componente majoritário é o hidróxido de cálcio. (D) a reação é exotérmica; o aquecimento do canister é sinal de absorvente em atividade.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os dispositivos proporcionadores atuam sobre um par específico de gases: oxigênio e óxido nitroso. Mecânica ou pneumaticamente, eles limitam a razão entre os dois de modo que a mistura resultante não caia abaixo de aproximadamente 25% de oxigênio. A válvula de corte, por sua vez, responde à queda de pressão na linha de oxigênio, interrompendo o óxido nitroso.&lt;/p&gt;&lt;p&gt;As lacunas dessa proteção são justamente aquilo que ela não vigia:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;administração de um terceiro gás — ar comprimido, hélio, dióxido de carbono — que dilui a mistura sem passar pelo proporcionador;&lt;/li&gt;&lt;li&gt;vazamentos a jusante do dispositivo, no vaporizador, no circuito ou no fole;&lt;/li&gt;&lt;li&gt;cruzamento de linhas na rede de parede, em que gás rotulado como oxigênio na verdade não é oxigênio;&lt;/li&gt;&lt;li&gt;administração de concentração excessiva de agente volátil, que também produz mistura hipóxica.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso o analisador de oxigênio no ramo inspiratório, com alarme de limite inferior, permanece a única salvaguarda que efetivamente mede o que o paciente recebe.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o proporcionador atua antes do circuito e nada sabe sobre o que ocorre depois dele. (C) a válvula de corte age apenas sobre o óxido nitroso; o vaporizador continua funcionando enquanto houver fluxo de gás carreador. (D) o cruzamento de linhas na fonte é exatamente o cenário clássico em que todos os dispositivos proporcionais falham, pois eles não identificam a natureza do gás que recebem.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os dispositivos proporcionadores atuam sobre um par específico de gases: oxigênio e óxido nitroso. Mecânica ou pneumaticamente, eles limitam a razão entre os dois de modo que a mistura resultante não caia abaixo de aproximadamente 25% de oxigênio. A válvula de corte, por sua vez, responde à queda de pressão na linha de oxigênio, interrompendo o óxido nitroso.&lt;/p&gt;&lt;p&gt;As lacunas dessa proteção são justamente aquilo que ela não vigia:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;administração de um terceiro gás (ar comprimido, hélio, dióxido de carbono) que dilui a mistura sem passar pelo proporcionador;&lt;/li&gt;&lt;li&gt;vazamentos a jusante do dispositivo, no vaporizador, no circuito ou no fole;&lt;/li&gt;&lt;li&gt;cruzamento de linhas na rede de parede, em que gás rotulado como oxigênio na verdade não é oxigênio;&lt;/li&gt;&lt;li&gt;administração de concentração excessiva de agente volátil, que também produz mistura hipóxica.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso o analisador de oxigênio no ramo inspiratório, com alarme de limite inferior, permanece a única salvaguarda que efetivamente mede o que o paciente recebe.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o proporcionador atua antes do circuito e nada sabe sobre o que ocorre depois dele. (C) a válvula de corte age apenas sobre o óxido nitroso; o vaporizador continua funcionando enquanto houver fluxo de gás carreador. (D) o cruzamento de linhas na fonte é exatamente o cenário clássico em que todos os dispositivos proporcionais falham, pois eles não identificam a natureza do gás que recebem.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O sistema de baixa pressão do aparelho de anestesia compreende tudo o que fica a jusante das válvulas de fluxo: tubos de fluxo, vaporizadores, coletor de mistura e a saída de gases frescos. É a região mais vulnerável do aparelho, porque reúne conexões, vedações de vaporizador e componentes de vidro.&lt;/p&gt;&lt;p&gt;O teste de pressão negativa cria vácuo nesse segmento com um bulbo de sucção. Se houver qualquer vazamento, o ar da atmosfera é aspirado para dentro e o bulbo reexpande. O critério é o inverso do enunciado em uma das alternativas: o bulbo deve &lt;strong&gt;permanecer colapsado&lt;/strong&gt; por pelo menos 10 segundos. A manobra precisa ser repetida com cada vaporizador ligado separadamente, porque a vedação interna só é exposta ao circuito quando o dial está aberto — vazamentos exclusivos do vaporizador aberto são um achado clássico e passam despercebidos se o teste for feito apenas com todos fechados.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o segmento de alta pressão fica entre o cilindro e o regulador e é avaliado por outra manobra, com o cilindro aberto e a rede desconectada, observando a queda do manômetro. (B) inverte o critério: a reexpansão do bulbo é justamente o sinal de vazamento. (C) o teste de pressão positiva do circuito respiratório, com a válvula fechada e o sistema pressurizado, avalia mangueiras, balão, cal sodada e conexões, e é complementar, não substituível pelo teste de pressão negativa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O sistema de baixa pressão do aparelho de anestesia compreende tudo o que fica a jusante das válvulas de fluxo: tubos de fluxo, vaporizadores, coletor de mistura e a saída de gases frescos. É a região mais vulnerável do aparelho, porque reúne conexões, vedações de vaporizador e componentes de vidro.&lt;/p&gt;&lt;p&gt;O teste de pressão negativa cria vácuo nesse segmento com um bulbo de sucção. Se houver qualquer vazamento, o ar da atmosfera é aspirado para dentro e o bulbo reexpande. O critério é o inverso do enunciado em uma das alternativas: o bulbo deve &lt;strong&gt;permanecer colapsado&lt;/strong&gt; por pelo menos 10 segundos. A manobra precisa ser repetida com cada vaporizador ligado separadamente, porque a vedação interna só é exposta ao circuito quando o dial está aberto; vazamentos exclusivos do vaporizador aberto são um achado clássico e passam despercebidos se o teste for feito apenas com todos fechados.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o segmento de alta pressão fica entre o cilindro e o regulador e é avaliado por outra manobra, com o cilindro aberto e a rede desconectada, observando a queda do manômetro. (B) inverte o critério: a reexpansão do bulbo é justamente o sinal de vazamento. (C) o teste de pressão positiva do circuito respiratório, com a válvula fechada e o sistema pressurizado, avalia mangueiras, balão, cal sodada e conexões, e é complementar, não substituível pelo teste de pressão negativa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O quadro descrito — hipoestesia no território do quarto e quinto dedos com fraqueza dos interósseos — corresponde à neuropatia ulnar, a lesão nervosa perioperatória mais frequentemente registrada. O nervo é vulnerável porque atravessa o túnel cubital, atrás do epicôndilo medial do úmero, com pouca proteção de partes moles. Homens, obesos e pacientes com estadia hospitalar prolongada concentram o risco.&lt;/p&gt;&lt;p&gt;A prevenção baseia-se na posição do antebraço e no grau de abdução:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;manter o antebraço em &lt;strong&gt;supinação&lt;/strong&gt; ou em posição neutra, com o polegar voltado para cima, o que afasta o epicôndilo medial da superfície de apoio;&lt;/li&gt;&lt;li&gt;limitar a abdução do braço a &lt;strong&gt;90 graus&lt;/strong&gt; em decúbito dorsal, reduzindo a tração do plexo braquial;&lt;/li&gt;&lt;li&gt;acolchoar o sulco do nervo ulnar e evitar flexão excessiva do cotovelo;&lt;/li&gt;&lt;li&gt;manter a cabeça alinhada e reavaliar a posição periodicamente em cirurgias longas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte a recomendação: é a pronação que rotaciona o epicôndilo medial contra a superfície de apoio e aumenta a compressão do nervo. (C) abdução acima de 90 graus traciona o plexo braquial e não se torna segura pelo simples acréscimo de acolchoamento. (D) o acolchoamento é necessário, mas não substitui a rotação correta do antebraço; a compressão persiste se o membro estiver pronado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O quadro descrito (hipoestesia no território do quarto e quinto dedos com fraqueza dos interósseos) corresponde à neuropatia ulnar, a lesão nervosa perioperatória mais frequentemente registrada. O nervo é vulnerável porque atravessa o túnel cubital, atrás do epicôndilo medial do úmero, com pouca proteção de partes moles. Homens, obesos e pacientes com estadia hospitalar prolongada concentram o risco.&lt;/p&gt;&lt;p&gt;A prevenção baseia-se na posição do antebraço e no grau de abdução:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;manter o antebraço em &lt;strong&gt;supinação&lt;/strong&gt; ou em posição neutra, com o polegar voltado para cima, o que afasta o epicôndilo medial da superfície de apoio;&lt;/li&gt;&lt;li&gt;limitar a abdução do braço a &lt;strong&gt;90 graus&lt;/strong&gt; em decúbito dorsal, reduzindo a tração do plexo braquial;&lt;/li&gt;&lt;li&gt;acolchoar o sulco do nervo ulnar e evitar flexão excessiva do cotovelo;&lt;/li&gt;&lt;li&gt;manter a cabeça alinhada e reavaliar a posição periodicamente em cirurgias longas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte a recomendação: é a pronação que rotaciona o epicôndilo medial contra a superfície de apoio e aumenta a compressão do nervo. (C) abdução acima de 90 graus traciona o plexo braquial e não se torna segura pelo simples acréscimo de acolchoamento. (D) o acolchoamento é necessário, mas não substitui a rotação correta do antebraço; a compressão persiste se o membro estiver pronado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Em qualquer posição não horizontal, a pressão medida vale apenas para o nível em que o transdutor foi zerado. Acima desse ponto, a pressão diminui pelo peso da coluna de sangue. A equivalência usada na prática é de aproximadamente &lt;strong&gt;1 mmHg para cada 1,25 cm de sangue&lt;/strong&gt;, derivada da densidade do sangue: 1 mmHg corresponde a 1,36 cm de água e o sangue tem densidade cerca de 6% maior.&lt;/p&gt;&lt;p&gt;Neste caso, 20 cm de desnível equivalem a cerca de 16 mmHg. A pressão arterial média encefálica é, portanto, próxima de 75 − 16 = 59 mmHg, ou seja, cerca de 60 mmHg — valor bastante inferior ao exibido no monitor e já no limite inferior da autorregulação em uma paciente que pode ter hipertensão crônica.&lt;/p&gt;&lt;p&gt;Daí a recomendação prática de, na posição sentada, zerar o transdutor no nível do meato acústico externo, de modo que o número exibido represente diretamente a perfusão cerebral. A mesma coluna hidrostática explica o risco de embolia gasosa venosa, pois a pressão nos seios durais torna-se subatmosférica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) ignora o gradiente hidrostático, erro que pode levar a hipoperfusão cerebral silenciosa. (B) usa um fator de correção subestimado, de 1 mmHg a cada 3 cm, que reduz artificialmente a magnitude do problema. (D) superestima a correção ao adotar 1,5 mmHg por centímetro, quase o dobro do valor real.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Em qualquer posição não horizontal, a pressão medida vale apenas para o nível em que o transdutor foi zerado. Acima desse ponto, a pressão diminui pelo peso da coluna de sangue. A equivalência usada na prática é de aproximadamente &lt;strong&gt;1 mmHg para cada 1,25 cm de sangue&lt;/strong&gt;, derivada da densidade do sangue: 1 mmHg corresponde a 1,36 cm de água e o sangue tem densidade cerca de 6% maior.&lt;/p&gt;&lt;p&gt;Neste caso, 20 cm de desnível equivalem a cerca de 16 mmHg. A pressão arterial média encefálica é, portanto, próxima de 75 − 16 = 59 mmHg, ou seja, cerca de 60 mmHg, valor bastante inferior ao exibido no monitor e já no limite inferior da autorregulação em uma paciente que pode ter hipertensão crônica.&lt;/p&gt;&lt;p&gt;Daí a recomendação prática de, na posição sentada, zerar o transdutor no nível do meato acústico externo, de modo que o número exibido represente diretamente a perfusão cerebral. A mesma coluna hidrostática explica o risco de embolia gasosa venosa, pois a pressão nos seios durais torna-se subatmosférica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) ignora o gradiente hidrostático, erro que pode levar a hipoperfusão cerebral silenciosa. (B) usa um fator de correção subestimado, de 1 mmHg a cada 3 cm, que reduz artificialmente a magnitude do problema. (D) superestima a correção ao adotar 1,5 mmHg por centímetro, quase o dobro do valor real.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A perda visual perioperatória em cirurgia de coluna em prona tem como causa mais frequente a neuropatia óptica isquêmica, predominantemente na forma posterior. O segmento retrolaminar do nervo óptico é irrigado por um plexo pial de perfusão precária e situa-se em compartimento pouco complacente; edema e congestão venosa, favorecidos pela posição prona prolongada e pelo declive cefálico, elevam a pressão nesse compartimento e reduzem a perfusão.&lt;/p&gt;&lt;p&gt;Os fatores de risco reconhecidos são exatamente os do caso: duração superior a seis horas, perda sanguínea acima de um litro, reposição com predomínio de cristaloides, anemia, hipotensão e sexo masculino. O quadro é de perda visual bilateral, indolor, com reflexos pupilares deficientes e — na forma posterior — fundoscopia inicialmente normal, pois o edema de papila só aparece quando a lesão é anterior. O prognóstico é reservado e não há tratamento estabelecido, o que torna a prevenção essencial: cabeça em posição neutra e no mesmo nível ou acima do coração, evitar compressão ocular, controlar sangramento e considerar cirurgia estagiada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a oclusão da artéria central da retina é tipicamente unilateral, decorre de compressão direta do globo e cursa com mancha vermelho-cereja à fundoscopia. (C) a cegueira cortical cursa com reflexos pupilares normais, o que contraria o exame descrito. (D) o glaucoma agudo é doloroso, com olho hiperemiado, córnea edemaciada e pupila em midríase média fixa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A perda visual perioperatória em cirurgia de coluna em prona tem como causa mais frequente a neuropatia óptica isquêmica, predominantemente na forma posterior. O segmento retrolaminar do nervo óptico é irrigado por um plexo pial de perfusão precária e situa-se em compartimento pouco complacente; edema e congestão venosa, favorecidos pela posição prona prolongada e pelo declive cefálico, elevam a pressão nesse compartimento e reduzem a perfusão.&lt;/p&gt;&lt;p&gt;Os fatores de risco reconhecidos são exatamente os do caso: duração superior a seis horas, perda sanguínea acima de um litro, reposição com predomínio de cristaloides, anemia, hipotensão e sexo masculino. O quadro é de perda visual bilateral, indolor, com reflexos pupilares deficientes e, na forma posterior, fundoscopia inicialmente normal, pois o edema de papila só aparece quando a lesão é anterior. O prognóstico é reservado e não há tratamento estabelecido, o que torna a prevenção essencial: cabeça em posição neutra e no mesmo nível ou acima do coração, evitar compressão ocular, controlar sangramento e considerar cirurgia estagiada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a oclusão da artéria central da retina é tipicamente unilateral, decorre de compressão direta do globo e cursa com mancha vermelho-cereja à fundoscopia. (C) a cegueira cortical cursa com reflexos pupilares normais, o que contraria o exame descrito. (D) o glaucoma agudo é doloroso, com olho hiperemiado, córnea edemaciada e pupila em midríase média fixa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A segurança da raquianestesia depende de puncionar &lt;strong&gt;abaixo do cone medular&lt;/strong&gt;. No adulto, a medula termina em média entre a borda inferior de L1 e a borda superior de L2; no recém-nascido, o cone alcança L3, e por isso a punção neonatal é feita em L4-L5 ou mais caudal. O saco dural termina em &lt;strong&gt;S2&lt;/strong&gt; no adulto e em torno de S3 no lactente, o que explica a via caudal como acesso peridural em crianças pequenas.&lt;/p&gt;&lt;p&gt;A linha intercristal (linha de Tuffier) une as cristas ilíacas e cruza o corpo de L4 ou o interespaço L4-L5. O ponto crítico é que a palpação é imprecisa: em obesos, gestantes e idosos, o nível estimado costuma ser &lt;strong&gt;um a dois espaços mais alto&lt;/strong&gt; que o real, erro quase sempre no sentido cefálico. Daí a recomendação de escolher L3-L4 ou mais caudal e de usar ultrassonografia quando as referências são ruins.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a linha intercristal marca L4 ou L4-L5, não L2-L3, e sua imprecisão vai justamente contra a segurança alegada; (B) o cone termina em L1-L2, e são as punções altas, não as baixas, que ameaçam a medula; (D) o saco dural do adulto termina em S2 — se terminasse em L5-S1, a punção lombar baixa seria impossível.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A segurança da raquianestesia depende de puncionar &lt;strong&gt;abaixo do cone medular&lt;/strong&gt;. No adulto, a medula termina em média entre a borda inferior de L1 e a borda superior de L2; no recém-nascido, o cone alcança L3, e por isso a punção neonatal é feita em L4-L5 ou mais caudal. O saco dural termina em &lt;strong&gt;S2&lt;/strong&gt; no adulto e em torno de S3 no lactente, o que explica a via caudal como acesso peridural em crianças pequenas.&lt;/p&gt;&lt;p&gt;A linha intercristal (linha de Tuffier) une as cristas ilíacas e cruza o corpo de L4 ou o interespaço L4-L5. O ponto crítico é que a palpação é imprecisa: em obesos, gestantes e idosos, o nível estimado costuma ser &lt;strong&gt;um a dois espaços mais alto&lt;/strong&gt; que o real, erro quase sempre no sentido cefálico. Daí a recomendação de escolher L3-L4 ou mais caudal e de usar ultrassonografia quando as referências são ruins.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a linha intercristal marca L4 ou L4-L5, não L2-L3, e sua imprecisão vai justamente contra a segurança alegada; (B) o cone termina em L1-L2, e são as punções altas, não as baixas, que ameaçam a medula; (D) o saco dural do adulto termina em S2; se terminasse em L5-S1, a punção lombar baixa seria impossível.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipotensão da raquianestesia para cesariana resulta do &lt;strong&gt;bloqueio simpático&lt;/strong&gt; extenso (nível sensitivo em torno de T4-T6), com queda da resistência vascular sistêmica e do retorno venoso, agravada pela compressão aortocava. O tratamento lógico restaura o tônus vascular perdido, e não o inotropismo.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;fenilefrina&lt;/strong&gt;, agonista alfa-1 puro, é o vasopressor de primeira linha nessa situação. Comparada à efedrina, associa-se a menor acidose fetal: a efedrina atravessa a placenta com facilidade e estimula o metabolismo fetal por via beta-adrenérgica, reduzindo o pH da artéria umbilical. A bradicardia reflexa é o efeito adverso esperado da fenilefrina e é tolerada enquanto a pressão se mantém; se houver bradicardia com hipotensão, a noradrenalina em doses baixas é alternativa razoável. Manter a pressão próxima ao valor basal (não apenas acima de 80% dele) reduz também náusea e vômito intraoperatórios.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a evidência — é a efedrina que se associa a pior perfil ácido-base fetal; (C) o reflexo de Bezold-Jarisch pode contribuir para bradicardia em bloqueios altos, mas o mecanismo dominante é a vasoplegia, e a paciente está taquicárdica; (D) a dopamina é de titulação lenta, arritmogênica e sem qualquer vantagem obstétrica, não sendo escolha para hipotensão aguda por simpatectomia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipotensão da raquianestesia para cesariana resulta do &lt;strong&gt;bloqueio simpático&lt;/strong&gt; extenso (nível sensitivo em torno de T4-T6), com queda da resistência vascular sistêmica e do retorno venoso, agravada pela compressão aortocava. O tratamento lógico restaura o tônus vascular perdido, e não o inotropismo.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;fenilefrina&lt;/strong&gt;, agonista alfa-1 puro, é o vasopressor de primeira linha nessa situação. Comparada à efedrina, associa-se a menor acidose fetal: a efedrina atravessa a placenta com facilidade e estimula o metabolismo fetal por via beta-adrenérgica, reduzindo o pH da artéria umbilical. A bradicardia reflexa é o efeito adverso esperado da fenilefrina e é tolerada enquanto a pressão se mantém; se houver bradicardia com hipotensão, a noradrenalina em doses baixas é alternativa razoável. Manter a pressão próxima ao valor basal (não apenas acima de 80% dele) reduz também náusea e vômito intraoperatórios.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a evidência: é a efedrina que se associa a pior perfil ácido-base fetal; (C) o reflexo de Bezold-Jarisch pode contribuir para bradicardia em bloqueios altos, mas o mecanismo dominante é a vasoplegia, e a paciente está taquicárdica; (D) a dopamina é de titulação lenta, arritmogênica e sem qualquer vantagem obstétrica, não sendo escolha para hipotensão aguda por simpatectomia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipotensão pós-raquianestesia é tão previsível na gestante que a estratégia moderna deixou de ser reativa e passou a ser &lt;strong&gt;profilática&lt;/strong&gt;. A medida com maior tamanho de efeito é a &lt;strong&gt;infusão de vasopressor iniciada simultaneamente ao bloqueio&lt;/strong&gt;, tipicamente fenilefrina titulada pela pressão arterial, combinada a bolus de resgate. Isso ataca diretamente a causa — a perda de tônus vascular pela simpatectomia.&lt;/p&gt;&lt;p&gt;As medidas volêmicas são coadjuvantes. A pré-carga com cristaloide tem eficácia modesta, pois o líquido redistribui-se antes do bloqueio; a &lt;strong&gt;co-carga&lt;/strong&gt; (infusão rápida no momento da injeção) é superior à pré-carga com cristaloide, e o coloide tem desempenho intermediário. O deslocamento uterino para a esquerda continua obrigatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a pré-carga com cristaloide, mesmo em volumes generosos, reduz pouco a incidência de hipotensão e jamais dispensa vasopressor; (C) o Trendelenburg com solução hiperbárica favorece dispersão cefálica e bloqueio alto, com risco de comprometimento respiratório e bradicardia; (D) doses muito baixas de bupivacaína reduzem a repercussão hemodinâmica, mas aumentam falha de bloqueio e necessidade de complementação, não sendo estratégia confiável para cesariana. A prevenção eficaz combina vasopressor profilático, co-carga e posicionamento adequado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipotensão pós-raquianestesia é tão previsível na gestante que a estratégia moderna deixou de ser reativa e passou a ser &lt;strong&gt;profilática&lt;/strong&gt;. A medida com maior tamanho de efeito é a &lt;strong&gt;infusão de vasopressor iniciada simultaneamente ao bloqueio&lt;/strong&gt;, tipicamente fenilefrina titulada pela pressão arterial, combinada a bolus de resgate. Isso ataca diretamente a causa: a perda de tônus vascular pela simpatectomia.&lt;/p&gt;&lt;p&gt;As medidas volêmicas são coadjuvantes. A pré-carga com cristaloide tem eficácia modesta, pois o líquido redistribui-se antes do bloqueio; a &lt;strong&gt;co-carga&lt;/strong&gt; (infusão rápida no momento da injeção) é superior à pré-carga com cristaloide, e o coloide tem desempenho intermediário. O deslocamento uterino para a esquerda continua obrigatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a pré-carga com cristaloide, mesmo em volumes generosos, reduz pouco a incidência de hipotensão e jamais dispensa vasopressor; (C) o Trendelenburg com solução hiperbárica favorece dispersão cefálica e bloqueio alto, com risco de comprometimento respiratório e bradicardia; (D) doses muito baixas de bupivacaína reduzem a repercussão hemodinâmica, mas aumentam falha de bloqueio e necessidade de complementação, não sendo estratégia confiável para cesariana. A prevenção eficaz combina vasopressor profilático, co-carga e posicionamento adequado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A via &lt;strong&gt;paramediana&lt;/strong&gt; é a solução clássica quando a linha média é inacessível: idosos com ligamentos calcificados, espondilite anquilosante, escoliose, cifose acentuada ou pacientes que não conseguem fletir a coluna. Ela contorna os ligamentos supraespinhoso e interespinhoso, entrando diretamente pelo &lt;em&gt;ligamento amarelo&lt;/em&gt; após a agulha passar lateralmente à apófise espinhosa.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;técnica de Taylor&lt;/strong&gt; é uma paramediana específica dirigida ao interespaço &lt;strong&gt;L5-S1&lt;/strong&gt;, o maior espaço interlaminar da coluna e, por isso, o mais tolerante a distorções anatômicas. O ponto de punção fica cerca de 1 cm medial e 1 cm caudal à espinha ilíaca póstero-superior, e a agulha é dirigida em sentido medial e cefálico, com angulação em torno de 45 graus, até atravessar o ligamento amarelo e a dura-máter.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve uma via mediana convencional em nível errado — a técnica de Taylor é paramediana e usa L5-S1; (B) a vantagem da paramediana é exatamente &lt;em&gt;evitar&lt;/em&gt; os ligamentos supraespinhoso e interespinhoso, que são os calcificados no paciente descrito; (C) a distância lateral usual é de cerca de 1 a 1,5 cm da linha média, e a agulha precisa de angulação cefálica além da medial, não apenas caudal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A via &lt;strong&gt;paramediana&lt;/strong&gt; é a solução clássica quando a linha média é inacessível: idosos com ligamentos calcificados, espondilite anquilosante, escoliose, cifose acentuada ou pacientes que não conseguem fletir a coluna. Ela contorna os ligamentos supraespinhoso e interespinhoso, entrando diretamente pelo &lt;em&gt;ligamento amarelo&lt;/em&gt; após a agulha passar lateralmente à apófise espinhosa.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;técnica de Taylor&lt;/strong&gt; é uma paramediana específica dirigida ao interespaço &lt;strong&gt;L5-S1&lt;/strong&gt;, o maior espaço interlaminar da coluna e, por isso, o mais tolerante a distorções anatômicas. O ponto de punção fica cerca de 1 cm medial e 1 cm caudal à espinha ilíaca póstero-superior, e a agulha é dirigida em sentido medial e cefálico, com angulação em torno de 45 graus, até atravessar o ligamento amarelo e a dura-máter.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve uma via mediana convencional em nível errado: a técnica de Taylor é paramediana e usa L5-S1; (B) a vantagem da paramediana é exatamente &lt;em&gt;evitar&lt;/em&gt; os ligamentos supraespinhoso e interespinhoso, que são os calcificados no paciente descrito; (C) a distância lateral usual é de cerca de 1 a 1,5 cm da linha média, e a agulha precisa de angulação cefálica além da medial, não apenas caudal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os adjuvantes neuroaxiais têm perfis de efeito adverso bem distintos, e a escolha se faz justamente por esse perfil. A &lt;strong&gt;clonidina&lt;/strong&gt;, agonista alfa-2, prolonga os bloqueios sensitivo e motor por ação em receptores do corno dorsal, sem os efeitos típicos dos opioides: não causa prurido, não causa retenção urinária e não produz depressão respiratória tardia. Em contrapartida, potencializa a hipotensão e a bradicardia do bloqueio simpático e produz sedação dose-dependente, o que limita a dose em ambiente ambulatorial.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;adrenalina&lt;/strong&gt; prolonga o bloqueio por vasoconstrição local — reduzindo a absorção do anestésico — e por ação alfa-2 espinhal. Os &lt;strong&gt;opioides&lt;/strong&gt; neuroaxiais melhoram a analgesia, mas trazem prurido, náusea, retenção urinária e, no caso dos hidrofílicos como a morfina, depressão respiratória tardia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a morfina subaracnóidea prolonga a analgesia e não o bloqueio motor, e seus efeitos adversos característicos são prurido, náusea, retenção urinária e depressão respiratória, não sedação isolada; (C) a adrenalina prolonga o bloqueio e reduz a absorção sistêmica, exatamente o oposto do descrito; (D) a retenção urinária dos opioides decorre de &lt;em&gt;inibição&lt;/em&gt; do tônus do detrusor por ação em receptores da medula sacral, com resposta pobre a anticolinérgicos e boa resposta à naloxona em dose baixa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os adjuvantes neuroaxiais têm perfis de efeito adverso bem distintos, e a escolha se faz justamente por esse perfil. A &lt;strong&gt;clonidina&lt;/strong&gt;, agonista alfa-2, prolonga os bloqueios sensitivo e motor por ação em receptores do corno dorsal, sem os efeitos típicos dos opioides: não causa prurido, não causa retenção urinária e não produz depressão respiratória tardia. Em contrapartida, potencializa a hipotensão e a bradicardia do bloqueio simpático e produz sedação dose-dependente, o que limita a dose em ambiente ambulatorial.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;adrenalina&lt;/strong&gt; prolonga o bloqueio por vasoconstrição local, reduzindo a absorção do anestésico, e por ação alfa-2 espinhal. Os &lt;strong&gt;opioides&lt;/strong&gt; neuroaxiais melhoram a analgesia, mas trazem prurido, náusea, retenção urinária e, no caso dos hidrofílicos como a morfina, depressão respiratória tardia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a morfina subaracnóidea prolonga a analgesia e não o bloqueio motor, e seus efeitos adversos característicos são prurido, náusea, retenção urinária e depressão respiratória, não sedação isolada; (C) a adrenalina prolonga o bloqueio e reduz a absorção sistêmica, exatamente o oposto do descrito; (D) a retenção urinária dos opioides decorre de &lt;em&gt;inibição&lt;/em&gt; do tônus do detrusor por ação em receptores da medula sacral, com resposta pobre a anticolinérgicos e boa resposta à naloxona em dose baixa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A medula é irrigada por &lt;strong&gt;uma única artéria espinhal anterior&lt;/strong&gt;, que percorre a fissura mediana anterior e supre os &lt;strong&gt;dois terços anteriores&lt;/strong&gt; do cordão — incluindo os tratos corticoespinhais e espinotalâmicos e os cornos anteriores — e por &lt;strong&gt;duas artérias espinhais posteriores&lt;/strong&gt;, que suprem o terço posterior, essencialmente as colunas posteriores (propriocepção, tato discriminativo e sensibilidade vibratória).&lt;/p&gt;&lt;p&gt;Esse arranjo torna o território anterior o mais vulnerável, sobretudo na medula torácica média, região de circulação limítrofe. A principal artéria radicular de reforço, a &lt;strong&gt;artéria radicular magna (de Adamkiewicz)&lt;/strong&gt;, origina-se em geral entre T9 e T12, mais frequentemente à esquerda, e sua interrupção durante cirurgia da aorta toracoabdominal produz o quadro descrito: &lt;strong&gt;paralisia motora com perda de dor e temperatura e preservação da propriocepção&lt;/strong&gt; — a assinatura da síndrome da artéria espinhal anterior.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os territórios: as posteriores irrigam o terço posterior, e sua lesão isolada pouparia a função motora; (C) a artéria de Adamkiewicz tem origem toracolombar baixa, tipicamente T9-T12 e à esquerda, não cervical; (D) a anatomia é o oposto — há uma anterior e duas posteriores, e é justamente a artéria única que fragiliza a face anterior. Medidas protetoras incluem drenagem liquórica e manutenção da pressão de perfusão medular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A medula é irrigada por &lt;strong&gt;uma única artéria espinhal anterior&lt;/strong&gt;, que percorre a fissura mediana anterior e supre os &lt;strong&gt;dois terços anteriores&lt;/strong&gt; do cordão (incluindo os tratos corticoespinhais e espinotalâmicos e os cornos anteriores) e por &lt;strong&gt;duas artérias espinhais posteriores&lt;/strong&gt;, que suprem o terço posterior, essencialmente as colunas posteriores (propriocepção, tato discriminativo e sensibilidade vibratória).&lt;/p&gt;&lt;p&gt;Esse arranjo torna o território anterior o mais vulnerável, sobretudo na medula torácica média, região de circulação limítrofe. A principal artéria radicular de reforço, a &lt;strong&gt;artéria radicular magna (de Adamkiewicz)&lt;/strong&gt;, origina-se em geral entre T9 e T12, mais frequentemente à esquerda, e sua interrupção durante cirurgia da aorta toracoabdominal produz o quadro descrito: &lt;strong&gt;paralisia motora com perda de dor e temperatura e preservação da propriocepção&lt;/strong&gt;, a assinatura da síndrome da artéria espinhal anterior.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os territórios: as posteriores irrigam o terço posterior, e sua lesão isolada pouparia a função motora; (C) a artéria de Adamkiewicz tem origem toracolombar baixa, tipicamente T9-T12 e à esquerda, não cervical; (D) a anatomia é o oposto: há uma anterior e duas posteriores, e é justamente a artéria única que fragiliza a face anterior. Medidas protetoras incluem drenagem liquórica e manutenção da pressão de perfusão medular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A neuroestimulação funciona por uma relação inversa entre &lt;strong&gt;corrente mínima de estimulação e distância agulha-nervo&lt;/strong&gt;. Correntes de busca situam-se entre 1,0 e 1,5 mA; a injeção costuma ser feita quando a resposta motora persiste entre 0,3 e 0,5 mA. Resposta motora que se mantém com &lt;strong&gt;corrente igual ou inferior a 0,2 mA&lt;/strong&gt; (com pulso de 0,1 ms) é sinal de alarme: indica contato íntimo ou ponta intraneural, e a conduta é recuar a agulha até que a resposta só ocorra acima de 0,3 mA.&lt;/p&gt;&lt;p&gt;No caso descrito, três sinais convergem: corrente muito baixa, &lt;strong&gt;alta pressão de injeção&lt;/strong&gt; (pressões de abertura acima de cerca de 15 psi sugerem posição intrafascicular) e expansão do nervo à ultrassonografia, além da parestesia intensa. A injeção deve ser interrompida imediatamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica da estimulação — quanto menor a corrente necessária, mais próxima ou mais interna está a ponta; (B) a ausência de resposta motora não exclui posição intraneural, pois a estimulação tem baixa sensibilidade, especialmente em nervos com fascículos predominantemente sensitivos ou em pacientes com neuropatia; (D) o padrão de segurança são agulhas de &lt;em&gt;bisel curto&lt;/em&gt;, que oferecem maior resistência tátil às camadas fasciais e menor tendência a penetrar fascículos, ao contrário das de bisel longo, que cortam com facilidade.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A neuroestimulação funciona por uma relação inversa entre &lt;strong&gt;corrente mínima de estimulação e distância agulha-nervo&lt;/strong&gt;. Correntes de busca situam-se entre 1,0 e 1,5 mA; a injeção costuma ser feita quando a resposta motora persiste entre 0,3 e 0,5 mA. Resposta motora que se mantém com &lt;strong&gt;corrente igual ou inferior a 0,2 mA&lt;/strong&gt; (com pulso de 0,1 ms) é sinal de alarme: indica contato íntimo ou ponta intraneural, e a conduta é recuar a agulha até que a resposta só ocorra acima de 0,3 mA.&lt;/p&gt;&lt;p&gt;No caso descrito, três sinais convergem: corrente muito baixa, &lt;strong&gt;alta pressão de injeção&lt;/strong&gt; (pressões de abertura acima de cerca de 15 psi sugerem posição intrafascicular) e expansão do nervo à ultrassonografia, além da parestesia intensa. A injeção deve ser interrompida imediatamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica da estimulação: quanto menor a corrente necessária, mais próxima ou mais interna está a ponta; (B) a ausência de resposta motora não exclui posição intraneural, pois a estimulação tem baixa sensibilidade, especialmente em nervos com fascículos predominantemente sensitivos ou em pacientes com neuropatia; (D) o padrão de segurança são agulhas de &lt;em&gt;bisel curto&lt;/em&gt;, que oferecem maior resistência tátil às camadas fasciais e menor tendência a penetrar fascículos, ao contrário das de bisel longo, que cortam com facilidade.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;plexo lombar&lt;/strong&gt; forma-se no interior do músculo psoas maior a partir dos ramos ventrais de &lt;strong&gt;L1 a L4&lt;/strong&gt;, com contribuição variável de T12. Dele derivam seis nervos: &lt;em&gt;ílio-hipogástrico&lt;/em&gt; e &lt;em&gt;ilioinguinal&lt;/em&gt; (L1), &lt;em&gt;genitofemoral&lt;/em&gt; (L1-L2), &lt;em&gt;cutâneo femoral lateral&lt;/em&gt; (L2-L3), &lt;em&gt;femoral&lt;/em&gt; (L2-L4) e &lt;em&gt;obturatório&lt;/em&gt; (L2-L4).&lt;/p&gt;&lt;p&gt;Essa anatomia explica o rendimento clínico do bloqueio do compartimento do psoas: com uma única injeção alcançam-se femoral, obturatório e cutâneo femoral lateral — os três componentes que o bloqueio femoral isolado não cobre de forma confiável. Como a inervação do quadril e de toda a perna abaixo do joelho depende também do &lt;strong&gt;plexo sacral&lt;/strong&gt;, é frequente a necessidade de complementar com bloqueio do nervo ciático.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o nervo ciático deriva do plexo sacral (L4-S3), e não do lombar; além disso, o plexo lombar não se estende até S1; (C) o nervo cutâneo femoral posterior também é do plexo sacral (S1-S3) e inerva a face posterior da coxa, não a face medial nem a região patelar — esta última é território do femoral; (D) o nervo pudendo (S2-S4) pertence ao plexo sacral e não compartilha raízes com o obturatório.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;plexo lombar&lt;/strong&gt; forma-se no interior do músculo psoas maior a partir dos ramos ventrais de &lt;strong&gt;L1 a L4&lt;/strong&gt;, com contribuição variável de T12. Dele derivam seis nervos: &lt;em&gt;ílio-hipogástrico&lt;/em&gt; e &lt;em&gt;ilioinguinal&lt;/em&gt; (L1), &lt;em&gt;genitofemoral&lt;/em&gt; (L1-L2), &lt;em&gt;cutâneo femoral lateral&lt;/em&gt; (L2-L3), &lt;em&gt;femoral&lt;/em&gt; (L2-L4) e &lt;em&gt;obturatório&lt;/em&gt; (L2-L4).&lt;/p&gt;&lt;p&gt;Essa anatomia explica o rendimento clínico do bloqueio do compartimento do psoas: com uma única injeção alcançam-se femoral, obturatório e cutâneo femoral lateral, os três componentes que o bloqueio femoral isolado não cobre de forma confiável. Como a inervação do quadril e de toda a perna abaixo do joelho depende também do &lt;strong&gt;plexo sacral&lt;/strong&gt;, é frequente a necessidade de complementar com bloqueio do nervo ciático.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o nervo ciático deriva do plexo sacral (L4-S3), e não do lombar; além disso, o plexo lombar não se estende até S1; (C) o nervo cutâneo femoral posterior também é do plexo sacral (S1-S3) e inerva a face posterior da coxa, não a face medial nem a região patelar, que é território do femoral; (D) o nervo pudendo (S2-S4) pertence ao plexo sacral e não compartilha raízes com o obturatório.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O bloqueio intercostal interrompe a condução dos ramos ventrais dos nervos torácicos no &lt;strong&gt;sulco costal&lt;/strong&gt;, situado na &lt;strong&gt;borda inferior&lt;/strong&gt; de cada costela, onde as estruturas se dispõem de cima para baixo na ordem &lt;em&gt;veia, artéria e nervo&lt;/em&gt;. Como cada dermátomo tem sobreposição, bloqueiam-se ao menos dois níveis acima e dois abaixo da incisão ou do dreno.&lt;/p&gt;&lt;p&gt;Clinicamente, produz analgesia somática eficaz da parede torácica e traduz-se em melhora objetiva da mecânica ventilatória — aumento da capacidade vital e do pico de fluxo expiratório, com melhor tosse e menos atelectasia. O preço é farmacocinético: o espaço intercostal é altamente vascularizado, e esse bloqueio gera as &lt;strong&gt;maiores concentrações plasmáticas de anestésico local por unidade de dose&lt;/strong&gt; entre as técnicas regionais, superando peridural, plexo braquial e infiltração subcutânea. Daí a atenção à dose total quando se bloqueiam múltiplos níveis, o uso de adrenalina e a vigilância para toxicidade sistêmica. Pneumotórax é a outra complicação relevante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte o dado essencial — é o bloqueio com maior absorção sistêmica, não a menor; (B) a dor da toracotomia é predominantemente somática, de parede, e o bloqueio melhora sim os volumes pulmonares; (D) o feixe neurovascular corre na borda &lt;em&gt;inferior&lt;/em&gt; da costela, e a ordem descrita, embora correta, está atribuída ao local errado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O bloqueio intercostal interrompe a condução dos ramos ventrais dos nervos torácicos no &lt;strong&gt;sulco costal&lt;/strong&gt;, situado na &lt;strong&gt;borda inferior&lt;/strong&gt; de cada costela, onde as estruturas se dispõem de cima para baixo na ordem &lt;em&gt;veia, artéria e nervo&lt;/em&gt;. Como cada dermátomo tem sobreposição, bloqueiam-se ao menos dois níveis acima e dois abaixo da incisão ou do dreno.&lt;/p&gt;&lt;p&gt;Clinicamente, produz analgesia somática eficaz da parede torácica e traduz-se em melhora objetiva da mecânica ventilatória: aumento da capacidade vital e do pico de fluxo expiratório, com melhor tosse e menos atelectasia. O preço é farmacocinético: o espaço intercostal é altamente vascularizado, e esse bloqueio gera as &lt;strong&gt;maiores concentrações plasmáticas de anestésico local por unidade de dose&lt;/strong&gt; entre as técnicas regionais, superando peridural, plexo braquial e infiltração subcutânea. Daí a atenção à dose total quando se bloqueiam múltiplos níveis, o uso de adrenalina e a vigilância para toxicidade sistêmica. Pneumotórax é a outra complicação relevante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte o dado essencial: é o bloqueio com maior absorção sistêmica, não a menor; (B) a dor da toracotomia é predominantemente somática, de parede, e o bloqueio melhora sim os volumes pulmonares; (D) o feixe neurovascular corre na borda &lt;em&gt;inferior&lt;/em&gt; da costela, e a ordem descrita, embora correta, está atribuída ao local errado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;sintomas neurológicos transitórios&lt;/strong&gt; constituem quadro doloroso, e não neurológico deficitário. Caracterizam-se por dor ou disestesia em nádegas e região lombar baixa, com irradiação para as coxas, que surge após a &lt;strong&gt;recuperação completa&lt;/strong&gt; do bloqueio — tipicamente entre 6 e 36 horas — e se resolve espontaneamente em poucos dias, em geral até uma semana. O exame neurológico é normal e os exames de imagem e a eletroneuromiografia não mostram alterações.&lt;/p&gt;&lt;p&gt;O fator de risco farmacológico mais consistente é a &lt;strong&gt;lidocaína&lt;/strong&gt; por via subaracnóidea, com incidência muito superior à de bupivacaína ou prilocaína. Somam-se fatores posicionais e cirúrgicos: posição de litotomia, artroscopia de joelho e regime ambulatorial com deambulação precoce. O tratamento é sintomático, com anti-inflamatórios não esteroidais como primeira linha.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a síndrome da cauda equina cursa com déficit objetivo — anestesia em sela, retenção urinária, incontinência fecal e fraqueza — nenhum deles presente aqui; (C) o hematoma peridural produz dor lombar acompanhada de déficit motor e sensitivo progressivo, sendo emergência cirúrgica, e não dor isolada com exame normal; (D) a aracnoidite adesiva é rara, de instalação insidiosa e com déficits progressivos, incompatível com quadro puramente doloroso e autolimitado. Reconhecer os sintomas neurológicos transitórios evita investigação e intervenção desnecessárias.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;sintomas neurológicos transitórios&lt;/strong&gt; constituem quadro doloroso, e não neurológico deficitário. Caracterizam-se por dor ou disestesia em nádegas e região lombar baixa, com irradiação para as coxas, que surge após a &lt;strong&gt;recuperação completa&lt;/strong&gt; do bloqueio (tipicamente entre 6 e 36 horas) e se resolve espontaneamente em poucos dias, em geral até uma semana. O exame neurológico é normal e os exames de imagem e a eletroneuromiografia não mostram alterações.&lt;/p&gt;&lt;p&gt;O fator de risco farmacológico mais consistente é a &lt;strong&gt;lidocaína&lt;/strong&gt; por via subaracnóidea, com incidência muito superior à de bupivacaína ou prilocaína. Somam-se fatores posicionais e cirúrgicos: posição de litotomia, artroscopia de joelho e regime ambulatorial com deambulação precoce. O tratamento é sintomático, com anti-inflamatórios não esteroidais como primeira linha.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a síndrome da cauda equina cursa com déficit objetivo (anestesia em sela, retenção urinária, incontinência fecal e fraqueza), nenhum deles presente aqui; (C) o hematoma peridural produz dor lombar acompanhada de déficit motor e sensitivo progressivo, sendo emergência cirúrgica, e não dor isolada com exame normal; (D) a aracnoidite adesiva é rara, de instalação insidiosa e com déficits progressivos, incompatível com quadro puramente doloroso e autolimitado. Reconhecer os sintomas neurológicos transitórios evita investigação e intervenção desnecessárias.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A divisão entre &lt;strong&gt;ésteres&lt;/strong&gt; e &lt;strong&gt;amidas&lt;/strong&gt; depende da ligação entre o anel aromático e a cadeia intermediária e determina metabolismo e potencial alergênico. Os ésteres — procaína, cloroprocaína, tetracaína, benzocaína — são hidrolisados pela &lt;strong&gt;colinesterase plasmática&lt;/strong&gt;, produzindo &lt;strong&gt;ácido para-aminobenzoico (PABA)&lt;/strong&gt;, um hapteno bem reconhecido, o que faz da alergia a ésteres um fenômeno relativamente mais comum. As amidas — lidocaína, bupivacaína, ropivacaína, prilocaína — são metabolizadas no fígado por enzimas microssomais e raramente causam alergia verdadeira, com incidência estimada em menos de 1% das reações relatadas.&lt;/p&gt;&lt;p&gt;Boa parte das reações atribuídas a amidas decorre de outros fatores: absorção sistêmica com sintomas de toxicidade, resposta à adrenalina associada, reação vasovagal ou sensibilização ao &lt;strong&gt;metilparabeno&lt;/strong&gt;, conservante de frascos multidose cuja estrutura lembra a do PABA. Por isso a investigação deve incluir apresentações sem conservante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as classes: são os ésteres que sofrem hidrólise plasmática e geram PABA, enquanto as amidas têm depuração hepática; (C) o primeiro anestésico local usado clinicamente foi a &lt;strong&gt;cocaína&lt;/strong&gt;, empregada em anestesia tópica oftalmológica no fim do século XIX; a lidocaína foi a primeira amida, muito posterior; (D) alergia verdadeira a amidas é rara, e o teste cutâneo universal não se justifica, sendo reservado a histórias sugestivas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A divisão entre &lt;strong&gt;ésteres&lt;/strong&gt; e &lt;strong&gt;amidas&lt;/strong&gt; depende da ligação entre o anel aromático e a cadeia intermediária e determina metabolismo e potencial alergênico. Os ésteres (procaína, cloroprocaína, tetracaína, benzocaína) são hidrolisados pela &lt;strong&gt;colinesterase plasmática&lt;/strong&gt;, produzindo &lt;strong&gt;ácido para-aminobenzoico (PABA)&lt;/strong&gt;, um hapteno bem reconhecido, o que faz da alergia a ésteres um fenômeno relativamente mais comum. As amidas (lidocaína, bupivacaína, ropivacaína, prilocaína) são metabolizadas no fígado por enzimas microssomais e raramente causam alergia verdadeira, com incidência estimada em menos de 1% das reações relatadas.&lt;/p&gt;&lt;p&gt;Boa parte das reações atribuídas a amidas decorre de outros fatores: absorção sistêmica com sintomas de toxicidade, resposta à adrenalina associada, reação vasovagal ou sensibilização ao &lt;strong&gt;metilparabeno&lt;/strong&gt;, conservante de frascos multidose cuja estrutura lembra a do PABA. Por isso a investigação deve incluir apresentações sem conservante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as classes: são os ésteres que sofrem hidrólise plasmática e geram PABA, enquanto as amidas têm depuração hepática; (C) o primeiro anestésico local usado clinicamente foi a &lt;strong&gt;cocaína&lt;/strong&gt;, empregada em anestesia tópica oftalmológica no fim do século XIX; a lidocaína foi a primeira amida, muito posterior; (D) alergia verdadeira a amidas é rara, e o teste cutâneo universal não se justifica, sendo reservado a histórias sugestivas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Anestésicos locais são bases fracas, lipossolúveis, e atravessam a placenta por difusão passiva. A extensão dessa transferência é expressa pela &lt;strong&gt;razão feto/materna&lt;/strong&gt;, determinada sobretudo pela ligação a proteínas maternas: a bupivacaína, muito ligada à alfa-1-glicoproteína ácida, tem razão em torno de 0,2 a 0,4; a lidocaína, menos ligada, situa-se por volta de 0,5 a 0,7.&lt;/p&gt;&lt;p&gt;O ponto crítico no feto acidótico é o &lt;strong&gt;aprisionamento iônico&lt;/strong&gt;: em pH mais baixo, a fração ionizada da base fraca aumenta no sangue fetal, e a molécula ionizada não retorna à circulação materna, acumulando-se. Por isso, com acidose fetal, prefere-se a &lt;strong&gt;cloroprocaína 3%&lt;/strong&gt;: éster hidrolisado pela colinesterase plasmática com meia-vida de poucos minutos, ela praticamente desaparece do plasma materno antes de exposição fetal significativa, e ainda oferece o início de ação mais rápido entre as opções peridurais, vantagem decisiva na emergência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) alta ligação proteica reduz, mas não impede, a passagem placentária, e a bupivacaína 0,5% tem latência longa demais para emergência; (B) a lidocaína tem razão feto/materna em torno de 0,5 a 0,6 e é opção aceitável em muitas situações — o problema aqui é a acidose fetal, não uma razão próxima de 1,0; (C) recusar a extensão do bloqueio obrigaria a anestesia geral desnecessária, com todos os seus riscos de via aérea na gestante.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Anestésicos locais são bases fracas, lipossolúveis, e atravessam a placenta por difusão passiva. A extensão dessa transferência é expressa pela &lt;strong&gt;razão feto/materna&lt;/strong&gt;, determinada sobretudo pela ligação a proteínas maternas: a bupivacaína, muito ligada à alfa-1-glicoproteína ácida, tem razão em torno de 0,2 a 0,4; a lidocaína, menos ligada, situa-se por volta de 0,5 a 0,7.&lt;/p&gt;&lt;p&gt;O ponto crítico no feto acidótico é o &lt;strong&gt;aprisionamento iônico&lt;/strong&gt;: em pH mais baixo, a fração ionizada da base fraca aumenta no sangue fetal, e a molécula ionizada não retorna à circulação materna, acumulando-se. Por isso, com acidose fetal, prefere-se a &lt;strong&gt;cloroprocaína 3%&lt;/strong&gt;: éster hidrolisado pela colinesterase plasmática com meia-vida de poucos minutos, ela praticamente desaparece do plasma materno antes de exposição fetal significativa, e ainda oferece o início de ação mais rápido entre as opções peridurais, vantagem decisiva na emergência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) alta ligação proteica reduz, mas não impede, a passagem placentária, e a bupivacaína 0,5% tem latência longa demais para emergência; (B) a lidocaína tem razão feto/materna em torno de 0,5 a 0,6 e é opção aceitável em muitas situações. O problema aqui é a acidose fetal, não uma razão próxima de 1,0; (C) recusar a extensão do bloqueio obrigaria a anestesia geral desnecessária, com todos os seus riscos de via aérea na gestante.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A convulsão imediata após volume mínimo é a assinatura da &lt;strong&gt;injeção intra-arterial em artéria vertebral&lt;/strong&gt;, cujo trajeto é próximo ao acesso interescalênico e à região do gânglio estrelado. O fármaco alcança o tronco encefálico em fluxo retrógrado, praticamente sem diluição, de modo que menos de 1 a 2 mL bastam para produzir convulsão — diferentemente da toxicidade por absorção, que exige doses muito maiores e costuma ter pródromos.&lt;/p&gt;&lt;p&gt;O manejo segue o protocolo de &lt;strong&gt;toxicidade sistêmica por anestésicos locais&lt;/strong&gt;: interromper a injeção, pedir ajuda, garantir via aérea e ventilação com oxigênio a 100% (a hipóxia e a acidose agravam a cardiotoxicidade), controlar a convulsão preferencialmente com benzodiazepínico e iniciar &lt;strong&gt;emulsão lipídica a 20%&lt;/strong&gt; — bolus de 1,5 mL/kg de peso magro em 2 a 3 minutos, seguido de infusão de 0,25 mL/kg/min; o bolus pode ser repetido uma a duas vezes e a infusão dobrada se persistir instabilidade, respeitando limite aproximado de 12 mL/kg. Na parada, a adrenalina deve ser usada em doses reduzidas, de até cerca de 1 mcg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o volume pequeno reforça, e não afasta, a injeção arterial direta; (B) as doses estão erradas por larga margem e são potencialmente perigosas; (D) devem-se evitar anestésicos locais, incluindo lidocaína, além de vasopressina, betabloqueadores e bloqueadores de canal de cálcio nesse cenário.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A convulsão imediata após volume mínimo é a assinatura da &lt;strong&gt;injeção intra-arterial em artéria vertebral&lt;/strong&gt;, cujo trajeto é próximo ao acesso interescalênico e à região do gânglio estrelado. O fármaco alcança o tronco encefálico em fluxo retrógrado, praticamente sem diluição, de modo que menos de 1 a 2 mL bastam para produzir convulsão, diferentemente da toxicidade por absorção, que exige doses muito maiores e costuma ter pródromos.&lt;/p&gt;&lt;p&gt;O manejo segue o protocolo de &lt;strong&gt;toxicidade sistêmica por anestésicos locais&lt;/strong&gt;: interromper a injeção, pedir ajuda, garantir via aérea e ventilação com oxigênio a 100% (a hipóxia e a acidose agravam a cardiotoxicidade), controlar a convulsão preferencialmente com benzodiazepínico e iniciar &lt;strong&gt;emulsão lipídica a 20%&lt;/strong&gt; (bolus de 1,5 mL/kg de peso magro em 2 a 3 minutos, seguido de infusão de 0,25 mL/kg/min); o bolus pode ser repetido uma a duas vezes e a infusão dobrada se persistir instabilidade, respeitando limite aproximado de 12 mL/kg. Na parada, a adrenalina deve ser usada em doses reduzidas, de até cerca de 1 mcg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o volume pequeno reforça, e não afasta, a injeção arterial direta; (B) as doses estão erradas por larga margem e são potencialmente perigosas; (D) devem-se evitar anestésicos locais, incluindo lidocaína, além de vasopressina, betabloqueadores e bloqueadores de canal de cálcio nesse cenário.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;metemoglobinemia&lt;/strong&gt; ocorre quando o ferro da hemoglobina é oxidado do estado ferroso para o férrico, tornando-se incapaz de transportar oxigênio e deslocando a curva de dissociação para a esquerda. Entre os anestésicos locais, os agentes clássicos são a &lt;strong&gt;benzocaína tópica&lt;/strong&gt; e a &lt;strong&gt;prilocaína&lt;/strong&gt;, esta por meio do metabólito &lt;em&gt;ortotoluidina&lt;/em&gt;; creme de lidocaína com prilocaína em lactentes é outra situação de risco.&lt;/p&gt;&lt;p&gt;O quadro típico é o do caso: cianose que não melhora com oxigênio, &lt;strong&gt;saturação de pulso que tende a estacionar em torno de 85%&lt;/strong&gt; independentemente da FiO2 (porque a metemoglobina absorve luz de forma semelhante em ambos os comprimentos de onda do oxímetro), &lt;strong&gt;PaO2 arterial normal ou elevada&lt;/strong&gt; — pois a gasometria mede oxigênio dissolvido — e sangue de coloração achocolatada. A confirmação é feita por co-oximetria.&lt;/p&gt;&lt;p&gt;O tratamento é o &lt;strong&gt;azul de metileno, 1 a 2 mg/kg por via intravenosa em cerca de 5 minutos&lt;/strong&gt;, que reduz a metemoglobina pela via da NADPH-metemoglobina redutase. Em deficiência de G6PD ele é ineficaz e potencialmente hemolítico, cabendo ácido ascórbico ou exsanguineotransfusão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) no tromboembolismo a PaO2 estaria reduzida, não em 180 mmHg; (C) a intoxicação por monóxido de carbono cursa com oximetria falsamente &lt;em&gt;normal&lt;/em&gt; e não guarda relação com anestesia tópica; (D) shunt e atelectasia respondem ao recrutamento e à FiO2, o que não ocorreu aqui.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;metemoglobinemia&lt;/strong&gt; ocorre quando o ferro da hemoglobina é oxidado do estado ferroso para o férrico, tornando-se incapaz de transportar oxigênio e deslocando a curva de dissociação para a esquerda. Entre os anestésicos locais, os agentes clássicos são a &lt;strong&gt;benzocaína tópica&lt;/strong&gt; e a &lt;strong&gt;prilocaína&lt;/strong&gt;, esta por meio do metabólito &lt;em&gt;ortotoluidina&lt;/em&gt;; creme de lidocaína com prilocaína em lactentes é outra situação de risco.&lt;/p&gt;&lt;p&gt;O quadro típico é o do caso: cianose que não melhora com oxigênio, &lt;strong&gt;saturação de pulso que tende a estacionar em torno de 85%&lt;/strong&gt; independentemente da FiO2 (porque a metemoglobina absorve luz de forma semelhante em ambos os comprimentos de onda do oxímetro), &lt;strong&gt;PaO2 arterial normal ou elevada&lt;/strong&gt; (pois a gasometria mede oxigênio dissolvido) e sangue de coloração achocolatada. A confirmação é feita por co-oximetria.&lt;/p&gt;&lt;p&gt;O tratamento é o &lt;strong&gt;azul de metileno, 1 a 2 mg/kg por via intravenosa em cerca de 5 minutos&lt;/strong&gt;, que reduz a metemoglobina pela via da NADPH-metemoglobina redutase. Em deficiência de G6PD ele é ineficaz e potencialmente hemolítico, cabendo ácido ascórbico ou exsanguineotransfusão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) no tromboembolismo a PaO2 estaria reduzida, não em 180 mmHg; (C) a intoxicação por monóxido de carbono cursa com oximetria falsamente &lt;em&gt;normal&lt;/em&gt; e não guarda relação com anestesia tópica; (D) shunt e atelectasia respondem ao recrutamento e à FiO2, o que não ocorreu aqui.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O cálculo exige duas etapas. Primeiro, a dose máxima: a lidocaína admite cerca de &lt;strong&gt;4,5 mg/kg sem adrenalina&lt;/strong&gt; e &lt;strong&gt;7 mg/kg com adrenalina&lt;/strong&gt;, pois a vasoconstrição local reduz a velocidade de absorção sistêmica e, portanto, o pico plasmático. Para 70 kg: 7 x 70 = &lt;strong&gt;490 mg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Segundo, a conversão em volume: solução a 1,5% contém 15 mg/mL, de modo que 490 mg correspondem a aproximadamente &lt;strong&gt;32 a 33 mL&lt;/strong&gt;. Vale lembrar que a concentração 1:200.000 equivale a 5 mcg/mL de adrenalina, o que nesse volume totaliza cerca de 160 mcg — quantidade que por si só recomenda cautela em coronariopatas e hipertensos graves.&lt;/p&gt;&lt;p&gt;Duas ressalvas conceituais importam mais que o número. A dose máxima é referência de segurança, não meta a ser atingida; e ela deve ser ajustada para baixo conforme o sítio de injeção, já que a absorção é maior em bloqueios muito vascularizados, como o intercostal, e menor na infiltração subcutânea. Idosos, hepatopatas, gestantes e pacientes com baixo débito também exigem redução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 4,5 mg/kg é o limite da lidocaína &lt;em&gt;sem&lt;/em&gt; vasoconstritor, resultando em 315 mg e cerca de 21 mL; (C) a adrenalina não eleva o limite a 10 mg/kg, valor que se aproxima de faixas tóxicas; (D) não existe regra de reduzir a dose máxima pela metade em bloqueio de plexo braquial, cuja absorção é intermediária.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O cálculo exige duas etapas. Primeiro, a dose máxima: a lidocaína admite cerca de &lt;strong&gt;4,5 mg/kg sem adrenalina&lt;/strong&gt; e &lt;strong&gt;7 mg/kg com adrenalina&lt;/strong&gt;, pois a vasoconstrição local reduz a velocidade de absorção sistêmica e, portanto, o pico plasmático. Para 70 kg: 7 x 70 = &lt;strong&gt;490 mg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Segundo, a conversão em volume: solução a 1,5% contém 15 mg/mL, de modo que 490 mg correspondem a aproximadamente &lt;strong&gt;32 a 33 mL&lt;/strong&gt;. Vale lembrar que a concentração 1:200.000 equivale a 5 mcg/mL de adrenalina, o que nesse volume totaliza cerca de 160 mcg, quantidade que por si só recomenda cautela em coronariopatas e hipertensos graves.&lt;/p&gt;&lt;p&gt;Duas ressalvas conceituais importam mais que o número. A dose máxima é referência de segurança, não meta a ser atingida; e ela deve ser ajustada para baixo conforme o sítio de injeção, já que a absorção é maior em bloqueios muito vascularizados, como o intercostal, e menor na infiltração subcutânea. Idosos, hepatopatas, gestantes e pacientes com baixo débito também exigem redução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 4,5 mg/kg é o limite da lidocaína &lt;em&gt;sem&lt;/em&gt; vasoconstritor, resultando em 315 mg e cerca de 21 mL; (C) a adrenalina não eleva o limite a 10 mg/kg, valor que se aproxima de faixas tóxicas; (D) não existe regra de reduzir a dose máxima pela metade em bloqueio de plexo braquial, cuja absorção é intermediária.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A succinilcolina produz inicialmente &lt;strong&gt;bloqueio de fase I&lt;/strong&gt;, por despolarização persistente da placa motora. Suas características monitoradas são típicas: ausência de decremento na sequência de quatro estímulos (relação T4/T1 próxima de 1), ausência de facilitação pós-tetânica e &lt;em&gt;potencialização&lt;/em&gt; do bloqueio por anticolinesterásicos.&lt;/p&gt;&lt;p&gt;Com exposição prolongada — dose cumulativa acima de cerca de 3 a 5 mg/kg ou infusão continuada — a placa motora se repolariza parcialmente e o bloqueio adquire comportamento de &lt;strong&gt;fase II&lt;/strong&gt;, que imita farmacologicamente o bloqueio adespolarizante: aparece &lt;strong&gt;decremento (fade)&lt;/strong&gt; na sequência de quatro estímulos com relação T4/T1 tipicamente inferior a 0,3, surge &lt;strong&gt;facilitação pós-tetânica&lt;/strong&gt;, há taquifilaxia com necessidade de doses crescentes e a recuperação torna-se prolongada.&lt;/p&gt;&lt;p&gt;A conduta é conservadora: manter ventilação, sedação e monitorização até a recuperação espontânea. A reversão com anticolinesterásico é controversa e pode aprofundar o bloqueio se ainda houver componente de fase I, além de exigir certeza sobre a atividade da colinesterase plasmática.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) no bloqueio de fase I não há decremento nem facilitação pós-tetânica, justamente os achados descritos; (B) a deficiência de colinesterase prolonga o bloqueio, mas a neostigmina não é conduta obrigatória e pode ser deletéria; (C) o sugamadex encapsula aminoesteroides como rocurônio e vecurônio e não tem qualquer efeito sobre a succinilcolina.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A succinilcolina produz inicialmente &lt;strong&gt;bloqueio de fase I&lt;/strong&gt;, por despolarização persistente da placa motora. Suas características monitoradas são típicas: ausência de decremento na sequência de quatro estímulos (relação T4/T1 próxima de 1), ausência de facilitação pós-tetânica e &lt;em&gt;potencialização&lt;/em&gt; do bloqueio por anticolinesterásicos.&lt;/p&gt;&lt;p&gt;Com exposição prolongada (dose cumulativa acima de cerca de 3 a 5 mg/kg ou infusão continuada), a placa motora se repolariza parcialmente e o bloqueio adquire comportamento de &lt;strong&gt;fase II&lt;/strong&gt;, que imita farmacologicamente o bloqueio adespolarizante: aparece &lt;strong&gt;decremento (fade)&lt;/strong&gt; na sequência de quatro estímulos com relação T4/T1 tipicamente inferior a 0,3, surge &lt;strong&gt;facilitação pós-tetânica&lt;/strong&gt;, há taquifilaxia com necessidade de doses crescentes e a recuperação torna-se prolongada.&lt;/p&gt;&lt;p&gt;A conduta é conservadora: manter ventilação, sedação e monitorização até a recuperação espontânea. A reversão com anticolinesterásico é controversa e pode aprofundar o bloqueio se ainda houver componente de fase I, além de exigir certeza sobre a atividade da colinesterase plasmática.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) no bloqueio de fase I não há decremento nem facilitação pós-tetânica, justamente os achados descritos; (B) a deficiência de colinesterase prolonga o bloqueio, mas a neostigmina não é conduta obrigatória e pode ser deletéria; (C) o sugamadex encapsula aminoesteroides como rocurônio e vecurônio e não tem qualquer efeito sobre a succinilcolina.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os anticolinesterásicos revertem o bloqueio adespolarizante &lt;strong&gt;indiretamente&lt;/strong&gt;: inibem a acetilcolinesterase e aumentam a concentração de acetilcolina na fenda sináptica, deslocando o bloqueador do receptor nicotínico por competição. Como o aumento de acetilcolina é generalizado, os efeitos muscarínicos — bradicardia, broncoespasmo, salivação, hiperperistaltismo — exigem associação de anticolinérgico.&lt;/p&gt;&lt;p&gt;O emparelhamento se faz pela &lt;strong&gt;latência&lt;/strong&gt;. A neostigmina tem início relativamente lento, com pico em torno de 7 a 11 minutos, e combina-se ao &lt;strong&gt;glicopirrolato&lt;/strong&gt; (cerca de 0,2 mg para cada 1 mg de neostigmina), que tem instalação igualmente mais lenta e, por ser amina quaternária, não atravessa a barreira hematoencefálica, evitando efeitos centrais. O edrofônio, de início rápido, pareia-se com a atropina.&lt;/p&gt;&lt;p&gt;Duas limitações são essenciais: a neostigmina tem &lt;strong&gt;efeito teto&lt;/strong&gt; em torno de 0,07 mg/kg (máximo aproximado de 5 mg), acima do qual não há benefício adicional; e ela não reverte bloqueio profundo — exige-se ao menos duas respostas na sequência de quatro estímulos, condição satisfeita neste caso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a atropina tem início rápido e pareia com o edrofônio, além de poder causar taquicardia e efeitos centrais; (B) inverte a lógica das latências, pois o edrofônio é rápido e o glicopirrolato, lento; (D) doses acima do teto apenas aumentam efeitos adversos e podem causar fraqueza paradoxal, sem reverter bloqueio profundo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os anticolinesterásicos revertem o bloqueio adespolarizante &lt;strong&gt;indiretamente&lt;/strong&gt;: inibem a acetilcolinesterase e aumentam a concentração de acetilcolina na fenda sináptica, deslocando o bloqueador do receptor nicotínico por competição. Como o aumento de acetilcolina é generalizado, os efeitos muscarínicos (bradicardia, broncoespasmo, salivação, hiperperistaltismo) exigem associação de anticolinérgico.&lt;/p&gt;&lt;p&gt;O emparelhamento se faz pela &lt;strong&gt;latência&lt;/strong&gt;. A neostigmina tem início relativamente lento, com pico em torno de 7 a 11 minutos, e combina-se ao &lt;strong&gt;glicopirrolato&lt;/strong&gt; (cerca de 0,2 mg para cada 1 mg de neostigmina), que tem instalação igualmente mais lenta e, por ser amina quaternária, não atravessa a barreira hematoencefálica, evitando efeitos centrais. O edrofônio, de início rápido, pareia-se com a atropina.&lt;/p&gt;&lt;p&gt;Duas limitações são essenciais: a neostigmina tem &lt;strong&gt;efeito teto&lt;/strong&gt; em torno de 0,07 mg/kg (máximo aproximado de 5 mg), acima do qual não há benefício adicional; e ela não reverte bloqueio profundo, pois se exigem ao menos duas respostas na sequência de quatro estímulos, condição satisfeita neste caso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a atropina tem início rápido e pareia com o edrofônio, além de poder causar taquicardia e efeitos centrais; (B) inverte a lógica das latências, pois o edrofônio é rápido e o glicopirrolato, lento; (D) doses acima do teto apenas aumentam efeitos adversos e podem causar fraqueza paradoxal, sem reverter bloqueio profundo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A succinilcolina despolariza a placa motora e provoca saída de potássio da célula muscular, elevando o potássio sérico em torno de &lt;strong&gt;0,5 mEq/L&lt;/strong&gt; em indivíduos normais. O ponto frequentemente mal compreendido é que &lt;strong&gt;o paciente com doença renal crônica apresenta elevação de magnitude semelhante&lt;/strong&gt;: a insuficiência renal, por si só, não amplifica essa resposta. Portanto, a doença renal não é contraindicação — o que contraindica é a &lt;strong&gt;hipercalemia preexistente&lt;/strong&gt; ou alterações eletrocardiográficas de hipercalemia, situação que exige tratar o potássio ou usar rocurônio em dose de sequência rápida.&lt;/p&gt;&lt;p&gt;As verdadeiras situações de risco para hipercalemia grave envolvem &lt;strong&gt;proliferação de receptores nicotínicos extrajuncionais imaturos&lt;/strong&gt;: queimaduras extensas (a partir de cerca de 24 a 48 horas e por até um a dois anos), lesão medular e outras desnervações após as primeiras 24 a 72 horas, imobilização prolongada, doenças neuromusculares degenerativas, sepse arrastada e rabdomiólise. Nesses casos a elevação pode ser de vários mEq/L e causar parada cardíaca.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) proibir a succinilcolina em todo renal crônico normocalêmico é conduta sem respaldo e priva o paciente da opção com melhores condições de intubação em curto prazo; (C) atribui à doença renal uma amplificação que não ocorre; (D) o término de ação depende da &lt;strong&gt;hidrólise pela colinesterase plasmática&lt;/strong&gt;, e não da excreção renal, de modo que a duração não se prolonga de forma clinicamente relevante.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A succinilcolina despolariza a placa motora e provoca saída de potássio da célula muscular, elevando o potássio sérico em torno de &lt;strong&gt;0,5 mEq/L&lt;/strong&gt; em indivíduos normais. O ponto frequentemente mal compreendido é que &lt;strong&gt;o paciente com doença renal crônica apresenta elevação de magnitude semelhante&lt;/strong&gt;: a insuficiência renal, por si só, não amplifica essa resposta. Portanto, a doença renal não é contraindicação; o que contraindica é a &lt;strong&gt;hipercalemia preexistente&lt;/strong&gt; ou alterações eletrocardiográficas de hipercalemia, situação que exige tratar o potássio ou usar rocurônio em dose de sequência rápida.&lt;/p&gt;&lt;p&gt;As verdadeiras situações de risco para hipercalemia grave envolvem &lt;strong&gt;proliferação de receptores nicotínicos extrajuncionais imaturos&lt;/strong&gt;: queimaduras extensas (a partir de cerca de 24 a 48 horas e por até um a dois anos), lesão medular e outras desnervações após as primeiras 24 a 72 horas, imobilização prolongada, doenças neuromusculares degenerativas, sepse arrastada e rabdomiólise. Nesses casos a elevação pode ser de vários mEq/L e causar parada cardíaca.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) proibir a succinilcolina em todo renal crônico normocalêmico é conduta sem respaldo e priva o paciente da opção com melhores condições de intubação em curto prazo; (C) atribui à doença renal uma amplificação que não ocorre; (D) o término de ação depende da &lt;strong&gt;hidrólise pela colinesterase plasmática&lt;/strong&gt;, e não da excreção renal, de modo que a duração não se prolonga de forma clinicamente relevante.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A distrofia muscular de Duchenne é doença recessiva ligada ao X, causada pela ausência de &lt;strong&gt;distrofina&lt;/strong&gt;, proteína que ancora o citoesqueleto ao sarcolema. Sem ela, a membrana muscular é frágil e se rompe sob estresse, liberando potássio e mioglobina. O quadro descrito — meninos com fraqueza proximal, marcha anserina, sinal de Gowers, pseudo-hipertrofia de panturrilhas e creatinoquinase elevada — é clássico.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;succinilcolina é absolutamente contraindicada&lt;/strong&gt;: a despolarização maciça pode desencadear rabdomiólise com hipercalemia grave, arritmias ventriculares e parada cardíaca refratária, evento descrito inclusive em meninos ainda sem diagnóstico, o que motivou a restrição do uso eletivo de succinilcolina em crianças. Os &lt;strong&gt;halogenados&lt;/strong&gt; também são evitados, pois podem precipitar rabdomiólise induzida por anestésico — quadro relacionado, porém distinto da hipertermia maligna verdadeira. A conduta é anestesia livre de agentes desencadeantes, com técnica venosa total.&lt;/p&gt;&lt;p&gt;Somam-se miocardiopatia dilatada, distúrbios de condução, restrição respiratória com tosse ineficaz e risco de aspiração por gastroparesia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a dose desfasciculante não protege contra a hipercalemia da rabdomiólise; (C) os halogenados estão associados a rabdomiólise nesses pacientes e devem ser evitados; (D) a sensibilidade aos adespolarizantes está &lt;em&gt;aumentada&lt;/em&gt;, com duração prolongada, exigindo doses menores e monitorização quantitativa rigorosa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A distrofia muscular de Duchenne é doença recessiva ligada ao X, causada pela ausência de &lt;strong&gt;distrofina&lt;/strong&gt;, proteína que ancora o citoesqueleto ao sarcolema. Sem ela, a membrana muscular é frágil e se rompe sob estresse, liberando potássio e mioglobina. O quadro descrito (meninos com fraqueza proximal, marcha anserina, sinal de Gowers, pseudo-hipertrofia de panturrilhas e creatinoquinase elevada) é clássico.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;succinilcolina é absolutamente contraindicada&lt;/strong&gt;: a despolarização maciça pode desencadear rabdomiólise com hipercalemia grave, arritmias ventriculares e parada cardíaca refratária, evento descrito inclusive em meninos ainda sem diagnóstico, o que motivou a restrição do uso eletivo de succinilcolina em crianças. Os &lt;strong&gt;halogenados&lt;/strong&gt; também são evitados, pois podem precipitar rabdomiólise induzida por anestésico, quadro relacionado, porém distinto da hipertermia maligna verdadeira. A conduta é anestesia livre de agentes desencadeantes, com técnica venosa total.&lt;/p&gt;&lt;p&gt;Somam-se miocardiopatia dilatada, distúrbios de condução, restrição respiratória com tosse ineficaz e risco de aspiração por gastroparesia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a dose desfasciculante não protege contra a hipercalemia da rabdomiólise; (C) os halogenados estão associados a rabdomiólise nesses pacientes e devem ser evitados; (D) a sensibilidade aos adespolarizantes está &lt;em&gt;aumentada&lt;/em&gt;, com duração prolongada, exigindo doses menores e monitorização quantitativa rigorosa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A succinilcolina tem ação breve porque é hidrolisada pela &lt;strong&gt;colinesterase plasmática&lt;/strong&gt; (pseudocolinesterase). Variantes genéticas dessa enzima prolongam o bloqueio de forma marcante, e o teste que as caracteriza é o &lt;strong&gt;número de dibucaína&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O conceito essencial é que o número de dibucaína mede &lt;strong&gt;qualidade&lt;/strong&gt; — o percentual de inibição da enzima pela dibucaína — e &lt;strong&gt;não a quantidade&lt;/strong&gt; de enzima circulante. Situações que reduzem a quantidade da enzima (gravidez, hepatopatia, desnutrição, neoplasia, plasmaférese, uso de inibidores como ecotiofato tópico, ciclofosfamida ou metoclopramida) prolongam modestamente o bloqueio, por poucos minutos, sem alterar o número de dibucaína.&lt;/p&gt;&lt;p&gt;A interpretação segue faixas conhecidas: valor em torno de &lt;strong&gt;80&lt;/strong&gt; corresponde ao homozigoto normal; entre &lt;strong&gt;40 e 60&lt;/strong&gt;, ao heterozigoto atípico, com prolongamento habitual de 20 a 30 minutos; e valores em torno de &lt;strong&gt;20&lt;/strong&gt;, como no caso, ao &lt;strong&gt;homozigoto atípico&lt;/strong&gt;, cujo bloqueio pode durar de 4 a 8 horas. Não existe antagonista específico: a conduta é manter ventilação mecânica, sedação e analgesia adequadas até a recuperação espontânea, com orientação genética posterior à paciente e à família.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde qualidade com quantidade, justamente o erro conceitual mais comum; (B) o padrão heterozigoto corresponde a valores intermediários, incompatíveis com três horas de apneia; (D) 22 é valor francamente anormal, e a dose única de 1 mg/kg não produz bloqueio de fase II.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A succinilcolina tem ação breve porque é hidrolisada pela &lt;strong&gt;colinesterase plasmática&lt;/strong&gt; (pseudocolinesterase). Variantes genéticas dessa enzima prolongam o bloqueio de forma marcante, e o teste que as caracteriza é o &lt;strong&gt;número de dibucaína&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O conceito essencial é que o número de dibucaína mede &lt;strong&gt;qualidade&lt;/strong&gt; (o percentual de inibição da enzima pela dibucaína) e &lt;strong&gt;não a quantidade&lt;/strong&gt; de enzima circulante. Situações que reduzem a quantidade da enzima (gravidez, hepatopatia, desnutrição, neoplasia, plasmaférese, uso de inibidores como ecotiofato tópico, ciclofosfamida ou metoclopramida) prolongam modestamente o bloqueio, por poucos minutos, sem alterar o número de dibucaína.&lt;/p&gt;&lt;p&gt;A interpretação segue faixas conhecidas: valor em torno de &lt;strong&gt;80&lt;/strong&gt; corresponde ao homozigoto normal; entre &lt;strong&gt;40 e 60&lt;/strong&gt;, ao heterozigoto atípico, com prolongamento habitual de 20 a 30 minutos; e valores em torno de &lt;strong&gt;20&lt;/strong&gt;, como no caso, ao &lt;strong&gt;homozigoto atípico&lt;/strong&gt;, cujo bloqueio pode durar de 4 a 8 horas. Não existe antagonista específico: a conduta é manter ventilação mecânica, sedação e analgesia adequadas até a recuperação espontânea, com orientação genética posterior à paciente e à família.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde qualidade com quantidade, justamente o erro conceitual mais comum; (B) o padrão heterozigoto corresponde a valores intermediários, incompatíveis com três horas de apneia; (D) 22 é valor francamente anormal, e a dose única de 1 mg/kg não produz bloqueio de fase II.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O sulfato de magnésio é a droga de escolha na profilaxia e no tratamento da eclâmpsia, e sua janela terapêutica é estreita. A faixa-alvo situa-se em torno de &lt;strong&gt;4 a 7 mEq/L (aproximadamente 4,8 a 8,4 mg/dL)&lt;/strong&gt;. Como o magnésio é eliminado quase inteiramente pelo rim, qualquer queda da filtração glomerular — frequente na pré-eclâmpsia grave — provoca acúmulo rápido.&lt;/p&gt;&lt;p&gt;A toxicidade segue uma progressão razoavelmente previsível:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Perda do reflexo patelar por volta de 10 mEq/L (cerca de 12 mg/dL);&lt;/li&gt;&lt;li&gt;Depressão respiratória e parada respiratória entre 12 e 15 mEq/L;&lt;/li&gt;&lt;li&gt;Bloqueio da condução cardíaca e assistolia em níveis acima de 25 mEq/L.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Diante de arreflexia com bradipneia, a conduta é suspender a infusão, oferecer oxigênio e administrar &lt;strong&gt;gluconato de cálcio 1 g por via venosa&lt;/strong&gt; (10 mL da solução a 10%), que antagoniza o efeito do magnésio na junção neuromuscular e no miocárdio. O suporte ventilatório deve estar disponível.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o reflexo patelar preservado é justamente o marcador clínico de segurança; sua perda sinaliza toxicidade e obriga suspensão, não redução. (C) a diurese forçada não é o tratamento de primeira linha e agrava a hipovolemia relativa da pré-eclâmpsia; o antídoto é o cálcio. (D) o flumazenil não tem qualquer ação sobre o magnésio, e o quadro descrito é típico de hipermagnesemia, não de sedação por benzodiazepínico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O sulfato de magnésio é a droga de escolha na profilaxia e no tratamento da eclâmpsia, e sua janela terapêutica é estreita. A faixa-alvo situa-se em torno de &lt;strong&gt;4 a 7 mEq/L (aproximadamente 4,8 a 8,4 mg/dL)&lt;/strong&gt;. Como o magnésio é eliminado quase inteiramente pelo rim, qualquer queda da filtração glomerular (frequente na pré-eclâmpsia grave) provoca acúmulo rápido.&lt;/p&gt;&lt;p&gt;A toxicidade segue uma progressão razoavelmente previsível:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Perda do reflexo patelar por volta de 10 mEq/L (cerca de 12 mg/dL);&lt;/li&gt;&lt;li&gt;Depressão respiratória e parada respiratória entre 12 e 15 mEq/L;&lt;/li&gt;&lt;li&gt;Bloqueio da condução cardíaca e assistolia em níveis acima de 25 mEq/L.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Diante de arreflexia com bradipneia, a conduta é suspender a infusão, oferecer oxigênio e administrar &lt;strong&gt;gluconato de cálcio 1 g por via venosa&lt;/strong&gt; (10 mL da solução a 10%), que antagoniza o efeito do magnésio na junção neuromuscular e no miocárdio. O suporte ventilatório deve estar disponível.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o reflexo patelar preservado é justamente o marcador clínico de segurança; sua perda sinaliza toxicidade e obriga suspensão, não redução. (C) a diurese forçada não é o tratamento de primeira linha e agrava a hipovolemia relativa da pré-eclâmpsia; o antídoto é o cálcio. (D) o flumazenil não tem qualquer ação sobre o magnésio, e o quadro descrito é típico de hipermagnesemia, não de sedação por benzodiazepínico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A tolerância à apneia depende essencialmente da relação entre o reservatório de oxigênio pulmonar (a capacidade residual funcional, ou CRF) e a velocidade com que esse reservatório é consumido (o VO&lt;sub&gt;2&lt;/sub&gt;). A gestante a termo piora nos dois lados dessa equação.&lt;/p&gt;&lt;p&gt;A elevação diafragmática pelo útero gravídico reduz o volume de reserva expiratório e o volume residual, derrubando a &lt;strong&gt;CRF em cerca de 20% na posição supina&lt;/strong&gt;. Ao mesmo tempo, a demanda metabólica materna, placentária e fetal eleva o &lt;strong&gt;consumo de oxigênio em 20% a 40%&lt;/strong&gt;, chegando a mais de 60% no trabalho de parto. O reservatório menor, drenado mais rápido, encurta muito o tempo de apneia segura — a dessaturação pode ocorrer em menos de um minuto, contra vários minutos em uma adulta não gestante. A obesidade agrava ainda mais a queda de CRF e favorece o fechamento de vias aéreas em volume corrente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve exatamente o oposto do que ocorre; se fosse verdadeira, a dessaturação seria mais lenta. (B) a CRF não permanece inalterada, e o volume residual está reduzido, não aumentado. (C) a gestante hiperventila por estímulo progestacional: a ventilação minuto sobe cerca de 50% e a PaCO&lt;sub&gt;2&lt;/sub&gt; cai para faixa de 28 a 32 mmHg, com bicarbonato compensatoriamente reduzido, e não há retenção de CO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A tolerância à apneia depende essencialmente da relação entre o reservatório de oxigênio pulmonar (a capacidade residual funcional, ou CRF) e a velocidade com que esse reservatório é consumido (o VO&lt;sub&gt;2&lt;/sub&gt;). A gestante a termo piora nos dois lados dessa equação.&lt;/p&gt;&lt;p&gt;A elevação diafragmática pelo útero gravídico reduz o volume de reserva expiratório e o volume residual, derrubando a &lt;strong&gt;CRF em cerca de 20% na posição supina&lt;/strong&gt;. Ao mesmo tempo, a demanda metabólica materna, placentária e fetal eleva o &lt;strong&gt;consumo de oxigênio em 20% a 40%&lt;/strong&gt;, chegando a mais de 60% no trabalho de parto. O reservatório menor, drenado mais rápido, encurta muito o tempo de apneia segura: a dessaturação pode ocorrer em menos de um minuto, contra vários minutos em uma adulta não gestante. A obesidade agrava ainda mais a queda de CRF e favorece o fechamento de vias aéreas em volume corrente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve exatamente o oposto do que ocorre; se fosse verdadeira, a dessaturação seria mais lenta. (B) a CRF não permanece inalterada, e o volume residual está reduzido, não aumentado. (C) a gestante hiperventila por estímulo progestacional: a ventilação minuto sobe cerca de 50% e a PaCO&lt;sub&gt;2&lt;/sub&gt; cai para faixa de 28 a 32 mmHg, com bicarbonato compensatoriamente reduzido, e não há retenção de CO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Praticamente todos os parâmetros hematológicos mudam na gestação, e reconhecer essa nova normalidade evita investigações e intervenções desnecessárias.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Série vermelha:&lt;/strong&gt; o volume plasmático aumenta proporcionalmente mais que a massa eritrocitária, gerando anemia dilucional. Hemoglobina em torno de 10,5 a 11 g/dL no terceiro trimestre é esperada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Série branca:&lt;/strong&gt; leucocitose fisiológica de 9.000 a 15.000/mm3 é comum no termo, podendo ultrapassar 20.000/mm3 no trabalho de parto, sem desvio significativo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Plaquetas:&lt;/strong&gt; caem discretamente por hemodiluição e aumento do consumo — a plaquetopenia gestacional benigna responde pela maioria das contagens entre 100.000 e 150.000/mm3.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Coagulação:&lt;/strong&gt; a gestação é um estado pró-trombótico. Fibrinogênio sobe para a faixa de 400 a 650 mg/dL e diversos fatores aumentam, o que encurta discretamente os tempos de coagulação.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Nesse cenário, com paciente assintomática e normotensa, o bloqueio neuroaxial pode ser realizado sem exames complementares adicionais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a leucocitose isolada, sem febre, sem desvio e sem foco clínico, é fisiológica na gestante. (C) o fibrinogênio elevado é o padrão do termo; na coagulação intravascular disseminada obstétrica ele &lt;em&gt;cai&lt;/em&gt;, e valores abaixo de 200 mg/dL já são preocupantes. (D) hemoglobina de 10,8 g/dL não caracteriza anemia grave nem indica transfusão em paciente assintomática.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Praticamente todos os parâmetros hematológicos mudam na gestação, e reconhecer essa nova normalidade evita investigações e intervenções desnecessárias.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Série vermelha:&lt;/strong&gt; o volume plasmático aumenta proporcionalmente mais que a massa eritrocitária, gerando anemia dilucional. Hemoglobina em torno de 10,5 a 11 g/dL no terceiro trimestre é esperada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Série branca:&lt;/strong&gt; leucocitose fisiológica de 9.000 a 15.000/mm3 é comum no termo, podendo ultrapassar 20.000/mm3 no trabalho de parto, sem desvio significativo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Plaquetas:&lt;/strong&gt; caem discretamente por hemodiluição e aumento do consumo; a plaquetopenia gestacional benigna responde pela maioria das contagens entre 100.000 e 150.000/mm3.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Coagulação:&lt;/strong&gt; a gestação é um estado pró-trombótico. Fibrinogênio sobe para a faixa de 400 a 650 mg/dL e diversos fatores aumentam, o que encurta discretamente os tempos de coagulação.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Nesse cenário, com paciente assintomática e normotensa, o bloqueio neuroaxial pode ser realizado sem exames complementares adicionais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a leucocitose isolada, sem febre, sem desvio e sem foco clínico, é fisiológica na gestante. (C) o fibrinogênio elevado é o padrão do termo; na coagulação intravascular disseminada obstétrica ele &lt;em&gt;cai&lt;/em&gt;, e valores abaixo de 200 mg/dL já são preocupantes. (D) hemoglobina de 10,8 g/dL não caracteriza anemia grave nem indica transfusão em paciente assintomática.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Algumas situações obstétricas exigem &lt;strong&gt;relaxamento uterino imediato e breve&lt;/strong&gt;: retenção placentária com anel de constrição, inversão uterina aguda, distocia da cabeça derradeira na apresentação pélvica, extração de segundo gemelar e algumas manobras de versão interna.&lt;/p&gt;&lt;p&gt;A nitroglicerina é a droga que melhor atende a esse perfil. Ela é doadora de óxido nítrico e relaxa a musculatura lisa uterina com &lt;strong&gt;início em 30 a 60 segundos e duração em torno de 1 a 2 minutos&lt;/strong&gt;, dose habitual de 50 a 100 mcg por via venosa, repetível conforme a resposta. A meia-vida curtíssima é a grande vantagem: permite que o tônus uterino se restabeleça logo em seguida, limitando o risco de atonia e hemorragia. Os efeitos adversos previsíveis são hipotensão e cefaleia, razão pela qual se exige paciente euvolêmica, monitorização e vasopressor disponível. A via sublingual também é descrita.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ocitocina é uterotônica: aumenta o tônus e agravaria o anel de constrição. (C) o sulfato de magnésio relaxa o útero, mas seu efeito é lento, prolongado e acompanhado de hipotensão e potencialização de bloqueadores neuromusculares — inadequado para uma manobra de poucos minutos. (D) os halogenados relaxam o útero de forma dose-dependente, porém exigem concentrações elevadas, acima de 1,5 a 2 CAM; 0,5 CAM é insuficiente, e administrar halogenado sob máscara em puérpera com risco de aspiração é conduta insegura.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Algumas situações obstétricas exigem &lt;strong&gt;relaxamento uterino imediato e breve&lt;/strong&gt;: retenção placentária com anel de constrição, inversão uterina aguda, distocia da cabeça derradeira na apresentação pélvica, extração de segundo gemelar e algumas manobras de versão interna.&lt;/p&gt;&lt;p&gt;A nitroglicerina é a droga que melhor atende a esse perfil. Ela é doadora de óxido nítrico e relaxa a musculatura lisa uterina com &lt;strong&gt;início em 30 a 60 segundos e duração em torno de 1 a 2 minutos&lt;/strong&gt;, dose habitual de 50 a 100 mcg por via venosa, repetível conforme a resposta. A meia-vida curtíssima é a grande vantagem: permite que o tônus uterino se restabeleça logo em seguida, limitando o risco de atonia e hemorragia. Os efeitos adversos previsíveis são hipotensão e cefaleia, razão pela qual se exige paciente euvolêmica, monitorização e vasopressor disponível. A via sublingual também é descrita.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ocitocina é uterotônica: aumenta o tônus e agravaria o anel de constrição. (C) o sulfato de magnésio relaxa o útero, mas seu efeito é lento, prolongado e acompanhado de hipotensão e potencialização de bloqueadores neuromusculares, inadequado para uma manobra de poucos minutos. (D) os halogenados relaxam o útero de forma dose-dependente, porém exigem concentrações elevadas, acima de 1,5 a 2 CAM; 0,5 CAM é insuficiente, e administrar halogenado sob máscara em puérpera com risco de aspiração é conduta insegura.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O quadro é clássico de &lt;strong&gt;descolamento prematuro de placenta&lt;/strong&gt;: dor abdominal súbita e contínua, hipertonia uterina (útero lenhoso), sangramento escuro frequentemente desproporcional à gravidade — porque grande parte é oculta, retroplacentária — e sofrimento fetal. Hipertensão, trauma, tabagismo, uso de cocaína e polidrâmnio são fatores de risco reconhecidos.&lt;/p&gt;&lt;p&gt;A coagulopatia é o achado que mais assusta o anestesiologista. A decídua e a placenta são ricas em &lt;strong&gt;fator tecidual (tromboplastina)&lt;/strong&gt;; o descolamento libera esse material na circulação materna, disparando a via extrínseca e consumindo fatores e plaquetas. O &lt;strong&gt;fibrinogênio é o marcador mais sensível e mais precoce&lt;/strong&gt; na hemorragia obstétrica: como no termo ele deveria estar entre 400 e 650 mg/dL, um valor de 118 mg/dL representa consumo grave. A reposição precoce de fibrinogênio, por crioprecipitado ou concentrado, é prioridade, e a coagulopatia estabelecida contraindica bloqueio neuroaxial, impondo anestesia geral.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a placenta prévia cursa com sangramento indolor, vermelho-vivo, útero amolecido e sem coagulopatia precoce — o oposto do descrito. (C) a embolia por líquido amniótico se manifesta com colapso cardiovascular súbito, hipoxemia grave e coagulopatia fulminante, geralmente durante ou logo após o parto, e não com útero lenhoso doloroso como quadro inicial. (D) a rotura uterina ocorre tipicamente em útero com cicatriz, cursa com perda do tônus e da apresentação, dor em pontada e frequentemente cessação das contrações.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O quadro é clássico de &lt;strong&gt;descolamento prematuro de placenta&lt;/strong&gt;: dor abdominal súbita e contínua, hipertonia uterina (útero lenhoso), sangramento escuro frequentemente desproporcional à gravidade (porque grande parte é oculta, retroplacentária) e sofrimento fetal. Hipertensão, trauma, tabagismo, uso de cocaína e polidrâmnio são fatores de risco reconhecidos.&lt;/p&gt;&lt;p&gt;A coagulopatia é o achado que mais assusta o anestesiologista. A decídua e a placenta são ricas em &lt;strong&gt;fator tecidual (tromboplastina)&lt;/strong&gt;; o descolamento libera esse material na circulação materna, disparando a via extrínseca e consumindo fatores e plaquetas. O &lt;strong&gt;fibrinogênio é o marcador mais sensível e mais precoce&lt;/strong&gt; na hemorragia obstétrica: como no termo ele deveria estar entre 400 e 650 mg/dL, um valor de 118 mg/dL representa consumo grave. A reposição precoce de fibrinogênio, por crioprecipitado ou concentrado, é prioridade, e a coagulopatia estabelecida contraindica bloqueio neuroaxial, impondo anestesia geral.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a placenta prévia cursa com sangramento indolor, vermelho-vivo, útero amolecido e sem coagulopatia precoce, o oposto do descrito. (C) a embolia por líquido amniótico se manifesta com colapso cardiovascular súbito, hipoxemia grave e coagulopatia fulminante, geralmente durante ou logo após o parto, e não com útero lenhoso doloroso como quadro inicial. (D) a rotura uterina ocorre tipicamente em útero com cicatriz, cursa com perda do tônus e da apresentação, dor em pontada e frequentemente cessação das contrações.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O neonato, e sobretudo o prematuro, é extraordinariamente vulnerável à hipotermia: tem &lt;strong&gt;grande relação entre superfície corporal e massa&lt;/strong&gt;, cabeça proporcionalmente enorme, pele fina e pouco tecido subcutâneo isolante. A anestesia agrava o quadro ao abolir a vasoconstrição e o comportamento termorregulador e ao reduzir o limiar de resposta.&lt;/p&gt;&lt;p&gt;As quatro vias de perda contribuem de forma desigual em sala cirúrgica. A &lt;strong&gt;radiação&lt;/strong&gt; — transferência de calor para superfícies frias ao redor, sem contato — responde pela maior parcela, seguida de convecção, evaporação e, por último, condução. Como a radiação depende do gradiente entre o paciente e as paredes e superfícies da sala, &lt;strong&gt;elevar a temperatura ambiente&lt;/strong&gt; é medida com grande impacto no neonato, e o &lt;strong&gt;aquecimento por ar forçado&lt;/strong&gt; é o dispositivo isolado mais eficaz. Somam-se cobertura de superfícies expostas, aquecimento de fluidos e umidificação dos gases.&lt;/p&gt;&lt;p&gt;Sobre a termogênese: o recém-nascido não treme de forma efetiva. Depende da &lt;strong&gt;termogênese sem tremor&lt;/strong&gt;, mediada por noradrenalina na gordura marrom, mecanismo que é limitado no prematuro (que tem pouca gordura marrom acumulada) e que ainda cobra caro em consumo de oxigênio e acidose metabólica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a convecção não é a via dominante, e aumentar o fluxo de gases frescos frios agrava a perda. (B) o prematuro praticamente não treme, e o tremor não é sua via termogênica principal. (D) o prematuro tem justamente &lt;em&gt;pouca&lt;/em&gt; gordura marrom, sendo o grupo que mais precisa de aquecimento ativo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O neonato, e sobretudo o prematuro, é extraordinariamente vulnerável à hipotermia: tem &lt;strong&gt;grande relação entre superfície corporal e massa&lt;/strong&gt;, cabeça proporcionalmente enorme, pele fina e pouco tecido subcutâneo isolante. A anestesia agrava o quadro ao abolir a vasoconstrição e o comportamento termorregulador e ao reduzir o limiar de resposta.&lt;/p&gt;&lt;p&gt;As quatro vias de perda contribuem de forma desigual em sala cirúrgica. A &lt;strong&gt;radiação&lt;/strong&gt; (transferência de calor para superfícies frias ao redor, sem contato) responde pela maior parcela, seguida de convecção, evaporação e, por último, condução. Como a radiação depende do gradiente entre o paciente e as paredes e superfícies da sala, &lt;strong&gt;elevar a temperatura ambiente&lt;/strong&gt; é medida com grande impacto no neonato, e o &lt;strong&gt;aquecimento por ar forçado&lt;/strong&gt; é o dispositivo isolado mais eficaz. Somam-se cobertura de superfícies expostas, aquecimento de fluidos e umidificação dos gases.&lt;/p&gt;&lt;p&gt;Sobre a termogênese: o recém-nascido não treme de forma efetiva. Depende da &lt;strong&gt;termogênese sem tremor&lt;/strong&gt;, mediada por noradrenalina na gordura marrom, mecanismo que é limitado no prematuro (que tem pouca gordura marrom acumulada) e que ainda cobra caro em consumo de oxigênio e acidose metabólica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a convecção não é a via dominante, e aumentar o fluxo de gases frescos frios agrava a perda. (B) o prematuro praticamente não treme, e o tremor não é sua via termogênica principal. (D) o prematuro tem justamente &lt;em&gt;pouca&lt;/em&gt; gordura marrom, sendo o grupo que mais precisa de aquecimento ativo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A falcização depende da polimerização da hemoglobina S desoxigenada, favorecida por &lt;strong&gt;hipóxia, acidose, hipotermia, desidratação, estase venosa, dor e infecção&lt;/strong&gt;. O manejo anestésico é, em essência, a prevenção sistemática de cada um desses gatilhos.&lt;/p&gt;&lt;p&gt;Quanto ao preparo hematológico, a conduta consagrada para cirurgias de risco baixo a moderado — e a colecistectomia videolaparoscópica se enquadra aqui — é a &lt;strong&gt;transfusão simples até hemoglobina de aproximadamente 10 g/dL&lt;/strong&gt;. Essa estratégia conservadora mostrou-se tão eficaz quanto a exsanguineotransfusão parcial agressiva para reduzir HbS, com muito menos complicações transfusionais e menor aloimunização. O regime de troca fica reservado a cirurgias de altíssimo risco, como neurocirurgia e circulação extracorpórea, ou a pacientes com doença muito grave.&lt;/p&gt;&lt;p&gt;No intraoperatório, valem: manutenção da normotermia com aquecimento ativo, hidratação generosa mas sem sobrecarga, oxigenação suplementar, evitar torniquete quando possível, analgesia multimodal e vigilância pós-operatória para &lt;strong&gt;síndrome torácica aguda&lt;/strong&gt;, principal complicação e causa de óbito nesse contexto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) tanto a hipotermia quanto a alcalose respiratória extrema por hiperventilação são deletérias: a hipotermia gera vasoconstrição e estase, precipitando falcização. (B) hematócrito acima de 45% eleva a viscosidade sanguínea e aumenta o risco de vaso-oclusão, exatamente o efeito oposto ao desejado. (C) a desidratação é um dos gatilhos mais potentes de crise; a hidratação deve ser mantida, e não suspensa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A falcização depende da polimerização da hemoglobina S desoxigenada, favorecida por &lt;strong&gt;hipóxia, acidose, hipotermia, desidratação, estase venosa, dor e infecção&lt;/strong&gt;. O manejo anestésico é, em essência, a prevenção sistemática de cada um desses gatilhos.&lt;/p&gt;&lt;p&gt;Quanto ao preparo hematológico, a conduta consagrada para cirurgias de risco baixo a moderado (e a colecistectomia videolaparoscópica se enquadra aqui) é a &lt;strong&gt;transfusão simples até hemoglobina de aproximadamente 10 g/dL&lt;/strong&gt;. Essa estratégia conservadora mostrou-se tão eficaz quanto a exsanguineotransfusão parcial agressiva para reduzir HbS, com muito menos complicações transfusionais e menor aloimunização. O regime de troca fica reservado a cirurgias de altíssimo risco, como neurocirurgia e circulação extracorpórea, ou a pacientes com doença muito grave.&lt;/p&gt;&lt;p&gt;No intraoperatório, valem: manutenção da normotermia com aquecimento ativo, hidratação generosa mas sem sobrecarga, oxigenação suplementar, evitar torniquete quando possível, analgesia multimodal e vigilância pós-operatória para &lt;strong&gt;síndrome torácica aguda&lt;/strong&gt;, principal complicação e causa de óbito nesse contexto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) tanto a hipotermia quanto a alcalose respiratória extrema por hiperventilação são deletérias: a hipotermia gera vasoconstrição e estase, precipitando falcização. (B) hematócrito acima de 45% eleva a viscosidade sanguínea e aumenta o risco de vaso-oclusão, exatamente o efeito oposto ao desejado. (C) a desidratação é um dos gatilhos mais potentes de crise; a hidratação deve ser mantida, e não suspensa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Na vida fetal, o canal arterial desvia a maior parte do débito do ventrículo direito da artéria pulmonar para a aorta, contornando os pulmões não ventilados. Sua patência é mantida por dois fatores principais: a &lt;strong&gt;baixa PaO2 fetal&lt;/strong&gt; (em torno de 25 a 30 mmHg) e as &lt;strong&gt;prostaglandinas vasodilatadoras circulantes&lt;/strong&gt;, sobretudo E1 e E2, produzidas pela placenta e pouco metabolizadas porque o pulmão fetal está pouco perfundido.&lt;/p&gt;&lt;p&gt;Ao nascimento, a expansão pulmonar e a ventilação elevam a PaO2, e a retirada da placenta somada ao aumento do metabolismo pulmonar derruba os níveis de prostaglandina. O músculo liso ductal se contrai, e ocorre o &lt;strong&gt;fechamento funcional em 24 a 72 horas&lt;/strong&gt;, com fechamento anatômico em algumas semanas.&lt;/p&gt;&lt;p&gt;Nas cardiopatias em que o fluxo pulmonar (ou o sistêmico) depende do canal — atresia pulmonar, atresia tricúspide, estenose pulmonar crítica, coarctação grave, interrupção do arco, síndrome do coração esquerdo hipoplásico — esse fechamento é catastrófico. O tratamento é a &lt;strong&gt;infusão contínua de prostaglandina E1&lt;/strong&gt;, tipicamente em doses da ordem de 0,01 a 0,1 mcg/kg/min, com atenção aos efeitos adversos de apneia, hipotensão e febre.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a PaO2 elevada é o principal estímulo ao &lt;em&gt;fechamento&lt;/em&gt;, não à manutenção; nesses pacientes evita-se hiperóxia. (C) a indometacina inibe a síntese de prostaglandinas e é usada para &lt;em&gt;fechar&lt;/em&gt; o canal no prematuro; aqui seria desastrosa. (D) o fechamento depende sobretudo de oxigênio e prostaglandinas, não apenas da resistência pulmonar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Na vida fetal, o canal arterial desvia a maior parte do débito do ventrículo direito da artéria pulmonar para a aorta, contornando os pulmões não ventilados. Sua patência é mantida por dois fatores principais: a &lt;strong&gt;baixa PaO2 fetal&lt;/strong&gt; (em torno de 25 a 30 mmHg) e as &lt;strong&gt;prostaglandinas vasodilatadoras circulantes&lt;/strong&gt;, sobretudo E1 e E2, produzidas pela placenta e pouco metabolizadas porque o pulmão fetal está pouco perfundido.&lt;/p&gt;&lt;p&gt;Ao nascimento, a expansão pulmonar e a ventilação elevam a PaO2, e a retirada da placenta somada ao aumento do metabolismo pulmonar derruba os níveis de prostaglandina. O músculo liso ductal se contrai, e ocorre o &lt;strong&gt;fechamento funcional em 24 a 72 horas&lt;/strong&gt;, com fechamento anatômico em algumas semanas.&lt;/p&gt;&lt;p&gt;Nas cardiopatias em que o fluxo pulmonar (ou o sistêmico) depende do canal, como atresia pulmonar, atresia tricúspide, estenose pulmonar crítica, coarctação grave, interrupção do arco e síndrome do coração esquerdo hipoplásico, esse fechamento é catastrófico. O tratamento é a &lt;strong&gt;infusão contínua de prostaglandina E1&lt;/strong&gt;, tipicamente em doses da ordem de 0,01 a 0,1 mcg/kg/min, com atenção aos efeitos adversos de apneia, hipotensão e febre.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a PaO2 elevada é o principal estímulo ao &lt;em&gt;fechamento&lt;/em&gt;, não à manutenção; nesses pacientes evita-se hiperóxia. (C) a indometacina inibe a síntese de prostaglandinas e é usada para &lt;em&gt;fechar&lt;/em&gt; o canal no prematuro; aqui seria desastrosa. (D) o fechamento depende sobretudo de oxigênio e prostaglandinas, não apenas da resistência pulmonar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hérnia diafragmática congênita não é primariamente um problema mecânico de conteúdo herniado, e sim de &lt;strong&gt;hipoplasia pulmonar bilateral&lt;/strong&gt; (mais grave do lado do defeito) somada a &lt;strong&gt;hipertensão pulmonar persistente&lt;/strong&gt;, com musculatura arteriolar hiper-reativa. O gradiente entre saturação pré e pós-ductal, como no caso, denuncia shunt direita-esquerda pelo canal arterial e pelo forame oval.&lt;/p&gt;&lt;p&gt;Essa compreensão mudou completamente a conduta. A doença deixou de ser tratada como emergência cirúrgica: opera-se &lt;strong&gt;após estabilização&lt;/strong&gt;, quando a hipertensão pulmonar está controlada, o que pode levar de horas a dias. A prioridade inicial é respiratória e hemodinâmica:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Intubação precoce&lt;/strong&gt;, evitando ventilação sob máscara — insuflar o estômago e as alças intratorácicas piora a compressão pulmonar;&lt;/li&gt;&lt;li&gt;Sonda gástrica para descompressão;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação gentil&lt;/strong&gt;, com pressões de pico baixas, habitualmente abaixo de 25 cmH&lt;sub&gt;2&lt;/sub&gt;O, volumes correntes pequenos e &lt;strong&gt;hipercapnia permissiva&lt;/strong&gt;, aceitando saturação pré-ductal em torno de 85% a 95%;&lt;/li&gt;&lt;li&gt;Evitar hipóxia, acidose e hipotermia, que agravam a vasoconstrição pulmonar; considerar óxido nítrico inalado e suporte inotrópico.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a ventilação sob máscara com pressões altas distende as vísceras herniadas e piora a compressão, além de aumentar muito o risco de pneumotórax no pulmão hipoplásico. (C) a cirurgia imediata não corrige a hipoplasia nem a hipertensão pulmonar e piora o desfecho em criança instável. (D) o óxido nitroso difunde para o intestino herniado, expandindo-o dentro do tórax, e é formalmente evitado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hérnia diafragmática congênita não é primariamente um problema mecânico de conteúdo herniado, e sim de &lt;strong&gt;hipoplasia pulmonar bilateral&lt;/strong&gt; (mais grave do lado do defeito) somada a &lt;strong&gt;hipertensão pulmonar persistente&lt;/strong&gt;, com musculatura arteriolar hiper-reativa. O gradiente entre saturação pré e pós-ductal, como no caso, denuncia shunt direita-esquerda pelo canal arterial e pelo forame oval.&lt;/p&gt;&lt;p&gt;Essa compreensão mudou completamente a conduta. A doença deixou de ser tratada como emergência cirúrgica: opera-se &lt;strong&gt;após estabilização&lt;/strong&gt;, quando a hipertensão pulmonar está controlada, o que pode levar de horas a dias. A prioridade inicial é respiratória e hemodinâmica:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Intubação precoce&lt;/strong&gt;, evitando ventilação sob máscara: insuflar o estômago e as alças intratorácicas piora a compressão pulmonar;&lt;/li&gt;&lt;li&gt;Sonda gástrica para descompressão;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação gentil&lt;/strong&gt;, com pressões de pico baixas, habitualmente abaixo de 25 cmH&lt;sub&gt;2&lt;/sub&gt;O, volumes correntes pequenos e &lt;strong&gt;hipercapnia permissiva&lt;/strong&gt;, aceitando saturação pré-ductal em torno de 85% a 95%;&lt;/li&gt;&lt;li&gt;Evitar hipóxia, acidose e hipotermia, que agravam a vasoconstrição pulmonar; considerar óxido nítrico inalado e suporte inotrópico.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a ventilação sob máscara com pressões altas distende as vísceras herniadas e piora a compressão, além de aumentar muito o risco de pneumotórax no pulmão hipoplásico. (C) a cirurgia imediata não corrige a hipoplasia nem a hipertensão pulmonar e piora o desfecho em criança instável. (D) o óxido nitroso difunde para o intestino herniado, expandindo-o dentro do tórax, e é formalmente evitado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A forma mais comum de atresia de esôfago, respondendo por cerca de 85% dos casos, é a que combina &lt;strong&gt;coto esofágico proximal cego com fístula entre a traqueia e o esôfago distal&lt;/strong&gt;. A tríade clínica é sialorreia, impossibilidade de progredir a sonda e distensão gástrica — esta última justamente porque o ar da traqueia escapa pela fístula para o estômago.&lt;/p&gt;&lt;p&gt;O ponto crítico do manejo anestésico decorre dessa anatomia. Se a ponta do tubo ficar &lt;strong&gt;acima do orifício fistuloso&lt;/strong&gt; e se aplicarem pressões positivas altas, o gás segue preferencialmente pelo caminho de menor resistência: insufla o estômago, eleva o diafragma, compromete a ventilação e pode chegar à perfuração gástrica. A estratégia é posicionar a &lt;strong&gt;ponta do tubo distal à fístula e proximal à carina&lt;/strong&gt;, o que costuma ser obtido intubando deliberadamente o brônquio principal direito e recuando o tubo até auscultar ambos os hemitórax, com o bisel voltado anteriormente. Prefere-se manter &lt;strong&gt;ventilação espontânea ou pressões baixas&lt;/strong&gt; até a ligadura da fístula, e a aspiração contínua do coto proximal reduz a aspiração de saliva.&lt;/p&gt;&lt;p&gt;Deve-se ainda rastrear as malformações associadas do espectro VACTERL, sobretudo as cardíacas e as renais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ventilação manual vigorosa é precisamente a manobra que insufla o estômago pela fístula. (B) a posição alta deixa o tubo acima da fístula, o cenário mais perigoso. (C) a intubação orotraqueal com posicionamento cuidadoso é a técnica padrão, e a traqueostomia não tem lugar na rotina.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A forma mais comum de atresia de esôfago, respondendo por cerca de 85% dos casos, é a que combina &lt;strong&gt;coto esofágico proximal cego com fístula entre a traqueia e o esôfago distal&lt;/strong&gt;. A tríade clínica é sialorreia, impossibilidade de progredir a sonda e distensão gástrica, esta última justamente porque o ar da traqueia escapa pela fístula para o estômago.&lt;/p&gt;&lt;p&gt;O ponto crítico do manejo anestésico decorre dessa anatomia. Se a ponta do tubo ficar &lt;strong&gt;acima do orifício fistuloso&lt;/strong&gt; e se aplicarem pressões positivas altas, o gás segue preferencialmente pelo caminho de menor resistência: insufla o estômago, eleva o diafragma, compromete a ventilação e pode chegar à perfuração gástrica. A estratégia é posicionar a &lt;strong&gt;ponta do tubo distal à fístula e proximal à carina&lt;/strong&gt;, o que costuma ser obtido intubando deliberadamente o brônquio principal direito e recuando o tubo até auscultar ambos os hemitórax, com o bisel voltado anteriormente. Prefere-se manter &lt;strong&gt;ventilação espontânea ou pressões baixas&lt;/strong&gt; até a ligadura da fístula, e a aspiração contínua do coto proximal reduz a aspiração de saliva.&lt;/p&gt;&lt;p&gt;Deve-se ainda rastrear as malformações associadas do espectro VACTERL, sobretudo as cardíacas e as renais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ventilação manual vigorosa é precisamente a manobra que insufla o estômago pela fístula. (B) a posição alta deixa o tubo acima da fístula, o cenário mais perigoso. (C) a intubação orotraqueal com posicionamento cuidadoso é a técnica padrão, e a traqueostomia não tem lugar na rotina.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As duas malformações de parede abdominal se distinguem por características anatômicas simples, que têm consequências anestésicas diretas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Gastrosquise:&lt;/strong&gt; defeito paraumbilical, quase sempre &lt;em&gt;à direita&lt;/em&gt; do cordão, &lt;strong&gt;sem saco de revestimento&lt;/strong&gt;. As alças ficam expostas ao líquido amniótico durante a gestação, o que as deixa espessadas, edemaciadas e com peritonite química. Associa-se pouco a outras malformações — a atresia intestinal é a exceção relevante — e é mais frequente em mães jovens.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Onfalocele:&lt;/strong&gt; defeito &lt;em&gt;central&lt;/em&gt;, na base do cordão, com o conteúdo &lt;strong&gt;recoberto por saco de âmnio e peritônio&lt;/strong&gt;, podendo incluir o fígado. Associa-se fortemente a outras anomalias: cardiopatias congênitas (em torno de um terço dos casos), trissomias 13, 18 e 21, síndrome de Beckwith-Wiedemann e pentalogia de Cantrell.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A implicação prática é clara. Na gastrosquise, a ausência de membrana produz &lt;strong&gt;perdas evaporativas de calor e de água muito maiores&lt;/strong&gt;, exigindo cobertura imediata das alças, aquecimento agressivo e reposição volêmica generosa. Na onfalocele, o esforço maior recai sobre a investigação das anomalias associadas, sobretudo a cardíaca, antes da anestesia. Em ambas, o fechamento da parede pode elevar a pressão intra-abdominal, comprometendo ventilação, retorno venoso e perfusão renal e intestinal, o que às vezes obriga o fechamento estagiado com silo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (D) o caso descreve defeito lateral e sem membrana, o que exclui onfalocele; e a onfalocele íntegra perde menos líquido. (C) as associações sindrômicas e cromossômicas pertencem à onfalocele, não à gastrosquise.&lt;/p&gt;</t>
+          <t>&lt;p&gt;As duas malformações de parede abdominal se distinguem por características anatômicas simples, que têm consequências anestésicas diretas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Gastrosquise:&lt;/strong&gt; defeito paraumbilical, quase sempre &lt;em&gt;à direita&lt;/em&gt; do cordão, &lt;strong&gt;sem saco de revestimento&lt;/strong&gt;. As alças ficam expostas ao líquido amniótico durante a gestação, o que as deixa espessadas, edemaciadas e com peritonite química. Associa-se pouco a outras malformações (a atresia intestinal é a exceção relevante) e é mais frequente em mães jovens.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Onfalocele:&lt;/strong&gt; defeito &lt;em&gt;central&lt;/em&gt;, na base do cordão, com o conteúdo &lt;strong&gt;recoberto por saco de âmnio e peritônio&lt;/strong&gt;, podendo incluir o fígado. Associa-se fortemente a outras anomalias: cardiopatias congênitas (em torno de um terço dos casos), trissomias 13, 18 e 21, síndrome de Beckwith-Wiedemann e pentalogia de Cantrell.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A implicação prática é clara. Na gastrosquise, a ausência de membrana produz &lt;strong&gt;perdas evaporativas de calor e de água muito maiores&lt;/strong&gt;, exigindo cobertura imediata das alças, aquecimento agressivo e reposição volêmica generosa. Na onfalocele, o esforço maior recai sobre a investigação das anomalias associadas, sobretudo a cardíaca, antes da anestesia. Em ambas, o fechamento da parede pode elevar a pressão intra-abdominal, comprometendo ventilação, retorno venoso e perfusão renal e intestinal, o que às vezes obriga o fechamento estagiado com silo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (D) o caso descreve defeito lateral e sem membrana, o que exclui onfalocele; e a onfalocele íntegra perde menos líquido. (C) as associações sindrômicas e cromossômicas pertencem à onfalocele, não à gastrosquise.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O tempo de apneia segura é determinado pela razão entre o reservatório de oxigênio (essencialmente a capacidade residual funcional, ou CRF, preenchida de oxigênio após a pré-oxigenação) e a taxa com que esse reservatório é consumido. O lactente está em desvantagem nas duas pontas.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;consumo de oxigênio no lactente situa-se entre 6 e 8 mL/kg/min&lt;/strong&gt;, aproximadamente o dobro dos 3 a 4 mL/kg/min do adulto, refletindo a alta taxa metabólica do crescimento. Ao mesmo tempo, a caixa torácica é muito complacente, as costelas são horizontalizadas e a musculatura intercostal é pouco eficiente, de modo que a parede não se opõe adequadamente ao recolhimento elástico pulmonar. A CRF real é pequena e, sobretudo, a &lt;strong&gt;capacidade de fechamento situa-se acima da CRF&lt;/strong&gt; até cerca de 6 anos, com colapso de vias aéreas já em volume corrente — fenômeno agravado pela anestesia e pelo decúbito dorsal.&lt;/p&gt;&lt;p&gt;Combinando reservatório reduzido com consumo dobrado, a dessaturação após a apneia ocorre em segundos, e não em minutos. Daí decorrem recomendações práticas como pré-oxigenação cuidadosa, uso de pressão positiva contínua durante a indução e, em muitos serviços, ventilação suave sob máscara mesmo em sequência rápida modificada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o consumo de oxigênio pediátrico é claramente maior, e a descrição da laringoscopia não sugere laringoespasmo. (B) a CRF do lactente não é proporcionalmente maior, e o achado é absolutamente típico da idade. (D) a hemoglobina fetal desloca a curva para a &lt;em&gt;esquerda&lt;/em&gt;, aumentando a afinidade pelo oxigênio, e aos 6 meses ela já é residual.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O tempo de apneia segura é determinado pela razão entre o reservatório de oxigênio (essencialmente a capacidade residual funcional, ou CRF, preenchida de oxigênio após a pré-oxigenação) e a taxa com que esse reservatório é consumido. O lactente está em desvantagem nas duas pontas.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;consumo de oxigênio no lactente situa-se entre 6 e 8 mL/kg/min&lt;/strong&gt;, aproximadamente o dobro dos 3 a 4 mL/kg/min do adulto, refletindo a alta taxa metabólica do crescimento. Ao mesmo tempo, a caixa torácica é muito complacente, as costelas são horizontalizadas e a musculatura intercostal é pouco eficiente, de modo que a parede não se opõe adequadamente ao recolhimento elástico pulmonar. A CRF real é pequena e, sobretudo, a &lt;strong&gt;capacidade de fechamento situa-se acima da CRF&lt;/strong&gt; até cerca de 6 anos, com colapso de vias aéreas já em volume corrente, fenômeno agravado pela anestesia e pelo decúbito dorsal.&lt;/p&gt;&lt;p&gt;Combinando reservatório reduzido com consumo dobrado, a dessaturação após a apneia ocorre em segundos, e não em minutos. Daí decorrem recomendações práticas como pré-oxigenação cuidadosa, uso de pressão positiva contínua durante a indução e, em muitos serviços, ventilação suave sob máscara mesmo em sequência rápida modificada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o consumo de oxigênio pediátrico é claramente maior, e a descrição da laringoscopia não sugere laringoespasmo. (B) a CRF do lactente não é proporcionalmente maior, e o achado é absolutamente típico da idade. (D) a hemoglobina fetal desloca a curva para a &lt;em&gt;esquerda&lt;/em&gt;, aumentando a afinidade pelo oxigênio, e aos 6 meses ela já é residual.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O miocárdio neonatal é imaturo em quase todos os sentidos: tem &lt;strong&gt;menor proporção de elementos contráteis&lt;/strong&gt; em relação ao tecido não contrátil, retículo sarcoplasmático pouco desenvolvido com maior dependência do cálcio extracelular, ventrículos pouco complacentes e interdependência ventricular acentuada. Como consequência, o neonato &lt;strong&gt;opera próximo ao topo da sua curva de Frank-Starling&lt;/strong&gt; e tem capacidade muito limitada de aumentar o volume sistólico.&lt;/p&gt;&lt;p&gt;Se o débito cardíaco é o produto do volume sistólico pela frequência e o primeiro termo é praticamente fixo, o débito passa a ser &lt;strong&gt;essencialmente dependente da frequência cardíaca&lt;/strong&gt;. Bradicardia, nessa faixa etária, equivale a baixo débito, e a resposta deve ser imediata.&lt;/p&gt;&lt;p&gt;A conduta segue uma sequência conhecida: antes de tudo, excluir e tratar a &lt;strong&gt;hipóxia&lt;/strong&gt;, causa mais comum de bradicardia na criança — ventilar com oxigênio a 100% e checar a via aérea. Em seguida, reconhecer a &lt;strong&gt;sobredose de halogenado&lt;/strong&gt;, causa provável aqui, e reduzir a concentração inspirada. Administrar &lt;strong&gt;atropina 0,02 mg/kg&lt;/strong&gt; por via venosa (dose mínima habitual de 0,1 mg) e, se a frequência não responder ou houver sinais de parada iminente, adrenalina e compressões torácicas conforme protocolo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o volume sistólico neonatal não compensa a bradicardia, e manter o halogenado perpetua a causa. (C) trata-se de bradicardia com baixo débito, não de vasoplegia isolada; noradrenalina não corrige a frequência. (D) frequência de 76 bpm em recém-nascido caracteriza bradicardia grave, e a queda pressórica associada exclui qualquer leitura de normalidade.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O miocárdio neonatal é imaturo em quase todos os sentidos: tem &lt;strong&gt;menor proporção de elementos contráteis&lt;/strong&gt; em relação ao tecido não contrátil, retículo sarcoplasmático pouco desenvolvido com maior dependência do cálcio extracelular, ventrículos pouco complacentes e interdependência ventricular acentuada. Como consequência, o neonato &lt;strong&gt;opera próximo ao topo da sua curva de Frank-Starling&lt;/strong&gt; e tem capacidade muito limitada de aumentar o volume sistólico.&lt;/p&gt;&lt;p&gt;Se o débito cardíaco é o produto do volume sistólico pela frequência e o primeiro termo é praticamente fixo, o débito passa a ser &lt;strong&gt;essencialmente dependente da frequência cardíaca&lt;/strong&gt;. Bradicardia, nessa faixa etária, equivale a baixo débito, e a resposta deve ser imediata.&lt;/p&gt;&lt;p&gt;A conduta segue uma sequência conhecida: antes de tudo, excluir e tratar a &lt;strong&gt;hipóxia&lt;/strong&gt;, causa mais comum de bradicardia na criança: ventilar com oxigênio a 100% e checar a via aérea. Em seguida, reconhecer a &lt;strong&gt;sobredose de halogenado&lt;/strong&gt;, causa provável aqui, e reduzir a concentração inspirada. Administrar &lt;strong&gt;atropina 0,02 mg/kg&lt;/strong&gt; por via venosa (dose mínima habitual de 0,1 mg) e, se a frequência não responder ou houver sinais de parada iminente, adrenalina e compressões torácicas conforme protocolo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o volume sistólico neonatal não compensa a bradicardia, e manter o halogenado perpetua a causa. (C) trata-se de bradicardia com baixo débito, não de vasoplegia isolada; noradrenalina não corrige a frequência. (D) frequência de 76 bpm em recém-nascido caracteriza bradicardia grave, e a queda pressórica associada exclui qualquer leitura de normalidade.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O envelhecimento cardiovascular tem um eixo central: a &lt;strong&gt;perda de elastina e o acúmulo de colágeno&lt;/strong&gt; nas grandes artérias e no miocárdio. Daí decorre praticamente tudo o que importa em sala.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Rigidez arterial:&lt;/strong&gt; a aorta perde complacência, a onda de pulso viaja mais rápido e reflete precocemente, elevando a pressão sistólica e a pressão de pulso enquanto a diastólica permanece normal ou baixa. É o padrão da &lt;strong&gt;hipertensão sistólica isolada&lt;/strong&gt;, exatamente o do caso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipertrofia e disfunção diastólica:&lt;/strong&gt; o ventrículo hipertrofiado enche-se mal e depende de forma crítica da pré-carga adequada e da &lt;strong&gt;contração atrial&lt;/strong&gt;, que pode responder por até 30% a 40% do enchimento. Perder o ritmo sinusal ou reduzir o volume intravascular derruba o débito de forma desproporcional.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dessensibilização beta-adrenérgica:&lt;/strong&gt; a resposta cronotrópica e inotrópica às catecolaminas cai, assim como a frequência cardíaca máxima. O idoso não taquicardiza para compensar hipotensão, e passa a depender mais do mecanismo de Frank-Starling — justamente o que a simpatectomia do bloqueio neuroaxial compromete.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Na prática, isso significa titular o bloqueio, corrigir a hipovolemia antes da punção e tratar a hipotensão com vasopressor precocemente, sem esperar por uma taquicardia que não virá.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a complacência arterial e ventricular &lt;em&gt;diminui&lt;/em&gt; com a idade. (C) e (D) descrevem uma reserva autonômica preservada ou aumentada, o oposto da dessensibilização beta-adrenérgica e da queda da frequência máxima observadas no envelhecimento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O envelhecimento cardiovascular tem um eixo central: a &lt;strong&gt;perda de elastina e o acúmulo de colágeno&lt;/strong&gt; nas grandes artérias e no miocárdio. Daí decorre praticamente tudo o que importa em sala.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Rigidez arterial:&lt;/strong&gt; a aorta perde complacência, a onda de pulso viaja mais rápido e reflete precocemente, elevando a pressão sistólica e a pressão de pulso enquanto a diastólica permanece normal ou baixa. É o padrão da &lt;strong&gt;hipertensão sistólica isolada&lt;/strong&gt;, exatamente o do caso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipertrofia e disfunção diastólica:&lt;/strong&gt; o ventrículo hipertrofiado enche-se mal e depende de forma crítica da pré-carga adequada e da &lt;strong&gt;contração atrial&lt;/strong&gt;, que pode responder por até 30% a 40% do enchimento. Perder o ritmo sinusal ou reduzir o volume intravascular derruba o débito de forma desproporcional.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dessensibilização beta-adrenérgica:&lt;/strong&gt; a resposta cronotrópica e inotrópica às catecolaminas cai, assim como a frequência cardíaca máxima. O idoso não taquicardiza para compensar hipotensão, e passa a depender mais do mecanismo de Frank-Starling, justamente o que a simpatectomia do bloqueio neuroaxial compromete.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Na prática, isso significa titular o bloqueio, corrigir a hipovolemia antes da punção e tratar a hipotensão com vasopressor precocemente, sem esperar por uma taquicardia que não virá.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a complacência arterial e ventricular &lt;em&gt;diminui&lt;/em&gt; com a idade. (C) e (D) descrevem uma reserva autonômica preservada ou aumentada, o oposto da dessensibilização beta-adrenérgica e da queda da frequência máxima observadas no envelhecimento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;buprenorfina&lt;/strong&gt; é agonista parcial do receptor &lt;em&gt;mu&lt;/em&gt; com afinidade muito elevada e dissociação lenta do receptor. Essa combinação explica seu perfil clínico: ocupa o receptor por horas, produz efeito submáximo (com teto para depressão respiratória) e, ao mesmo tempo, dificulta que agonistas plenos como fentanil, morfina ou hidromorfona alcancem efeito máximo, porque competem mal por um receptor já ocupado por um ligante de alta afinidade.&lt;/p&gt;&lt;p&gt;Na prática, o paciente em uso crônico de buprenorfina apresenta tolerância e ocupação receptorial, e a analgesia pós-operatória deve ser planejada com &lt;strong&gt;estratégia multimodal&lt;/strong&gt;: bloqueios regionais ou infiltração, anti-inflamatórios, dipirona ou paracetamol, cetamina em dose baixa e, quando necessário, agonista pleno titulado em doses maiores que as habituais, sob vigilância. Suspender abruptamente a buprenorfina não é conduta de rotina, pois expõe o paciente à abstinência e à recaída.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a buprenorfina não é antagonista puro — esse papel cabe à naloxona e ao naltrexone; ela mantém atividade intrínseca parcial. (B) não é agonista pleno, e a dose de manutenção antiadictiva, tomada uma vez ao dia, não cobre a dor aguda cirúrgica. (D) a afinidade pelo receptor mu é alta, e não baixa; justamente por isso o deslocamento por doses convencionais de agonista pleno é difícil e a reversão com naloxona é incompleta.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;buprenorfina&lt;/strong&gt; é agonista parcial do receptor &lt;em&gt;mu&lt;/em&gt; com afinidade muito elevada e dissociação lenta do receptor. Essa combinação explica seu perfil clínico: ocupa o receptor por horas, produz efeito submáximo (com teto para depressão respiratória) e, ao mesmo tempo, dificulta que agonistas plenos como fentanil, morfina ou hidromorfona alcancem efeito máximo, porque competem mal por um receptor já ocupado por um ligante de alta afinidade.&lt;/p&gt;&lt;p&gt;Na prática, o paciente em uso crônico de buprenorfina apresenta tolerância e ocupação receptorial, e a analgesia pós-operatória deve ser planejada com &lt;strong&gt;estratégia multimodal&lt;/strong&gt;: bloqueios regionais ou infiltração, anti-inflamatórios, dipirona ou paracetamol, cetamina em dose baixa e, quando necessário, agonista pleno titulado em doses maiores que as habituais, sob vigilância. Suspender abruptamente a buprenorfina não é conduta de rotina, pois expõe o paciente à abstinência e à recaída.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a buprenorfina não é antagonista puro: esse papel cabe à naloxona e ao naltrexone; ela mantém atividade intrínseca parcial. (B) não é agonista pleno, e a dose de manutenção antiadictiva, tomada uma vez ao dia, não cobre a dor aguda cirúrgica. (D) a afinidade pelo receptor mu é alta, e não baixa; justamente por isso o deslocamento por doses convencionais de agonista pleno é difícil e a reversão com naloxona é incompleta.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O receptor &lt;strong&gt;NMDA&lt;/strong&gt; é um canal iônico ativado por glutamato cuja peculiaridade é o &lt;strong&gt;bloqueio pelo íon magnésio no interior do poro&lt;/strong&gt;, dependente do potencial de membrana. Em repouso, ainda que o glutamato se ligue, o canal permanece obstruído. Quando estímulos repetitivos de fibras C despolarizam de forma sustentada o neurônio de segunda ordem, o magnésio é expulso e o canal se torna condutivo a sódio e, sobretudo, a &lt;strong&gt;cálcio&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O influxo de cálcio desencadeia cascatas intracelulares — proteinocinase C, óxido nítrico sintase, expressão de genes precoces — que aumentam a excitabilidade do neurônio. Esse é o substrato do fenômeno de &lt;em&gt;wind-up&lt;/em&gt; e da &lt;strong&gt;sensibilização central&lt;/strong&gt;, com hiperalgesia, alodinia e ampliação do campo receptivo. Também é a base racional do uso de antagonistas NMDA, como a cetamina em dose baixa, para reduzir hiperalgesia e consumo de opioides.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a transmissão sináptica rápida de um estímulo nociceptivo isolado é mediada pelo receptor &lt;em&gt;AMPA&lt;/em&gt;; o NMDA entra em cena na estimulação repetitiva. (B) o canal é permeável a cálcio além de sódio, e sua abertura depende simultaneamente do ligante e da despolarização — é um detector de coincidência. (C) a ativação do NMDA despolariza e &lt;em&gt;amplifica&lt;/em&gt; a resposta a estímulos repetidos, exatamente o oposto de uma hiperpolarização com adaptação progressiva.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O receptor &lt;strong&gt;NMDA&lt;/strong&gt; é um canal iônico ativado por glutamato cuja peculiaridade é o &lt;strong&gt;bloqueio pelo íon magnésio no interior do poro&lt;/strong&gt;, dependente do potencial de membrana. Em repouso, ainda que o glutamato se ligue, o canal permanece obstruído. Quando estímulos repetitivos de fibras C despolarizam de forma sustentada o neurônio de segunda ordem, o magnésio é expulso e o canal se torna condutivo a sódio e, sobretudo, a &lt;strong&gt;cálcio&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O influxo de cálcio desencadeia cascatas intracelulares (proteinocinase C, óxido nítrico sintase, expressão de genes precoces) que aumentam a excitabilidade do neurônio. Esse é o substrato do fenômeno de &lt;em&gt;wind-up&lt;/em&gt; e da &lt;strong&gt;sensibilização central&lt;/strong&gt;, com hiperalgesia, alodinia e ampliação do campo receptivo. Também é a base racional do uso de antagonistas NMDA, como a cetamina em dose baixa, para reduzir hiperalgesia e consumo de opioides.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a transmissão sináptica rápida de um estímulo nociceptivo isolado é mediada pelo receptor &lt;em&gt;AMPA&lt;/em&gt;; o NMDA entra em cena na estimulação repetitiva. (B) o canal é permeável a cálcio além de sódio, e sua abertura depende simultaneamente do ligante e da despolarização: é um detector de coincidência. (C) a ativação do NMDA despolariza e &lt;em&gt;amplifica&lt;/em&gt; a resposta a estímulos repetidos, exatamente o oposto de uma hiperpolarização com adaptação progressiva.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;neuralgia pós-herpética&lt;/strong&gt; é a complicação mais temida do herpes-zóster e costuma ser definida pela persistência da dor por mais de três meses após a cicatrização das lesões cutâneas. Sua fisiopatologia combina lesão do gânglio da raiz dorsal, perda de aferentes de grosso calibre e sensibilização central, o que explica o padrão neuropático com queimação contínua, choques e &lt;em&gt;alodinia&lt;/em&gt; mecânica.&lt;/p&gt;&lt;p&gt;Dois dados epidemiológicos são consagrados: a incidência cresce de forma acentuada com a &lt;strong&gt;idade&lt;/strong&gt;, sendo pouco frequente antes dos 50 anos e muito comum acima dos 70; e a distribuição preferencial é &lt;strong&gt;torácica&lt;/strong&gt;, seguida pelo ramo oftálmico do trigêmeo. Outros preditores são dor aguda intensa, pródromo doloroso e exantema extenso. O tratamento apoia-se em gabapentinoides, antidepressivos tricíclicos e lidocaína tópica, com opioides em segunda linha.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o intervalo consagrado é de cerca de três meses após a cicatrização, e não de sete dias — nesse prazo ainda se trata da dor da fase aguda ou subaguda. (C) inverte a frequência: a forma torácica supera amplamente a oftálmica, e a idade é o principal fator de risco. (D) o antiviral tem benefício quando iniciado nas primeiras 72 horas do exantema, reduzindo a duração da dor aguda; instituído após a cicatrização, não modifica o desfecho — a prevenção mais efetiva é a vacinação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;neuralgia pós-herpética&lt;/strong&gt; é a complicação mais temida do herpes-zóster e costuma ser definida pela persistência da dor por mais de três meses após a cicatrização das lesões cutâneas. Sua fisiopatologia combina lesão do gânglio da raiz dorsal, perda de aferentes de grosso calibre e sensibilização central, o que explica o padrão neuropático com queimação contínua, choques e &lt;em&gt;alodinia&lt;/em&gt; mecânica.&lt;/p&gt;&lt;p&gt;Dois dados epidemiológicos são consagrados: a incidência cresce de forma acentuada com a &lt;strong&gt;idade&lt;/strong&gt;, sendo pouco frequente antes dos 50 anos e muito comum acima dos 70; e a distribuição preferencial é &lt;strong&gt;torácica&lt;/strong&gt;, seguida pelo ramo oftálmico do trigêmeo. Outros preditores são dor aguda intensa, pródromo doloroso e exantema extenso. O tratamento apoia-se em gabapentinoides, antidepressivos tricíclicos e lidocaína tópica, com opioides em segunda linha.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o intervalo consagrado é de cerca de três meses após a cicatrização, e não de sete dias; nesse prazo ainda se trata da dor da fase aguda ou subaguda. (C) inverte a frequência: a forma torácica supera amplamente a oftálmica, e a idade é o principal fator de risco. (D) o antiviral tem benefício quando iniciado nas primeiras 72 horas do exantema, reduzindo a duração da dor aguda; instituído após a cicatrização, não modifica o desfecho; a prevenção mais efetiva é a vacinação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Rexed dividiu a substância cinzenta medular em dez lâminas com base na citoarquitetura. No corno dorsal, as camadas superficiais são o ponto de entrada da informação nociceptiva. A &lt;strong&gt;lâmina I&lt;/strong&gt;, ou zona marginal, recebe fibras A-delta e C e concentra neurônios nociceptivos específicos. A &lt;strong&gt;lâmina II&lt;/strong&gt; corresponde à &lt;strong&gt;substância gelatinosa&lt;/strong&gt;, densamente povoada por interneurônios, e é o principal alvo das &lt;strong&gt;fibras C&lt;/strong&gt; amielínicas. A &lt;strong&gt;lâmina V&lt;/strong&gt; abriga os neurônios de ampla faixa dinâmica, que recebem convergência de aferências somáticas e viscerais — base anatômica da dor referida.&lt;/p&gt;&lt;p&gt;A substância gelatinosa é também o local de maior densidade de &lt;strong&gt;receptores opioides&lt;/strong&gt; espinhais e o ponto onde interneurônios inibitórios, ativados por fibras A-beta de grosso calibre, modulam a transmissão nociceptiva — o substrato da teoria da comporta e do efeito do TENS.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde as camadas: a lâmina V é a dos neurônios de ampla faixa dinâmica, e a substância gelatinosa é a lâmina II. (B) as lâminas VII e VIII são regiões intermediária e do corno ventral, ligadas ao processamento motor; as fibras C terminam superficialmente, nas lâminas I e II, com projeções para a V. (D) a lâmina I é essencialmente nociceptiva e termorreceptiva; a propriocepção de fibras grossas segue pelas colunas dorsais e projeta-se a camadas mais profundas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Rexed dividiu a substância cinzenta medular em dez lâminas com base na citoarquitetura. No corno dorsal, as camadas superficiais são o ponto de entrada da informação nociceptiva. A &lt;strong&gt;lâmina I&lt;/strong&gt;, ou zona marginal, recebe fibras A-delta e C e concentra neurônios nociceptivos específicos. A &lt;strong&gt;lâmina II&lt;/strong&gt; corresponde à &lt;strong&gt;substância gelatinosa&lt;/strong&gt;, densamente povoada por interneurônios, e é o principal alvo das &lt;strong&gt;fibras C&lt;/strong&gt; amielínicas. A &lt;strong&gt;lâmina V&lt;/strong&gt; abriga os neurônios de ampla faixa dinâmica, que recebem convergência de aferências somáticas e viscerais, base anatômica da dor referida.&lt;/p&gt;&lt;p&gt;A substância gelatinosa é também o local de maior densidade de &lt;strong&gt;receptores opioides&lt;/strong&gt; espinhais e o ponto onde interneurônios inibitórios, ativados por fibras A-beta de grosso calibre, modulam a transmissão nociceptiva, o substrato da teoria da comporta e do efeito do TENS.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde as camadas: a lâmina V é a dos neurônios de ampla faixa dinâmica, e a substância gelatinosa é a lâmina II. (B) as lâminas VII e VIII são regiões intermediária e do corno ventral, ligadas ao processamento motor; as fibras C terminam superficialmente, nas lâminas I e II, com projeções para a V. (D) a lâmina I é essencialmente nociceptiva e termorreceptiva; a propriocepção de fibras grossas segue pelas colunas dorsais e projeta-se a camadas mais profundas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;dor visceral&lt;/strong&gt; tem características próprias que decorrem da inervação esparsa das vísceras e da organização das vias aferentes. Os nociceptores viscerais são poucos e amplamente distribuídos, e suas fibras aferentes — em grande parte amielínicas — acompanham os nervos simpáticos, mas têm corpo celular no gânglio da raiz dorsal e entram na medula pelas &lt;strong&gt;raízes dorsais&lt;/strong&gt;, convergindo sobre neurônios de ampla faixa dinâmica que também recebem aferências cutâneas.&lt;/p&gt;&lt;p&gt;Dessa convergência nasce a &lt;strong&gt;dor referida&lt;/strong&gt;: o córtex interpreta o sinal como proveniente do dermátomo somático correspondente, daí a irradiação para o dorso na pancreatite ou para o ombro na irritação diafragmática. A ativação simultânea de reflexos autonômicos explica náusea, sudorese, palidez e alterações hemodinâmicas. Os &lt;strong&gt;estímulos adequados&lt;/strong&gt; são distensão, isquemia, tração, espasmo e inflamação — não o corte nem a queimadura, que podem ser aplicados a uma víscera sem provocar dor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a boa localização e a reprodutibilidade à palpação são atributos da dor somática, especialmente da somática superficial. (C) inverte os estímulos adequados: seccionar ou cauterizar uma alça intestinal costuma ser indolor, enquanto distendê-la produz dor intensa. (D) as fibras são predominantemente C e A-delta, entram pela raiz dorsal e convergem com aferências somáticas — convergência que é justamente a base da dor referida.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;dor visceral&lt;/strong&gt; tem características próprias que decorrem da inervação esparsa das vísceras e da organização das vias aferentes. Os nociceptores viscerais são poucos e amplamente distribuídos, e suas fibras aferentes (em grande parte amielínicas) acompanham os nervos simpáticos, mas têm corpo celular no gânglio da raiz dorsal e entram na medula pelas &lt;strong&gt;raízes dorsais&lt;/strong&gt;, convergindo sobre neurônios de ampla faixa dinâmica que também recebem aferências cutâneas.&lt;/p&gt;&lt;p&gt;Dessa convergência nasce a &lt;strong&gt;dor referida&lt;/strong&gt;: o córtex interpreta o sinal como proveniente do dermátomo somático correspondente, daí a irradiação para o dorso na pancreatite ou para o ombro na irritação diafragmática. A ativação simultânea de reflexos autonômicos explica náusea, sudorese, palidez e alterações hemodinâmicas. Os &lt;strong&gt;estímulos adequados&lt;/strong&gt; são distensão, isquemia, tração, espasmo e inflamação, não o corte nem a queimadura, que podem ser aplicados a uma víscera sem provocar dor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a boa localização e a reprodutibilidade à palpação são atributos da dor somática, especialmente da somática superficial. (C) inverte os estímulos adequados: seccionar ou cauterizar uma alça intestinal costuma ser indolor, enquanto distendê-la produz dor intensa. (D) as fibras são predominantemente C e A-delta, entram pela raiz dorsal e convergem com aferências somáticas, convergência que é justamente a base da dor referida.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os receptores opioides &lt;em&gt;mu&lt;/em&gt;, &lt;em&gt;delta&lt;/em&gt; e &lt;em&gt;kappa&lt;/em&gt; pertencem à família dos receptores acoplados à proteína G, especificamente à subunidade inibitória &lt;strong&gt;Gi/Go&lt;/strong&gt;. Sua ativação produz três efeitos convergentes, todos redutores da transmissão nociceptiva.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Inibição da &lt;strong&gt;adenilato ciclase&lt;/strong&gt;, com queda do AMP cíclico intracelular.&lt;/li&gt;&lt;li&gt;Abertura de &lt;strong&gt;canais de potássio&lt;/strong&gt; na membrana pós-sináptica, com efluxo de potássio, hiperpolarização e menor probabilidade de disparo do neurônio de segunda ordem.&lt;/li&gt;&lt;li&gt;Inibição de &lt;strong&gt;canais de cálcio voltagem-dependentes&lt;/strong&gt; na terminação pré-sináptica, reduzindo o influxo de cálcio e, com ele, a liberação de neurotransmissores excitatórios como glutamato, substância P e peptídeo relacionado ao gene da calcitonina.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A combinação de ação pré e pós-sináptica na substância gelatinosa é o que fundamenta a eficácia dos opioides administrados por via neuroaxial, onde atuam diretamente sobre receptores medulares em doses muito menores que as sistêmicas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o acoplamento é a Gi, e não a Gs; o AMP cíclico &lt;em&gt;cai&lt;/em&gt;, e a excitabilidade neuronal diminui. (B) os opioides não abrem canais de sódio nem atuam por depleção de neurotransmissor; a redução da liberação decorre do bloqueio do influxo de cálcio. (C) o efeito sobre o cloreto não é bloqueio da ação gabaérgica — isso aumentaria a excitabilidade e seria pró-nociceptivo, exatamente o contrário do observado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os receptores opioides &lt;em&gt;mu&lt;/em&gt;, &lt;em&gt;delta&lt;/em&gt; e &lt;em&gt;kappa&lt;/em&gt; pertencem à família dos receptores acoplados à proteína G, especificamente à subunidade inibitória &lt;strong&gt;Gi/Go&lt;/strong&gt;. Sua ativação produz três efeitos convergentes, todos redutores da transmissão nociceptiva.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Inibição da &lt;strong&gt;adenilato ciclase&lt;/strong&gt;, com queda do AMP cíclico intracelular.&lt;/li&gt;&lt;li&gt;Abertura de &lt;strong&gt;canais de potássio&lt;/strong&gt; na membrana pós-sináptica, com efluxo de potássio, hiperpolarização e menor probabilidade de disparo do neurônio de segunda ordem.&lt;/li&gt;&lt;li&gt;Inibição de &lt;strong&gt;canais de cálcio voltagem-dependentes&lt;/strong&gt; na terminação pré-sináptica, reduzindo o influxo de cálcio e, com ele, a liberação de neurotransmissores excitatórios como glutamato, substância P e peptídeo relacionado ao gene da calcitonina.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A combinação de ação pré e pós-sináptica na substância gelatinosa é o que fundamenta a eficácia dos opioides administrados por via neuroaxial, onde atuam diretamente sobre receptores medulares em doses muito menores que as sistêmicas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o acoplamento é a Gi, e não a Gs; o AMP cíclico &lt;em&gt;cai&lt;/em&gt;, e a excitabilidade neuronal diminui. (B) os opioides não abrem canais de sódio nem atuam por depleção de neurotransmissor; a redução da liberação decorre do bloqueio do influxo de cálcio. (C) o efeito sobre o cloreto não é bloqueio da ação gabaérgica: isso aumentaria a excitabilidade e seria pró-nociceptivo, exatamente o contrário do observado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A administração de opioides por via &lt;strong&gt;neuroaxial&lt;/strong&gt; aproveita a alta densidade de receptores na substância gelatinosa. Como a via intratecal deposita o fármaco diretamente no liquor, sem a barreira da dura-máter e sem a absorção pela gordura e pelo plexo venoso peridural, a dose necessária é muito menor. A regra prática consagrada é uma relação aproximada de &lt;strong&gt;10:1 entre a dose peridural e a intratecal&lt;/strong&gt; — e de cerca de 10:1 entre a dose sistêmica e a peridural. Assim, doses intratecais de morfina na faixa de 0,1 a 0,2 mg produzem analgesia comparável a alguns miligramas por via peridural.&lt;/p&gt;&lt;p&gt;A morfina é &lt;strong&gt;hidrofílica&lt;/strong&gt;, o que prolonga sua permanência no liquor e permite analgesia de 18 a 24 horas, mas também favorece a &lt;strong&gt;migração rostral&lt;/strong&gt; até os centros respiratórios bulbares. Daí a característica depressão respiratória &lt;em&gt;tardia&lt;/em&gt;, que pode ocorrer de 6 a 12 horas após a injeção, exigindo monitorização da frequência respiratória e do nível de consciência por até 24 horas. Prurido e náusea são os efeitos adversos mais frequentes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte a relação — a via intratecal exige dose bem menor, não maior. (C) as doses não são equivalentes, e o risco respiratório da morfina neuroaxial é justamente tardio, e não restrito aos primeiros minutos. (D) a menor dose não decorre de absorção sistêmica mais rápida, e encerrar a vigilância na sala de recuperação deixa o paciente desprotegido no período de maior risco.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A administração de opioides por via &lt;strong&gt;neuroaxial&lt;/strong&gt; aproveita a alta densidade de receptores na substância gelatinosa. Como a via intratecal deposita o fármaco diretamente no liquor, sem a barreira da dura-máter e sem a absorção pela gordura e pelo plexo venoso peridural, a dose necessária é muito menor. A regra prática consagrada é uma relação aproximada de &lt;strong&gt;10:1 entre a dose peridural e a intratecal&lt;/strong&gt;, e de cerca de 10:1 entre a dose sistêmica e a peridural. Assim, doses intratecais de morfina na faixa de 0,1 a 0,2 mg produzem analgesia comparável a alguns miligramas por via peridural.&lt;/p&gt;&lt;p&gt;A morfina é &lt;strong&gt;hidrofílica&lt;/strong&gt;, o que prolonga sua permanência no liquor e permite analgesia de 18 a 24 horas, mas também favorece a &lt;strong&gt;migração rostral&lt;/strong&gt; até os centros respiratórios bulbares. Daí a característica depressão respiratória &lt;em&gt;tardia&lt;/em&gt;, que pode ocorrer de 6 a 12 horas após a injeção, exigindo monitorização da frequência respiratória e do nível de consciência por até 24 horas. Prurido e náusea são os efeitos adversos mais frequentes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte a relação: a via intratecal exige dose bem menor, não maior. (C) as doses não são equivalentes, e o risco respiratório da morfina neuroaxial é justamente tardio, e não restrito aos primeiros minutos. (D) a menor dose não decorre de absorção sistêmica mais rápida, e encerrar a vigilância na sala de recuperação deixa o paciente desprotegido no período de maior risco.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;analgesia controlada pelo paciente&lt;/strong&gt; funciona porque incorpora uma alça de segurança: só o próprio paciente aciona o dispositivo e, se estiver sedado demais, deixa de acioná-lo. Os parâmetros essenciais são a &lt;strong&gt;dose em bolus&lt;/strong&gt;, o &lt;strong&gt;intervalo de bloqueio&lt;/strong&gt; (habitualmente de 5 a 10 minutos para a morfina) e eventuais limites de dose acumulada. A relação entre tentativas e doses liberadas é um dado clínico útil: uma razão elevada, como as 9 tentativas para 5 liberações do caso, sugere subdose e indica aumento do bolus ou revisão da analgesia de base.&lt;/p&gt;&lt;p&gt;Acrescentar &lt;strong&gt;infusão basal&lt;/strong&gt; de rotina em adultos não demonstra melhora consistente da analgesia e aumenta o consumo total de opioide, a incidência de náusea e, sobretudo, o risco de &lt;strong&gt;depressão respiratória&lt;/strong&gt; — risco agravado neste paciente pela obesidade e pela apneia obstrutiva do sono. A conduta racional é otimizar a dose por demanda e reforçar componentes não opioides: dipirona ou paracetamol, anti-inflamatório se não houver contraindicação, e bloqueio de parede abdominal ou peridural.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a infusão basal aumenta, sim, o risco de eventos respiratórios, sem ganho analgésico proporcional. (B) o acionamento por terceiros anula a principal salvaguarda do método e é uma prática formalmente desaconselhada. (D) a via intramuscular em horários fixos oferece analgesia errática, com picos e vales, e representa retrocesso frente a um dispositivo bem titulado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;analgesia controlada pelo paciente&lt;/strong&gt; funciona porque incorpora uma alça de segurança: só o próprio paciente aciona o dispositivo e, se estiver sedado demais, deixa de acioná-lo. Os parâmetros essenciais são a &lt;strong&gt;dose em bolus&lt;/strong&gt;, o &lt;strong&gt;intervalo de bloqueio&lt;/strong&gt; (habitualmente de 5 a 10 minutos para a morfina) e eventuais limites de dose acumulada. A relação entre tentativas e doses liberadas é um dado clínico útil: uma razão elevada, como as 9 tentativas para 5 liberações do caso, sugere subdose e indica aumento do bolus ou revisão da analgesia de base.&lt;/p&gt;&lt;p&gt;Acrescentar &lt;strong&gt;infusão basal&lt;/strong&gt; de rotina em adultos não demonstra melhora consistente da analgesia e aumenta o consumo total de opioide, a incidência de náusea e, sobretudo, o risco de &lt;strong&gt;depressão respiratória&lt;/strong&gt;, risco agravado neste paciente pela obesidade e pela apneia obstrutiva do sono. A conduta racional é otimizar a dose por demanda e reforçar componentes não opioides: dipirona ou paracetamol, anti-inflamatório se não houver contraindicação, e bloqueio de parede abdominal ou peridural.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a infusão basal aumenta, sim, o risco de eventos respiratórios, sem ganho analgésico proporcional. (B) o acionamento por terceiros anula a principal salvaguarda do método e é uma prática formalmente desaconselhada. (D) a via intramuscular em horários fixos oferece analgesia errática, com picos e vales, e representa retrocesso frente a um dispositivo bem titulado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Apesar do nome, a &lt;strong&gt;gabapentina&lt;/strong&gt; não atua sobre receptores do ácido gama-aminobutírico. Seu alvo é a &lt;strong&gt;subunidade alfa-2-delta&lt;/strong&gt; dos canais de cálcio voltagem-dependentes nos terminais pré-sinápticos. A ligação reduz o tráfego desses canais para a membrana e diminui a liberação de neurotransmissores excitatórios — glutamato, substância P e peptídeo relacionado ao gene da calcitonina — atenuando a sensibilização central. A pregabalina compartilha o mecanismo, com farmacocinética linear e absorção mais previsível.&lt;/p&gt;&lt;p&gt;Um ponto de segurança frequentemente cobrado é a &lt;strong&gt;eliminação renal na forma inalterada&lt;/strong&gt;: não há metabolismo hepático significativo nem interações relevantes pelo citocromo P450, mas a dose precisa ser reduzida conforme a depuração de creatinina, sob pena de sedação intensa, ataxia e confusão. Sonolência, tontura e edema periférico são os efeitos adversos mais comuns.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;oxcarbazepina&lt;/strong&gt;, por sua vez, é um bloqueador de canais de sódio usado sobretudo na neuralgia do trigêmeo, e seu efeito adverso metabólico característico é a &lt;strong&gt;hiponatremia&lt;/strong&gt;, mais frequente que com a carbamazepina, exigindo controle do sódio sérico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve o mecanismo dos bloqueadores de canais de sódio e atribui à gabapentina um metabolismo hepático que ela não tem. (C) inverte o distúrbio eletrolítico: a oxcarbazepina causa hiponatremia, não hipernatremia. (D) o nome sugere ação gabaérgica, mas ela não existe; não há agonismo em receptores do ácido gama-aminobutírico nem tolerância cruzada com benzodiazepínicos.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Apesar do nome, a &lt;strong&gt;gabapentina&lt;/strong&gt; não atua sobre receptores do ácido gama-aminobutírico. Seu alvo é a &lt;strong&gt;subunidade alfa-2-delta&lt;/strong&gt; dos canais de cálcio voltagem-dependentes nos terminais pré-sinápticos. A ligação reduz o tráfego desses canais para a membrana e diminui a liberação de neurotransmissores excitatórios (glutamato, substância P e peptídeo relacionado ao gene da calcitonina), atenuando a sensibilização central. A pregabalina compartilha o mecanismo, com farmacocinética linear e absorção mais previsível.&lt;/p&gt;&lt;p&gt;Um ponto de segurança frequentemente cobrado é a &lt;strong&gt;eliminação renal na forma inalterada&lt;/strong&gt;: não há metabolismo hepático significativo nem interações relevantes pelo citocromo P450, mas a dose precisa ser reduzida conforme a depuração de creatinina, sob pena de sedação intensa, ataxia e confusão. Sonolência, tontura e edema periférico são os efeitos adversos mais comuns.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;oxcarbazepina&lt;/strong&gt;, por sua vez, é um bloqueador de canais de sódio usado sobretudo na neuralgia do trigêmeo, e seu efeito adverso metabólico característico é a &lt;strong&gt;hiponatremia&lt;/strong&gt;, mais frequente que com a carbamazepina, exigindo controle do sódio sérico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve o mecanismo dos bloqueadores de canais de sódio e atribui à gabapentina um metabolismo hepático que ela não tem. (C) inverte o distúrbio eletrolítico: a oxcarbazepina causa hiponatremia, não hipernatremia. (D) o nome sugere ação gabaérgica, mas ela não existe; não há agonismo em receptores do ácido gama-aminobutírico nem tolerância cruzada com benzodiazepínicos.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome dolorosa regional complexa&lt;/strong&gt; é diagnóstico eminentemente &lt;strong&gt;clínico&lt;/strong&gt;. Os critérios atualmente aceitos exigem dor contínua desproporcional ao evento desencadeante, além de manifestações distribuídas em quatro categorias: &lt;em&gt;sensorial&lt;/em&gt; (hiperalgesia, alodinia), &lt;em&gt;vasomotora&lt;/em&gt; (assimetria de temperatura ou de coloração), &lt;em&gt;sudomotora e edema&lt;/em&gt; e &lt;em&gt;motora e trófica&lt;/em&gt; (redução de amplitude, tremor, distonia, alterações de pelos, unhas e pele). Exige-se relato de sintomas em pelo menos &lt;strong&gt;três&lt;/strong&gt; dessas categorias e constatação de sinais ao exame em pelo menos &lt;strong&gt;duas&lt;/strong&gt;, sem outro diagnóstico que explique melhor o quadro.&lt;/p&gt;&lt;p&gt;A distinção entre &lt;strong&gt;tipo I&lt;/strong&gt; e &lt;strong&gt;tipo II&lt;/strong&gt; depende exclusivamente da existência de lesão nervosa demonstrável: sua ausência, como no caso descrito, caracteriza o tipo I. O pilar do tratamento é a &lt;strong&gt;reabilitação funcional precoce&lt;/strong&gt;, com analgesia adequada e bloqueios simpáticos como recurso adjuvante para viabilizar a fisioterapia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cintilografia trifásica pode apoiar o diagnóstico, mas tem sensibilidade e especificidade insuficientes e não é padrão de referência; nenhum exame complementar confirma a síndrome. (B) a dor caracteristicamente ultrapassa o território de um nervo específico, assumindo distribuição regional — exigir esse padrão descaracterizaria a síndrome. (C) a resposta ao bloqueio simpático é variável; há formas mantidas e independentes do simpático, e a ausência de alívio não exclui o diagnóstico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome dolorosa regional complexa&lt;/strong&gt; é diagnóstico eminentemente &lt;strong&gt;clínico&lt;/strong&gt;. Os critérios atualmente aceitos exigem dor contínua desproporcional ao evento desencadeante, além de manifestações distribuídas em quatro categorias: &lt;em&gt;sensorial&lt;/em&gt; (hiperalgesia, alodinia), &lt;em&gt;vasomotora&lt;/em&gt; (assimetria de temperatura ou de coloração), &lt;em&gt;sudomotora e edema&lt;/em&gt; e &lt;em&gt;motora e trófica&lt;/em&gt; (redução de amplitude, tremor, distonia, alterações de pelos, unhas e pele). Exige-se relato de sintomas em pelo menos &lt;strong&gt;três&lt;/strong&gt; dessas categorias e constatação de sinais ao exame em pelo menos &lt;strong&gt;duas&lt;/strong&gt;, sem outro diagnóstico que explique melhor o quadro.&lt;/p&gt;&lt;p&gt;A distinção entre &lt;strong&gt;tipo I&lt;/strong&gt; e &lt;strong&gt;tipo II&lt;/strong&gt; depende exclusivamente da existência de lesão nervosa demonstrável: sua ausência, como no caso descrito, caracteriza o tipo I. O pilar do tratamento é a &lt;strong&gt;reabilitação funcional precoce&lt;/strong&gt;, com analgesia adequada e bloqueios simpáticos como recurso adjuvante para viabilizar a fisioterapia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cintilografia trifásica pode apoiar o diagnóstico, mas tem sensibilidade e especificidade insuficientes e não é padrão de referência; nenhum exame complementar confirma a síndrome. (B) a dor caracteristicamente ultrapassa o território de um nervo específico, assumindo distribuição regional; exigir esse padrão descaracterizaria a síndrome. (C) a resposta ao bloqueio simpático é variável; há formas mantidas e independentes do simpático, e a ausência de alívio não exclui o diagnóstico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;gânglio estrelado&lt;/strong&gt; resulta da fusão do gânglio cervical inferior com o primeiro gânglio torácico e situa-se anteriormente à cabeça da primeira costela e ao processo transverso de C7, em relação próxima com a cúpula pleural e a artéria vertebral. Justamente por isso, a punção clássica é realizada um nível acima, no &lt;strong&gt;tubérculo de Chassaignac&lt;/strong&gt;, o processo transverso de &lt;strong&gt;C6&lt;/strong&gt;: o anestésico local difunde-se caudalmente pelo plano pré-vertebral até o gânglio, com risco substancialmente menor de pneumotórax e de punção da artéria vertebral, que a esse nível já cursa dentro do forame transverso.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;síndrome de Horner&lt;/strong&gt; — ptose, miose e anidrose ipsilaterais — junto com congestão nasal e hiperemia conjuntival, confirma que houve bloqueio simpático da cabeça e do pescoço. Ela não assegura, porém, a denervação simpática do membro superior, que pode receber contribuição de fibras dos nervos de Kuntz vindas de T2 e T3. A verificação adequada é o &lt;strong&gt;aumento da temperatura cutânea&lt;/strong&gt; do membro alvo. Complicações incluem rouquidão por bloqueio do laríngeo recorrente, bloqueio do nervo frênico e convulsão por injeção intravascular de volume mínimo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o gânglio não está em C6; a punção nesse nível é escolhida por segurança, contando com a difusão do anestésico. (C) a síndrome de Horner não comprova bloqueio simpático do braço, e a temperatura cutânea segue sendo o parâmetro objetivo. (D) inverte o raciocínio: é a abordagem em C7 que aproxima a agulha da pleura e da artéria vertebral, aumentando o risco.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;gânglio estrelado&lt;/strong&gt; resulta da fusão do gânglio cervical inferior com o primeiro gânglio torácico e situa-se anteriormente à cabeça da primeira costela e ao processo transverso de C7, em relação próxima com a cúpula pleural e a artéria vertebral. Justamente por isso, a punção clássica é realizada um nível acima, no &lt;strong&gt;tubérculo de Chassaignac&lt;/strong&gt;, o processo transverso de &lt;strong&gt;C6&lt;/strong&gt;: o anestésico local difunde-se caudalmente pelo plano pré-vertebral até o gânglio, com risco substancialmente menor de pneumotórax e de punção da artéria vertebral, que a esse nível já cursa dentro do forame transverso.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;síndrome de Horner&lt;/strong&gt; (ptose, miose e anidrose ipsilaterais), junto com congestão nasal e hiperemia conjuntival, confirma que houve bloqueio simpático da cabeça e do pescoço. Ela não assegura, porém, a denervação simpática do membro superior, que pode receber contribuição de fibras dos nervos de Kuntz vindas de T2 e T3. A verificação adequada é o &lt;strong&gt;aumento da temperatura cutânea&lt;/strong&gt; do membro alvo. Complicações incluem rouquidão por bloqueio do laríngeo recorrente, bloqueio do nervo frênico e convulsão por injeção intravascular de volume mínimo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o gânglio não está em C6; a punção nesse nível é escolhida por segurança, contando com a difusão do anestésico. (C) a síndrome de Horner não comprova bloqueio simpático do braço, e a temperatura cutânea segue sendo o parâmetro objetivo. (D) inverte o raciocínio: é a abordagem em C7 que aproxima a agulha da pleura e da artéria vertebral, aumentando o risco.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;plexo celíaco&lt;/strong&gt; conduz as aferências nociceptivas das vísceras abdominais superiores — pâncreas, fígado, vias biliares, estômago e intestino até o ângulo esplênico — e concentra fibras simpáticas pré e pós-ganglionares. Sua neurólise com álcool ou fenol é indicada sobretudo na dor por neoplasia de pâncreas, com bom controle álgico e redução do consumo de opioides.&lt;/p&gt;&lt;p&gt;As consequências mais frequentes derivam diretamente do &lt;strong&gt;bloqueio simpático esplâncnico&lt;/strong&gt;: vasodilatação no leito visceral, com &lt;strong&gt;hipotensão&lt;/strong&gt;, particularmente ortostática, e predomínio parassimpático no trato gastrointestinal, com aumento do peristaltismo e &lt;strong&gt;diarreia&lt;/strong&gt;. Ambas costumam ser autolimitadas em alguns dias, e a hipotensão é atenuada com hidratação prévia e mobilização cuidadosa. Dor local no dorso após a injeção também é comum.&lt;/p&gt;&lt;p&gt;Complicações graves existem, mas são &lt;em&gt;raras&lt;/em&gt;: paraplegia por lesão da artéria de Adamkiewicz ou por espasmo arterial, pneumotórax, punção aórtica, lesão renal, injeção intravascular e disseminação do neurolítico para raízes somáticas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) retenção urinária e íleo paralítico não são o padrão esperado; o efeito gastrointestinal é oposto, com trânsito acelerado. (C) paraplegia e lesão renal são complicações reconhecidas, porém raras, e não podem ser apresentadas como esperadas. (D) inverte a fisiologia do bloqueio: com o simpático interrompido, ocorrem hipotensão e diarreia, e não hipertensão com constipação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;plexo celíaco&lt;/strong&gt; conduz as aferências nociceptivas das vísceras abdominais superiores (pâncreas, fígado, vias biliares, estômago e intestino até o ângulo esplênico) e concentra fibras simpáticas pré e pós-ganglionares. Sua neurólise com álcool ou fenol é indicada sobretudo na dor por neoplasia de pâncreas, com bom controle álgico e redução do consumo de opioides.&lt;/p&gt;&lt;p&gt;As consequências mais frequentes derivam diretamente do &lt;strong&gt;bloqueio simpático esplâncnico&lt;/strong&gt;: vasodilatação no leito visceral, com &lt;strong&gt;hipotensão&lt;/strong&gt;, particularmente ortostática, e predomínio parassimpático no trato gastrointestinal, com aumento do peristaltismo e &lt;strong&gt;diarreia&lt;/strong&gt;. Ambas costumam ser autolimitadas em alguns dias, e a hipotensão é atenuada com hidratação prévia e mobilização cuidadosa. Dor local no dorso após a injeção também é comum.&lt;/p&gt;&lt;p&gt;Complicações graves existem, mas são &lt;em&gt;raras&lt;/em&gt;: paraplegia por lesão da artéria de Adamkiewicz ou por espasmo arterial, pneumotórax, punção aórtica, lesão renal, injeção intravascular e disseminação do neurolítico para raízes somáticas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) retenção urinária e íleo paralítico não são o padrão esperado; o efeito gastrointestinal é oposto, com trânsito acelerado. (C) paraplegia e lesão renal são complicações reconhecidas, porém raras, e não podem ser apresentadas como esperadas. (D) inverte a fisiologia do bloqueio: com o simpático interrompido, ocorrem hipotensão e diarreia, e não hipertensão com constipação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A conversão entre vias na &lt;strong&gt;dor oncológica&lt;/strong&gt; é uma competência prática essencial e exige aritmética simples feita em etapas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dose diária oral:&lt;/strong&gt; 30 mg a cada 4 horas equivalem a 6 doses em 24 horas, ou seja, &lt;strong&gt;180 mg por dia por via oral&lt;/strong&gt;.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Conversão para parenteral:&lt;/strong&gt; a morfina oral sofre extenso efeito de primeira passagem, com biodisponibilidade em torno de um terço; aplicando a relação 3:1, obtém-se &lt;strong&gt;60 mg por dia por via intravenosa&lt;/strong&gt;.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Velocidade de infusão:&lt;/strong&gt; 60 mg divididos por 24 horas resultam em &lt;strong&gt;2,5 mg por hora&lt;/strong&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Vale lembrar os princípios que acompanham o cálculo: na dor oncológica moderada a intensa, o opioide deve ser prescrito em &lt;strong&gt;horários fixos&lt;/strong&gt;, e não apenas se necessário, com doses de resgate disponíveis correspondentes a cerca de 10% a 15% da dose diária total. Ao trocar de &lt;em&gt;fármaco&lt;/em&gt;, e não apenas de via, costuma-se reduzir a dose calculada em 25% a 50% pela tolerância cruzada incompleta — precaução especialmente relevante na conversão para metadona. Adjuvantes como bifosfonatos, corticoide e radioterapia paliativa complementam o controle da dor por metástase óssea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 1,25 mg por hora corresponde a metade da dose necessária, resultado de aplicar duas vezes um fator de redução. (B) 5 mg por hora dobra a dose equivalente, erro típico de usar relação 3:1 sobre uma dose diária superestimada. (D) 7,5 mg por hora equivale a manter os 180 mg diários por via intravenosa, ignorando a diferença de biodisponibilidade e expondo a paciente a risco elevado de depressão respiratória.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A conversão entre vias na &lt;strong&gt;dor oncológica&lt;/strong&gt; é uma competência prática essencial e exige aritmética simples feita em etapas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dose diária oral:&lt;/strong&gt; 30 mg a cada 4 horas equivalem a 6 doses em 24 horas, ou seja, &lt;strong&gt;180 mg por dia por via oral&lt;/strong&gt;.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Conversão para parenteral:&lt;/strong&gt; a morfina oral sofre extenso efeito de primeira passagem, com biodisponibilidade em torno de um terço; aplicando a relação 3:1, obtém-se &lt;strong&gt;60 mg por dia por via intravenosa&lt;/strong&gt;.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Velocidade de infusão:&lt;/strong&gt; 60 mg divididos por 24 horas resultam em &lt;strong&gt;2,5 mg por hora&lt;/strong&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Vale lembrar os princípios que acompanham o cálculo: na dor oncológica moderada a intensa, o opioide deve ser prescrito em &lt;strong&gt;horários fixos&lt;/strong&gt;, e não apenas se necessário, com doses de resgate disponíveis correspondentes a cerca de 10% a 15% da dose diária total. Ao trocar de &lt;em&gt;fármaco&lt;/em&gt;, e não apenas de via, costuma-se reduzir a dose calculada em 25% a 50% pela tolerância cruzada incompleta, precaução especialmente relevante na conversão para metadona. Adjuvantes como bifosfonatos, corticoide e radioterapia paliativa complementam o controle da dor por metástase óssea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 1,25 mg por hora corresponde a metade da dose necessária, resultado de aplicar duas vezes um fator de redução. (B) 5 mg por hora dobra a dose equivalente, erro típico de usar relação 3:1 sobre uma dose diária superestimada. (D) 7,5 mg por hora equivale a manter os 180 mg diários por via intravenosa, ignorando a diferença de biodisponibilidade e expondo a paciente a risco elevado de depressão respiratória.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os anestésicos venosos, com exceção da cetamina, deprimem o metabolismo cerebral e, como o &lt;strong&gt;acoplamento entre fluxo e metabolismo&lt;/strong&gt; permanece íntegro, reduzem secundariamente o fluxo sanguíneo cerebral, o volume sanguíneo intracraniano e a pressão intracraniana. O &lt;strong&gt;propofol&lt;/strong&gt; é o protótipo dessa resposta e, por isso, é escolha habitual para indução e manutenção em pacientes com complacência intracraniana reduzida. O cuidado essencial é preservar a pressão arterial média: como PPC = PAM − PIC, uma queda pressórica expressiva pode anular o ganho obtido com a redução da PIC.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;halogenados&lt;/strong&gt; têm efeito duplo — reduzem o consumo cerebral de oxigênio, mas provocam vasodilatação direta; acima de aproximadamente 1 CAM, o componente vasodilatador predomina e o fluxo sanguíneo cerebral aumenta. O &lt;strong&gt;óxido nitroso&lt;/strong&gt; eleva tanto o fluxo quanto o consumo cerebral de oxigênio e ainda expande cavidades gasosas, motivo pelo qual costuma ser evitado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o óxido nitroso não é neutro: aumenta fluxo e metabolismo cerebrais, sendo pouco apropriado em lesão expansiva com desvio de linha média. (C) o isoflurano a 2 CAM vasodilata de forma marcante e tende a elevar a pressão intracraniana, não a reduzir. (D) inverte o perfil do etomidato, que &lt;em&gt;diminui&lt;/em&gt; o consumo cerebral de oxigênio, o fluxo e a pressão intracraniana com boa estabilidade hemodinâmica; suas ressalvas dizem respeito à supressão adrenocortical e a movimentos mioclônicos.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os anestésicos venosos, com exceção da cetamina, deprimem o metabolismo cerebral e, como o &lt;strong&gt;acoplamento entre fluxo e metabolismo&lt;/strong&gt; permanece íntegro, reduzem secundariamente o fluxo sanguíneo cerebral, o volume sanguíneo intracraniano e a pressão intracraniana. O &lt;strong&gt;propofol&lt;/strong&gt; é o protótipo dessa resposta e, por isso, é escolha habitual para indução e manutenção em pacientes com complacência intracraniana reduzida. O cuidado essencial é preservar a pressão arterial média: como PPC = PAM − PIC, uma queda pressórica expressiva pode anular o ganho obtido com a redução da PIC.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;halogenados&lt;/strong&gt; têm efeito duplo: reduzem o consumo cerebral de oxigênio, mas provocam vasodilatação direta; acima de aproximadamente 1 CAM, o componente vasodilatador predomina e o fluxo sanguíneo cerebral aumenta. O &lt;strong&gt;óxido nitroso&lt;/strong&gt; eleva tanto o fluxo quanto o consumo cerebral de oxigênio e ainda expande cavidades gasosas, motivo pelo qual costuma ser evitado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o óxido nitroso não é neutro: aumenta fluxo e metabolismo cerebrais, sendo pouco apropriado em lesão expansiva com desvio de linha média. (C) o isoflurano a 2 CAM vasodilata de forma marcante e tende a elevar a pressão intracraniana, não a reduzir. (D) inverte o perfil do etomidato, que &lt;em&gt;diminui&lt;/em&gt; o consumo cerebral de oxigênio, o fluxo e a pressão intracraniana com boa estabilidade hemodinâmica; suas ressalvas dizem respeito à supressão adrenocortical e a movimentos mioclônicos.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O fluxo sanguíneo cerebral responde de forma quase linear à &lt;strong&gt;PaCO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt; na faixa aproximada de 20 a 80 mmHg, variando cerca de 1 a 2 mL por 100 g por minuto para cada mmHg. Por isso, a hiperventilação reduz rapidamente o volume sanguíneo cerebral e é ferramenta eficaz de relaxamento do encéfalo — mas com margem estreita.&lt;/p&gt;&lt;p&gt;O alvo recomendado é &lt;strong&gt;PaCO&lt;sub&gt;2&lt;/sub&gt; entre 30 e 35 mmHg&lt;/strong&gt;, de forma &lt;strong&gt;transitória&lt;/strong&gt;. Abaixo desse patamar, a vasoconstrição pode ser intensa o bastante para gerar isquemia em territórios já comprometidos, e o desvio da curva de dissociação da hemoglobina para a esquerda dificulta ainda mais a liberação de oxigênio ao tecido. Além disso, o efeito se atenua em algumas horas, quando o bicarbonato liquórico se ajusta e o pH perivascular se normaliza; a suspensão abrupta nessa fase provoca hiperemia de rebote. A hiperventilação profunda profilática está formalmente desaconselhada nas primeiras 24 horas do traumatismo cranioencefálico.&lt;/p&gt;&lt;p&gt;Outras medidas simultâneas incluem aprofundar sedação e bloqueio neuromuscular, revisar o posicionamento da cabeça, administrar manitol ou salina hipertônica e drenar liquor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipercapnia vasodilata, aumenta o volume sanguíneo cerebral e piora o encéfalo tenso. (C) PaCO&lt;sub&gt;2&lt;/sub&gt; de 20 mmHg ultrapassa amplamente o limite de segurança, e a manutenção prolongada acumula risco isquêmico sem benefício sustentado. (D) elevar a pressão expiratória final positiva a esse nível reduz o retorno venoso cerebral e a pressão arterial média, podendo agravar a hipertensão intracraniana e reduzir a perfusão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O fluxo sanguíneo cerebral responde de forma quase linear à &lt;strong&gt;PaCO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt; na faixa aproximada de 20 a 80 mmHg, variando cerca de 1 a 2 mL por 100 g por minuto para cada mmHg. Por isso, a hiperventilação reduz rapidamente o volume sanguíneo cerebral e é ferramenta eficaz de relaxamento do encéfalo, mas com margem estreita.&lt;/p&gt;&lt;p&gt;O alvo recomendado é &lt;strong&gt;PaCO&lt;sub&gt;2&lt;/sub&gt; entre 30 e 35 mmHg&lt;/strong&gt;, de forma &lt;strong&gt;transitória&lt;/strong&gt;. Abaixo desse patamar, a vasoconstrição pode ser intensa o bastante para gerar isquemia em territórios já comprometidos, e o desvio da curva de dissociação da hemoglobina para a esquerda dificulta ainda mais a liberação de oxigênio ao tecido. Além disso, o efeito se atenua em algumas horas, quando o bicarbonato liquórico se ajusta e o pH perivascular se normaliza; a suspensão abrupta nessa fase provoca hiperemia de rebote. A hiperventilação profunda profilática está formalmente desaconselhada nas primeiras 24 horas do traumatismo cranioencefálico.&lt;/p&gt;&lt;p&gt;Outras medidas simultâneas incluem aprofundar sedação e bloqueio neuromuscular, revisar o posicionamento da cabeça, administrar manitol ou salina hipertônica e drenar liquor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a hipercapnia vasodilata, aumenta o volume sanguíneo cerebral e piora o encéfalo tenso. (C) PaCO&lt;sub&gt;2&lt;/sub&gt; de 20 mmHg ultrapassa amplamente o limite de segurança, e a manutenção prolongada acumula risco isquêmico sem benefício sustentado. (D) elevar a pressão expiratória final positiva a esse nível reduz o retorno venoso cerebral e a pressão arterial média, podendo agravar a hipertensão intracraniana e reduzir a perfusão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escala de &lt;strong&gt;Hunt e Hess&lt;/strong&gt; gradua clinicamente a hemorragia subaracnóidea aneurismática e correlaciona-se com morbidade, mortalidade e risco de vasoespasmo, orientando também o momento do tratamento do aneurisma.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Grau I:&lt;/strong&gt; assintomático ou cefaleia leve, com discreta rigidez de nuca.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau II:&lt;/strong&gt; cefaleia intensa e rigidez de nuca, podendo haver paralisia de nervo craniano, sem outro déficit e com consciência preservada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau III:&lt;/strong&gt; sonolência, confusão ou déficit neurológico focal leve.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau IV:&lt;/strong&gt; estupor, hemiparesia moderada a grave, podendo haver rigidez de descerebração precoce.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau V:&lt;/strong&gt; coma profundo, rigidez de descerebração, aspecto moribundo.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;O quadro descrito — sonolência com confusão e hemiparesia discreta — corresponde ao &lt;strong&gt;grau III&lt;/strong&gt;. Graus mais altos implicam maior risco anestésico, maior probabilidade de hipertensão intracraniana e pior prognóstico funcional. Convém lembrar que a escala de Hunt e Hess é &lt;em&gt;clínica&lt;/em&gt;, enquanto a graduação de Fisher avalia a quantidade e a distribuição do sangue na tomografia e prediz melhor o risco de vasoespasmo; a escala da federação mundial de sociedades neurocirúrgicas combina escala de coma de Glasgow e déficit motor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o grau I pressupõe consciência normal, incompatível com sonolência e confusão. (B) o grau II também exige nível de consciência preservado e ausência de déficit motor. (C) o grau V descreve coma profundo com descerebração, muito além da gravidade apresentada pela paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escala de &lt;strong&gt;Hunt e Hess&lt;/strong&gt; gradua clinicamente a hemorragia subaracnóidea aneurismática e correlaciona-se com morbidade, mortalidade e risco de vasoespasmo, orientando também o momento do tratamento do aneurisma.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Grau I:&lt;/strong&gt; assintomático ou cefaleia leve, com discreta rigidez de nuca.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau II:&lt;/strong&gt; cefaleia intensa e rigidez de nuca, podendo haver paralisia de nervo craniano, sem outro déficit e com consciência preservada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau III:&lt;/strong&gt; sonolência, confusão ou déficit neurológico focal leve.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau IV:&lt;/strong&gt; estupor, hemiparesia moderada a grave, podendo haver rigidez de descerebração precoce.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grau V:&lt;/strong&gt; coma profundo, rigidez de descerebração, aspecto moribundo.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;O quadro descrito (sonolência com confusão e hemiparesia discreta) corresponde ao &lt;strong&gt;grau III&lt;/strong&gt;. Graus mais altos implicam maior risco anestésico, maior probabilidade de hipertensão intracraniana e pior prognóstico funcional. Convém lembrar que a escala de Hunt e Hess é &lt;em&gt;clínica&lt;/em&gt;, enquanto a graduação de Fisher avalia a quantidade e a distribuição do sangue na tomografia e prediz melhor o risco de vasoespasmo; a escala da federação mundial de sociedades neurocirúrgicas combina escala de coma de Glasgow e déficit motor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o grau I pressupõe consciência normal, incompatível com sonolência e confusão. (B) o grau II também exige nível de consciência preservado e ausência de déficit motor. (C) o grau V descreve coma profundo com descerebração, muito além da gravidade apresentada pela paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome anticolinérgica central&lt;/strong&gt; resulta do bloqueio de receptores muscarínicos no sistema nervoso central e manifesta-se com agitação, desorientação, alucinações, delírio, disartria e, em casos graves, convulsão ou depressão do nível de consciência. Vêm acompanhados os sinais periféricos do bloqueio muscarínico: midríase, pele seca e quente, taquicardia e retenção urinária.&lt;/p&gt;&lt;p&gt;A chave farmacológica está na estrutura química. &lt;strong&gt;Atropina&lt;/strong&gt; e &lt;strong&gt;escopolamina&lt;/strong&gt; são &lt;em&gt;aminas terciárias&lt;/em&gt;, lipossolúveis e sem carga permanente, e por isso atravessam a barreira hematoencefálica — a escopolamina de forma particularmente marcante. O &lt;strong&gt;glicopirrolato&lt;/strong&gt; é um &lt;em&gt;amônio quaternário&lt;/em&gt;, com carga positiva permanente, que não penetra no sistema nervoso central e por isso é preferido no idoso.&lt;/p&gt;&lt;p&gt;O tratamento é a &lt;strong&gt;fisostigmina&lt;/strong&gt;, único anticolinesterásico de uso clínico que também é amina terciária e alcança o cérebro. Neostigmina, piridostigmina e edrofônio são quaternários e revertem apenas os efeitos periféricos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a neostigmina é amônio quaternário e não atravessa a barreira hematoencefálica, sendo inútil para o componente central. (C) o quadro tem sinais periféricos antimuscarínicos evidentes, e o flumazenil não trata delírio anticolinérgico. (D) administrar mais atropina agravaria o bloqueio muscarínico central, piorando o delírio em vez de resolvê-lo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome anticolinérgica central&lt;/strong&gt; resulta do bloqueio de receptores muscarínicos no sistema nervoso central e manifesta-se com agitação, desorientação, alucinações, delírio, disartria e, em casos graves, convulsão ou depressão do nível de consciência. Vêm acompanhados os sinais periféricos do bloqueio muscarínico: midríase, pele seca e quente, taquicardia e retenção urinária.&lt;/p&gt;&lt;p&gt;A chave farmacológica está na estrutura química. &lt;strong&gt;Atropina&lt;/strong&gt; e &lt;strong&gt;escopolamina&lt;/strong&gt; são &lt;em&gt;aminas terciárias&lt;/em&gt;, lipossolúveis e sem carga permanente, e por isso atravessam a barreira hematoencefálica, a escopolamina de forma particularmente marcante. O &lt;strong&gt;glicopirrolato&lt;/strong&gt; é um &lt;em&gt;amônio quaternário&lt;/em&gt;, com carga positiva permanente, que não penetra no sistema nervoso central e por isso é preferido no idoso.&lt;/p&gt;&lt;p&gt;O tratamento é a &lt;strong&gt;fisostigmina&lt;/strong&gt;, único anticolinesterásico de uso clínico que também é amina terciária e alcança o cérebro. Neostigmina, piridostigmina e edrofônio são quaternários e revertem apenas os efeitos periféricos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a neostigmina é amônio quaternário e não atravessa a barreira hematoencefálica, sendo inútil para o componente central. (C) o quadro tem sinais periféricos antimuscarínicos evidentes, e o flumazenil não trata delírio anticolinérgico. (D) administrar mais atropina agravaria o bloqueio muscarínico central, piorando o delírio em vez de resolvê-lo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;hiperreflexia autonômica&lt;/strong&gt; surge após a fase de choque medular, em lesões situadas &lt;strong&gt;acima de T6&lt;/strong&gt;, quando os segmentos abaixo da lesão perdem a modulação inibitória supraespinhal. Um estímulo nociceptivo abaixo do nível lesional — distensão vesical ou retal, manipulação cirúrgica, cateterismo — desencadeia descarga simpática maciça, com vasoconstrição intensa no território desnervado.&lt;/p&gt;&lt;p&gt;O resultado é hipertensão grave com &lt;strong&gt;bradicardia reflexa&lt;/strong&gt; mediada por barorreceptores e vasodilatação compensatória acima da lesão, o que explica a combinação de rubor e sudorese cefálica com palidez e piloereção nos membros. O risco é de hemorragia intracraniana, edema agudo de pulmão e arritmias.&lt;/p&gt;&lt;p&gt;O manejo imediato é remover o estímulo e usar vasodilatador de latência e duração curtas, como nitroprussiato de sódio ou nitroglicerina. A prevenção mais eficaz é o bloqueio da via aferente: raquianestesia ou peridural bloqueiam o arco reflexo, o que a sedação isolada não faz.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o paciente não percebe dor abaixo da lesão e a sedação não interrompe o arco reflexo espinhal; opioide sistêmico não previne o quadro. (C) inverte dois pontos centrais: a síndrome exige lesão acima de T6 e cursa com bradicardia, não taquicardia. (D) subestima uma emergência hipertensiva com risco real de acidente vascular encefálico hemorrágico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;hiperreflexia autonômica&lt;/strong&gt; surge após a fase de choque medular, em lesões situadas &lt;strong&gt;acima de T6&lt;/strong&gt;, quando os segmentos abaixo da lesão perdem a modulação inibitória supraespinhal. Um estímulo nociceptivo abaixo do nível lesional (distensão vesical ou retal, manipulação cirúrgica, cateterismo), desencadeia descarga simpática maciça, com vasoconstrição intensa no território desnervado.&lt;/p&gt;&lt;p&gt;O resultado é hipertensão grave com &lt;strong&gt;bradicardia reflexa&lt;/strong&gt; mediada por barorreceptores e vasodilatação compensatória acima da lesão, o que explica a combinação de rubor e sudorese cefálica com palidez e piloereção nos membros. O risco é de hemorragia intracraniana, edema agudo de pulmão e arritmias.&lt;/p&gt;&lt;p&gt;O manejo imediato é remover o estímulo e usar vasodilatador de latência e duração curtas, como nitroprussiato de sódio ou nitroglicerina. A prevenção mais eficaz é o bloqueio da via aferente: raquianestesia ou peridural bloqueiam o arco reflexo, o que a sedação isolada não faz.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o paciente não percebe dor abaixo da lesão e a sedação não interrompe o arco reflexo espinhal; opioide sistêmico não previne o quadro. (C) inverte dois pontos centrais: a síndrome exige lesão acima de T6 e cursa com bradicardia, não taquicardia. (D) subestima uma emergência hipertensiva com risco real de acidente vascular encefálico hemorrágico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome de embolia gordurosa&lt;/strong&gt; é complicação clássica de fraturas de ossos longos e da pelve, especialmente do fêmur, e da manipulação do canal medular. O intervalo é típico: as manifestações surgem em geral entre &lt;strong&gt;12 e 72 horas&lt;/strong&gt; após o trauma, com pico em torno de 24 a 48 horas.&lt;/p&gt;&lt;p&gt;A tríade que define o quadro reúne &lt;strong&gt;insuficiência respiratória hipoxêmica&lt;/strong&gt;, &lt;strong&gt;alterações neurológicas&lt;/strong&gt; (confusão, agitação, sonolência, por vezes convulsão) e &lt;strong&gt;rash petequial&lt;/strong&gt; em conjuntivas, axilas, pescoço e tórax anterior — distribuição explicada pela embolização de gotículas em capilares de plexos subcutâneos. Plaquetopenia, anemia e febre completam o quadro. O tratamento é essencialmente de suporte, com oxigenação adequada e, se necessário, ventilação mecânica; a fixação precoce da fratura reduz a incidência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) contusão pulmonar exige trauma torácico e manifesta-se nas primeiras horas, com piora até 24 a 48 horas, mas não produz petéquias nem plaquetopenia. (C) o tromboembolismo pulmonar é raro nas primeiras 48 horas de trauma, cursa com sinais de sobrecarga ventricular direita e não provoca rash petequial nem essa combinação de febre e plaquetopenia. (D) a lesão pulmonar relacionada à transfusão ocorre até seis horas após o hemoderivado, sem petéquias e sem o intervalo livre de 36 horas descrito.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome de embolia gordurosa&lt;/strong&gt; é complicação clássica de fraturas de ossos longos e da pelve, especialmente do fêmur, e da manipulação do canal medular. O intervalo é típico: as manifestações surgem em geral entre &lt;strong&gt;12 e 72 horas&lt;/strong&gt; após o trauma, com pico em torno de 24 a 48 horas.&lt;/p&gt;&lt;p&gt;A tríade que define o quadro reúne &lt;strong&gt;insuficiência respiratória hipoxêmica&lt;/strong&gt;, &lt;strong&gt;alterações neurológicas&lt;/strong&gt; (confusão, agitação, sonolência, por vezes convulsão) e &lt;strong&gt;rash petequial&lt;/strong&gt; em conjuntivas, axilas, pescoço e tórax anterior, distribuição explicada pela embolização de gotículas em capilares de plexos subcutâneos. Plaquetopenia, anemia e febre completam o quadro. O tratamento é essencialmente de suporte, com oxigenação adequada e, se necessário, ventilação mecânica; a fixação precoce da fratura reduz a incidência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) contusão pulmonar exige trauma torácico e manifesta-se nas primeiras horas, com piora até 24 a 48 horas, mas não produz petéquias nem plaquetopenia. (C) o tromboembolismo pulmonar é raro nas primeiras 48 horas de trauma, cursa com sinais de sobrecarga ventricular direita e não provoca rash petequial nem essa combinação de febre e plaquetopenia. (D) a lesão pulmonar relacionada à transfusão ocorre até seis horas após o hemoderivado, sem petéquias e sem o intervalo livre de 36 horas descrito.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os dois escores respondem a perguntas diferentes. A &lt;strong&gt;classificação de Child-Pugh&lt;/strong&gt; reúne cinco variáveis, três laboratoriais — bilirrubina total, albumina e tempo de protrombina/INR — e duas clínicas — &lt;strong&gt;ascite&lt;/strong&gt; e &lt;strong&gt;encefalopatia&lt;/strong&gt;. Cada uma recebe de 1 a 3 pontos, gerando as classes A (5 a 6 pontos), B (7 a 9) e C (10 a 15). A dependência de julgamento clínico é sua principal limitação, pois introduz subjetividade.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;MELD&lt;/strong&gt; foi construído justamente para eliminar esse problema: usa apenas &lt;strong&gt;bilirrubina, INR e creatinina&lt;/strong&gt;, com resultado numérico contínuo, o que o tornou o instrumento adotado para priorização em lista de transplante hepático. Versões posteriores incorporaram o sódio sérico, mantendo a natureza exclusivamente laboratorial do escore.&lt;/p&gt;&lt;p&gt;Para o anestesiologista, ambos permanecem úteis: Child-Pugh C e MELD elevado identificam pacientes com mortalidade proibitiva em cirurgia eletiva, sobretudo abdominal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve variáveis do MELD atribuindo-as ao Child-Pugh, que não usa creatinina nem sódio e depende de avaliação clínica. (B) inverte a lógica: ascite e encefalopatia são exatamente as variáveis que o MELD não contém. (D) a faixa de 5 a 6 pontos corresponde à classe A, de melhor prognóstico; a classe C é a de pior reserva funcional.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os dois escores respondem a perguntas diferentes. A &lt;strong&gt;classificação de Child-Pugh&lt;/strong&gt; reúne cinco variáveis, três laboratoriais (bilirrubina total, albumina e tempo de protrombina/INR) e duas clínicas, &lt;strong&gt;ascite&lt;/strong&gt; e &lt;strong&gt;encefalopatia&lt;/strong&gt;. Cada uma recebe de 1 a 3 pontos, gerando as classes A (5 a 6 pontos), B (7 a 9) e C (10 a 15). A dependência de julgamento clínico é sua principal limitação, pois introduz subjetividade.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;MELD&lt;/strong&gt; foi construído justamente para eliminar esse problema: usa apenas &lt;strong&gt;bilirrubina, INR e creatinina&lt;/strong&gt;, com resultado numérico contínuo, o que o tornou o instrumento adotado para priorização em lista de transplante hepático. Versões posteriores incorporaram o sódio sérico, mantendo a natureza exclusivamente laboratorial do escore.&lt;/p&gt;&lt;p&gt;Para o anestesiologista, ambos permanecem úteis: Child-Pugh C e MELD elevado identificam pacientes com mortalidade proibitiva em cirurgia eletiva, sobretudo abdominal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve variáveis do MELD atribuindo-as ao Child-Pugh, que não usa creatinina nem sódio e depende de avaliação clínica. (B) inverte a lógica: ascite e encefalopatia são exatamente as variáveis que o MELD não contém. (D) a faixa de 5 a 6 pontos corresponde à classe A, de melhor prognóstico; a classe C é a de pior reserva funcional.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome da implantação do cimento ósseo&lt;/strong&gt; concentra-se em momentos previsíveis: pressurização do canal medular, inserção da prótese, redução da articulação e liberação do torniquete. A explicação predominante é &lt;strong&gt;mecânica e embólica&lt;/strong&gt;: a pressão intramedular gerada pela impactação, que pode ultrapassar várias centenas de milímetros de mercúrio, empurra medula óssea, gordura, ar e agregados para o leito venoso femoral.&lt;/p&gt;&lt;p&gt;Esse material atinge a circulação pulmonar e eleva de forma aguda a resistência vascular pulmonar, com sobrecarga ventricular direita, queda do débito cardíaco e aumento do espaço morto — daí a &lt;strong&gt;queda do dióxido de carbono expirado&lt;/strong&gt; simultânea à hipotensão e à hipoxemia, assinatura fisiológica que orienta o diagnóstico. Liberação de mediadores e efeito vasodilatador direto do monômero absorvido contribuem, mas não são o mecanismo dominante.&lt;/p&gt;&lt;p&gt;A conduta é imediata: fração inspirada de oxigênio de 100%, expansão volêmica, vasopressor com efeito alfa-adrenérgico e comunicação com a equipe cirúrgica. Prótese não cimentada e lavagem do canal reduzem o risco em pacientes frágeis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) reações anafiláticas verdadeiras ao metilmetacrilato são raras e não explicam a queda do dióxido de carbono expirado com esse padrão temporal. (B) o bloqueio simpático da raquianestesia instala-se nos primeiros 15 a 20 minutos e causa hipotensão com bradicardia, sem hipoxemia aguda. (D) sangramento produz hipotensão e taquicardia, mas de instalação mais gradual e sem dessaturação súbita sincronizada com a cimentação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome da implantação do cimento ósseo&lt;/strong&gt; concentra-se em momentos previsíveis: pressurização do canal medular, inserção da prótese, redução da articulação e liberação do torniquete. A explicação predominante é &lt;strong&gt;mecânica e embólica&lt;/strong&gt;: a pressão intramedular gerada pela impactação, que pode ultrapassar várias centenas de milímetros de mercúrio, empurra medula óssea, gordura, ar e agregados para o leito venoso femoral.&lt;/p&gt;&lt;p&gt;Esse material atinge a circulação pulmonar e eleva de forma aguda a resistência vascular pulmonar, com sobrecarga ventricular direita, queda do débito cardíaco e aumento do espaço morto; daí a &lt;strong&gt;queda do dióxido de carbono expirado&lt;/strong&gt; simultânea à hipotensão e à hipoxemia, assinatura fisiológica que orienta o diagnóstico. Liberação de mediadores e efeito vasodilatador direto do monômero absorvido contribuem, mas não são o mecanismo dominante.&lt;/p&gt;&lt;p&gt;A conduta é imediata: fração inspirada de oxigênio de 100%, expansão volêmica, vasopressor com efeito alfa-adrenérgico e comunicação com a equipe cirúrgica. Prótese não cimentada e lavagem do canal reduzem o risco em pacientes frágeis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) reações anafiláticas verdadeiras ao metilmetacrilato são raras e não explicam a queda do dióxido de carbono expirado com esse padrão temporal. (B) o bloqueio simpático da raquianestesia instala-se nos primeiros 15 a 20 minutos e causa hipotensão com bradicardia, sem hipoxemia aguda. (D) sangramento produz hipotensão e taquicardia, mas de instalação mais gradual e sem dessaturação súbita sincronizada com a cimentação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;dor do torniquete&lt;/strong&gt; é fenômeno bem descrito e frequentemente confundido com falha de bloqueio. Manifesta-se tipicamente entre &lt;strong&gt;45 e 60 minutos&lt;/strong&gt; de insuflação, como desconforto profundo, em queimação e mal localizado, acompanhado de hipertensão progressiva e taquicardia.&lt;/p&gt;&lt;p&gt;A explicação está no tipo de fibra envolvida: a condução é feita por &lt;strong&gt;fibras C amielínicas&lt;/strong&gt; de baixo calibre, sensibilizadas pela isquemia e pela compressão. Como essas fibras são relativamente resistentes ao bloqueio pelo anestésico local em concentrações que já aboliram a sensibilidade cirúrgica, o paciente pode ter nível sensitivo adequado e ainda assim sentir dor — exatamente o que descreve o enunciado, com nível estável em T10. O manejo envolve aprofundar a sedação, opioide venoso, e, sobretudo, comunicar ao cirurgião a necessidade de desinsuflar.&lt;/p&gt;&lt;p&gt;Vale lembrar que a desinsuflação traz seu próprio conjunto de repercussões: queda da pressão arterial, &lt;strong&gt;aumento do dióxido de carbono expirado&lt;/strong&gt;, acidose metabólica e elevação transitória do potássio, pela lavagem dos metabólitos do membro isquêmico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o nível sensitivo permanece em T10, o que descarta regressão do bloqueio. (C) a hipertermia maligna não é desencadeada por isquemia de membro e exige exposição a halogenado ou suxametônio, além de cursar com hipercapnia e rigidez. (D) enquanto o torniquete está insuflado, os metabólitos ficam &lt;em&gt;confinados&lt;/em&gt; ao membro; a liberação sistêmica de dióxido de carbono ocorre justamente após a desinsuflação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;dor do torniquete&lt;/strong&gt; é fenômeno bem descrito e frequentemente confundido com falha de bloqueio. Manifesta-se tipicamente entre &lt;strong&gt;45 e 60 minutos&lt;/strong&gt; de insuflação, como desconforto profundo, em queimação e mal localizado, acompanhado de hipertensão progressiva e taquicardia.&lt;/p&gt;&lt;p&gt;A explicação está no tipo de fibra envolvida: a condução é feita por &lt;strong&gt;fibras C amielínicas&lt;/strong&gt; de baixo calibre, sensibilizadas pela isquemia e pela compressão. Como essas fibras são relativamente resistentes ao bloqueio pelo anestésico local em concentrações que já aboliram a sensibilidade cirúrgica, o paciente pode ter nível sensitivo adequado e ainda assim sentir dor, exatamente o que descreve o enunciado, com nível estável em T10. O manejo envolve aprofundar a sedação, opioide venoso, e, sobretudo, comunicar ao cirurgião a necessidade de desinsuflar.&lt;/p&gt;&lt;p&gt;Vale lembrar que a desinsuflação traz seu próprio conjunto de repercussões: queda da pressão arterial, &lt;strong&gt;aumento do dióxido de carbono expirado&lt;/strong&gt;, acidose metabólica e elevação transitória do potássio, pela lavagem dos metabólitos do membro isquêmico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o nível sensitivo permanece em T10, o que descarta regressão do bloqueio. (C) a hipertermia maligna não é desencadeada por isquemia de membro e exige exposição a halogenado ou suxametônio, além de cursar com hipercapnia e rigidez. (D) enquanto o torniquete está insuflado, os metabólitos ficam &lt;em&gt;confinados&lt;/em&gt; ao membro; a liberação sistêmica de dióxido de carbono ocorre justamente após a desinsuflação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;reflexo oculocardíaco&lt;/strong&gt; é desencadeado por tração dos músculos extraoculares — o reto medial é o mais implicado —, por pressão sobre o globo, por hematoma orbitário ou pela injeção de anestésico local no bloqueio retrobulbar. É particularmente exuberante em crianças, pelo tônus vagal basal elevado.&lt;/p&gt;&lt;p&gt;O arco reflexo tem trajeto bem definido. A &lt;strong&gt;via aferente&lt;/strong&gt; parte dos nervos ciliares curtos e longos, atinge o gânglio ciliar e segue pelo &lt;strong&gt;ramo oftálmico do nervo trigêmeo&lt;/strong&gt; até o núcleo sensitivo no tronco encefálico. A &lt;strong&gt;via eferente&lt;/strong&gt; parte do núcleo motor dorsal do vago e alcança o coração pelo &lt;strong&gt;nervo vago&lt;/strong&gt;, produzindo bradicardia sinusal, ritmo juncional, extrassístoles e, nos casos extremos, assistolia.&lt;/p&gt;&lt;p&gt;A conduta prioritária é &lt;strong&gt;interromper o estímulo&lt;/strong&gt;, o que costuma reverter o quadro em segundos. Verificam-se então ventilação e plano anestésico, já que hipoxemia, hipercapnia e plano superficial acentuam o reflexo. Se recorrer ou for grave, administra-se atropina; a atropina profilática de rotina não é consenso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as vias: o trigêmeo é a aferência e o vago a eferência. (C) nem o facial nem o glossofaríngeo participam do arco, e o bloqueio peribulbar pode inclusive deflagrar o reflexo. (D) o reflexo é vagal e cursa com bradicardia e hipotensão, não com resposta simpática.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;reflexo oculocardíaco&lt;/strong&gt; é desencadeado por tração dos músculos extraoculares (o reto medial é o mais implicado), por pressão sobre o globo, por hematoma orbitário ou pela injeção de anestésico local no bloqueio retrobulbar. É particularmente exuberante em crianças, pelo tônus vagal basal elevado.&lt;/p&gt;&lt;p&gt;O arco reflexo tem trajeto bem definido. A &lt;strong&gt;via aferente&lt;/strong&gt; parte dos nervos ciliares curtos e longos, atinge o gânglio ciliar e segue pelo &lt;strong&gt;ramo oftálmico do nervo trigêmeo&lt;/strong&gt; até o núcleo sensitivo no tronco encefálico. A &lt;strong&gt;via eferente&lt;/strong&gt; parte do núcleo motor dorsal do vago e alcança o coração pelo &lt;strong&gt;nervo vago&lt;/strong&gt;, produzindo bradicardia sinusal, ritmo juncional, extrassístoles e, nos casos extremos, assistolia.&lt;/p&gt;&lt;p&gt;A conduta prioritária é &lt;strong&gt;interromper o estímulo&lt;/strong&gt;, o que costuma reverter o quadro em segundos. Verificam-se então ventilação e plano anestésico, já que hipoxemia, hipercapnia e plano superficial acentuam o reflexo. Se recorrer ou for grave, administra-se atropina; a atropina profilática de rotina não é consenso.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as vias: o trigêmeo é a aferência e o vago a eferência. (C) nem o facial nem o glossofaríngeo participam do arco, e o bloqueio peribulbar pode inclusive deflagrar o reflexo. (D) o reflexo é vagal e cursa com bradicardia e hipotensão, não com resposta simpática.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O cenário do &lt;strong&gt;olho aberto com estômago cheio&lt;/strong&gt; opõe dois riscos: a broncoaspiração, que ameaça a vida, e a elevação da pressão intraocular, que ameaça o olho. A solução moderna elimina o conflito.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;suxametônio&lt;/strong&gt; eleva a pressão intraocular em torno de 5 a 10 mmHg, com pico entre 2 e 4 minutos, por contração tônica sustentada da musculatura extraocular somada à congestão coroideana. Em um globo aberto, esse aumento pode contribuir para extrusão de humor vítreo. O &lt;strong&gt;rocurônio em dose de 1,2 mg/kg&lt;/strong&gt; — cerca de três a quatro vezes a dose efetiva 95 — oferece condições de intubação comparáveis em aproximadamente 60 segundos, sem elevar a pressão intraocular, e hoje conta com reversão rápida por sugamadex se necessário.&lt;/p&gt;&lt;p&gt;Completam a estratégia a indução venosa com propofol, opioide para abolir a resposta pressora à laringoscopia, lidocaína venosa como adjuvante, evitar pressão sobre o globo com a máscara e prevenir tosse e vômito, que elevam a pressão intraocular muito mais do que qualquer fármaco.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) parte de premissa falsa, pois o suxametônio comprovadamente eleva a pressão intraocular. (B) indução inalatória com estômago cheio expõe a broncoaspiração e a laringoscopia em plano insuficiente provoca tosse, com pico de pressão intraocular. (D) a pré-curarização atenua, mas não abole de forma confiável a elevação induzida pelo suxametônio, e ainda acrescenta risco de fraqueza e desconforto respiratório antes da hipnose.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O cenário do &lt;strong&gt;olho aberto com estômago cheio&lt;/strong&gt; opõe dois riscos: a broncoaspiração, que ameaça a vida, e a elevação da pressão intraocular, que ameaça o olho. A solução moderna elimina o conflito.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;suxametônio&lt;/strong&gt; eleva a pressão intraocular em torno de 5 a 10 mmHg, com pico entre 2 e 4 minutos, por contração tônica sustentada da musculatura extraocular somada à congestão coroideana. Em um globo aberto, esse aumento pode contribuir para extrusão de humor vítreo. O &lt;strong&gt;rocurônio em dose de 1,2 mg/kg&lt;/strong&gt; (cerca de três a quatro vezes a dose efetiva 95) oferece condições de intubação comparáveis em aproximadamente 60 segundos, sem elevar a pressão intraocular, e hoje conta com reversão rápida por sugamadex se necessário.&lt;/p&gt;&lt;p&gt;Completam a estratégia a indução venosa com propofol, opioide para abolir a resposta pressora à laringoscopia, lidocaína venosa como adjuvante, evitar pressão sobre o globo com a máscara e prevenir tosse e vômito, que elevam a pressão intraocular muito mais do que qualquer fármaco.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) parte de premissa falsa, pois o suxametônio comprovadamente eleva a pressão intraocular. (B) indução inalatória com estômago cheio expõe a broncoaspiração e a laringoscopia em plano insuficiente provoca tosse, com pico de pressão intraocular. (D) a pré-curarização atenua, mas não abole de forma confiável a elevação induzida pelo suxametônio, e ainda acrescenta risco de fraqueza e desconforto respiratório antes da hipnose.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A onda de choque da litotripsia extracorpórea propaga-se pelos tecidos e, ao atingir o coração, pode atuar como estímulo mecânico capaz de deflagrar despolarização prematura — fenômeno análogo ao &lt;em&gt;commotio cordis&lt;/em&gt;. Daí o risco de extrassístoles supraventriculares e ventriculares e, com menor frequência, de arritmias sustentadas.&lt;/p&gt;&lt;p&gt;A proteção clássica é o acoplamento do disparo ao eletrocardiograma. O choque é liberado aproximadamente &lt;strong&gt;20 milissegundos após a onda R&lt;/strong&gt;, intervalo que o coloca dentro do &lt;strong&gt;período refratário ventricular absoluto&lt;/strong&gt;, quando o miocárdio não pode ser despolarizado por um novo estímulo. O que se evita a todo custo é o disparo sobre a onda T, correspondente ao &lt;strong&gt;período vulnerável&lt;/strong&gt; da repolarização, em que um estímulo pode desencadear taquicardia ou fibrilação ventricular.&lt;/p&gt;&lt;p&gt;Uma consequência prática é que a frequência de disparo fica limitada pela frequência cardíaca, prolongando o procedimento em pacientes bradicárdicos, como os em uso de betabloqueador. Pacientes com marca-passo ou cardiodesfibrilador implantável exigem avaliação prévia do dispositivo e plano definido para o intraoperatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a onda T corresponde ao período vulnerável, exatamente a fase que a sincronização procura evitar. (C) o alvo da sincronização é o ventrículo, e não o átrio; a onda P não define o período refratário ventricular. (D) equipamentos modernos reduziram, mas não aboliram o risco arritmogênico, e a sincronização segue recomendada, sobretudo em cardiopatas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A onda de choque da litotripsia extracorpórea propaga-se pelos tecidos e, ao atingir o coração, pode atuar como estímulo mecânico capaz de deflagrar despolarização prematura, fenômeno análogo ao &lt;em&gt;commotio cordis&lt;/em&gt;. Daí o risco de extrassístoles supraventriculares e ventriculares e, com menor frequência, de arritmias sustentadas.&lt;/p&gt;&lt;p&gt;A proteção clássica é o acoplamento do disparo ao eletrocardiograma. O choque é liberado aproximadamente &lt;strong&gt;20 milissegundos após a onda R&lt;/strong&gt;, intervalo que o coloca dentro do &lt;strong&gt;período refratário ventricular absoluto&lt;/strong&gt;, quando o miocárdio não pode ser despolarizado por um novo estímulo. O que se evita a todo custo é o disparo sobre a onda T, correspondente ao &lt;strong&gt;período vulnerável&lt;/strong&gt; da repolarização, em que um estímulo pode desencadear taquicardia ou fibrilação ventricular.&lt;/p&gt;&lt;p&gt;Uma consequência prática é que a frequência de disparo fica limitada pela frequência cardíaca, prolongando o procedimento em pacientes bradicárdicos, como os em uso de betabloqueador. Pacientes com marca-passo ou cardiodesfibrilador implantável exigem avaliação prévia do dispositivo e plano definido para o intraoperatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a onda T corresponde ao período vulnerável, exatamente a fase que a sincronização procura evitar. (C) o alvo da sincronização é o ventrículo, e não o átrio; a onda P não define o período refratário ventricular. (D) equipamentos modernos reduziram, mas não aboliram o risco arritmogênico, e a sincronização segue recomendada, sobretudo em cardiopatas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A ruptura do aneurisma durante o tratamento endovascular é a complicação mais temida da sala de hemodinâmica neurovascular. O reconhecimento é combinado: o intervencionista vê &lt;strong&gt;extravasamento de contraste&lt;/strong&gt; e o anestesiologista observa a &lt;strong&gt;resposta de Cushing&lt;/strong&gt; — hipertensão arterial abrupta com bradicardia —, que traduz elevação súbita da pressão intracraniana.&lt;/p&gt;&lt;p&gt;As prioridades são três e simultâneas. Primeira, &lt;strong&gt;reverter a anticoagulação&lt;/strong&gt;: protamina na proporção aproximada de 1 mg para cada 100 unidades de heparina circulante, guiada pelo tempo de coagulação ativado, pois o sangramento prossegue enquanto o paciente estiver anticoagulado. Segunda, &lt;strong&gt;controlar a pressão arterial&lt;/strong&gt;, reduzindo-a para limitar a extensão do sangramento sem comprometer a pressão de perfusão cerebral. Terceira, &lt;strong&gt;sustentar o paciente&lt;/strong&gt; — ventilação com normocapnia a leve hipocapnia, manitol ou salina hipertônica se houver hipertensão intracraniana, e cabeceira elevada — enquanto o intervencionista oclui rapidamente o ponto de ruptura com as próprias molas ou com balão.&lt;/p&gt;&lt;p&gt;A drenagem ventricular externa e a abordagem cirúrgica são consideradas após a estabilização e a definição da imagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) hipertensão induzida agrava o extravasamento; ela tem lugar no vasoespasmo tardio, não na ruptura aguda. (B) aprofundar a anticoagulação diante de sangramento intracraniano ativo é conduta contrária ao objetivo terapêutico. (D) transportar uma paciente instável e anticoagulada, sem hemostasia nem controle pressórico, retarda o único tratamento imediatamente eficaz, que é a oclusão endovascular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A ruptura do aneurisma durante o tratamento endovascular é a complicação mais temida da sala de hemodinâmica neurovascular. O reconhecimento é combinado: o intervencionista vê &lt;strong&gt;extravasamento de contraste&lt;/strong&gt; e o anestesiologista observa a &lt;strong&gt;resposta de Cushing&lt;/strong&gt; (hipertensão arterial abrupta com bradicardia), que traduz elevação súbita da pressão intracraniana.&lt;/p&gt;&lt;p&gt;As prioridades são três e simultâneas. Primeira, &lt;strong&gt;reverter a anticoagulação&lt;/strong&gt;: protamina na proporção aproximada de 1 mg para cada 100 unidades de heparina circulante, guiada pelo tempo de coagulação ativado, pois o sangramento prossegue enquanto o paciente estiver anticoagulado. Segunda, &lt;strong&gt;controlar a pressão arterial&lt;/strong&gt;, reduzindo-a para limitar a extensão do sangramento sem comprometer a pressão de perfusão cerebral. Terceira, &lt;strong&gt;sustentar o paciente&lt;/strong&gt; (ventilação com normocapnia a leve hipocapnia, manitol ou salina hipertônica se houver hipertensão intracraniana, e cabeceira elevada) enquanto o intervencionista oclui rapidamente o ponto de ruptura com as próprias molas ou com balão.&lt;/p&gt;&lt;p&gt;A drenagem ventricular externa e a abordagem cirúrgica são consideradas após a estabilização e a definição da imagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) hipertensão induzida agrava o extravasamento; ela tem lugar no vasoespasmo tardio, não na ruptura aguda. (B) aprofundar a anticoagulação diante de sangramento intracraniano ativo é conduta contrária ao objetivo terapêutico. (D) transportar uma paciente instável e anticoagulada, sem hemostasia nem controle pressórico, retarda o único tratamento imediatamente eficaz, que é a oclusão endovascular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A perda de calor no centro cirúrgico ocorre por quatro mecanismos, com contribuições muito desiguais. A &lt;strong&gt;radiação&lt;/strong&gt; — troca por ondas eletromagnéticas entre a pele e as superfícies frias da sala — é a via dominante, responsável por algo em torno de 40% a 60% da perda. Seguem-se a &lt;strong&gt;convecção&lt;/strong&gt; (ar frio circulante), a &lt;strong&gt;evaporação&lt;/strong&gt; (pele, cavidades abertas e trato respiratório) e, por último, a &lt;strong&gt;condução&lt;/strong&gt;, que é pequena porque a mesa e os campos rapidamente se equilibram com a temperatura corporal.&lt;/p&gt;&lt;p&gt;A curva térmica tem três fases características. Na &lt;strong&gt;primeira hora&lt;/strong&gt;, a temperatura central cai de forma abrupta, tipicamente de 1 a 1,5 °C, não por perda para o ambiente, mas por &lt;strong&gt;redistribuição&lt;/strong&gt;: a vasodilatação induzida pelos anestésicos abole a vasoconstrição tônica e o calor migra do compartimento central para o periférico. Segue-se uma fase linear e lenta, em que a perda supera a produção, e depois um platô, quando a vasoconstrição termorreguladora reaparece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a perda pela via respiratória representa apenas cerca de 10% do total, e a curva de temperatura não é linear. (C) a medida isolada mais eficaz é o &lt;strong&gt;aquecimento ativo de superfície por ar forçado&lt;/strong&gt;; aquecer os gases tem impacto marginal. (D) a condução é a via de menor contribuição, e dispositivos passivos apenas reduzem a perda, sem transferir calor ao paciente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A perda de calor no centro cirúrgico ocorre por quatro mecanismos, com contribuições muito desiguais. A &lt;strong&gt;radiação&lt;/strong&gt; (troca por ondas eletromagnéticas entre a pele e as superfícies frias da sala) é a via dominante, responsável por algo em torno de 40% a 60% da perda. Seguem-se a &lt;strong&gt;convecção&lt;/strong&gt; (ar frio circulante), a &lt;strong&gt;evaporação&lt;/strong&gt; (pele, cavidades abertas e trato respiratório) e, por último, a &lt;strong&gt;condução&lt;/strong&gt;, que é pequena porque a mesa e os campos rapidamente se equilibram com a temperatura corporal.&lt;/p&gt;&lt;p&gt;A curva térmica tem três fases características. Na &lt;strong&gt;primeira hora&lt;/strong&gt;, a temperatura central cai de forma abrupta, tipicamente de 1 a 1,5 °C, não por perda para o ambiente, mas por &lt;strong&gt;redistribuição&lt;/strong&gt;: a vasodilatação induzida pelos anestésicos abole a vasoconstrição tônica e o calor migra do compartimento central para o periférico. Segue-se uma fase linear e lenta, em que a perda supera a produção, e depois um platô, quando a vasoconstrição termorreguladora reaparece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a perda pela via respiratória representa apenas cerca de 10% do total, e a curva de temperatura não é linear. (C) a medida isolada mais eficaz é o &lt;strong&gt;aquecimento ativo de superfície por ar forçado&lt;/strong&gt;; aquecer os gases tem impacto marginal. (D) a condução é a via de menor contribuição, e dispositivos passivos apenas reduzem a perda, sem transferir calor ao paciente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escolha do teste estatístico depende de três perguntas: qual o &lt;strong&gt;tipo de variável&lt;/strong&gt; de desfecho, quantos &lt;strong&gt;grupos&lt;/strong&gt; são comparados e se as amostras são &lt;strong&gt;independentes ou pareadas&lt;/strong&gt;. A distribuição da variável define, então, se o teste será paramétrico ou não paramétrico.&lt;/p&gt;&lt;p&gt;Aqui a variável é contínua (tempo em minutos), há dois grupos &lt;strong&gt;independentes&lt;/strong&gt; e a distribuição é assimétrica, com rejeição da normalidade. O teste indicado é o de &lt;strong&gt;Mann-Whitney&lt;/strong&gt;, também chamado de teste U ou de Wilcoxon para amostras independentes, que compara distribuições por meio de postos e não pressupõe normalidade.&lt;/p&gt;&lt;p&gt;A escolha da estatística descritiva segue a mesma lógica: em distribuições assimétricas, a &lt;strong&gt;mediana com intervalo interquartil&lt;/strong&gt; representa melhor a tendência central do que a média com desvio-padrão, porque a média é arrastada pelos valores extremos da cauda.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o teste t pareado exige medidas dependentes no mesmo indivíduo, como antes e depois, e além disso pressupõe normalidade — os grupos aqui são independentes. (B) o qui-quadrado compara proporções entre variáveis categóricas, não é aplicável a uma variável contínua. (C) a análise de variância é a extensão do teste t para três ou mais grupos, pressupõe normalidade e homogeneidade de variâncias, e seria inadequada mesmo para dois grupos com essa distribuição; o equivalente não paramétrico para três ou mais grupos seria o teste de Kruskal-Wallis.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escolha do teste estatístico depende de três perguntas: qual o &lt;strong&gt;tipo de variável&lt;/strong&gt; de desfecho, quantos &lt;strong&gt;grupos&lt;/strong&gt; são comparados e se as amostras são &lt;strong&gt;independentes ou pareadas&lt;/strong&gt;. A distribuição da variável define, então, se o teste será paramétrico ou não paramétrico.&lt;/p&gt;&lt;p&gt;Aqui a variável é contínua (tempo em minutos), há dois grupos &lt;strong&gt;independentes&lt;/strong&gt; e a distribuição é assimétrica, com rejeição da normalidade. O teste indicado é o de &lt;strong&gt;Mann-Whitney&lt;/strong&gt;, também chamado de teste U ou de Wilcoxon para amostras independentes, que compara distribuições por meio de postos e não pressupõe normalidade.&lt;/p&gt;&lt;p&gt;A escolha da estatística descritiva segue a mesma lógica: em distribuições assimétricas, a &lt;strong&gt;mediana com intervalo interquartil&lt;/strong&gt; representa melhor a tendência central do que a média com desvio-padrão, porque a média é arrastada pelos valores extremos da cauda.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o teste t pareado exige medidas dependentes no mesmo indivíduo, como antes e depois, e além disso pressupõe normalidade; os grupos aqui são independentes. (B) o qui-quadrado compara proporções entre variáveis categóricas, não é aplicável a uma variável contínua. (C) a análise de variância é a extensão do teste t para três ou mais grupos, pressupõe normalidade e homogeneidade de variâncias, e seria inadequada mesmo para dois grupos com essa distribuição; o equivalente não paramétrico para três ou mais grupos seria o teste de Kruskal-Wallis.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No direito brasileiro, o Código de Defesa do Consumidor estabelece, em seu artigo 14, parágrafo 4º, que a responsabilidade dos &lt;strong&gt;profissionais liberais&lt;/strong&gt; — categoria em que se enquadra o médico — é apurada mediante &lt;strong&gt;verificação de culpa&lt;/strong&gt;. Trata-se, portanto, de &lt;strong&gt;responsabilidade subjetiva&lt;/strong&gt;, e não objetiva.&lt;/p&gt;&lt;p&gt;Para que haja dever de indenizar, é preciso demonstrar quatro elementos: conduta do profissional, &lt;strong&gt;culpa&lt;/strong&gt; em uma de suas modalidades — &lt;em&gt;imperícia&lt;/em&gt; (falta de conhecimento ou habilidade técnica), &lt;em&gt;imprudência&lt;/em&gt; (ação precipitada) ou &lt;em&gt;negligência&lt;/em&gt; (omissão de cuidado devido) —, &lt;strong&gt;dano&lt;/strong&gt; e &lt;strong&gt;nexo causal&lt;/strong&gt; entre a conduta e o dano. Ausente a culpa, não há responsabilização, ainda que o resultado tenha sido desfavorável.&lt;/p&gt;&lt;p&gt;Na prática, isso valoriza o registro anestésico completo, a documentação do posicionamento e da proteção de proeminências e o consentimento livre e esclarecido, que são os instrumentos que demonstram diligência. É importante notar que a responsabilidade do &lt;strong&gt;hospital&lt;/strong&gt;, como fornecedor de serviços, segue regra distinta e objetiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a responsabilidade objetiva não se aplica ao profissional liberal, apenas à pessoa jurídica prestadora do serviço. (B) a anestesia é obrigação &lt;em&gt;de meio&lt;/em&gt;: o profissional se compromete a empregar diligência e a técnica adequada, não a garantir determinado resultado. (D) as esferas penal, civil e ético-profissional são independentes entre si; a absolvição penal só repercute nas demais quando reconhece a inexistência do fato ou a negativa de autoria.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No direito brasileiro, o Código de Defesa do Consumidor estabelece, em seu artigo 14, parágrafo 4º, que a responsabilidade dos &lt;strong&gt;profissionais liberais&lt;/strong&gt; (categoria em que se enquadra o médico) é apurada mediante &lt;strong&gt;verificação de culpa&lt;/strong&gt;. Trata-se, portanto, de &lt;strong&gt;responsabilidade subjetiva&lt;/strong&gt;, e não objetiva.&lt;/p&gt;&lt;p&gt;Para que haja dever de indenizar, é preciso demonstrar quatro elementos: conduta do profissional, &lt;strong&gt;culpa&lt;/strong&gt; em uma de suas modalidades (&lt;em&gt;imperícia&lt;/em&gt;, falta de conhecimento ou habilidade técnica; &lt;em&gt;imprudência&lt;/em&gt;, ação precipitada; ou &lt;em&gt;negligência&lt;/em&gt;, omissão de cuidado devido), &lt;strong&gt;dano&lt;/strong&gt; e &lt;strong&gt;nexo causal&lt;/strong&gt; entre a conduta e o dano. Ausente a culpa, não há responsabilização, ainda que o resultado tenha sido desfavorável.&lt;/p&gt;&lt;p&gt;Na prática, isso valoriza o registro anestésico completo, a documentação do posicionamento e da proteção de proeminências e o consentimento livre e esclarecido, que são os instrumentos que demonstram diligência. É importante notar que a responsabilidade do &lt;strong&gt;hospital&lt;/strong&gt;, como fornecedor de serviços, segue regra distinta e objetiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a responsabilidade objetiva não se aplica ao profissional liberal, apenas à pessoa jurídica prestadora do serviço. (B) a anestesia é obrigação &lt;em&gt;de meio&lt;/em&gt;: o profissional se compromete a empregar diligência e a técnica adequada, não a garantir determinado resultado. (D) as esferas penal, civil e ético-profissional são independentes entre si; a absolvição penal só repercute nas demais quando reconhece a inexistência do fato ou a negativa de autoria.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
